--- a/tools/importer/reports/import-grace-master.report.xlsx
+++ b/tools/importer/reports/import-grace-master.report.xlsx
@@ -415,7 +415,7 @@
     <t>insights/4-ways-cdmos-help-nutraceutical-companies-grow</t>
   </si>
   <si>
-    <t>2026-08-07T12:00:09.982Z</t>
+    <t>2026-08-07T14:30:16.203Z</t>
   </si>
   <si>
     <t>4 Ways CDMOs help Nutraceutical Companies Grow</t>
@@ -465,7 +465,7 @@
     <t>insights/5-things-to-consider-when-selecting-a-chromatography-silica</t>
   </si>
   <si>
-    <t>2026-08-07T12:44:10.671Z</t>
+    <t>2026-08-07T14:26:17.707Z</t>
   </si>
   <si>
     <t>5 Things to Consider When Selecting a Chromatography Silica</t>
@@ -480,7 +480,7 @@
     <t>insights/80-years-of-fcc</t>
   </si>
   <si>
-    <t>2026-08-07T11:44:23.430Z</t>
+    <t>2026-08-07T15:15:49.836Z</t>
   </si>
   <si>
     <t>80 Years of FCC</t>
@@ -495,7 +495,7 @@
     <t>insights/a-better-way-to-dehydrate-ethanol</t>
   </si>
   <si>
-    <t>2026-08-07T11:37:16.405Z</t>
+    <t>2026-08-07T14:51:13.405Z</t>
   </si>
   <si>
     <t>A Better Way to Dehydrate Ethanol</t>
@@ -510,7 +510,7 @@
     <t>insights/a-brewers-challenge</t>
   </si>
   <si>
-    <t>2026-08-07T11:52:14.763Z</t>
+    <t>2026-08-07T14:22:20.830Z</t>
   </si>
   <si>
     <t>A Brewer’s Challenge</t>
@@ -525,7 +525,7 @@
     <t>insights/a-brewery-goes-green</t>
   </si>
   <si>
-    <t>2026-08-07T12:43:17.323Z</t>
+    <t>2026-08-07T14:49:29.830Z</t>
   </si>
   <si>
     <t>A Brewery Goes Green</t>
@@ -540,7 +540,7 @@
     <t>insights/a-legacy-of-innovation</t>
   </si>
   <si>
-    <t>2026-08-07T11:36:16.504Z</t>
+    <t>2026-08-07T14:50:11.281Z</t>
   </si>
   <si>
     <t>A Legacy of Innovation</t>
@@ -555,7 +555,7 @@
     <t>insights/a-matte-that-lasts</t>
   </si>
   <si>
-    <t>2026-08-07T11:35:29.781Z</t>
+    <t>2026-08-07T14:49:27.933Z</t>
   </si>
   <si>
     <t>A Matte That Lasts</t>
@@ -600,7 +600,7 @@
     <t>insights/a-refined-view-on-environmental-additives</t>
   </si>
   <si>
-    <t>2026-08-07T11:33:38.661Z</t>
+    <t>2026-08-07T14:47:31.440Z</t>
   </si>
   <si>
     <t>A Refined View on Environmental Additives</t>
@@ -615,7 +615,7 @@
     <t>insights/a-successful-case-of-resid-to-propylene-maximization</t>
   </si>
   <si>
-    <t>2026-08-07T11:46:55.670Z</t>
+    <t>2026-08-07T14:17:00.551Z</t>
   </si>
   <si>
     <t>A Successful Case of Resid-to-Propylene Maximization at OQ</t>
@@ -630,7 +630,7 @@
     <t>insights/activcat-catalyst-technologies-for-blown-film</t>
   </si>
   <si>
-    <t>2026-08-07T11:40:44.593Z</t>
+    <t>2026-08-07T14:10:51.328Z</t>
   </si>
   <si>
     <t>The ActivCat® Catalyst Advantage: Using Metallocene PE for Blown Film</t>
@@ -645,7 +645,7 @@
     <t>insights/activcat-catalyst-technologies-for-cast-film</t>
   </si>
   <si>
-    <t>2026-08-07T11:40:55.681Z</t>
+    <t>2026-08-07T14:11:02.505Z</t>
   </si>
   <si>
     <t>ActivCat® Catalyst Technologies for Cast Film</t>
@@ -660,7 +660,7 @@
     <t>insights/activcat-catalyst-technologies-for-pert</t>
   </si>
   <si>
-    <t>2026-08-07T11:40:50.611Z</t>
+    <t>2026-08-07T14:10:59.905Z</t>
   </si>
   <si>
     <t>ActivCat® Catalyst Technologies for PE-RT</t>
@@ -675,7 +675,7 @@
     <t>insights/activcat-innovation-solutions</t>
   </si>
   <si>
-    <t>2026-08-07T11:49:01.907Z</t>
+    <t>2026-08-07T14:19:07.158Z</t>
   </si>
   <si>
     <t>ActivCat® Catalyst Innovative Solutions</t>
@@ -690,7 +690,7 @@
     <t>insights/activcat-metallocene-catalysts-pe-film-pert-resins-zpc</t>
   </si>
   <si>
-    <t>2026-08-07T11:50:41.401Z</t>
+    <t>2026-08-07T14:20:51.288Z</t>
   </si>
   <si>
     <t>Grace ActivCat® Catalyst Technology Partners to Develop Innovative Metallocene Polyethylene Resins</t>
@@ -705,7 +705,7 @@
     <t>insights/activcat-wins-chemical-weeks-sustainable-product-innovation-award</t>
   </si>
   <si>
-    <t>2026-08-07T11:44:36.042Z</t>
+    <t>2026-08-07T14:14:42.217Z</t>
   </si>
   <si>
     <t>ActivCat® Catalyst Wins Chemical Week’s Sustainable Product Innovation Award</t>
@@ -720,7 +720,7 @@
     <t>insights/advancing-encapsulation-technologies</t>
   </si>
   <si>
-    <t>2026-08-07T11:45:08.136Z</t>
+    <t>2026-08-07T14:15:15.145Z</t>
   </si>
   <si>
     <t>Advancing Encapsulation Technologies with Colloidal Silica</t>
@@ -735,7 +735,7 @@
     <t>insights/amino-acid-chemistry</t>
   </si>
   <si>
-    <t>2026-08-07T11:48:08.267Z</t>
+    <t>2026-08-07T14:18:14.748Z</t>
   </si>
   <si>
     <t>Amino Acid Chemistry</t>
@@ -750,7 +750,7 @@
     <t>insights/answering-refiners-questions</t>
   </si>
   <si>
-    <t>2026-08-07T11:53:26.437Z</t>
+    <t>2026-08-07T14:23:37.407Z</t>
   </si>
   <si>
     <t>Answering Refiners’ Questions</t>
@@ -765,7 +765,7 @@
     <t>insights/anti-blocking-technology-in-pet-and-bopet-films</t>
   </si>
   <si>
-    <t>2026-08-07T11:42:48.699Z</t>
+    <t>2026-08-07T14:12:52.931Z</t>
   </si>
   <si>
     <t>Anti-Blocking Technology in PET and BOPET Films</t>
@@ -780,7 +780,7 @@
     <t>insights/benefits-of-vyvid-superparamagnetic-silica-in-medical-diagnostics</t>
   </si>
   <si>
-    <t>2026-08-07T11:55:03.703Z</t>
+    <t>2026-08-07T14:25:19.295Z</t>
   </si>
   <si>
     <t>Benefits of VYVID™ Superparamagnetic Silica in Medical Diagnostics</t>
@@ -810,7 +810,7 @@
     <t>insights/capture-value-by-processing-resid-in-the-fcc</t>
   </si>
   <si>
-    <t>2026-08-07T11:39:51.422Z</t>
+    <t>2026-08-07T14:09:58.246Z</t>
   </si>
   <si>
     <t>Capture Value by Processing Resid in the FCC</t>
@@ -825,7 +825,7 @@
     <t>insights/catalagram-126</t>
   </si>
   <si>
-    <t>2026-08-07T11:39:56.704Z</t>
+    <t>2026-08-07T14:10:05.390Z</t>
   </si>
   <si>
     <t>Catalagram 126</t>
@@ -840,7 +840,7 @@
     <t>insights/catalagram-127</t>
   </si>
   <si>
-    <t>2026-08-07T11:46:02.932Z</t>
+    <t>2026-08-07T14:16:07.913Z</t>
   </si>
   <si>
     <t>Catalagram 127</t>
@@ -855,7 +855,7 @@
     <t>insights/catalagram-issue-128</t>
   </si>
   <si>
-    <t>2026-08-07T11:50:27.627Z</t>
+    <t>2026-08-07T14:20:35.496Z</t>
   </si>
   <si>
     <t>Download the Latest Issue of Catalagram® Magazine</t>
@@ -870,7 +870,7 @@
     <t>insights/catalysts-for-a-more-sustainable-future</t>
   </si>
   <si>
-    <t>2026-08-07T11:42:36.761Z</t>
+    <t>2026-08-07T14:12:49.931Z</t>
   </si>
   <si>
     <t>Catalysts for a More Sustainable Future</t>
@@ -885,7 +885,7 @@
     <t>insights/catalysts-pave-sustainable-path-po-manufacturers</t>
   </si>
   <si>
-    <t>2026-08-07T11:57:30.651Z</t>
+    <t>2026-08-07T14:27:37.188Z</t>
   </si>
   <si>
     <t>Catalysts Can Help Pave a Sustainable Path for Polyolefin Manufacturers</t>
@@ -900,7 +900,7 @@
     <t>insights/challenge-accepted-teams-of-innovators-compete-to-revolutionize</t>
   </si>
   <si>
-    <t>2026-08-07T11:56:37.837Z</t>
+    <t>2026-08-07T14:26:43.403Z</t>
   </si>
   <si>
     <t>Challenge Accepted! Teams of Innovators Compete to Revolutionize Chemical Synthesis</t>
@@ -915,7 +915,7 @@
     <t>insights/choosing-a-small-molecule-drug-substance-partner</t>
   </si>
   <si>
-    <t>2026-08-07T11:54:53.729Z</t>
+    <t>2026-08-07T14:24:59.122Z</t>
   </si>
   <si>
     <t>Choosing a small-molecule drug substance partner</t>
@@ -930,7 +930,7 @@
     <t>insights/chromadex-cdmo-grace-fcms</t>
   </si>
   <si>
-    <t>2026-08-07T11:48:45.997Z</t>
+    <t>2026-08-07T14:19:03.459Z</t>
   </si>
   <si>
     <t>ChromaDex’s CDMO: Grace’s FCMS</t>
@@ -948,7 +948,7 @@
     <t>insights/chromatography-separation-specifics</t>
   </si>
   <si>
-    <t>2026-08-07T11:46:16.039Z</t>
+    <t>2026-08-07T14:16:21.325Z</t>
   </si>
   <si>
     <t>Chromatography Separation Specifics</t>
@@ -963,7 +963,7 @@
     <t>insights/cleaner-greener-biofuel</t>
   </si>
   <si>
-    <t>2026-08-07T11:36:28.439Z</t>
+    <t>2026-08-07T14:50:22.643Z</t>
   </si>
   <si>
     <t>Cleaner Greener Biofuel</t>
@@ -978,7 +978,7 @@
     <t>insights/co-processing-bio-based-feedstocks-in-the-fcc</t>
   </si>
   <si>
-    <t>2026-08-07T11:45:29.033Z</t>
+    <t>2026-08-07T14:15:34.571Z</t>
   </si>
   <si>
     <t>Co-processing Bio-based Feedstocks in the FCC</t>
@@ -993,7 +993,7 @@
     <t>insights/collaboration-consista-catalyst</t>
   </si>
   <si>
-    <t>2026-08-07T11:38:02.398Z</t>
+    <t>2026-08-07T14:51:58.347Z</t>
   </si>
   <si>
     <t>Collaboration and CONSISTA® Catalyst</t>
@@ -1008,7 +1008,7 @@
     <t>insights/colloidal-silica-and-corrosion-resistance-stabilizing-a-safer</t>
   </si>
   <si>
-    <t>2026-08-07T11:38:16.100Z</t>
+    <t>2026-08-07T14:52:08.907Z</t>
   </si>
   <si>
     <t>Colloidal Silica and Corrosion Resistance – Stabilizing a Safer Alternative</t>
@@ -1023,7 +1023,7 @@
     <t>insights/colloidal-silica-as-a-foundation-for-3-d-printed-replacement-tissues</t>
   </si>
   <si>
-    <t>2026-08-07T11:41:43.973Z</t>
+    <t>2026-08-07T14:11:52.810Z</t>
   </si>
   <si>
     <t>Colloidal Silica as a Foundation for 3-D Printed Replacement Tissues</t>
@@ -1038,7 +1038,7 @@
     <t>insights/colloidal-silica-coatings-in-food-contact-applications</t>
   </si>
   <si>
-    <t>2026-08-07T11:38:08.870Z</t>
+    <t>2026-08-07T14:52:06.689Z</t>
   </si>
   <si>
     <t>Colloidal Silica Coatings in Food-Contact Applications</t>
@@ -1053,7 +1053,7 @@
     <t>insights/colloidal-silica-small-particles-enormous-potential</t>
   </si>
   <si>
-    <t>2026-08-07T11:38:56.450Z</t>
+    <t>2026-08-07T14:52:50.997Z</t>
   </si>
   <si>
     <t>Colloidal Silica: Small Particles, Enormous Potential</t>
@@ -1068,7 +1068,7 @@
     <t>insights/colloidal-silica-takes-on-extreme-environments</t>
   </si>
   <si>
-    <t>2026-08-07T11:41:50.073Z</t>
+    <t>2026-08-07T14:11:56.310Z</t>
   </si>
   <si>
     <t>Colloidal Silica Takes on Extreme Environments</t>
@@ -1083,7 +1083,7 @@
     <t>insights/colloidal-silica-water-sample-analysis</t>
   </si>
   <si>
-    <t>2026-08-07T11:38:19.571Z</t>
+    <t>2026-08-07T14:52:11.445Z</t>
   </si>
   <si>
     <t>Colloidal Silica Can Help Expedite Water Sample Analysis of Toxic Pesticides</t>
@@ -1098,7 +1098,7 @@
     <t>insights/consista-c602-terpolymer-china-yth</t>
   </si>
   <si>
-    <t>2026-08-07T11:49:34.505Z</t>
+    <t>2026-08-07T14:19:41.181Z</t>
   </si>
   <si>
     <t>UNIPOL® PP Technology is the Premier PP Producer for Terpolymer Grade Resins Using CONSISTA® C602 Catalyst System</t>
@@ -1128,7 +1128,7 @@
     <t>insights/control-api-impurities-to-achieve-therapeutic-safety-and-efficac</t>
   </si>
   <si>
-    <t>2026-08-07T12:01:02.034Z</t>
+    <t>2026-08-07T14:31:11.142Z</t>
   </si>
   <si>
     <t>Control API Impurities to Achieve Therapeutic Safety and Efficacy for Patients</t>
@@ -1143,7 +1143,7 @@
     <t>insights/could-ai-enabled-retrosynthesis-lead-to-the-next-big-breakthrough</t>
   </si>
   <si>
-    <t>2026-08-07T11:56:58.066Z</t>
+    <t>2026-08-07T14:27:11.654Z</t>
   </si>
   <si>
     <t>Could AI-enabled Retrosynthesis Lead to the Next Big Breakthrough?</t>
@@ -1158,7 +1158,7 @@
     <t>insights/dcr-pilot-plant-creates-opportunities-in-oman</t>
   </si>
   <si>
-    <t>2026-08-07T11:46:22.486Z</t>
+    <t>2026-08-07T14:16:27.440Z</t>
   </si>
   <si>
     <t>DCR™ Pilot Plant Creates Opportunities in Oman</t>
@@ -1176,7 +1176,7 @@
     <t>insights/demand-for-high-octane-fuel-drives-refiners-to-alkylate</t>
   </si>
   <si>
-    <t>2026-08-07T11:47:08.015Z</t>
+    <t>2026-08-07T14:17:15.894Z</t>
   </si>
   <si>
     <t>Demand for High-octane Fuel Drives Refiners to Alkylate</t>
@@ -1206,7 +1206,7 @@
     <t>insights/ebook-water-based-technologies-wood-coatings</t>
   </si>
   <si>
-    <t>2026-08-07T11:45:22.562Z</t>
+    <t>2026-08-07T14:15:28.929Z</t>
   </si>
   <si>
     <t>Exclusive eBook – Water-based Technologies for Wood Coatings</t>
@@ -1221,7 +1221,7 @@
     <t>insights/eliminating-gels-in-film-activcat-catalysts</t>
   </si>
   <si>
-    <t>2026-08-07T11:36:23.042Z</t>
+    <t>2026-08-07T14:50:20.607Z</t>
   </si>
   <si>
     <t>Eliminating Gels in Film with ActivCat® Catalysts</t>
@@ -1236,7 +1236,7 @@
     <t>insights/ending-the-matting-compromise</t>
   </si>
   <si>
-    <t>2026-08-07T11:32:56.012Z</t>
+    <t>2026-08-07T14:46:49.407Z</t>
   </si>
   <si>
     <t>Ending the Matting Compromise</t>
@@ -1281,7 +1281,7 @@
     <t>insights/enhancing-stability-and-bioavailability-of-poorly-soluble-apis</t>
   </si>
   <si>
-    <t>2026-08-07T11:39:12.809Z</t>
+    <t>2026-08-07T14:53:05.004Z</t>
   </si>
   <si>
     <t>Grace Webinar - Enhancing Stability and Bioavailability of Poorly Soluble APIs</t>
@@ -1296,7 +1296,7 @@
     <t>insights/fcc-catalyst-solutions-for-an-evolving-market</t>
   </si>
   <si>
-    <t>2026-08-07T11:32:50.906Z</t>
+    <t>2026-08-07T14:46:44.330Z</t>
   </si>
   <si>
     <t>FCC Catalyst Solutions for An Evolving Market</t>
@@ -1311,7 +1311,7 @@
     <t>insights/fccu-partial-combustion-transition</t>
   </si>
   <si>
-    <t>2026-08-07T11:42:43.004Z</t>
+    <t>2026-08-07T14:12:50.905Z</t>
   </si>
   <si>
     <t>FCCU Partial Combustion Transition</t>
@@ -1361,7 +1361,7 @@
     <t>insights/feedstock-pre-treatment-for-renewable-diesel</t>
   </si>
   <si>
-    <t>2026-08-07T11:42:30.381Z</t>
+    <t>2026-08-07T14:12:36.456Z</t>
   </si>
   <si>
     <t>Feedstock Pre-treatment for Renewable Diesel</t>
@@ -1373,7 +1373,7 @@
     <t>insights/fighting-corrosion-with-silica-based-coatings</t>
   </si>
   <si>
-    <t>2026-08-07T11:59:16.595Z</t>
+    <t>2026-08-07T14:29:23.407Z</t>
   </si>
   <si>
     <t>Fighting Corrosion with Silica-based Coatings</t>
@@ -1388,7 +1388,7 @@
     <t>insights/finding-the-right-matting-agent-for-uv-cured-coatings</t>
   </si>
   <si>
-    <t>2026-08-07T11:55:47.880Z</t>
+    <t>2026-08-07T14:26:12.108Z</t>
   </si>
   <si>
     <t>Finding the Right Matting Agent for UV-cured Coatings</t>
@@ -1403,7 +1403,7 @@
     <t>insights/first-grace-dcr-pilot-plant-inauguarated-oman</t>
   </si>
   <si>
-    <t>2026-08-07T11:49:38.539Z</t>
+    <t>2026-08-07T14:19:56.044Z</t>
   </si>
   <si>
     <t>First Grace DCR™ Pilot Plant Inaugurated in Oman</t>
@@ -1418,7 +1418,7 @@
     <t>insights/fusion-catalyst-hp-awards-finalist</t>
   </si>
   <si>
-    <t>2026-08-07T11:32:51.673Z</t>
+    <t>2026-08-07T14:46:45.486Z</t>
   </si>
   <si>
     <t>FUSION® FCC Catalyst a Finalist for “Best Catalyst Technology”</t>
@@ -1448,7 +1448,7 @@
     <t>insights/grace-awarded-2022-top-supplier-akzonobel</t>
   </si>
   <si>
-    <t>2026-08-07T11:43:36.606Z</t>
+    <t>2026-08-07T14:13:43.216Z</t>
   </si>
   <si>
     <t>Grace Awarded 2022 Top Supplier Designation by AkzoNobel South America</t>
@@ -1463,7 +1463,7 @@
     <t>insights/grace-completes-south-haven-expansion-project-celebrates-with-r</t>
   </si>
   <si>
-    <t>2026-08-07T11:54:55.222Z</t>
+    <t>2026-08-07T14:25:19.164Z</t>
   </si>
   <si>
     <t>Grace Completes South Haven Expansion Project, Celebrates with Ribbon Cutting</t>
@@ -1478,7 +1478,7 @@
     <t>insights/grace-east-chicago-indiana-lab-investment</t>
   </si>
   <si>
-    <t>2026-08-07T11:39:08.043Z</t>
+    <t>2026-08-07T14:53:02.034Z</t>
   </si>
   <si>
     <t>Grace East Chicago, Indiana Lab Investment</t>
@@ -1493,7 +1493,7 @@
     <t>insights/grace-expands-unipol-pp-technology-capacity-in-china-by-1550kta</t>
   </si>
   <si>
-    <t>2026-08-07T11:49:55.091Z</t>
+    <t>2026-08-07T14:20:02.071Z</t>
   </si>
   <si>
     <t>Grace Expands UNIPOL® PP Technology Capacity in China by 1,550KTA</t>
@@ -1508,7 +1508,7 @@
     <t>insights/grace-fine-chemicals-expertise</t>
   </si>
   <si>
-    <t>2026-08-07T11:47:48.202Z</t>
+    <t>2026-08-07T14:17:54.638Z</t>
   </si>
   <si>
     <t>Grace Fine Chemicals Expertise</t>
@@ -1523,7 +1523,7 @@
     <t>insights/grace-helps-make-lighter-cars-to-save-gas</t>
   </si>
   <si>
-    <t>2026-08-07T11:50:48.667Z</t>
+    <t>2026-08-07T14:20:55.305Z</t>
   </si>
   <si>
     <t>Grace Helps Make Lighter Cars to Save Gas</t>
@@ -1538,7 +1538,7 @@
     <t>insights/grace-in-your-world</t>
   </si>
   <si>
-    <t>2026-08-07T11:37:21.666Z</t>
+    <t>2026-08-07T14:51:15.662Z</t>
   </si>
   <si>
     <t>Where is Grace in Your World?</t>
@@ -1553,7 +1553,7 @@
     <t>insights/grace-named-catalyst-provider-of-the-year</t>
   </si>
   <si>
-    <t>2026-08-07T11:46:06.938Z</t>
+    <t>2026-08-07T14:16:21.033Z</t>
   </si>
   <si>
     <t>Grace Named Catalyst Provider of the Year</t>
@@ -1568,7 +1568,7 @@
     <t>insights/grace-recognized-as-a-top-coatings-supplier-by-akzonobel-again</t>
   </si>
   <si>
-    <t>2026-08-07T11:56:49.501Z</t>
+    <t>2026-08-07T14:27:08.055Z</t>
   </si>
   <si>
     <t>Grace recognized as a top coatings supplier by AkzoNobel – again!</t>
@@ -1598,7 +1598,7 @@
     <t>insights/grace-silica-goes-into-promegas-purification-kits</t>
   </si>
   <si>
-    <t>2026-08-07T11:40:02.705Z</t>
+    <t>2026-08-07T14:10:07.464Z</t>
   </si>
   <si>
     <t>Grace Silica Goes into Promega’s Purification Kits to Enable COVID-19 PCR Testing</t>
@@ -1613,7 +1613,7 @@
     <t>insights/graces-fcms-supports-us-biosecurity</t>
   </si>
   <si>
-    <t>2026-08-07T11:48:40.640Z</t>
+    <t>2026-08-07T14:18:48.037Z</t>
   </si>
   <si>
     <t>Grace’s FCMS Supports US Biosecurity</t>
@@ -1643,7 +1643,7 @@
     <t>insights/helping-to-decarbonize-the-fccu</t>
   </si>
   <si>
-    <t>2026-08-07T11:54:19.677Z</t>
+    <t>2026-08-07T14:24:30.460Z</t>
   </si>
   <si>
     <t>Helping to Decarbonize the FCCU</t>
@@ -1673,7 +1673,7 @@
     <t>insights/how-customers-benefit-from-program-teams-at-grace-fcms</t>
   </si>
   <si>
-    <t>2026-08-07T11:51:34.354Z</t>
+    <t>2026-08-07T14:21:43.407Z</t>
   </si>
   <si>
     <t>How Customers Benefit From Program Teams at Grace FCMS</t>
@@ -1688,7 +1688,7 @@
     <t>insights/how-grace-built-a-better-vanadium-trap</t>
   </si>
   <si>
-    <t>2026-08-07T11:52:16.584Z</t>
+    <t>2026-08-07T14:22:37.527Z</t>
   </si>
   <si>
     <t>How Grace Built a Better Vanadium Trap</t>
@@ -1703,7 +1703,7 @@
     <t>insights/how-to-achieve-a-matte-wood-finish-without-compromising-performa</t>
   </si>
   <si>
-    <t>2026-08-07T11:57:41.345Z</t>
+    <t>2026-08-07T14:28:01.442Z</t>
   </si>
   <si>
     <t>How to Achieve a Matte Wood Finish without Compromising Performance</t>
@@ -1733,7 +1733,7 @@
     <t>insights/how-to-achieve-refinery-flexibility-with-effective-renewable-fue</t>
   </si>
   <si>
-    <t>2026-08-07T11:59:26.516Z</t>
+    <t>2026-08-07T14:29:47.605Z</t>
   </si>
   <si>
     <t>How to Achieve Refinery Flexibility with Effective Renewable Fuel Pretreatment</t>
@@ -1748,7 +1748,7 @@
     <t>insights/how-to-improve-reactor-operations-and-product-versatility</t>
   </si>
   <si>
-    <t>2026-08-07T11:58:43.281Z</t>
+    <t>2026-08-07T14:28:57.214Z</t>
   </si>
   <si>
     <t>How to improve reactor operations and product versatility</t>
@@ -1778,7 +1778,7 @@
     <t>insights/hydrogenation-innovations</t>
   </si>
   <si>
-    <t>2026-08-07T11:35:23.929Z</t>
+    <t>2026-08-07T14:49:17.825Z</t>
   </si>
   <si>
     <t>Hydrogenation Innovations</t>
@@ -1793,7 +1793,7 @@
     <t>insights/identifying-value-from-co2-reduction-in-the-fcc-unit</t>
   </si>
   <si>
-    <t>2026-08-07T11:46:59.604Z</t>
+    <t>2026-08-07T14:17:14.089Z</t>
   </si>
   <si>
     <t>Identifying Value from CO2 Reduction in the FCC Unit</t>
@@ -1823,7 +1823,7 @@
     <t>insights/improving-fuel-production</t>
   </si>
   <si>
-    <t>2026-08-07T11:34:40.805Z</t>
+    <t>2026-08-07T14:48:34.537Z</t>
   </si>
   <si>
     <t>Improving Fuel Production</t>
@@ -1883,7 +1883,7 @@
     <t>insights/keeping-surfaces-cool-with-colloidal-silica</t>
   </si>
   <si>
-    <t>2026-08-07T11:57:34.037Z</t>
+    <t>2026-08-07T14:27:57.307Z</t>
   </si>
   <si>
     <t>Keeping Surfaces Cool with Colloidal Silica</t>
@@ -1898,7 +1898,7 @@
     <t>insights/let-the-oil-free-flow</t>
   </si>
   <si>
-    <t>2026-08-07T11:49:48.542Z</t>
+    <t>2026-08-07T14:19:58.367Z</t>
   </si>
   <si>
     <t>Let the Oil Free-Flow</t>
@@ -1913,7 +1913,7 @@
     <t>insights/ludox-colloidal-silica-plays-critical-role-customized-catalysts</t>
   </si>
   <si>
-    <t>2026-08-07T11:34:37.469Z</t>
+    <t>2026-08-07T14:48:32.746Z</t>
   </si>
   <si>
     <t>LUDOX® Colloidal Silica Plays Critical Role in Customized Catalysts</t>
@@ -1943,7 +1943,7 @@
     <t>insights/maximize-savings-using-catalysts-that-enhance-polyethylene-resin</t>
   </si>
   <si>
-    <t>2026-08-07T12:00:30.144Z</t>
+    <t>2026-08-07T14:30:45.129Z</t>
   </si>
   <si>
     <t>Maximize Savings using Catalysts that Enhance Polyethylene Resin Production in Film Manufacturing</t>
@@ -1958,7 +1958,7 @@
     <t>insights/measuring-quality</t>
   </si>
   <si>
-    <t>2026-08-07T11:53:09.670Z</t>
+    <t>2026-08-07T14:23:32.302Z</t>
   </si>
   <si>
     <t>Measuring Quality</t>
@@ -1973,7 +1973,7 @@
     <t>insights/metallocene-vs-ziegler-natta-catalysts</t>
   </si>
   <si>
-    <t>2026-08-07T11:58:34.948Z</t>
+    <t>2026-08-07T14:28:54.311Z</t>
   </si>
   <si>
     <t>Metallocene vs. Ziegler-Natta Catalysts: Which to Choose?</t>
@@ -2003,7 +2003,7 @@
     <t>insights/multi-functional-silicas-in-pharmaceutical-nutraceutical</t>
   </si>
   <si>
-    <t>2026-08-07T12:00:15.037Z</t>
+    <t>2026-08-07T14:30:38.589Z</t>
   </si>
   <si>
     <t>Multi-functional Silicas in Pharmaceutical &amp; Nutraceutical Applications</t>
@@ -2018,7 +2018,7 @@
     <t>insights/new-solution-for-removing-glycidyl-esters-from-edible-oils</t>
   </si>
   <si>
-    <t>2026-08-07T11:32:43.882Z</t>
+    <t>2026-08-07T14:46:38.127Z</t>
   </si>
   <si>
     <t>A New Solution for Removing Glycidyl Esters from Once-Refined Edible and Specialty Oils</t>
@@ -2048,7 +2048,7 @@
     <t>insights/pharmas-almanac-cites-grace-experts-in-q3-2021-round-table</t>
   </si>
   <si>
-    <t>2026-08-07T11:41:53.831Z</t>
+    <t>2026-08-07T14:11:58.298Z</t>
   </si>
   <si>
     <t>Pharma’s Almanac Cites Grace Experts in Q3 2021 Round Table</t>
@@ -2063,7 +2063,7 @@
     <t>insights/powerful-technology-through-tiny-particles</t>
   </si>
   <si>
-    <t>2026-08-07T11:43:30.317Z</t>
+    <t>2026-08-07T14:13:42.307Z</t>
   </si>
   <si>
     <t>Powerful Technology Through Tiny Particles</t>
@@ -2078,7 +2078,7 @@
     <t>insights/providing-customers-with-new-catalyst-options</t>
   </si>
   <si>
-    <t>2026-08-07T11:35:34.932Z</t>
+    <t>2026-08-07T14:49:29.528Z</t>
   </si>
   <si>
     <t>Providing Customers with New Catalyst Options</t>
@@ -2093,7 +2093,7 @@
     <t>insights/q-and-a-sudhakar-jale</t>
   </si>
   <si>
-    <t>2026-08-07T11:37:25.539Z</t>
+    <t>2026-08-07T14:51:17.773Z</t>
   </si>
   <si>
     <t>Q&amp;A Sudhakar Jale</t>
@@ -2108,7 +2108,7 @@
     <t>insights/random-copolymer-resins-using-consista</t>
   </si>
   <si>
-    <t>2026-08-07T11:52:27.674Z</t>
+    <t>2026-08-07T14:22:36.607Z</t>
   </si>
   <si>
     <t>Innovation and Performance for Random Copolymer Resins with CONSISTA® Catalysts and Donors</t>
@@ -2123,7 +2123,7 @@
     <t>insights/raney-catalyst-historic-chemical-landmark-award-acs</t>
   </si>
   <si>
-    <t>2026-08-07T11:44:29.571Z</t>
+    <t>2026-08-07T14:14:36.038Z</t>
   </si>
   <si>
     <t>Grace RANEY® Brand of Catalyst Earns Historic Chemical Landmark Award from American Chemical Society</t>
@@ -2138,7 +2138,7 @@
     <t>insights/refolution-project-explores-potential-cost-effective-biofuels</t>
   </si>
   <si>
-    <t>2026-08-07T11:51:41.808Z</t>
+    <t>2026-08-07T14:21:49.636Z</t>
   </si>
   <si>
     <t>REFOLUTION Project Explores Europe’s Potential for Cost-effective Biofuels</t>
@@ -2153,7 +2153,7 @@
     <t>insights/regulatory-compliance-in-fine-chemical-manufacturing</t>
   </si>
   <si>
-    <t>2026-08-07T11:47:14.743Z</t>
+    <t>2026-08-07T14:17:20.796Z</t>
   </si>
   <si>
     <t>Regulatory Compliance in Fine Chemical Manufacturing</t>
@@ -2168,7 +2168,7 @@
     <t>insights/reliance-celebrated-25-years-at-first-pp-plant</t>
   </si>
   <si>
-    <t>2026-08-07T11:44:16.171Z</t>
+    <t>2026-08-07T14:14:22.214Z</t>
   </si>
   <si>
     <t>Reliance Celebrated 25 Years at First PP Plant</t>
@@ -2213,7 +2213,7 @@
     <t>insights/shieldex-silica-for-land-sea-air</t>
   </si>
   <si>
-    <t>2026-08-07T11:43:23.531Z</t>
+    <t>2026-08-07T14:13:28.969Z</t>
   </si>
   <si>
     <t>Environmentally Friendly Corrosion Protection for Land, Sea, and Air</t>
@@ -2228,7 +2228,7 @@
     <t>insights/silica-and-nutraceuticals</t>
   </si>
   <si>
-    <t>2026-08-07T11:34:44.205Z</t>
+    <t>2026-08-07T14:48:35.872Z</t>
   </si>
   <si>
     <t>Silica and Nutraceuticals</t>
@@ -2258,7 +2258,7 @@
     <t>insights/silica-science-on-the-road</t>
   </si>
   <si>
-    <t>2026-08-07T11:53:59.831Z</t>
+    <t>2026-08-07T14:24:07.418Z</t>
   </si>
   <si>
     <t>Silica Science on the Road</t>
@@ -2273,7 +2273,7 @@
     <t>insights/silica-versus-pandemic</t>
   </si>
   <si>
-    <t>2026-08-07T11:37:08.906Z</t>
+    <t>2026-08-07T14:51:05.124Z</t>
   </si>
   <si>
     <t>Silica Versus Pandemic</t>
@@ -2303,7 +2303,7 @@
     <t>insights/small-scale-big-impact-the-advantages-of-flexible-pilot-plant</t>
   </si>
   <si>
-    <t>2026-08-07T11:57:50.864Z</t>
+    <t>2026-08-07T14:28:05.238Z</t>
   </si>
   <si>
     <t>Small scale, big impact: The advantages of flexible pilot plant equipment</t>
@@ -2318,7 +2318,7 @@
     <t>insights/standard-industries-challenge-puts-ai-and-ml-to-work-for-chemist</t>
   </si>
   <si>
-    <t>2026-08-07T11:58:27.445Z</t>
+    <t>2026-08-07T14:28:51.105Z</t>
   </si>
   <si>
     <t>Standard Industries Challenge Puts AI and ML to Work for Chemistry</t>
@@ -2348,7 +2348,7 @@
     <t>insights/supporting-refinery-sustainability-goals</t>
   </si>
   <si>
-    <t>2026-08-07T11:41:37.227Z</t>
+    <t>2026-08-07T14:11:44.161Z</t>
   </si>
   <si>
     <t>Supporting Refinery Sustainability Goals</t>
@@ -2363,7 +2363,7 @@
     <t>insights/sustainable-innovation</t>
   </si>
   <si>
-    <t>2026-08-07T11:45:14.856Z</t>
+    <t>2026-08-07T14:15:28.341Z</t>
   </si>
   <si>
     <t>Sustainable Innovation</t>
@@ -2378,7 +2378,7 @@
     <t>insights/syloid-cat-11-silica-a-matting-additive-with-superior-efficiency</t>
   </si>
   <si>
-    <t>2026-08-07T11:41:00.408Z</t>
+    <t>2026-08-07T14:11:04.744Z</t>
   </si>
   <si>
     <t>SYLOID® CAT 11 Silica - a Matting Additive with Superior Efficiency</t>
@@ -2396,7 +2396,7 @@
     <t>insights/syloid-mx110-silica-a-matting-additive-with-superior-efficiency</t>
   </si>
   <si>
-    <t>2026-08-07T11:40:05.907Z</t>
+    <t>2026-08-07T14:10:10.943Z</t>
   </si>
   <si>
     <t>SYLOID® MX 110 Silica - a Matting Additive with Superior Efficiency</t>
@@ -2426,7 +2426,7 @@
     <t>insights/technical-support-for-fluid-catalytic-cracking</t>
   </si>
   <si>
-    <t>2026-08-07T11:36:32.079Z</t>
+    <t>2026-08-07T14:50:24.445Z</t>
   </si>
   <si>
     <t>Technical Support for Fluid Catalytic Cracking</t>
@@ -2456,7 +2456,7 @@
     <t>insights/the-art-of-process-development</t>
   </si>
   <si>
-    <t>2026-08-07T11:53:07.815Z</t>
+    <t>2026-08-07T14:23:14.646Z</t>
   </si>
   <si>
     <t>The Art of Process Development</t>
@@ -2471,7 +2471,7 @@
     <t>insights/the-benefits-of-custom-bonded-silica</t>
   </si>
   <si>
-    <t>2026-08-07T11:54:03.178Z</t>
+    <t>2026-08-07T14:24:24.833Z</t>
   </si>
   <si>
     <t>The Benefits of Custom Bonded Silica</t>
@@ -2486,7 +2486,7 @@
     <t>insights/the-case-for-colloidal-silica</t>
   </si>
   <si>
-    <t>2026-08-07T11:39:01.820Z</t>
+    <t>2026-08-07T14:53:01.106Z</t>
   </si>
   <si>
     <t>The Case for Colloidal Silica</t>
@@ -2513,7 +2513,7 @@
     <t>insights/the-flexible-fcc</t>
   </si>
   <si>
-    <t>2026-08-07T11:59:35.970Z</t>
+    <t>2026-08-07T14:29:51.029Z</t>
   </si>
   <si>
     <t>The Flexible FCC</t>
@@ -2528,7 +2528,7 @@
     <t>insights/the-growth-of-nutraceuticals</t>
   </si>
   <si>
-    <t>2026-08-07T11:51:24.428Z</t>
+    <t>2026-08-07T14:21:44.107Z</t>
   </si>
   <si>
     <t>The Growth of Nutraceuticals</t>
@@ -2543,7 +2543,7 @@
     <t>insights/the-latest-innovations-and-trends-in-the-wood-coatings-market</t>
   </si>
   <si>
-    <t>2026-08-07T12:00:19.094Z</t>
+    <t>2026-08-07T14:30:41.729Z</t>
   </si>
   <si>
     <t>The Latest Innovations and Trends in the Wood Coatings Market</t>
@@ -2573,7 +2573,7 @@
     <t>insights/the-trisyl-silica-advantage-for-renewable-feedstock-pretreatment</t>
   </si>
   <si>
-    <t>2026-08-07T11:55:46.043Z</t>
+    <t>2026-08-07T14:25:50.880Z</t>
   </si>
   <si>
     <t>The TRISYL® Silica Advantage for Renewable Feedstock Pretreatment</t>
@@ -2588,7 +2588,7 @@
     <t>insights/three-ways-grace-helps-refiners-with-feedstock-flexibility</t>
   </si>
   <si>
-    <t>2026-08-07T11:54:12.151Z</t>
+    <t>2026-08-07T14:24:25.167Z</t>
   </si>
   <si>
     <t>Three Ways Grace Helps Refiners with Feedstock Flexibility</t>
@@ -2618,7 +2618,7 @@
     <t>insights/transparent-transfer</t>
   </si>
   <si>
-    <t>2026-08-07T11:51:21.231Z</t>
+    <t>2026-08-07T14:21:28.976Z</t>
   </si>
   <si>
     <t>Transparent Transfer</t>
@@ -2633,7 +2633,7 @@
     <t>insights/troubleshoot-fcc-reactor-level-control-with-fluidization-princip</t>
   </si>
   <si>
-    <t>2026-08-07T11:58:23.635Z</t>
+    <t>2026-08-07T14:28:28.904Z</t>
   </si>
   <si>
     <t>Troubleshoot FCC Reactor Level Control with Fluidization Principles</t>
@@ -2648,7 +2648,7 @@
     <t>insights/unipol-polypropylene-technology-learn-more</t>
   </si>
   <si>
-    <t>2026-08-07T11:48:54.772Z</t>
+    <t>2026-08-07T14:19:03.631Z</t>
   </si>
   <si>
     <t>What You Need to Know About UNIPOL® Polypropylene Technology</t>
@@ -2663,7 +2663,7 @@
     <t>insights/unipol-pp-technology-advances-terpolymer-solutions-in-china</t>
   </si>
   <si>
-    <t>2026-08-07T11:59:20.607Z</t>
+    <t>2026-08-07T14:29:44.507Z</t>
   </si>
   <si>
     <t>UNIPOL® PP Technology Advances Terpolymer Solutions in China</t>
@@ -2681,7 +2681,7 @@
     <t>insights/unipol-pp-technology-battery-case</t>
   </si>
   <si>
-    <t>2026-08-07T11:50:32.061Z</t>
+    <t>2026-08-07T14:20:50.537Z</t>
   </si>
   <si>
     <t>Leveraging UNIPOL® PP Technology for High-Performance Battery Cases</t>
@@ -2696,7 +2696,7 @@
     <t>insights/unipol-pp-technology-delivers-plant-lifetime-performance</t>
   </si>
   <si>
-    <t>2026-08-07T11:33:49.804Z</t>
+    <t>2026-08-07T14:47:43.753Z</t>
   </si>
   <si>
     <t>UNIPOL® PP Technology Delivers Plant Lifetime Performance™</t>
@@ -2711,7 +2711,7 @@
     <t>insights/unipol-pp-technology-leading-the-way-in-innovation-and-growth</t>
   </si>
   <si>
-    <t>2026-08-07T11:53:19.280Z</t>
+    <t>2026-08-07T14:23:31.106Z</t>
   </si>
   <si>
     <t>UNIPOL® PP Technology: Leading the Way in Innovation and Growth</t>
@@ -2771,7 +2771,7 @@
     <t>insights/unlocking-fcc-value-grace-s-guide-to-fluid-catalytic-cracking</t>
   </si>
   <si>
-    <t>2026-08-07T11:55:11.911Z</t>
+    <t>2026-08-07T14:25:22.904Z</t>
   </si>
   <si>
     <t>Unlocking FCC Value: Grace’s Guide to Fluid Catalytic Cracking</t>
@@ -2786,7 +2786,7 @@
     <t>insights/unlocking-innovation-in-polypropylene-process-technology</t>
   </si>
   <si>
-    <t>2026-08-07T11:55:56.336Z</t>
+    <t>2026-08-07T14:26:13.904Z</t>
   </si>
   <si>
     <t>Unlocking Innovation in Polypropylene Process Technology</t>
@@ -2801,7 +2801,7 @@
     <t>insights/upgrading-your-anti-blocking-agent-for-thin-plastic-films</t>
   </si>
   <si>
-    <t>2026-08-07T11:56:41.706Z</t>
+    <t>2026-08-07T14:27:04.485Z</t>
   </si>
   <si>
     <t>Upgrading Your Anti-blocking Agent for Thin Plastic Films</t>
@@ -2816,7 +2816,7 @@
     <t>insights/visit-grace-at-cphi-worldwide-2021</t>
   </si>
   <si>
-    <t>2026-08-07T11:33:45.692Z</t>
+    <t>2026-08-07T14:47:39.914Z</t>
   </si>
   <si>
     <t>Visit Grace at CPhI Worldwide 2021</t>
@@ -2831,7 +2831,7 @@
     <t>insights/visit-grace-at-supplyside-west-2021</t>
   </si>
   <si>
-    <t>2026-08-07T11:34:31.005Z</t>
+    <t>2026-08-07T14:48:24.927Z</t>
   </si>
   <si>
     <t>Visit Grace at SupplySide West 2021</t>
@@ -2846,7 +2846,7 @@
     <t>insights/visit-grace-at-vitafoods-europe-2021</t>
   </si>
   <si>
-    <t>2026-08-07T11:33:44.995Z</t>
+    <t>2026-08-07T14:47:39.202Z</t>
   </si>
   <si>
     <t>Visit Grace at Vitafoods Europe 2021</t>
@@ -2861,7 +2861,7 @@
     <t>insights/vitafoods-europe-2022</t>
   </si>
   <si>
-    <t>2026-08-07T11:43:42.592Z</t>
+    <t>2026-08-07T14:13:47.869Z</t>
   </si>
   <si>
     <t>Vitafoods Europe 2022</t>
@@ -2876,7 +2876,7 @@
     <t>insights/well-characterized-rsms-free-of-impurities</t>
   </si>
   <si>
-    <t>2026-08-07T11:48:01.913Z</t>
+    <t>2026-08-07T14:18:09.901Z</t>
   </si>
   <si>
     <t>Well Characterized RSMs Free of Impurities</t>
@@ -2891,7 +2891,7 @@
     <t>insights/who-was-murray-raney</t>
   </si>
   <si>
-    <t>2026-08-07T11:52:33.844Z</t>
+    <t>2026-08-07T14:22:42.976Z</t>
   </si>
   <si>
     <t>Who was Murray Raney?</t>
@@ -2906,7 +2906,7 @@
     <t>insights/why-local-cdmo-matters</t>
   </si>
   <si>
-    <t>2026-08-07T11:47:52.421Z</t>
+    <t>2026-08-07T14:18:08.653Z</t>
   </si>
   <si>
     <t>Keeping it Local</t>
@@ -4789,7 +4789,7 @@
         <v>19</v>
       </c>
       <c r="E24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F24" t="s">
         <v>19</v>
@@ -5189,7 +5189,7 @@
         <v>19</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F32" t="s">
         <v>19</v>
@@ -7289,7 +7289,7 @@
         <v>19</v>
       </c>
       <c r="E74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F74" t="s">
         <v>19</v>
@@ -7489,7 +7489,7 @@
         <v>19</v>
       </c>
       <c r="E78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F78" t="s">
         <v>19</v>
@@ -8089,7 +8089,7 @@
         <v>19</v>
       </c>
       <c r="E90">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F90" t="s">
         <v>19</v>

--- a/tools/importer/reports/import-grace-master.report.xlsx
+++ b/tools/importer/reports/import-grace-master.report.xlsx
@@ -415,7 +415,7 @@
     <t>insights/4-ways-cdmos-help-nutraceutical-companies-grow</t>
   </si>
   <si>
-    <t>2026-08-07T14:30:16.203Z</t>
+    <t>2026-08-07T17:02:20.305Z</t>
   </si>
   <si>
     <t>4 Ways CDMOs help Nutraceutical Companies Grow</t>
@@ -453,7 +453,7 @@
     <t>insights/5-benefits-of-leveraging-machine-learning-in-pd-workflows</t>
   </si>
   <si>
-    <t>2026-08-07T10:14:33.484Z</t>
+    <t>2026-08-07T17:02:56.172Z</t>
   </si>
   <si>
     <t>5 Benefits Of Leveraging Machine Learning In Your Process Development Workflows</t>
@@ -465,7 +465,7 @@
     <t>insights/5-things-to-consider-when-selecting-a-chromatography-silica</t>
   </si>
   <si>
-    <t>2026-08-07T14:26:17.707Z</t>
+    <t>2026-08-07T16:56:39.489Z</t>
   </si>
   <si>
     <t>5 Things to Consider When Selecting a Chromatography Silica</t>
@@ -480,7 +480,7 @@
     <t>insights/80-years-of-fcc</t>
   </si>
   <si>
-    <t>2026-08-07T15:15:49.836Z</t>
+    <t>2026-08-07T16:43:59.955Z</t>
   </si>
   <si>
     <t>80 Years of FCC</t>
@@ -495,7 +495,7 @@
     <t>insights/a-better-way-to-dehydrate-ethanol</t>
   </si>
   <si>
-    <t>2026-08-07T14:51:13.405Z</t>
+    <t>2026-08-07T16:33:08.877Z</t>
   </si>
   <si>
     <t>A Better Way to Dehydrate Ethanol</t>
@@ -510,7 +510,7 @@
     <t>insights/a-brewers-challenge</t>
   </si>
   <si>
-    <t>2026-08-07T14:22:20.830Z</t>
+    <t>2026-08-07T16:57:01.270Z</t>
   </si>
   <si>
     <t>A Brewer’s Challenge</t>
@@ -525,7 +525,7 @@
     <t>insights/a-brewery-goes-green</t>
   </si>
   <si>
-    <t>2026-08-07T14:49:29.830Z</t>
+    <t>2026-08-07T16:36:45.670Z</t>
   </si>
   <si>
     <t>A Brewery Goes Green</t>
@@ -540,7 +540,7 @@
     <t>insights/a-legacy-of-innovation</t>
   </si>
   <si>
-    <t>2026-08-07T14:50:11.281Z</t>
+    <t>2026-08-07T16:37:39.607Z</t>
   </si>
   <si>
     <t>A Legacy of Innovation</t>
@@ -555,7 +555,7 @@
     <t>insights/a-matte-that-lasts</t>
   </si>
   <si>
-    <t>2026-08-07T14:49:27.933Z</t>
+    <t>2026-08-07T16:34:58.429Z</t>
   </si>
   <si>
     <t>A Matte That Lasts</t>
@@ -570,7 +570,7 @@
     <t>insights/a-path-to-co-processing-chemical-recycling-products</t>
   </si>
   <si>
-    <t>2026-08-07T12:02:55.464Z</t>
+    <t>2026-08-07T17:05:30.879Z</t>
   </si>
   <si>
     <t>A Path to Co-processing Chemical Recycling Products</t>
@@ -585,7 +585,7 @@
     <t>insights/a-proven-approach-to-impurity-control-across-api-and-rsm-synthes</t>
   </si>
   <si>
-    <t>2026-08-07T12:01:08.866Z</t>
+    <t>2026-08-07T17:06:44.475Z</t>
   </si>
   <si>
     <t>A Proven Approach to Impurity Control Across API and RSM Synthesis</t>
@@ -600,7 +600,7 @@
     <t>insights/a-refined-view-on-environmental-additives</t>
   </si>
   <si>
-    <t>2026-08-07T14:47:31.440Z</t>
+    <t>2026-08-07T16:35:59.605Z</t>
   </si>
   <si>
     <t>A Refined View on Environmental Additives</t>
@@ -615,7 +615,7 @@
     <t>insights/a-successful-case-of-resid-to-propylene-maximization</t>
   </si>
   <si>
-    <t>2026-08-07T14:17:00.551Z</t>
+    <t>2026-08-07T16:44:57.837Z</t>
   </si>
   <si>
     <t>A Successful Case of Resid-to-Propylene Maximization at OQ</t>
@@ -630,7 +630,7 @@
     <t>insights/activcat-catalyst-technologies-for-blown-film</t>
   </si>
   <si>
-    <t>2026-08-07T14:10:51.328Z</t>
+    <t>2026-08-07T16:37:40.141Z</t>
   </si>
   <si>
     <t>The ActivCat® Catalyst Advantage: Using Metallocene PE for Blown Film</t>
@@ -645,7 +645,7 @@
     <t>insights/activcat-catalyst-technologies-for-cast-film</t>
   </si>
   <si>
-    <t>2026-08-07T14:11:02.505Z</t>
+    <t>2026-08-07T16:39:28.134Z</t>
   </si>
   <si>
     <t>ActivCat® Catalyst Technologies for Cast Film</t>
@@ -660,7 +660,7 @@
     <t>insights/activcat-catalyst-technologies-for-pert</t>
   </si>
   <si>
-    <t>2026-08-07T14:10:59.905Z</t>
+    <t>2026-08-07T16:38:34.109Z</t>
   </si>
   <si>
     <t>ActivCat® Catalyst Technologies for PE-RT</t>
@@ -675,7 +675,7 @@
     <t>insights/activcat-innovation-solutions</t>
   </si>
   <si>
-    <t>2026-08-07T14:19:07.158Z</t>
+    <t>2026-08-07T16:45:52.799Z</t>
   </si>
   <si>
     <t>ActivCat® Catalyst Innovative Solutions</t>
@@ -690,7 +690,7 @@
     <t>insights/activcat-metallocene-catalysts-pe-film-pert-resins-zpc</t>
   </si>
   <si>
-    <t>2026-08-07T14:20:51.288Z</t>
+    <t>2026-08-07T16:51:48.332Z</t>
   </si>
   <si>
     <t>Grace ActivCat® Catalyst Technology Partners to Develop Innovative Metallocene Polyethylene Resins</t>
@@ -705,7 +705,7 @@
     <t>insights/activcat-wins-chemical-weeks-sustainable-product-innovation-award</t>
   </si>
   <si>
-    <t>2026-08-07T14:14:42.217Z</t>
+    <t>2026-08-07T16:45:47.230Z</t>
   </si>
   <si>
     <t>ActivCat® Catalyst Wins Chemical Week’s Sustainable Product Innovation Award</t>
@@ -720,7 +720,7 @@
     <t>insights/advancing-encapsulation-technologies</t>
   </si>
   <si>
-    <t>2026-08-07T14:15:15.145Z</t>
+    <t>2026-08-07T16:46:42.050Z</t>
   </si>
   <si>
     <t>Advancing Encapsulation Technologies with Colloidal Silica</t>
@@ -735,7 +735,7 @@
     <t>insights/amino-acid-chemistry</t>
   </si>
   <si>
-    <t>2026-08-07T14:18:14.748Z</t>
+    <t>2026-08-07T16:42:18.845Z</t>
   </si>
   <si>
     <t>Amino Acid Chemistry</t>
@@ -750,7 +750,7 @@
     <t>insights/answering-refiners-questions</t>
   </si>
   <si>
-    <t>2026-08-07T14:23:37.407Z</t>
+    <t>2026-08-07T16:54:48.908Z</t>
   </si>
   <si>
     <t>Answering Refiners’ Questions</t>
@@ -765,7 +765,7 @@
     <t>insights/anti-blocking-technology-in-pet-and-bopet-films</t>
   </si>
   <si>
-    <t>2026-08-07T14:12:52.931Z</t>
+    <t>2026-08-07T16:47:21.863Z</t>
   </si>
   <si>
     <t>Anti-Blocking Technology in PET and BOPET Films</t>
@@ -780,7 +780,7 @@
     <t>insights/benefits-of-vyvid-superparamagnetic-silica-in-medical-diagnostics</t>
   </si>
   <si>
-    <t>2026-08-07T14:25:19.295Z</t>
+    <t>2026-08-07T16:52:09.606Z</t>
   </si>
   <si>
     <t>Benefits of VYVID™ Superparamagnetic Silica in Medical Diagnostics</t>
@@ -795,7 +795,7 @@
     <t>insights/building-a-resilient-supply-chain-for-your-next-generation-pepti</t>
   </si>
   <si>
-    <t>2026-08-07T12:02:15.730Z</t>
+    <t>2026-08-07T17:03:42.806Z</t>
   </si>
   <si>
     <t>Building A Resilient Supply Chain For Your Next-Generation Peptide Therapeutic</t>
@@ -810,7 +810,7 @@
     <t>insights/capture-value-by-processing-resid-in-the-fcc</t>
   </si>
   <si>
-    <t>2026-08-07T14:09:58.246Z</t>
+    <t>2026-08-07T16:34:03.963Z</t>
   </si>
   <si>
     <t>Capture Value by Processing Resid in the FCC</t>
@@ -825,7 +825,7 @@
     <t>insights/catalagram-126</t>
   </si>
   <si>
-    <t>2026-08-07T14:10:05.390Z</t>
+    <t>2026-08-07T16:34:59.263Z</t>
   </si>
   <si>
     <t>Catalagram 126</t>
@@ -840,7 +840,7 @@
     <t>insights/catalagram-127</t>
   </si>
   <si>
-    <t>2026-08-07T14:16:07.913Z</t>
+    <t>2026-08-07T16:41:23.307Z</t>
   </si>
   <si>
     <t>Catalagram 127</t>
@@ -855,7 +855,7 @@
     <t>insights/catalagram-issue-128</t>
   </si>
   <si>
-    <t>2026-08-07T14:20:35.496Z</t>
+    <t>2026-08-07T16:50:01.438Z</t>
   </si>
   <si>
     <t>Download the Latest Issue of Catalagram® Magazine</t>
@@ -870,7 +870,7 @@
     <t>insights/catalysts-for-a-more-sustainable-future</t>
   </si>
   <si>
-    <t>2026-08-07T14:12:49.931Z</t>
+    <t>2026-08-07T16:45:38.704Z</t>
   </si>
   <si>
     <t>Catalysts for a More Sustainable Future</t>
@@ -885,7 +885,7 @@
     <t>insights/catalysts-pave-sustainable-path-po-manufacturers</t>
   </si>
   <si>
-    <t>2026-08-07T14:27:37.188Z</t>
+    <t>2026-08-07T16:52:14.906Z</t>
   </si>
   <si>
     <t>Catalysts Can Help Pave a Sustainable Path for Polyolefin Manufacturers</t>
@@ -900,7 +900,7 @@
     <t>insights/challenge-accepted-teams-of-innovators-compete-to-revolutionize</t>
   </si>
   <si>
-    <t>2026-08-07T14:26:43.403Z</t>
+    <t>2026-08-07T16:57:32.261Z</t>
   </si>
   <si>
     <t>Challenge Accepted! Teams of Innovators Compete to Revolutionize Chemical Synthesis</t>
@@ -915,7 +915,7 @@
     <t>insights/choosing-a-small-molecule-drug-substance-partner</t>
   </si>
   <si>
-    <t>2026-08-07T14:24:59.122Z</t>
+    <t>2026-08-07T16:50:21.378Z</t>
   </si>
   <si>
     <t>Choosing a small-molecule drug substance partner</t>
@@ -930,7 +930,7 @@
     <t>insights/chromadex-cdmo-grace-fcms</t>
   </si>
   <si>
-    <t>2026-08-07T14:19:03.459Z</t>
+    <t>2026-08-07T16:44:06.207Z</t>
   </si>
   <si>
     <t>ChromaDex’s CDMO: Grace’s FCMS</t>
@@ -948,7 +948,7 @@
     <t>insights/chromatography-separation-specifics</t>
   </si>
   <si>
-    <t>2026-08-07T14:16:21.325Z</t>
+    <t>2026-08-07T16:43:10.907Z</t>
   </si>
   <si>
     <t>Chromatography Separation Specifics</t>
@@ -963,7 +963,7 @@
     <t>insights/cleaner-greener-biofuel</t>
   </si>
   <si>
-    <t>2026-08-07T14:50:22.643Z</t>
+    <t>2026-08-07T16:39:25.830Z</t>
   </si>
   <si>
     <t>Cleaner Greener Biofuel</t>
@@ -978,7 +978,7 @@
     <t>insights/co-processing-bio-based-feedstocks-in-the-fcc</t>
   </si>
   <si>
-    <t>2026-08-07T14:15:34.571Z</t>
+    <t>2026-08-07T16:49:24.784Z</t>
   </si>
   <si>
     <t>Co-processing Bio-based Feedstocks in the FCC</t>
@@ -993,7 +993,7 @@
     <t>insights/collaboration-consista-catalyst</t>
   </si>
   <si>
-    <t>2026-08-07T14:51:58.347Z</t>
+    <t>2026-08-07T16:35:53.140Z</t>
   </si>
   <si>
     <t>Collaboration and CONSISTA® Catalyst</t>
@@ -1008,7 +1008,7 @@
     <t>insights/colloidal-silica-and-corrosion-resistance-stabilizing-a-safer</t>
   </si>
   <si>
-    <t>2026-08-07T14:52:08.907Z</t>
+    <t>2026-08-07T16:37:41.930Z</t>
   </si>
   <si>
     <t>Colloidal Silica and Corrosion Resistance – Stabilizing a Safer Alternative</t>
@@ -1023,7 +1023,7 @@
     <t>insights/colloidal-silica-as-a-foundation-for-3-d-printed-replacement-tissues</t>
   </si>
   <si>
-    <t>2026-08-07T14:11:52.810Z</t>
+    <t>2026-08-07T16:42:06.343Z</t>
   </si>
   <si>
     <t>Colloidal Silica as a Foundation for 3-D Printed Replacement Tissues</t>
@@ -1038,7 +1038,7 @@
     <t>insights/colloidal-silica-coatings-in-food-contact-applications</t>
   </si>
   <si>
-    <t>2026-08-07T14:52:06.689Z</t>
+    <t>2026-08-07T16:36:47.743Z</t>
   </si>
   <si>
     <t>Colloidal Silica Coatings in Food-Contact Applications</t>
@@ -1053,7 +1053,7 @@
     <t>insights/colloidal-silica-small-particles-enormous-potential</t>
   </si>
   <si>
-    <t>2026-08-07T14:52:50.997Z</t>
+    <t>2026-08-07T16:39:32.673Z</t>
   </si>
   <si>
     <t>Colloidal Silica: Small Particles, Enormous Potential</t>
@@ -1068,7 +1068,7 @@
     <t>insights/colloidal-silica-takes-on-extreme-environments</t>
   </si>
   <si>
-    <t>2026-08-07T14:11:56.310Z</t>
+    <t>2026-08-07T16:42:59.560Z</t>
   </si>
   <si>
     <t>Colloidal Silica Takes on Extreme Environments</t>
@@ -1083,7 +1083,7 @@
     <t>insights/colloidal-silica-water-sample-analysis</t>
   </si>
   <si>
-    <t>2026-08-07T14:52:11.445Z</t>
+    <t>2026-08-07T16:38:36.932Z</t>
   </si>
   <si>
     <t>Colloidal Silica Can Help Expedite Water Sample Analysis of Toxic Pesticides</t>
@@ -1098,7 +1098,7 @@
     <t>insights/consista-c602-terpolymer-china-yth</t>
   </si>
   <si>
-    <t>2026-08-07T14:19:41.181Z</t>
+    <t>2026-08-07T16:46:47.506Z</t>
   </si>
   <si>
     <t>UNIPOL® PP Technology is the Premier PP Producer for Terpolymer Grade Resins Using CONSISTA® C602 Catalyst System</t>
@@ -1113,7 +1113,7 @@
     <t>insights/consista-provide-optimal-performance-in-unipol-pp</t>
   </si>
   <si>
-    <t>2026-08-07T12:01:56.193Z</t>
+    <t>2026-08-07T17:01:04.506Z</t>
   </si>
   <si>
     <t>Unlock Peak Performance and Efficiency in UNIPOL® Polypropylene Process Technology using CONSISTA® Catalysts</t>
@@ -1128,7 +1128,7 @@
     <t>insights/control-api-impurities-to-achieve-therapeutic-safety-and-efficac</t>
   </si>
   <si>
-    <t>2026-08-07T14:31:11.142Z</t>
+    <t>2026-08-07T17:05:52.228Z</t>
   </si>
   <si>
     <t>Control API Impurities to Achieve Therapeutic Safety and Efficacy for Patients</t>
@@ -1143,7 +1143,7 @@
     <t>insights/could-ai-enabled-retrosynthesis-lead-to-the-next-big-breakthrough</t>
   </si>
   <si>
-    <t>2026-08-07T14:27:11.654Z</t>
+    <t>2026-08-07T16:51:20.269Z</t>
   </si>
   <si>
     <t>Could AI-enabled Retrosynthesis Lead to the Next Big Breakthrough?</t>
@@ -1158,7 +1158,7 @@
     <t>insights/dcr-pilot-plant-creates-opportunities-in-oman</t>
   </si>
   <si>
-    <t>2026-08-07T14:16:27.440Z</t>
+    <t>2026-08-07T16:44:03.906Z</t>
   </si>
   <si>
     <t>DCR™ Pilot Plant Creates Opportunities in Oman</t>
@@ -1176,7 +1176,7 @@
     <t>insights/demand-for-high-octane-fuel-drives-refiners-to-alkylate</t>
   </si>
   <si>
-    <t>2026-08-07T14:17:15.894Z</t>
+    <t>2026-08-07T16:46:44.703Z</t>
   </si>
   <si>
     <t>Demand for High-octane Fuel Drives Refiners to Alkylate</t>
@@ -1191,7 +1191,7 @@
     <t>insights/driving-energy-efficiences-in-germanys-industry-hub</t>
   </si>
   <si>
-    <t>2026-08-07T12:03:50.246Z</t>
+    <t>2026-08-07T17:01:08.646Z</t>
   </si>
   <si>
     <t>From Water Glass to Wind Turbines: Driving Energy Efficiencies in Germany's Industry Hub</t>
@@ -1206,7 +1206,7 @@
     <t>insights/ebook-water-based-technologies-wood-coatings</t>
   </si>
   <si>
-    <t>2026-08-07T14:15:28.929Z</t>
+    <t>2026-08-07T16:48:31.667Z</t>
   </si>
   <si>
     <t>Exclusive eBook – Water-based Technologies for Wood Coatings</t>
@@ -1221,7 +1221,7 @@
     <t>insights/eliminating-gels-in-film-activcat-catalysts</t>
   </si>
   <si>
-    <t>2026-08-07T14:50:20.607Z</t>
+    <t>2026-08-07T16:38:31.928Z</t>
   </si>
   <si>
     <t>Eliminating Gels in Film with ActivCat® Catalysts</t>
@@ -1236,7 +1236,7 @@
     <t>insights/ending-the-matting-compromise</t>
   </si>
   <si>
-    <t>2026-08-07T14:46:49.407Z</t>
+    <t>2026-08-07T16:35:02.536Z</t>
   </si>
   <si>
     <t>Ending the Matting Compromise</t>
@@ -1251,7 +1251,7 @@
     <t>insights/enhance-peptide-innovation-with-a-high-quality-supply-of-buildin</t>
   </si>
   <si>
-    <t>2026-08-07T12:02:57.337Z</t>
+    <t>2026-08-07T17:06:24.144Z</t>
   </si>
   <si>
     <t>Enhance Peptide Innovation With a High-Quality Supply of Building Blocks</t>
@@ -1266,7 +1266,7 @@
     <t>insights/enhancing-micronization-processes-with-syloid-mesoporous-silica</t>
   </si>
   <si>
-    <t>2026-08-07T12:04:35.905Z</t>
+    <t>2026-08-07T17:02:54.652Z</t>
   </si>
   <si>
     <t>Enhancing Micronization Processes with SYLOID® Mesoporous Silica</t>
@@ -1281,7 +1281,7 @@
     <t>insights/enhancing-stability-and-bioavailability-of-poorly-soluble-apis</t>
   </si>
   <si>
-    <t>2026-08-07T14:53:05.004Z</t>
+    <t>2026-08-07T16:33:10.374Z</t>
   </si>
   <si>
     <t>Grace Webinar - Enhancing Stability and Bioavailability of Poorly Soluble APIs</t>
@@ -1296,7 +1296,7 @@
     <t>insights/fcc-catalyst-solutions-for-an-evolving-market</t>
   </si>
   <si>
-    <t>2026-08-07T14:46:44.330Z</t>
+    <t>2026-08-07T16:33:13.307Z</t>
   </si>
   <si>
     <t>FCC Catalyst Solutions for An Evolving Market</t>
@@ -1311,7 +1311,7 @@
     <t>insights/fccu-partial-combustion-transition</t>
   </si>
   <si>
-    <t>2026-08-07T14:12:50.905Z</t>
+    <t>2026-08-07T16:46:30.140Z</t>
   </si>
   <si>
     <t>FCCU Partial Combustion Transition</t>
@@ -1326,7 +1326,7 @@
     <t>insights/feedstock-focus-why-pretreatment-is-critical</t>
   </si>
   <si>
-    <t>2026-08-07T12:05:35.075Z</t>
+    <t>2026-08-07T16:59:22.509Z</t>
   </si>
   <si>
     <t>Feedstock focus: Why Pretreatment is Especially Critical for Renewable Fuels</t>
@@ -1361,7 +1361,7 @@
     <t>insights/feedstock-pre-treatment-for-renewable-diesel</t>
   </si>
   <si>
-    <t>2026-08-07T14:12:36.456Z</t>
+    <t>2026-08-07T16:44:46.874Z</t>
   </si>
   <si>
     <t>Feedstock Pre-treatment for Renewable Diesel</t>
@@ -1373,7 +1373,7 @@
     <t>insights/fighting-corrosion-with-silica-based-coatings</t>
   </si>
   <si>
-    <t>2026-08-07T14:29:23.407Z</t>
+    <t>2026-08-07T16:58:49.229Z</t>
   </si>
   <si>
     <t>Fighting Corrosion with Silica-based Coatings</t>
@@ -1388,7 +1388,7 @@
     <t>insights/finding-the-right-matting-agent-for-uv-cured-coatings</t>
   </si>
   <si>
-    <t>2026-08-07T14:26:12.108Z</t>
+    <t>2026-08-07T16:54:52.549Z</t>
   </si>
   <si>
     <t>Finding the Right Matting Agent for UV-cured Coatings</t>
@@ -1403,7 +1403,7 @@
     <t>insights/first-grace-dcr-pilot-plant-inauguarated-oman</t>
   </si>
   <si>
-    <t>2026-08-07T14:19:56.044Z</t>
+    <t>2026-08-07T16:47:40.268Z</t>
   </si>
   <si>
     <t>First Grace DCR™ Pilot Plant Inaugurated in Oman</t>
@@ -1418,7 +1418,7 @@
     <t>insights/fusion-catalyst-hp-awards-finalist</t>
   </si>
   <si>
-    <t>2026-08-07T14:46:45.486Z</t>
+    <t>2026-08-07T16:34:08.235Z</t>
   </si>
   <si>
     <t>FUSION® FCC Catalyst a Finalist for “Best Catalyst Technology”</t>
@@ -1433,7 +1433,7 @@
     <t>insights/giving-grace-building-stronger-communities-together</t>
   </si>
   <si>
-    <t>2026-08-07T12:06:19.447Z</t>
+    <t>2026-08-07T17:01:10.197Z</t>
   </si>
   <si>
     <t>Giving Grace Building Stronger Communities Together</t>
@@ -1448,7 +1448,7 @@
     <t>insights/grace-awarded-2022-top-supplier-akzonobel</t>
   </si>
   <si>
-    <t>2026-08-07T14:13:43.216Z</t>
+    <t>2026-08-07T16:41:19.740Z</t>
   </si>
   <si>
     <t>Grace Awarded 2022 Top Supplier Designation by AkzoNobel South America</t>
@@ -1463,7 +1463,7 @@
     <t>insights/grace-completes-south-haven-expansion-project-celebrates-with-r</t>
   </si>
   <si>
-    <t>2026-08-07T14:25:19.164Z</t>
+    <t>2026-08-07T16:51:13.803Z</t>
   </si>
   <si>
     <t>Grace Completes South Haven Expansion Project, Celebrates with Ribbon Cutting</t>
@@ -1478,7 +1478,7 @@
     <t>insights/grace-east-chicago-indiana-lab-investment</t>
   </si>
   <si>
-    <t>2026-08-07T14:53:02.034Z</t>
+    <t>2026-08-07T16:32:16.533Z</t>
   </si>
   <si>
     <t>Grace East Chicago, Indiana Lab Investment</t>
@@ -1493,7 +1493,7 @@
     <t>insights/grace-expands-unipol-pp-technology-capacity-in-china-by-1550kta</t>
   </si>
   <si>
-    <t>2026-08-07T14:20:02.071Z</t>
+    <t>2026-08-07T16:49:28.733Z</t>
   </si>
   <si>
     <t>Grace Expands UNIPOL® PP Technology Capacity in China by 1,550KTA</t>
@@ -1508,7 +1508,7 @@
     <t>insights/grace-fine-chemicals-expertise</t>
   </si>
   <si>
-    <t>2026-08-07T14:17:54.638Z</t>
+    <t>2026-08-07T16:48:32.370Z</t>
   </si>
   <si>
     <t>Grace Fine Chemicals Expertise</t>
@@ -1523,7 +1523,7 @@
     <t>insights/grace-helps-make-lighter-cars-to-save-gas</t>
   </si>
   <si>
-    <t>2026-08-07T14:20:55.305Z</t>
+    <t>2026-08-07T16:52:40.334Z</t>
   </si>
   <si>
     <t>Grace Helps Make Lighter Cars to Save Gas</t>
@@ -1538,7 +1538,7 @@
     <t>insights/grace-in-your-world</t>
   </si>
   <si>
-    <t>2026-08-07T14:51:15.662Z</t>
+    <t>2026-08-07T16:34:02.971Z</t>
   </si>
   <si>
     <t>Where is Grace in Your World?</t>
@@ -1553,7 +1553,7 @@
     <t>insights/grace-named-catalyst-provider-of-the-year</t>
   </si>
   <si>
-    <t>2026-08-07T14:16:21.033Z</t>
+    <t>2026-08-07T16:42:16.767Z</t>
   </si>
   <si>
     <t>Grace Named Catalyst Provider of the Year</t>
@@ -1568,7 +1568,7 @@
     <t>insights/grace-recognized-as-a-top-coatings-supplier-by-akzonobel-again</t>
   </si>
   <si>
-    <t>2026-08-07T14:27:08.055Z</t>
+    <t>2026-08-07T16:50:24.841Z</t>
   </si>
   <si>
     <t>Grace recognized as a top coatings supplier by AkzoNobel – again!</t>
@@ -1583,7 +1583,7 @@
     <t>insights/grace-showcases-cutting-edge-coatings-solutions-at-chinacoat</t>
   </si>
   <si>
-    <t>2026-08-07T12:02:48.177Z</t>
+    <t>2026-08-07T17:04:37.165Z</t>
   </si>
   <si>
     <t>Grace Showcases Cutting-edge Coatings Solutions at CHINACOAT</t>
@@ -1598,7 +1598,7 @@
     <t>insights/grace-silica-goes-into-promegas-purification-kits</t>
   </si>
   <si>
-    <t>2026-08-07T14:10:07.464Z</t>
+    <t>2026-08-07T16:35:54.304Z</t>
   </si>
   <si>
     <t>Grace Silica Goes into Promega’s Purification Kits to Enable COVID-19 PCR Testing</t>
@@ -1613,7 +1613,7 @@
     <t>insights/graces-fcms-supports-us-biosecurity</t>
   </si>
   <si>
-    <t>2026-08-07T14:18:48.037Z</t>
+    <t>2026-08-07T16:43:12.578Z</t>
   </si>
   <si>
     <t>Grace’s FCMS Supports US Biosecurity</t>
@@ -1628,7 +1628,7 @@
     <t>insights/growing-the-next-generation-of-manufacturing-leaders</t>
   </si>
   <si>
-    <t>2026-08-07T12:01:11.567Z</t>
+    <t>2026-08-07T16:59:16.387Z</t>
   </si>
   <si>
     <t>Growing the Next Generation of Manufacturing Leaders</t>
@@ -1643,7 +1643,7 @@
     <t>insights/helping-to-decarbonize-the-fccu</t>
   </si>
   <si>
-    <t>2026-08-07T14:24:30.460Z</t>
+    <t>2026-08-07T16:58:21.204Z</t>
   </si>
   <si>
     <t>Helping to Decarbonize the FCCU</t>
@@ -1658,7 +1658,7 @@
     <t>insights/hot-off-the-press-grace-s-catalagram-summer-2025-issue-is-here</t>
   </si>
   <si>
-    <t>2026-08-07T12:05:35.996Z</t>
+    <t>2026-08-07T17:07:20.119Z</t>
   </si>
   <si>
     <t>Hot Off the Press: Grace’s Catalagram® Summer 2025 Issue Is Here!</t>
@@ -1673,7 +1673,7 @@
     <t>insights/how-customers-benefit-from-program-teams-at-grace-fcms</t>
   </si>
   <si>
-    <t>2026-08-07T14:21:43.407Z</t>
+    <t>2026-08-07T16:55:16.808Z</t>
   </si>
   <si>
     <t>How Customers Benefit From Program Teams at Grace FCMS</t>
@@ -1688,7 +1688,7 @@
     <t>insights/how-grace-built-a-better-vanadium-trap</t>
   </si>
   <si>
-    <t>2026-08-07T14:22:37.527Z</t>
+    <t>2026-08-07T16:57:54.972Z</t>
   </si>
   <si>
     <t>How Grace Built a Better Vanadium Trap</t>
@@ -1703,7 +1703,7 @@
     <t>insights/how-to-achieve-a-matte-wood-finish-without-compromising-performa</t>
   </si>
   <si>
-    <t>2026-08-07T14:28:01.442Z</t>
+    <t>2026-08-07T16:54:01.471Z</t>
   </si>
   <si>
     <t>How to Achieve a Matte Wood Finish without Compromising Performance</t>
@@ -1718,7 +1718,7 @@
     <t>insights/how-to-achieve-moisture-control-in-nutraceutical-tablets</t>
   </si>
   <si>
-    <t>2026-08-07T12:06:28.868Z</t>
+    <t>2026-08-07T17:02:02.506Z</t>
   </si>
   <si>
     <t>How to Achieve Moisture Control in Nutraceutical Tablets</t>
@@ -1733,7 +1733,7 @@
     <t>insights/how-to-achieve-refinery-flexibility-with-effective-renewable-fue</t>
   </si>
   <si>
-    <t>2026-08-07T14:29:47.605Z</t>
+    <t>2026-08-07T17:00:35.686Z</t>
   </si>
   <si>
     <t>How to Achieve Refinery Flexibility with Effective Renewable Fuel Pretreatment</t>
@@ -1748,7 +1748,7 @@
     <t>insights/how-to-improve-reactor-operations-and-product-versatility</t>
   </si>
   <si>
-    <t>2026-08-07T14:28:57.214Z</t>
+    <t>2026-08-07T16:58:27.249Z</t>
   </si>
   <si>
     <t>How to improve reactor operations and product versatility</t>
@@ -1763,7 +1763,7 @@
     <t>insights/how-to-select-ethanol-molecular-sieves</t>
   </si>
   <si>
-    <t>2026-08-07T12:08:14.535Z</t>
+    <t>2026-08-07T17:08:31.369Z</t>
   </si>
   <si>
     <t>How to Select Molecular Sieves to Optimize Your Ethanol Dehydration Process</t>
@@ -1778,7 +1778,7 @@
     <t>insights/hydrogenation-innovations</t>
   </si>
   <si>
-    <t>2026-08-07T14:49:17.825Z</t>
+    <t>2026-08-07T16:34:04.483Z</t>
   </si>
   <si>
     <t>Hydrogenation Innovations</t>
@@ -1793,7 +1793,7 @@
     <t>insights/identifying-value-from-co2-reduction-in-the-fcc-unit</t>
   </si>
   <si>
-    <t>2026-08-07T14:17:14.089Z</t>
+    <t>2026-08-07T16:45:52.005Z</t>
   </si>
   <si>
     <t>Identifying Value from CO2 Reduction in the FCC Unit</t>
@@ -1808,7 +1808,7 @@
     <t>insights/improve-pla-film-performance-with-high-efficiency-anti-blocking-silica</t>
   </si>
   <si>
-    <t>2026-08-07T12:06:28.435Z</t>
+    <t>2026-08-07T17:06:31.148Z</t>
   </si>
   <si>
     <t>Improve PLA Film Performance with High Efficiency Anti-Blocking Silica</t>
@@ -1823,7 +1823,7 @@
     <t>insights/improving-fuel-production</t>
   </si>
   <si>
-    <t>2026-08-07T14:48:34.537Z</t>
+    <t>2026-08-07T16:32:16.743Z</t>
   </si>
   <si>
     <t>Improving Fuel Production</t>
@@ -1838,7 +1838,7 @@
     <t>insights/incubator-program-helps-accelerates-superparamagnetic-silica-innovation</t>
   </si>
   <si>
-    <t>2026-08-07T12:07:21.437Z</t>
+    <t>2026-08-07T17:05:37.401Z</t>
   </si>
   <si>
     <t>Incubator Program Helps Accelerate Superparamagnetic Silica Innovation</t>
@@ -1853,7 +1853,7 @@
     <t>insights/insights-from-the-2025-aci-future-of-chemical-recycling-conference</t>
   </si>
   <si>
-    <t>2026-08-07T12:02:04.869Z</t>
+    <t>2026-08-07T17:02:49.275Z</t>
   </si>
   <si>
     <t>Insights from the 2025 ACI Future of Chemical Recycling Conference</t>
@@ -1868,7 +1868,7 @@
     <t>insights/introducing-grace-essential-articles-vol-1</t>
   </si>
   <si>
-    <t>2026-08-07T12:02:01.863Z</t>
+    <t>2026-08-07T17:01:57.027Z</t>
   </si>
   <si>
     <t>Introducing Grace Essential Articles, Vol. 1</t>
@@ -1883,7 +1883,7 @@
     <t>insights/keeping-surfaces-cool-with-colloidal-silica</t>
   </si>
   <si>
-    <t>2026-08-07T14:27:57.307Z</t>
+    <t>2026-08-07T16:53:08.363Z</t>
   </si>
   <si>
     <t>Keeping Surfaces Cool with Colloidal Silica</t>
@@ -1898,7 +1898,7 @@
     <t>insights/let-the-oil-free-flow</t>
   </si>
   <si>
-    <t>2026-08-07T14:19:58.367Z</t>
+    <t>2026-08-07T16:48:33.620Z</t>
   </si>
   <si>
     <t>Let the Oil Free-Flow</t>
@@ -1913,7 +1913,7 @@
     <t>insights/ludox-colloidal-silica-plays-critical-role-customized-catalysts</t>
   </si>
   <si>
-    <t>2026-08-07T14:48:32.746Z</t>
+    <t>2026-08-07T16:40:29.941Z</t>
   </si>
   <si>
     <t>LUDOX® Colloidal Silica Plays Critical Role in Customized Catalysts</t>
@@ -1928,7 +1928,7 @@
     <t>insights/matte-finishes-reimagined</t>
   </si>
   <si>
-    <t>2026-08-07T12:08:27.127Z</t>
+    <t>2026-08-07T17:10:17.185Z</t>
   </si>
   <si>
     <t>Matte Finishes, Reimagined: How to Achieve Lasting Coatings Performance Without Tradeoffs</t>
@@ -1943,7 +1943,7 @@
     <t>insights/maximize-savings-using-catalysts-that-enhance-polyethylene-resin</t>
   </si>
   <si>
-    <t>2026-08-07T14:30:45.129Z</t>
+    <t>2026-08-07T17:04:59.825Z</t>
   </si>
   <si>
     <t>Maximize Savings using Catalysts that Enhance Polyethylene Resin Production in Film Manufacturing</t>
@@ -1958,7 +1958,7 @@
     <t>insights/measuring-quality</t>
   </si>
   <si>
-    <t>2026-08-07T14:23:32.302Z</t>
+    <t>2026-08-07T16:53:03.234Z</t>
   </si>
   <si>
     <t>Measuring Quality</t>
@@ -1973,7 +1973,7 @@
     <t>insights/metallocene-vs-ziegler-natta-catalysts</t>
   </si>
   <si>
-    <t>2026-08-07T14:28:54.311Z</t>
+    <t>2026-08-07T16:57:33.644Z</t>
   </si>
   <si>
     <t>Metallocene vs. Ziegler-Natta Catalysts: Which to Choose?</t>
@@ -1988,7 +1988,7 @@
     <t>insights/molecule-one-wins-standard-industries-chemical-innovation-challenge</t>
   </si>
   <si>
-    <t>2026-08-07T12:03:09.256Z</t>
+    <t>2026-08-07T17:07:17.595Z</t>
   </si>
   <si>
     <t>Molecule.one Wins Standard Industries Chemical Innovation Challenge</t>
@@ -2003,7 +2003,7 @@
     <t>insights/multi-functional-silicas-in-pharmaceutical-nutraceutical</t>
   </si>
   <si>
-    <t>2026-08-07T14:30:38.589Z</t>
+    <t>2026-08-07T17:03:14.685Z</t>
   </si>
   <si>
     <t>Multi-functional Silicas in Pharmaceutical &amp; Nutraceutical Applications</t>
@@ -2018,7 +2018,7 @@
     <t>insights/new-solution-for-removing-glycidyl-esters-from-edible-oils</t>
   </si>
   <si>
-    <t>2026-08-07T14:46:38.127Z</t>
+    <t>2026-08-07T16:32:16.003Z</t>
   </si>
   <si>
     <t>A New Solution for Removing Glycidyl Esters from Once-Refined Edible and Specialty Oils</t>
@@ -2033,7 +2033,7 @@
     <t>insights/optimize-your-formulations-with-a-multifunctional-silica-excipie</t>
   </si>
   <si>
-    <t>2026-08-07T12:04:56.242Z</t>
+    <t>2026-08-07T17:05:32.964Z</t>
   </si>
   <si>
     <t>Optimize Your Formulations with a Multifunctional Silica Excipient</t>
@@ -2048,7 +2048,7 @@
     <t>insights/pharmas-almanac-cites-grace-experts-in-q3-2021-round-table</t>
   </si>
   <si>
-    <t>2026-08-07T14:11:58.298Z</t>
+    <t>2026-08-07T16:43:53.190Z</t>
   </si>
   <si>
     <t>Pharma’s Almanac Cites Grace Experts in Q3 2021 Round Table</t>
@@ -2063,7 +2063,7 @@
     <t>insights/powerful-technology-through-tiny-particles</t>
   </si>
   <si>
-    <t>2026-08-07T14:13:42.307Z</t>
+    <t>2026-08-07T16:49:06.808Z</t>
   </si>
   <si>
     <t>Powerful Technology Through Tiny Particles</t>
@@ -2078,7 +2078,7 @@
     <t>insights/providing-customers-with-new-catalyst-options</t>
   </si>
   <si>
-    <t>2026-08-07T14:49:29.528Z</t>
+    <t>2026-08-07T16:35:53.005Z</t>
   </si>
   <si>
     <t>Providing Customers with New Catalyst Options</t>
@@ -2093,7 +2093,7 @@
     <t>insights/q-and-a-sudhakar-jale</t>
   </si>
   <si>
-    <t>2026-08-07T14:51:17.773Z</t>
+    <t>2026-08-07T16:34:57.892Z</t>
   </si>
   <si>
     <t>Q&amp;A Sudhakar Jale</t>
@@ -2108,7 +2108,7 @@
     <t>insights/random-copolymer-resins-using-consista</t>
   </si>
   <si>
-    <t>2026-08-07T14:22:36.607Z</t>
+    <t>2026-08-07T16:50:20.419Z</t>
   </si>
   <si>
     <t>Innovation and Performance for Random Copolymer Resins with CONSISTA® Catalysts and Donors</t>
@@ -2123,7 +2123,7 @@
     <t>insights/raney-catalyst-historic-chemical-landmark-award-acs</t>
   </si>
   <si>
-    <t>2026-08-07T14:14:36.038Z</t>
+    <t>2026-08-07T16:44:54.632Z</t>
   </si>
   <si>
     <t>Grace RANEY® Brand of Catalyst Earns Historic Chemical Landmark Award from American Chemical Society</t>
@@ -2138,7 +2138,7 @@
     <t>insights/refolution-project-explores-potential-cost-effective-biofuels</t>
   </si>
   <si>
-    <t>2026-08-07T14:21:49.636Z</t>
+    <t>2026-08-07T16:56:08.388Z</t>
   </si>
   <si>
     <t>REFOLUTION Project Explores Europe’s Potential for Cost-effective Biofuels</t>
@@ -2153,7 +2153,7 @@
     <t>insights/regulatory-compliance-in-fine-chemical-manufacturing</t>
   </si>
   <si>
-    <t>2026-08-07T14:17:20.796Z</t>
+    <t>2026-08-07T16:47:38.393Z</t>
   </si>
   <si>
     <t>Regulatory Compliance in Fine Chemical Manufacturing</t>
@@ -2168,7 +2168,7 @@
     <t>insights/reliance-celebrated-25-years-at-first-pp-plant</t>
   </si>
   <si>
-    <t>2026-08-07T14:14:22.214Z</t>
+    <t>2026-08-07T16:43:07.104Z</t>
   </si>
   <si>
     <t>Reliance Celebrated 25 Years at First PP Plant</t>
@@ -2183,7 +2183,7 @@
     <t>insights/role-of-the-kilo-lab-in-seamless-scaleup</t>
   </si>
   <si>
-    <t>2026-08-07T12:05:50.086Z</t>
+    <t>2026-08-07T17:00:16.619Z</t>
   </si>
   <si>
     <t>From IND to NDA: The Role of the Kilo Lab in a Seamless Scaleup</t>
@@ -2198,7 +2198,7 @@
     <t>insights/safety-of-sas-reaffirmed-by-efsa</t>
   </si>
   <si>
-    <t>2026-08-07T12:01:22.896Z</t>
+    <t>2026-08-07T17:00:10.460Z</t>
   </si>
   <si>
     <t>Safety of Synthetic Amorphous Silica (SAS) Reaffirmed by European Food Safety Authority</t>
@@ -2213,7 +2213,7 @@
     <t>insights/shieldex-silica-for-land-sea-air</t>
   </si>
   <si>
-    <t>2026-08-07T14:13:28.969Z</t>
+    <t>2026-08-07T16:48:14.926Z</t>
   </si>
   <si>
     <t>Environmentally Friendly Corrosion Protection for Land, Sea, and Air</t>
@@ -2228,7 +2228,7 @@
     <t>insights/silica-and-nutraceuticals</t>
   </si>
   <si>
-    <t>2026-08-07T14:48:35.872Z</t>
+    <t>2026-08-07T16:33:11.261Z</t>
   </si>
   <si>
     <t>Silica and Nutraceuticals</t>
@@ -2243,7 +2243,7 @@
     <t>insights/silica-chromatography-resins-for-lnp-purification</t>
   </si>
   <si>
-    <t>2026-08-07T12:06:43.124Z</t>
+    <t>2026-08-07T17:03:49.067Z</t>
   </si>
   <si>
     <t>The Power of Silica Chromatography Resins in Delivering Superior LNP Lipid Purification</t>
@@ -2258,7 +2258,7 @@
     <t>insights/silica-science-on-the-road</t>
   </si>
   <si>
-    <t>2026-08-07T14:24:07.418Z</t>
+    <t>2026-08-07T16:55:42.083Z</t>
   </si>
   <si>
     <t>Silica Science on the Road</t>
@@ -2273,7 +2273,7 @@
     <t>insights/silica-versus-pandemic</t>
   </si>
   <si>
-    <t>2026-08-07T14:51:05.124Z</t>
+    <t>2026-08-07T16:32:15.727Z</t>
   </si>
   <si>
     <t>Silica Versus Pandemic</t>
@@ -2288,7 +2288,7 @@
     <t>insights/six-benefits-from-cdmo-team</t>
   </si>
   <si>
-    <t>2026-08-07T12:03:48.194Z</t>
+    <t>2026-08-07T17:00:15.008Z</t>
   </si>
   <si>
     <t>Six Benefits a Biotech Company Should Expect from Their CDMO Program Team</t>
@@ -2303,7 +2303,7 @@
     <t>insights/small-scale-big-impact-the-advantages-of-flexible-pilot-plant</t>
   </si>
   <si>
-    <t>2026-08-07T14:28:05.238Z</t>
+    <t>2026-08-07T16:54:55.348Z</t>
   </si>
   <si>
     <t>Small scale, big impact: The advantages of flexible pilot plant equipment</t>
@@ -2318,7 +2318,7 @@
     <t>insights/standard-industries-challenge-puts-ai-and-ml-to-work-for-chemist</t>
   </si>
   <si>
-    <t>2026-08-07T14:28:51.105Z</t>
+    <t>2026-08-07T16:56:42.285Z</t>
   </si>
   <si>
     <t>Standard Industries Challenge Puts AI and ML to Work for Chemistry</t>
@@ -2333,7 +2333,7 @@
     <t>insights/strengthen-pharmaceutical-supply-chains-with-a-u-s-based-cdmo</t>
   </si>
   <si>
-    <t>2026-08-07T12:04:02.884Z</t>
+    <t>2026-08-07T17:02:02.539Z</t>
   </si>
   <si>
     <t>Strengthen Pharmaceutical Supply Chains with a U.S.-Based CDMO</t>
@@ -2348,7 +2348,7 @@
     <t>insights/supporting-refinery-sustainability-goals</t>
   </si>
   <si>
-    <t>2026-08-07T14:11:44.161Z</t>
+    <t>2026-08-07T16:41:14.014Z</t>
   </si>
   <si>
     <t>Supporting Refinery Sustainability Goals</t>
@@ -2363,7 +2363,7 @@
     <t>insights/sustainable-innovation</t>
   </si>
   <si>
-    <t>2026-08-07T14:15:28.341Z</t>
+    <t>2026-08-07T16:47:37.371Z</t>
   </si>
   <si>
     <t>Sustainable Innovation</t>
@@ -2378,7 +2378,7 @@
     <t>insights/syloid-cat-11-silica-a-matting-additive-with-superior-efficiency</t>
   </si>
   <si>
-    <t>2026-08-07T14:11:04.744Z</t>
+    <t>2026-08-07T16:40:21.622Z</t>
   </si>
   <si>
     <t>SYLOID® CAT 11 Silica - a Matting Additive with Superior Efficiency</t>
@@ -2396,7 +2396,7 @@
     <t>insights/syloid-mx110-silica-a-matting-additive-with-superior-efficiency</t>
   </si>
   <si>
-    <t>2026-08-07T14:10:10.943Z</t>
+    <t>2026-08-07T16:36:47.265Z</t>
   </si>
   <si>
     <t>SYLOID® MX 110 Silica - a Matting Additive with Superior Efficiency</t>
@@ -2411,7 +2411,7 @@
     <t>insights/tech-transfer-risks-and-how-to-mitigate</t>
   </si>
   <si>
-    <t>2026-08-07T12:07:35.839Z</t>
+    <t>2026-08-07T17:07:23.609Z</t>
   </si>
   <si>
     <t>The Top Tech Transfer Risks at Multi-Site CDMOs (And How to Mitigate Them With a Single-Site)</t>
@@ -2426,7 +2426,7 @@
     <t>insights/technical-support-for-fluid-catalytic-cracking</t>
   </si>
   <si>
-    <t>2026-08-07T14:50:24.445Z</t>
+    <t>2026-08-07T16:40:18.506Z</t>
   </si>
   <si>
     <t>Technical Support for Fluid Catalytic Cracking</t>
@@ -2441,7 +2441,7 @@
     <t>insights/the-advantages-of-solid-silica-supports-for-enzyme-immobilizatio</t>
   </si>
   <si>
-    <t>2026-08-07T12:05:27.708Z</t>
+    <t>2026-08-07T17:06:26.300Z</t>
   </si>
   <si>
     <t>The Advantages of Solid Silica Supports for Enzyme Immobilization</t>
@@ -2456,7 +2456,7 @@
     <t>insights/the-art-of-process-development</t>
   </si>
   <si>
-    <t>2026-08-07T14:23:14.646Z</t>
+    <t>2026-08-07T16:52:08.407Z</t>
   </si>
   <si>
     <t>The Art of Process Development</t>
@@ -2471,7 +2471,7 @@
     <t>insights/the-benefits-of-custom-bonded-silica</t>
   </si>
   <si>
-    <t>2026-08-07T14:24:24.833Z</t>
+    <t>2026-08-07T16:56:35.811Z</t>
   </si>
   <si>
     <t>The Benefits of Custom Bonded Silica</t>
@@ -2486,7 +2486,7 @@
     <t>insights/the-case-for-colloidal-silica</t>
   </si>
   <si>
-    <t>2026-08-07T14:53:01.106Z</t>
+    <t>2026-08-07T16:40:26.607Z</t>
   </si>
   <si>
     <t>The Case for Colloidal Silica</t>
@@ -2513,7 +2513,7 @@
     <t>insights/the-flexible-fcc</t>
   </si>
   <si>
-    <t>2026-08-07T14:29:51.029Z</t>
+    <t>2026-08-07T17:01:28.801Z</t>
   </si>
   <si>
     <t>The Flexible FCC</t>
@@ -2528,7 +2528,7 @@
     <t>insights/the-growth-of-nutraceuticals</t>
   </si>
   <si>
-    <t>2026-08-07T14:21:44.107Z</t>
+    <t>2026-08-07T16:54:24.205Z</t>
   </si>
   <si>
     <t>The Growth of Nutraceuticals</t>
@@ -2543,7 +2543,7 @@
     <t>insights/the-latest-innovations-and-trends-in-the-wood-coatings-market</t>
   </si>
   <si>
-    <t>2026-08-07T14:30:41.729Z</t>
+    <t>2026-08-07T17:04:07.018Z</t>
   </si>
   <si>
     <t>The Latest Innovations and Trends in the Wood Coatings Market</t>
@@ -2558,7 +2558,7 @@
     <t>insights/the-many-manufacturing-challenges-solved-by-ludox</t>
   </si>
   <si>
-    <t>2026-08-07T12:08:04.608Z</t>
+    <t>2026-08-07T17:07:38.770Z</t>
   </si>
   <si>
     <t>From Adhesion to Zeolite Synthesis: The Many Manufacturing Challenges Solved by LUDOX® Colloidal Silica</t>
@@ -2573,7 +2573,7 @@
     <t>insights/the-trisyl-silica-advantage-for-renewable-feedstock-pretreatment</t>
   </si>
   <si>
-    <t>2026-08-07T14:25:50.880Z</t>
+    <t>2026-08-07T16:53:58.609Z</t>
   </si>
   <si>
     <t>The TRISYL® Silica Advantage for Renewable Feedstock Pretreatment</t>
@@ -2588,7 +2588,7 @@
     <t>insights/three-ways-grace-helps-refiners-with-feedstock-flexibility</t>
   </si>
   <si>
-    <t>2026-08-07T14:24:25.167Z</t>
+    <t>2026-08-07T16:57:28.406Z</t>
   </si>
   <si>
     <t>Three Ways Grace Helps Refiners with Feedstock Flexibility</t>
@@ -2603,7 +2603,7 @@
     <t>insights/transforming-waste-cooking-oils-into-renewable-fuels</t>
   </si>
   <si>
-    <t>2026-08-07T12:03:41.681Z</t>
+    <t>2026-08-07T16:59:21.535Z</t>
   </si>
   <si>
     <t>Transforming Waste Cooking Oils into Renewable Fuels</t>
@@ -2618,7 +2618,7 @@
     <t>insights/transparent-transfer</t>
   </si>
   <si>
-    <t>2026-08-07T14:21:28.976Z</t>
+    <t>2026-08-07T16:53:32.183Z</t>
   </si>
   <si>
     <t>Transparent Transfer</t>
@@ -2633,7 +2633,7 @@
     <t>insights/troubleshoot-fcc-reactor-level-control-with-fluidization-princip</t>
   </si>
   <si>
-    <t>2026-08-07T14:28:28.904Z</t>
+    <t>2026-08-07T16:55:49.459Z</t>
   </si>
   <si>
     <t>Troubleshoot FCC Reactor Level Control with Fluidization Principles</t>
@@ -2648,7 +2648,7 @@
     <t>insights/unipol-polypropylene-technology-learn-more</t>
   </si>
   <si>
-    <t>2026-08-07T14:19:03.631Z</t>
+    <t>2026-08-07T16:44:58.908Z</t>
   </si>
   <si>
     <t>What You Need to Know About UNIPOL® Polypropylene Technology</t>
@@ -2663,7 +2663,7 @@
     <t>insights/unipol-pp-technology-advances-terpolymer-solutions-in-china</t>
   </si>
   <si>
-    <t>2026-08-07T14:29:44.507Z</t>
+    <t>2026-08-07T16:59:42.228Z</t>
   </si>
   <si>
     <t>UNIPOL® PP Technology Advances Terpolymer Solutions in China</t>
@@ -2681,7 +2681,7 @@
     <t>insights/unipol-pp-technology-battery-case</t>
   </si>
   <si>
-    <t>2026-08-07T14:20:50.537Z</t>
+    <t>2026-08-07T16:50:54.874Z</t>
   </si>
   <si>
     <t>Leveraging UNIPOL® PP Technology for High-Performance Battery Cases</t>
@@ -2696,7 +2696,7 @@
     <t>insights/unipol-pp-technology-delivers-plant-lifetime-performance</t>
   </si>
   <si>
-    <t>2026-08-07T14:47:43.753Z</t>
+    <t>2026-08-07T16:38:42.228Z</t>
   </si>
   <si>
     <t>UNIPOL® PP Technology Delivers Plant Lifetime Performance™</t>
@@ -2711,7 +2711,7 @@
     <t>insights/unipol-pp-technology-leading-the-way-in-innovation-and-growth</t>
   </si>
   <si>
-    <t>2026-08-07T14:23:31.106Z</t>
+    <t>2026-08-07T16:53:55.697Z</t>
   </si>
   <si>
     <t>UNIPOL® PP Technology: Leading the Way in Innovation and Growth</t>
@@ -2726,7 +2726,7 @@
     <t>insights/unipol-pp-techx-2025-recap</t>
   </si>
   <si>
-    <t>2026-08-07T12:04:41.886Z</t>
+    <t>2026-08-07T17:03:46.507Z</t>
   </si>
   <si>
     <t>Reflections from techX 2025: Advancing UNIPOL® Polypropylene Process Technology</t>
@@ -2741,7 +2741,7 @@
     <t>insights/unlock-faster-fcc-decisions</t>
   </si>
   <si>
-    <t>2026-08-07T12:07:11.484Z</t>
+    <t>2026-08-07T17:04:43.503Z</t>
   </si>
   <si>
     <t>Unlock faster FCC decisions with insight that works as hard as your unit</t>
@@ -2756,7 +2756,7 @@
     <t>insights/unlock-premium-film-performance-with-activcat-104-catalyst</t>
   </si>
   <si>
-    <t>2026-08-07T12:07:21.152Z</t>
+    <t>2026-08-07T17:09:24.088Z</t>
   </si>
   <si>
     <t>Unlock premium film performance with ActivCat® 104 catalyst</t>
@@ -2771,7 +2771,7 @@
     <t>insights/unlocking-fcc-value-grace-s-guide-to-fluid-catalytic-cracking</t>
   </si>
   <si>
-    <t>2026-08-07T14:25:22.904Z</t>
+    <t>2026-08-07T16:53:03.606Z</t>
   </si>
   <si>
     <t>Unlocking FCC Value: Grace’s Guide to Fluid Catalytic Cracking</t>
@@ -2786,7 +2786,7 @@
     <t>insights/unlocking-innovation-in-polypropylene-process-technology</t>
   </si>
   <si>
-    <t>2026-08-07T14:26:13.904Z</t>
+    <t>2026-08-07T16:55:45.683Z</t>
   </si>
   <si>
     <t>Unlocking Innovation in Polypropylene Process Technology</t>
@@ -2801,7 +2801,7 @@
     <t>insights/upgrading-your-anti-blocking-agent-for-thin-plastic-films</t>
   </si>
   <si>
-    <t>2026-08-07T14:27:04.485Z</t>
+    <t>2026-08-07T16:58:26.263Z</t>
   </si>
   <si>
     <t>Upgrading Your Anti-blocking Agent for Thin Plastic Films</t>
@@ -2816,7 +2816,7 @@
     <t>insights/visit-grace-at-cphi-worldwide-2021</t>
   </si>
   <si>
-    <t>2026-08-07T14:47:39.914Z</t>
+    <t>2026-08-07T16:37:47.908Z</t>
   </si>
   <si>
     <t>Visit Grace at CPhI Worldwide 2021</t>
@@ -2831,7 +2831,7 @@
     <t>insights/visit-grace-at-supplyside-west-2021</t>
   </si>
   <si>
-    <t>2026-08-07T14:48:24.927Z</t>
+    <t>2026-08-07T16:39:35.428Z</t>
   </si>
   <si>
     <t>Visit Grace at SupplySide West 2021</t>
@@ -2846,7 +2846,7 @@
     <t>insights/visit-grace-at-vitafoods-europe-2021</t>
   </si>
   <si>
-    <t>2026-08-07T14:47:39.202Z</t>
+    <t>2026-08-07T16:36:53.704Z</t>
   </si>
   <si>
     <t>Visit Grace at Vitafoods Europe 2021</t>
@@ -2861,7 +2861,7 @@
     <t>insights/vitafoods-europe-2022</t>
   </si>
   <si>
-    <t>2026-08-07T14:13:47.869Z</t>
+    <t>2026-08-07T16:42:12.418Z</t>
   </si>
   <si>
     <t>Vitafoods Europe 2022</t>
@@ -2876,7 +2876,7 @@
     <t>insights/well-characterized-rsms-free-of-impurities</t>
   </si>
   <si>
-    <t>2026-08-07T14:18:09.901Z</t>
+    <t>2026-08-07T16:41:26.210Z</t>
   </si>
   <si>
     <t>Well Characterized RSMs Free of Impurities</t>
@@ -2891,7 +2891,7 @@
     <t>insights/who-was-murray-raney</t>
   </si>
   <si>
-    <t>2026-08-07T14:22:42.976Z</t>
+    <t>2026-08-07T16:51:15.231Z</t>
   </si>
   <si>
     <t>Who was Murray Raney?</t>
@@ -2906,7 +2906,7 @@
     <t>insights/why-local-cdmo-matters</t>
   </si>
   <si>
-    <t>2026-08-07T14:18:08.653Z</t>
+    <t>2026-08-07T16:49:25.427Z</t>
   </si>
   <si>
     <t>Keeping it Local</t>
@@ -2921,7 +2921,7 @@
     <t>insights/women-engineers-of-grace-leading-with-purpose</t>
   </si>
   <si>
-    <t>2026-08-07T12:04:42.606Z</t>
+    <t>2026-08-07T17:04:39.200Z</t>
   </si>
   <si>
     <t>Women Engineers of Grace: Leading with Purpose</t>
@@ -6089,7 +6089,7 @@
         <v>19</v>
       </c>
       <c r="E50">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F50" t="s">
         <v>19</v>
@@ -6439,7 +6439,7 @@
         <v>19</v>
       </c>
       <c r="E57">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F57" t="s">
         <v>19</v>
@@ -7039,7 +7039,7 @@
         <v>19</v>
       </c>
       <c r="E69">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F69" t="s">
         <v>19</v>
@@ -7089,7 +7089,7 @@
         <v>19</v>
       </c>
       <c r="E70">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F70" t="s">
         <v>19</v>
@@ -7839,7 +7839,7 @@
         <v>19</v>
       </c>
       <c r="E85">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F85" t="s">
         <v>19</v>
@@ -8039,7 +8039,7 @@
         <v>19</v>
       </c>
       <c r="E89">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F89" t="s">
         <v>19</v>
@@ -10239,7 +10239,7 @@
         <v>19</v>
       </c>
       <c r="E133">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F133" t="s">
         <v>19</v>
@@ -10389,7 +10389,7 @@
         <v>19</v>
       </c>
       <c r="E136">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F136" t="s">
         <v>19</v>
@@ -10989,7 +10989,7 @@
         <v>19</v>
       </c>
       <c r="E148">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F148" t="s">
         <v>19</v>
@@ -12239,7 +12239,7 @@
         <v>19</v>
       </c>
       <c r="E173">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F173" t="s">
         <v>19</v>
@@ -12439,7 +12439,7 @@
         <v>19</v>
       </c>
       <c r="E177">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F177" t="s">
         <v>19</v>
@@ -12789,7 +12789,7 @@
         <v>19</v>
       </c>
       <c r="E184">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F184" t="s">
         <v>19</v>

--- a/tools/importer/reports/import-grace-master.report.xlsx
+++ b/tools/importer/reports/import-grace-master.report.xlsx
@@ -919,13 +919,13 @@
     <t>insights/chromatography-separation-specifics.report.json</t>
   </si>
   <si>
-    <t>["cards-product","social-follow","cards-featured-content"]</t>
+    <t>["social-follow","cards-featured-content"]</t>
   </si>
   <si>
     <t>insights/chromatography-separation-specifics</t>
   </si>
   <si>
-    <t>2026-08-07T19:21:58.300Z</t>
+    <t>2026-08-08T20:56:00.028Z</t>
   </si>
   <si>
     <t>Chromatography Separation Specifics</t>
@@ -985,7 +985,7 @@
     <t>insights/colloidal-silica-and-corrosion-resistance-stabilizing-a-safer</t>
   </si>
   <si>
-    <t>2026-08-07T19:16:26.859Z</t>
+    <t>2026-08-08T20:56:55.456Z</t>
   </si>
   <si>
     <t>Colloidal Silica and Corrosion Resistance – Stabilizing a Safer Alternative</t>
@@ -1000,7 +1000,7 @@
     <t>insights/colloidal-silica-as-a-foundation-for-3-d-printed-replacement-tissues</t>
   </si>
   <si>
-    <t>2026-08-07T19:20:56.195Z</t>
+    <t>2026-08-08T20:57:50.008Z</t>
   </si>
   <si>
     <t>Colloidal Silica as a Foundation for 3-D Printed Replacement Tissues</t>
@@ -1015,7 +1015,7 @@
     <t>insights/colloidal-silica-coatings-in-food-contact-applications</t>
   </si>
   <si>
-    <t>2026-08-07T19:15:33.706Z</t>
+    <t>2026-08-08T20:58:43.706Z</t>
   </si>
   <si>
     <t>Colloidal Silica Coatings in Food-Contact Applications</t>
@@ -1030,7 +1030,7 @@
     <t>insights/colloidal-silica-small-particles-enormous-potential</t>
   </si>
   <si>
-    <t>2026-08-07T19:18:14.034Z</t>
+    <t>2026-08-08T20:59:37.351Z</t>
   </si>
   <si>
     <t>Colloidal Silica: Small Particles, Enormous Potential</t>
@@ -1045,7 +1045,7 @@
     <t>insights/colloidal-silica-takes-on-extreme-environments</t>
   </si>
   <si>
-    <t>2026-08-07T19:21:49.227Z</t>
+    <t>2026-08-08T20:56:00.208Z</t>
   </si>
   <si>
     <t>Colloidal Silica Takes on Extreme Environments</t>
@@ -1060,7 +1060,7 @@
     <t>insights/colloidal-silica-water-sample-analysis</t>
   </si>
   <si>
-    <t>2026-08-07T19:17:21.071Z</t>
+    <t>2026-08-08T20:56:53.510Z</t>
   </si>
   <si>
     <t>Colloidal Silica Can Help Expedite Water Sample Analysis of Toxic Pesticides</t>
@@ -1258,7 +1258,7 @@
     <t>insights/enhancing-stability-and-bioavailability-of-poorly-soluble-apis</t>
   </si>
   <si>
-    <t>2026-08-07T19:11:58.105Z</t>
+    <t>2026-08-08T20:57:46.604Z</t>
   </si>
   <si>
     <t>Grace Webinar - Enhancing Stability and Bioavailability of Poorly Soluble APIs</t>
@@ -1408,7 +1408,7 @@
     <t>insights/grace-awarded-2022-top-supplier-akzonobel</t>
   </si>
   <si>
-    <t>2026-08-07T19:20:05.450Z</t>
+    <t>2026-08-08T20:58:39.344Z</t>
   </si>
   <si>
     <t>Grace Awarded 2022 Top Supplier Designation by AkzoNobel South America</t>
@@ -1438,7 +1438,7 @@
     <t>insights/grace-east-chicago-indiana-lab-investment</t>
   </si>
   <si>
-    <t>2026-08-07T19:11:04.069Z</t>
+    <t>2026-08-08T20:59:33.427Z</t>
   </si>
   <si>
     <t>Grace East Chicago, Indiana Lab Investment</t>
@@ -1558,7 +1558,7 @@
     <t>insights/grace-silica-goes-into-promegas-purification-kits</t>
   </si>
   <si>
-    <t>2026-08-07T19:14:41.705Z</t>
+    <t>2026-08-08T20:56:01.196Z</t>
   </si>
   <si>
     <t>Grace Silica Goes into Promega’s Purification Kits to Enable COVID-19 PCR Testing</t>
@@ -1873,7 +1873,7 @@
     <t>insights/ludox-colloidal-silica-plays-critical-role-customized-catalysts</t>
   </si>
   <si>
-    <t>2026-08-07T19:19:18.238Z</t>
+    <t>2026-08-08T20:56:54.934Z</t>
   </si>
   <si>
     <t>LUDOX® Colloidal Silica Plays Critical Role in Customized Catalysts</t>
@@ -2008,7 +2008,7 @@
     <t>insights/pharmas-almanac-cites-grace-experts-in-q3-2021-round-table</t>
   </si>
   <si>
-    <t>2026-08-07T19:22:43.659Z</t>
+    <t>2026-08-08T20:57:47.762Z</t>
   </si>
   <si>
     <t>Pharma’s Almanac Cites Grace Experts in Q3 2021 Round Table</t>
@@ -2023,7 +2023,7 @@
     <t>insights/powerful-technology-through-tiny-particles</t>
   </si>
   <si>
-    <t>2026-08-07T19:28:00.617Z</t>
+    <t>2026-08-08T20:58:41.640Z</t>
   </si>
   <si>
     <t>Powerful Technology Through Tiny Particles</t>
@@ -2173,7 +2173,7 @@
     <t>insights/shieldex-silica-for-land-sea-air</t>
   </si>
   <si>
-    <t>2026-08-07T19:27:06.992Z</t>
+    <t>2026-08-08T20:59:35.623Z</t>
   </si>
   <si>
     <t>Environmentally Friendly Corrosion Protection for Land, Sea, and Air</t>
@@ -2356,7 +2356,7 @@
     <t>insights/syloid-mx110-silica-a-matting-additive-with-superior-efficiency</t>
   </si>
   <si>
-    <t>2026-08-07T19:15:36.413Z</t>
+    <t>2026-08-08T21:07:42.450Z</t>
   </si>
   <si>
     <t>SYLOID® MX 110 Silica - a Matting Additive with Superior Efficiency</t>
@@ -2446,7 +2446,7 @@
     <t>insights/the-case-for-colloidal-silica</t>
   </si>
   <si>
-    <t>2026-08-07T19:19:07.370Z</t>
+    <t>2026-08-08T20:56:00.734Z</t>
   </si>
   <si>
     <t>The Case for Colloidal Silica</t>
@@ -2821,7 +2821,7 @@
     <t>insights/vitafoods-europe-2022</t>
   </si>
   <si>
-    <t>2026-08-07T19:20:58.665Z</t>
+    <t>2026-08-08T20:56:57.242Z</t>
   </si>
   <si>
     <t>Vitafoods Europe 2022</t>

--- a/tools/importer/reports/import-grace-master.report.xlsx
+++ b/tools/importer/reports/import-grace-master.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2370" uniqueCount="1057">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2370" uniqueCount="1058">
   <si>
     <t>_reportFile</t>
   </si>
@@ -925,7 +925,7 @@
     <t>insights/chromatography-separation-specifics</t>
   </si>
   <si>
-    <t>2026-08-08T20:56:00.028Z</t>
+    <t>2026-08-09T03:41:55.932Z</t>
   </si>
   <si>
     <t>Chromatography Separation Specifics</t>
@@ -982,10 +982,13 @@
     <t>insights/colloidal-silica-and-corrosion-resistance-stabilizing-a-safer.report.json</t>
   </si>
   <si>
+    <t>["cards-featured-content","social-follow"]</t>
+  </si>
+  <si>
     <t>insights/colloidal-silica-and-corrosion-resistance-stabilizing-a-safer</t>
   </si>
   <si>
-    <t>2026-08-08T20:56:55.456Z</t>
+    <t>2026-08-09T04:43:01.757Z</t>
   </si>
   <si>
     <t>Colloidal Silica and Corrosion Resistance – Stabilizing a Safer Alternative</t>
@@ -1000,7 +1003,7 @@
     <t>insights/colloidal-silica-as-a-foundation-for-3-d-printed-replacement-tissues</t>
   </si>
   <si>
-    <t>2026-08-08T20:57:50.008Z</t>
+    <t>2026-08-09T03:43:45.579Z</t>
   </si>
   <si>
     <t>Colloidal Silica as a Foundation for 3-D Printed Replacement Tissues</t>
@@ -1015,7 +1018,7 @@
     <t>insights/colloidal-silica-coatings-in-food-contact-applications</t>
   </si>
   <si>
-    <t>2026-08-08T20:58:43.706Z</t>
+    <t>2026-08-09T03:44:37.733Z</t>
   </si>
   <si>
     <t>Colloidal Silica Coatings in Food-Contact Applications</t>
@@ -1030,7 +1033,7 @@
     <t>insights/colloidal-silica-small-particles-enormous-potential</t>
   </si>
   <si>
-    <t>2026-08-08T20:59:37.351Z</t>
+    <t>2026-08-09T03:45:30.733Z</t>
   </si>
   <si>
     <t>Colloidal Silica: Small Particles, Enormous Potential</t>
@@ -1045,7 +1048,7 @@
     <t>insights/colloidal-silica-takes-on-extreme-environments</t>
   </si>
   <si>
-    <t>2026-08-08T20:56:00.208Z</t>
+    <t>2026-08-09T03:41:56.476Z</t>
   </si>
   <si>
     <t>Colloidal Silica Takes on Extreme Environments</t>
@@ -1060,7 +1063,7 @@
     <t>insights/colloidal-silica-water-sample-analysis</t>
   </si>
   <si>
-    <t>2026-08-08T20:56:53.510Z</t>
+    <t>2026-08-09T03:42:50.231Z</t>
   </si>
   <si>
     <t>Colloidal Silica Can Help Expedite Water Sample Analysis of Toxic Pesticides</t>
@@ -1258,7 +1261,7 @@
     <t>insights/enhancing-stability-and-bioavailability-of-poorly-soluble-apis</t>
   </si>
   <si>
-    <t>2026-08-08T20:57:46.604Z</t>
+    <t>2026-08-09T03:43:42.927Z</t>
   </si>
   <si>
     <t>Grace Webinar - Enhancing Stability and Bioavailability of Poorly Soluble APIs</t>
@@ -1408,7 +1411,7 @@
     <t>insights/grace-awarded-2022-top-supplier-akzonobel</t>
   </si>
   <si>
-    <t>2026-08-08T20:58:39.344Z</t>
+    <t>2026-08-09T03:44:36.039Z</t>
   </si>
   <si>
     <t>Grace Awarded 2022 Top Supplier Designation by AkzoNobel South America</t>
@@ -1438,7 +1441,7 @@
     <t>insights/grace-east-chicago-indiana-lab-investment</t>
   </si>
   <si>
-    <t>2026-08-08T20:59:33.427Z</t>
+    <t>2026-08-09T03:45:30.058Z</t>
   </si>
   <si>
     <t>Grace East Chicago, Indiana Lab Investment</t>
@@ -1558,7 +1561,7 @@
     <t>insights/grace-silica-goes-into-promegas-purification-kits</t>
   </si>
   <si>
-    <t>2026-08-08T20:56:01.196Z</t>
+    <t>2026-08-09T03:41:55.206Z</t>
   </si>
   <si>
     <t>Grace Silica Goes into Promega’s Purification Kits to Enable COVID-19 PCR Testing</t>
@@ -1873,7 +1876,7 @@
     <t>insights/ludox-colloidal-silica-plays-critical-role-customized-catalysts</t>
   </si>
   <si>
-    <t>2026-08-08T20:56:54.934Z</t>
+    <t>2026-08-09T03:42:48.008Z</t>
   </si>
   <si>
     <t>LUDOX® Colloidal Silica Plays Critical Role in Customized Catalysts</t>
@@ -2008,7 +2011,7 @@
     <t>insights/pharmas-almanac-cites-grace-experts-in-q3-2021-round-table</t>
   </si>
   <si>
-    <t>2026-08-08T20:57:47.762Z</t>
+    <t>2026-08-09T03:43:40.779Z</t>
   </si>
   <si>
     <t>Pharma’s Almanac Cites Grace Experts in Q3 2021 Round Table</t>
@@ -2023,7 +2026,7 @@
     <t>insights/powerful-technology-through-tiny-particles</t>
   </si>
   <si>
-    <t>2026-08-08T20:58:41.640Z</t>
+    <t>2026-08-09T03:44:33.969Z</t>
   </si>
   <si>
     <t>Powerful Technology Through Tiny Particles</t>
@@ -2173,7 +2176,7 @@
     <t>insights/shieldex-silica-for-land-sea-air</t>
   </si>
   <si>
-    <t>2026-08-08T20:59:35.623Z</t>
+    <t>2026-08-09T03:45:28.027Z</t>
   </si>
   <si>
     <t>Environmentally Friendly Corrosion Protection for Land, Sea, and Air</t>
@@ -2446,7 +2449,7 @@
     <t>insights/the-case-for-colloidal-silica</t>
   </si>
   <si>
-    <t>2026-08-08T20:56:00.734Z</t>
+    <t>2026-08-09T03:41:56.482Z</t>
   </si>
   <si>
     <t>The Case for Colloidal Silica</t>
@@ -2821,7 +2824,7 @@
     <t>insights/vitafoods-europe-2022</t>
   </si>
   <si>
-    <t>2026-08-08T20:56:57.242Z</t>
+    <t>2026-08-09T03:50:31.667Z</t>
   </si>
   <si>
     <t>Vitafoods Europe 2022</t>
@@ -6097,7 +6100,7 @@
         <v>322</v>
       </c>
       <c r="B58" t="s">
-        <v>302</v>
+        <v>323</v>
       </c>
       <c r="C58" t="s">
         <v>16</v>
@@ -6118,7 +6121,7 @@
         <v>131</v>
       </c>
       <c r="I58" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J58" t="s">
         <v>17</v>
@@ -6127,18 +6130,18 @@
         <v>20</v>
       </c>
       <c r="L58" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M58" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N58" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B59" t="s">
         <v>302</v>
@@ -6162,7 +6165,7 @@
         <v>131</v>
       </c>
       <c r="I59" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J59" t="s">
         <v>17</v>
@@ -6171,18 +6174,18 @@
         <v>20</v>
       </c>
       <c r="L59" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M59" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N59" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B60" t="s">
         <v>302</v>
@@ -6206,7 +6209,7 @@
         <v>131</v>
       </c>
       <c r="I60" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="J60" t="s">
         <v>17</v>
@@ -6215,18 +6218,18 @@
         <v>20</v>
       </c>
       <c r="L60" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N60" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B61" t="s">
         <v>302</v>
@@ -6250,7 +6253,7 @@
         <v>131</v>
       </c>
       <c r="I61" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J61" t="s">
         <v>17</v>
@@ -6259,18 +6262,18 @@
         <v>20</v>
       </c>
       <c r="L61" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M61" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N61" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B62" t="s">
         <v>302</v>
@@ -6294,7 +6297,7 @@
         <v>131</v>
       </c>
       <c r="I62" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J62" t="s">
         <v>17</v>
@@ -6303,18 +6306,18 @@
         <v>20</v>
       </c>
       <c r="L62" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M62" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N62" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B63" t="s">
         <v>302</v>
@@ -6338,7 +6341,7 @@
         <v>131</v>
       </c>
       <c r="I63" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J63" t="s">
         <v>17</v>
@@ -6347,18 +6350,18 @@
         <v>20</v>
       </c>
       <c r="L63" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M63" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N63" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B64" t="s">
         <v>129</v>
@@ -6382,7 +6385,7 @@
         <v>131</v>
       </c>
       <c r="I64" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J64" t="s">
         <v>17</v>
@@ -6391,18 +6394,18 @@
         <v>20</v>
       </c>
       <c r="L64" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M64" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N64" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B65" t="s">
         <v>129</v>
@@ -6426,7 +6429,7 @@
         <v>131</v>
       </c>
       <c r="I65" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J65" t="s">
         <v>17</v>
@@ -6435,18 +6438,18 @@
         <v>20</v>
       </c>
       <c r="L65" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M65" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N65" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B66" t="s">
         <v>129</v>
@@ -6470,7 +6473,7 @@
         <v>131</v>
       </c>
       <c r="I66" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J66" t="s">
         <v>17</v>
@@ -6479,18 +6482,18 @@
         <v>20</v>
       </c>
       <c r="L66" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M66" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N66" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B67" t="s">
         <v>129</v>
@@ -6514,7 +6517,7 @@
         <v>131</v>
       </c>
       <c r="I67" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J67" t="s">
         <v>17</v>
@@ -6523,18 +6526,18 @@
         <v>20</v>
       </c>
       <c r="L67" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M67" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N67" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B68" t="s">
         <v>129</v>
@@ -6558,7 +6561,7 @@
         <v>131</v>
       </c>
       <c r="I68" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J68" t="s">
         <v>17</v>
@@ -6567,21 +6570,21 @@
         <v>20</v>
       </c>
       <c r="L68" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M68" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N68" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B69" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C69" t="s">
         <v>16</v>
@@ -6602,7 +6605,7 @@
         <v>131</v>
       </c>
       <c r="I69" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J69" t="s">
         <v>17</v>
@@ -6611,18 +6614,18 @@
         <v>20</v>
       </c>
       <c r="L69" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M69" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N69" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B70" t="s">
         <v>129</v>
@@ -6646,7 +6649,7 @@
         <v>131</v>
       </c>
       <c r="I70" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J70" t="s">
         <v>17</v>
@@ -6655,18 +6658,18 @@
         <v>20</v>
       </c>
       <c r="L70" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M70" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N70" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B71" t="s">
         <v>129</v>
@@ -6690,7 +6693,7 @@
         <v>131</v>
       </c>
       <c r="I71" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J71" t="s">
         <v>17</v>
@@ -6699,18 +6702,18 @@
         <v>20</v>
       </c>
       <c r="L71" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M71" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N71" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B72" t="s">
         <v>129</v>
@@ -6734,7 +6737,7 @@
         <v>131</v>
       </c>
       <c r="I72" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J72" t="s">
         <v>17</v>
@@ -6743,18 +6746,18 @@
         <v>20</v>
       </c>
       <c r="L72" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M72" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N72" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B73" t="s">
         <v>129</v>
@@ -6778,7 +6781,7 @@
         <v>131</v>
       </c>
       <c r="I73" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J73" t="s">
         <v>17</v>
@@ -6787,18 +6790,18 @@
         <v>20</v>
       </c>
       <c r="L73" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M73" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N73" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B74" t="s">
         <v>129</v>
@@ -6822,7 +6825,7 @@
         <v>131</v>
       </c>
       <c r="I74" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J74" t="s">
         <v>17</v>
@@ -6831,18 +6834,18 @@
         <v>20</v>
       </c>
       <c r="L74" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M74" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N74" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B75" t="s">
         <v>129</v>
@@ -6866,7 +6869,7 @@
         <v>131</v>
       </c>
       <c r="I75" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J75" t="s">
         <v>17</v>
@@ -6875,18 +6878,18 @@
         <v>20</v>
       </c>
       <c r="L75" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M75" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N75" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B76" t="s">
         <v>302</v>
@@ -6910,7 +6913,7 @@
         <v>131</v>
       </c>
       <c r="I76" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="J76" t="s">
         <v>17</v>
@@ -6919,18 +6922,18 @@
         <v>20</v>
       </c>
       <c r="L76" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M76" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N76" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B77" t="s">
         <v>129</v>
@@ -6954,7 +6957,7 @@
         <v>131</v>
       </c>
       <c r="I77" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J77" t="s">
         <v>17</v>
@@ -6963,18 +6966,18 @@
         <v>20</v>
       </c>
       <c r="L77" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M77" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N77" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B78" t="s">
         <v>129</v>
@@ -6998,7 +7001,7 @@
         <v>131</v>
       </c>
       <c r="I78" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J78" t="s">
         <v>17</v>
@@ -7007,18 +7010,18 @@
         <v>20</v>
       </c>
       <c r="L78" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M78" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N78" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B79" t="s">
         <v>129</v>
@@ -7042,7 +7045,7 @@
         <v>131</v>
       </c>
       <c r="I79" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J79" t="s">
         <v>17</v>
@@ -7051,18 +7054,18 @@
         <v>20</v>
       </c>
       <c r="L79" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M79" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N79" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B80" t="s">
         <v>129</v>
@@ -7086,7 +7089,7 @@
         <v>131</v>
       </c>
       <c r="I80" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J80" t="s">
         <v>17</v>
@@ -7095,18 +7098,18 @@
         <v>20</v>
       </c>
       <c r="L80" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M80" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N80" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B81" t="s">
         <v>129</v>
@@ -7130,7 +7133,7 @@
         <v>131</v>
       </c>
       <c r="I81" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J81" t="s">
         <v>17</v>
@@ -7139,18 +7142,18 @@
         <v>20</v>
       </c>
       <c r="L81" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M81" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N81" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B82" t="s">
         <v>129</v>
@@ -7174,7 +7177,7 @@
         <v>131</v>
       </c>
       <c r="I82" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J82" t="s">
         <v>17</v>
@@ -7183,18 +7186,18 @@
         <v>20</v>
       </c>
       <c r="L82" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M82" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N82" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B83" t="s">
         <v>129</v>
@@ -7218,7 +7221,7 @@
         <v>131</v>
       </c>
       <c r="I83" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J83" t="s">
         <v>17</v>
@@ -7227,18 +7230,18 @@
         <v>20</v>
       </c>
       <c r="L83" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M83" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N83" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B84" t="s">
         <v>129</v>
@@ -7262,7 +7265,7 @@
         <v>131</v>
       </c>
       <c r="I84" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="J84" t="s">
         <v>17</v>
@@ -7271,18 +7274,18 @@
         <v>20</v>
       </c>
       <c r="L84" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M84" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N84" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B85" t="s">
         <v>129</v>
@@ -7306,7 +7309,7 @@
         <v>131</v>
       </c>
       <c r="I85" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J85" t="s">
         <v>17</v>
@@ -7315,18 +7318,18 @@
         <v>20</v>
       </c>
       <c r="L85" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M85" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N85" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B86" t="s">
         <v>302</v>
@@ -7350,7 +7353,7 @@
         <v>131</v>
       </c>
       <c r="I86" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="J86" t="s">
         <v>17</v>
@@ -7359,18 +7362,18 @@
         <v>20</v>
       </c>
       <c r="L86" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M86" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N86" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B87" t="s">
         <v>129</v>
@@ -7394,7 +7397,7 @@
         <v>131</v>
       </c>
       <c r="I87" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="J87" t="s">
         <v>17</v>
@@ -7403,18 +7406,18 @@
         <v>20</v>
       </c>
       <c r="L87" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M87" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N87" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B88" t="s">
         <v>302</v>
@@ -7438,7 +7441,7 @@
         <v>131</v>
       </c>
       <c r="I88" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="J88" t="s">
         <v>17</v>
@@ -7447,18 +7450,18 @@
         <v>20</v>
       </c>
       <c r="L88" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M88" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N88" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B89" t="s">
         <v>129</v>
@@ -7482,7 +7485,7 @@
         <v>131</v>
       </c>
       <c r="I89" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="J89" t="s">
         <v>17</v>
@@ -7491,18 +7494,18 @@
         <v>20</v>
       </c>
       <c r="L89" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M89" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N89" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B90" t="s">
         <v>129</v>
@@ -7526,7 +7529,7 @@
         <v>131</v>
       </c>
       <c r="I90" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J90" t="s">
         <v>17</v>
@@ -7535,18 +7538,18 @@
         <v>20</v>
       </c>
       <c r="L90" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M90" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N90" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B91" t="s">
         <v>129</v>
@@ -7570,7 +7573,7 @@
         <v>131</v>
       </c>
       <c r="I91" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="J91" t="s">
         <v>17</v>
@@ -7579,18 +7582,18 @@
         <v>20</v>
       </c>
       <c r="L91" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M91" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N91" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B92" t="s">
         <v>129</v>
@@ -7614,7 +7617,7 @@
         <v>131</v>
       </c>
       <c r="I92" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="J92" t="s">
         <v>17</v>
@@ -7623,18 +7626,18 @@
         <v>20</v>
       </c>
       <c r="L92" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M92" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N92" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B93" t="s">
         <v>129</v>
@@ -7658,7 +7661,7 @@
         <v>131</v>
       </c>
       <c r="I93" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J93" t="s">
         <v>17</v>
@@ -7667,18 +7670,18 @@
         <v>20</v>
       </c>
       <c r="L93" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M93" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N93" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B94" t="s">
         <v>129</v>
@@ -7702,7 +7705,7 @@
         <v>131</v>
       </c>
       <c r="I94" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="J94" t="s">
         <v>17</v>
@@ -7711,18 +7714,18 @@
         <v>20</v>
       </c>
       <c r="L94" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M94" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N94" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B95" t="s">
         <v>129</v>
@@ -7746,7 +7749,7 @@
         <v>131</v>
       </c>
       <c r="I95" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="J95" t="s">
         <v>17</v>
@@ -7755,18 +7758,18 @@
         <v>20</v>
       </c>
       <c r="L95" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M95" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N95" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B96" t="s">
         <v>302</v>
@@ -7790,7 +7793,7 @@
         <v>131</v>
       </c>
       <c r="I96" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="J96" t="s">
         <v>17</v>
@@ -7799,18 +7802,18 @@
         <v>20</v>
       </c>
       <c r="L96" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M96" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N96" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B97" t="s">
         <v>129</v>
@@ -7834,7 +7837,7 @@
         <v>131</v>
       </c>
       <c r="I97" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="J97" t="s">
         <v>17</v>
@@ -7843,18 +7846,18 @@
         <v>20</v>
       </c>
       <c r="L97" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M97" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N97" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B98" t="s">
         <v>129</v>
@@ -7878,7 +7881,7 @@
         <v>131</v>
       </c>
       <c r="I98" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="J98" t="s">
         <v>17</v>
@@ -7887,18 +7890,18 @@
         <v>20</v>
       </c>
       <c r="L98" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M98" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N98" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B99" t="s">
         <v>129</v>
@@ -7922,7 +7925,7 @@
         <v>131</v>
       </c>
       <c r="I99" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="J99" t="s">
         <v>17</v>
@@ -7931,18 +7934,18 @@
         <v>20</v>
       </c>
       <c r="L99" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M99" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N99" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B100" t="s">
         <v>129</v>
@@ -7966,7 +7969,7 @@
         <v>131</v>
       </c>
       <c r="I100" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="J100" t="s">
         <v>17</v>
@@ -7975,18 +7978,18 @@
         <v>20</v>
       </c>
       <c r="L100" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M100" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N100" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B101" t="s">
         <v>129</v>
@@ -8010,7 +8013,7 @@
         <v>131</v>
       </c>
       <c r="I101" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="J101" t="s">
         <v>17</v>
@@ -8019,18 +8022,18 @@
         <v>20</v>
       </c>
       <c r="L101" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M101" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N101" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B102" t="s">
         <v>129</v>
@@ -8054,7 +8057,7 @@
         <v>131</v>
       </c>
       <c r="I102" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J102" t="s">
         <v>17</v>
@@ -8063,18 +8066,18 @@
         <v>20</v>
       </c>
       <c r="L102" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M102" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N102" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B103" t="s">
         <v>129</v>
@@ -8098,7 +8101,7 @@
         <v>131</v>
       </c>
       <c r="I103" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="J103" t="s">
         <v>17</v>
@@ -8107,18 +8110,18 @@
         <v>20</v>
       </c>
       <c r="L103" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M103" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N103" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B104" t="s">
         <v>129</v>
@@ -8142,7 +8145,7 @@
         <v>131</v>
       </c>
       <c r="I104" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="J104" t="s">
         <v>17</v>
@@ -8151,18 +8154,18 @@
         <v>20</v>
       </c>
       <c r="L104" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M104" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N104" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B105" t="s">
         <v>129</v>
@@ -8186,7 +8189,7 @@
         <v>131</v>
       </c>
       <c r="I105" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="J105" t="s">
         <v>17</v>
@@ -8195,18 +8198,18 @@
         <v>20</v>
       </c>
       <c r="L105" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M105" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N105" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B106" t="s">
         <v>129</v>
@@ -8230,7 +8233,7 @@
         <v>131</v>
       </c>
       <c r="I106" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="J106" t="s">
         <v>17</v>
@@ -8239,18 +8242,18 @@
         <v>20</v>
       </c>
       <c r="L106" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M106" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N106" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B107" t="s">
         <v>129</v>
@@ -8274,7 +8277,7 @@
         <v>131</v>
       </c>
       <c r="I107" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="J107" t="s">
         <v>17</v>
@@ -8283,18 +8286,18 @@
         <v>20</v>
       </c>
       <c r="L107" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M107" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N107" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B108" t="s">
         <v>129</v>
@@ -8318,7 +8321,7 @@
         <v>131</v>
       </c>
       <c r="I108" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="J108" t="s">
         <v>17</v>
@@ -8327,21 +8330,21 @@
         <v>20</v>
       </c>
       <c r="L108" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M108" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N108" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B109" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C109" t="s">
         <v>16</v>
@@ -8362,7 +8365,7 @@
         <v>131</v>
       </c>
       <c r="I109" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="J109" t="s">
         <v>17</v>
@@ -8371,18 +8374,18 @@
         <v>20</v>
       </c>
       <c r="L109" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M109" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N109" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B110" t="s">
         <v>129</v>
@@ -8406,7 +8409,7 @@
         <v>131</v>
       </c>
       <c r="I110" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="J110" t="s">
         <v>17</v>
@@ -8415,18 +8418,18 @@
         <v>20</v>
       </c>
       <c r="L110" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M110" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N110" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B111" t="s">
         <v>129</v>
@@ -8450,7 +8453,7 @@
         <v>131</v>
       </c>
       <c r="I111" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="J111" t="s">
         <v>17</v>
@@ -8459,18 +8462,18 @@
         <v>20</v>
       </c>
       <c r="L111" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M111" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N111" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B112" t="s">
         <v>129</v>
@@ -8494,7 +8497,7 @@
         <v>131</v>
       </c>
       <c r="I112" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="J112" t="s">
         <v>17</v>
@@ -8503,18 +8506,18 @@
         <v>20</v>
       </c>
       <c r="L112" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M112" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N112" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B113" t="s">
         <v>129</v>
@@ -8538,7 +8541,7 @@
         <v>131</v>
       </c>
       <c r="I113" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="J113" t="s">
         <v>17</v>
@@ -8547,18 +8550,18 @@
         <v>20</v>
       </c>
       <c r="L113" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M113" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N113" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B114" t="s">
         <v>129</v>
@@ -8582,7 +8585,7 @@
         <v>131</v>
       </c>
       <c r="I114" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="J114" t="s">
         <v>17</v>
@@ -8591,18 +8594,18 @@
         <v>20</v>
       </c>
       <c r="L114" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M114" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N114" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B115" t="s">
         <v>129</v>
@@ -8626,7 +8629,7 @@
         <v>131</v>
       </c>
       <c r="I115" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="J115" t="s">
         <v>17</v>
@@ -8635,18 +8638,18 @@
         <v>20</v>
       </c>
       <c r="L115" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M115" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N115" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B116" t="s">
         <v>129</v>
@@ -8670,7 +8673,7 @@
         <v>131</v>
       </c>
       <c r="I116" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="J116" t="s">
         <v>17</v>
@@ -8679,18 +8682,18 @@
         <v>20</v>
       </c>
       <c r="L116" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="M116" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="N116" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B117" t="s">
         <v>302</v>
@@ -8714,7 +8717,7 @@
         <v>131</v>
       </c>
       <c r="I117" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="J117" t="s">
         <v>17</v>
@@ -8723,18 +8726,18 @@
         <v>20</v>
       </c>
       <c r="L117" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M117" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N117" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B118" t="s">
         <v>129</v>
@@ -8758,7 +8761,7 @@
         <v>131</v>
       </c>
       <c r="I118" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="J118" t="s">
         <v>17</v>
@@ -8767,18 +8770,18 @@
         <v>20</v>
       </c>
       <c r="L118" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="M118" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="N118" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B119" t="s">
         <v>129</v>
@@ -8802,7 +8805,7 @@
         <v>131</v>
       </c>
       <c r="I119" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="J119" t="s">
         <v>17</v>
@@ -8811,18 +8814,18 @@
         <v>20</v>
       </c>
       <c r="L119" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M119" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N119" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B120" t="s">
         <v>129</v>
@@ -8846,7 +8849,7 @@
         <v>131</v>
       </c>
       <c r="I120" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="J120" t="s">
         <v>17</v>
@@ -8855,18 +8858,18 @@
         <v>20</v>
       </c>
       <c r="L120" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M120" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="N120" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B121" t="s">
         <v>129</v>
@@ -8890,7 +8893,7 @@
         <v>131</v>
       </c>
       <c r="I121" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="J121" t="s">
         <v>17</v>
@@ -8899,18 +8902,18 @@
         <v>20</v>
       </c>
       <c r="L121" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="M121" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="N121" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B122" t="s">
         <v>129</v>
@@ -8934,7 +8937,7 @@
         <v>131</v>
       </c>
       <c r="I122" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="J122" t="s">
         <v>17</v>
@@ -8943,18 +8946,18 @@
         <v>20</v>
       </c>
       <c r="L122" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="M122" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="N122" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B123" t="s">
         <v>129</v>
@@ -8978,7 +8981,7 @@
         <v>131</v>
       </c>
       <c r="I123" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="J123" t="s">
         <v>17</v>
@@ -8987,18 +8990,18 @@
         <v>20</v>
       </c>
       <c r="L123" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="M123" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="N123" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B124" t="s">
         <v>129</v>
@@ -9022,7 +9025,7 @@
         <v>131</v>
       </c>
       <c r="I124" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="J124" t="s">
         <v>17</v>
@@ -9031,18 +9034,18 @@
         <v>20</v>
       </c>
       <c r="L124" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M124" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N124" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B125" t="s">
         <v>129</v>
@@ -9066,7 +9069,7 @@
         <v>131</v>
       </c>
       <c r="I125" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="J125" t="s">
         <v>17</v>
@@ -9075,18 +9078,18 @@
         <v>20</v>
       </c>
       <c r="L125" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="M125" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="N125" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B126" t="s">
         <v>302</v>
@@ -9110,7 +9113,7 @@
         <v>131</v>
       </c>
       <c r="I126" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="J126" t="s">
         <v>17</v>
@@ -9119,18 +9122,18 @@
         <v>20</v>
       </c>
       <c r="L126" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M126" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N126" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B127" t="s">
         <v>302</v>
@@ -9154,7 +9157,7 @@
         <v>131</v>
       </c>
       <c r="I127" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="J127" t="s">
         <v>17</v>
@@ -9163,18 +9166,18 @@
         <v>20</v>
       </c>
       <c r="L127" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="M127" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N127" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B128" t="s">
         <v>129</v>
@@ -9198,7 +9201,7 @@
         <v>131</v>
       </c>
       <c r="I128" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="J128" t="s">
         <v>17</v>
@@ -9207,18 +9210,18 @@
         <v>20</v>
       </c>
       <c r="L128" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="M128" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="N128" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B129" t="s">
         <v>129</v>
@@ -9242,7 +9245,7 @@
         <v>131</v>
       </c>
       <c r="I129" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="J129" t="s">
         <v>17</v>
@@ -9251,18 +9254,18 @@
         <v>20</v>
       </c>
       <c r="L129" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M129" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N129" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B130" t="s">
         <v>129</v>
@@ -9286,7 +9289,7 @@
         <v>131</v>
       </c>
       <c r="I130" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="J130" t="s">
         <v>17</v>
@@ -9295,18 +9298,18 @@
         <v>20</v>
       </c>
       <c r="L130" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="M130" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="N130" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B131" t="s">
         <v>129</v>
@@ -9330,7 +9333,7 @@
         <v>131</v>
       </c>
       <c r="I131" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="J131" t="s">
         <v>17</v>
@@ -9339,18 +9342,18 @@
         <v>20</v>
       </c>
       <c r="L131" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="M131" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="N131" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B132" t="s">
         <v>129</v>
@@ -9374,7 +9377,7 @@
         <v>131</v>
       </c>
       <c r="I132" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="J132" t="s">
         <v>17</v>
@@ -9383,18 +9386,18 @@
         <v>20</v>
       </c>
       <c r="L132" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="M132" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="N132" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B133" t="s">
         <v>129</v>
@@ -9418,7 +9421,7 @@
         <v>131</v>
       </c>
       <c r="I133" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="J133" t="s">
         <v>17</v>
@@ -9427,18 +9430,18 @@
         <v>20</v>
       </c>
       <c r="L133" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="M133" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N133" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B134" t="s">
         <v>129</v>
@@ -9462,7 +9465,7 @@
         <v>131</v>
       </c>
       <c r="I134" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="J134" t="s">
         <v>17</v>
@@ -9471,18 +9474,18 @@
         <v>20</v>
       </c>
       <c r="L134" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="M134" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="N134" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B135" t="s">
         <v>129</v>
@@ -9506,7 +9509,7 @@
         <v>131</v>
       </c>
       <c r="I135" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="J135" t="s">
         <v>17</v>
@@ -9515,18 +9518,18 @@
         <v>20</v>
       </c>
       <c r="L135" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="M135" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="N135" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B136" t="s">
         <v>129</v>
@@ -9550,7 +9553,7 @@
         <v>131</v>
       </c>
       <c r="I136" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="J136" t="s">
         <v>17</v>
@@ -9559,18 +9562,18 @@
         <v>20</v>
       </c>
       <c r="L136" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="M136" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="N136" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B137" t="s">
         <v>302</v>
@@ -9594,7 +9597,7 @@
         <v>131</v>
       </c>
       <c r="I137" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="J137" t="s">
         <v>17</v>
@@ -9603,18 +9606,18 @@
         <v>20</v>
       </c>
       <c r="L137" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M137" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="N137" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B138" t="s">
         <v>129</v>
@@ -9638,7 +9641,7 @@
         <v>131</v>
       </c>
       <c r="I138" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="J138" t="s">
         <v>17</v>
@@ -9647,18 +9650,18 @@
         <v>20</v>
       </c>
       <c r="L138" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="M138" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="N138" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B139" t="s">
         <v>129</v>
@@ -9682,7 +9685,7 @@
         <v>131</v>
       </c>
       <c r="I139" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="J139" t="s">
         <v>17</v>
@@ -9691,18 +9694,18 @@
         <v>20</v>
       </c>
       <c r="L139" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="M139" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N139" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B140" t="s">
         <v>16</v>
@@ -9726,7 +9729,7 @@
         <v>131</v>
       </c>
       <c r="I140" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="J140" t="s">
         <v>17</v>
@@ -9735,18 +9738,18 @@
         <v>20</v>
       </c>
       <c r="L140" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M140" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N140" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B141" t="s">
         <v>129</v>
@@ -9770,7 +9773,7 @@
         <v>131</v>
       </c>
       <c r="I141" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="J141" t="s">
         <v>17</v>
@@ -9779,18 +9782,18 @@
         <v>20</v>
       </c>
       <c r="L141" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="M141" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="N141" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B142" t="s">
         <v>129</v>
@@ -9814,7 +9817,7 @@
         <v>131</v>
       </c>
       <c r="I142" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="J142" t="s">
         <v>17</v>
@@ -9823,18 +9826,18 @@
         <v>20</v>
       </c>
       <c r="L142" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="M142" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="N142" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B143" t="s">
         <v>129</v>
@@ -9858,7 +9861,7 @@
         <v>131</v>
       </c>
       <c r="I143" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="J143" t="s">
         <v>17</v>
@@ -9867,18 +9870,18 @@
         <v>20</v>
       </c>
       <c r="L143" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="M143" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="N143" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B144" t="s">
         <v>129</v>
@@ -9902,7 +9905,7 @@
         <v>131</v>
       </c>
       <c r="I144" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="J144" t="s">
         <v>17</v>
@@ -9911,18 +9914,18 @@
         <v>20</v>
       </c>
       <c r="L144" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="M144" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="N144" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B145" t="s">
         <v>129</v>
@@ -9946,7 +9949,7 @@
         <v>131</v>
       </c>
       <c r="I145" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="J145" t="s">
         <v>17</v>
@@ -9955,18 +9958,18 @@
         <v>20</v>
       </c>
       <c r="L145" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="M145" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="N145" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B146" t="s">
         <v>129</v>
@@ -9990,7 +9993,7 @@
         <v>131</v>
       </c>
       <c r="I146" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="J146" t="s">
         <v>17</v>
@@ -9999,18 +10002,18 @@
         <v>20</v>
       </c>
       <c r="L146" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="M146" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="N146" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B147" t="s">
         <v>129</v>
@@ -10034,7 +10037,7 @@
         <v>131</v>
       </c>
       <c r="I147" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="J147" t="s">
         <v>17</v>
@@ -10043,18 +10046,18 @@
         <v>20</v>
       </c>
       <c r="L147" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="M147" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="N147" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B148" t="s">
         <v>129</v>
@@ -10078,7 +10081,7 @@
         <v>131</v>
       </c>
       <c r="I148" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="J148" t="s">
         <v>17</v>
@@ -10087,21 +10090,21 @@
         <v>20</v>
       </c>
       <c r="L148" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="M148" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="N148" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B149" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C149" t="s">
         <v>16</v>
@@ -10122,7 +10125,7 @@
         <v>131</v>
       </c>
       <c r="I149" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="J149" t="s">
         <v>17</v>
@@ -10131,18 +10134,18 @@
         <v>20</v>
       </c>
       <c r="L149" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="M149" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="N149" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B150" t="s">
         <v>129</v>
@@ -10166,7 +10169,7 @@
         <v>131</v>
       </c>
       <c r="I150" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="J150" t="s">
         <v>17</v>
@@ -10175,18 +10178,18 @@
         <v>20</v>
       </c>
       <c r="L150" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="M150" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="N150" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B151" t="s">
         <v>129</v>
@@ -10210,7 +10213,7 @@
         <v>131</v>
       </c>
       <c r="I151" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="J151" t="s">
         <v>17</v>
@@ -10219,18 +10222,18 @@
         <v>20</v>
       </c>
       <c r="L151" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="M151" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="N151" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B152" t="s">
         <v>129</v>
@@ -10254,7 +10257,7 @@
         <v>131</v>
       </c>
       <c r="I152" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="J152" t="s">
         <v>17</v>
@@ -10263,18 +10266,18 @@
         <v>20</v>
       </c>
       <c r="L152" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="M152" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="N152" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B153" t="s">
         <v>129</v>
@@ -10298,7 +10301,7 @@
         <v>131</v>
       </c>
       <c r="I153" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="J153" t="s">
         <v>17</v>
@@ -10307,18 +10310,18 @@
         <v>20</v>
       </c>
       <c r="L153" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="M153" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="N153" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B154" t="s">
         <v>129</v>
@@ -10342,7 +10345,7 @@
         <v>131</v>
       </c>
       <c r="I154" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="J154" t="s">
         <v>17</v>
@@ -10351,18 +10354,18 @@
         <v>20</v>
       </c>
       <c r="L154" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="M154" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="N154" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B155" t="s">
         <v>302</v>
@@ -10386,7 +10389,7 @@
         <v>131</v>
       </c>
       <c r="I155" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="J155" t="s">
         <v>17</v>
@@ -10395,18 +10398,18 @@
         <v>20</v>
       </c>
       <c r="L155" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="M155" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="N155" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B156" t="s">
         <v>16</v>
@@ -10430,7 +10433,7 @@
         <v>40</v>
       </c>
       <c r="I156" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="J156" t="b">
         <v>0</v>
@@ -10439,18 +10442,18 @@
         <v>20</v>
       </c>
       <c r="L156" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="M156" t="s">
         <v>43</v>
       </c>
       <c r="N156" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B157" t="s">
         <v>129</v>
@@ -10474,7 +10477,7 @@
         <v>131</v>
       </c>
       <c r="I157" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="J157" t="s">
         <v>17</v>
@@ -10483,18 +10486,18 @@
         <v>20</v>
       </c>
       <c r="L157" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="M157" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="N157" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B158" t="s">
         <v>129</v>
@@ -10518,7 +10521,7 @@
         <v>131</v>
       </c>
       <c r="I158" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="J158" t="s">
         <v>17</v>
@@ -10527,18 +10530,18 @@
         <v>20</v>
       </c>
       <c r="L158" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="M158" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="N158" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B159" t="s">
         <v>129</v>
@@ -10562,7 +10565,7 @@
         <v>131</v>
       </c>
       <c r="I159" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="J159" t="s">
         <v>17</v>
@@ -10571,18 +10574,18 @@
         <v>20</v>
       </c>
       <c r="L159" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="M159" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="N159" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B160" t="s">
         <v>129</v>
@@ -10606,7 +10609,7 @@
         <v>131</v>
       </c>
       <c r="I160" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="J160" t="s">
         <v>17</v>
@@ -10615,18 +10618,18 @@
         <v>20</v>
       </c>
       <c r="L160" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="M160" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="N160" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B161" t="s">
         <v>129</v>
@@ -10650,7 +10653,7 @@
         <v>131</v>
       </c>
       <c r="I161" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="J161" t="s">
         <v>17</v>
@@ -10659,18 +10662,18 @@
         <v>20</v>
       </c>
       <c r="L161" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="M161" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="N161" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B162" t="s">
         <v>129</v>
@@ -10694,7 +10697,7 @@
         <v>131</v>
       </c>
       <c r="I162" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="J162" t="s">
         <v>17</v>
@@ -10703,18 +10706,18 @@
         <v>20</v>
       </c>
       <c r="L162" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="M162" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="N162" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B163" t="s">
         <v>129</v>
@@ -10738,7 +10741,7 @@
         <v>131</v>
       </c>
       <c r="I163" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="J163" t="s">
         <v>17</v>
@@ -10747,18 +10750,18 @@
         <v>20</v>
       </c>
       <c r="L163" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="M163" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="N163" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B164" t="s">
         <v>129</v>
@@ -10782,7 +10785,7 @@
         <v>131</v>
       </c>
       <c r="I164" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="J164" t="s">
         <v>17</v>
@@ -10791,18 +10794,18 @@
         <v>20</v>
       </c>
       <c r="L164" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="M164" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="N164" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B165" t="s">
         <v>129</v>
@@ -10826,7 +10829,7 @@
         <v>131</v>
       </c>
       <c r="I165" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="J165" t="s">
         <v>17</v>
@@ -10835,18 +10838,18 @@
         <v>20</v>
       </c>
       <c r="L165" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="M165" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="N165" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B166" t="s">
         <v>129</v>
@@ -10870,7 +10873,7 @@
         <v>131</v>
       </c>
       <c r="I166" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="J166" t="s">
         <v>17</v>
@@ -10879,18 +10882,18 @@
         <v>20</v>
       </c>
       <c r="L166" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="M166" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="N166" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B167" t="s">
         <v>129</v>
@@ -10914,7 +10917,7 @@
         <v>131</v>
       </c>
       <c r="I167" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="J167" t="s">
         <v>17</v>
@@ -10923,21 +10926,21 @@
         <v>20</v>
       </c>
       <c r="L167" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="M167" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="N167" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B168" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C168" t="s">
         <v>16</v>
@@ -10958,7 +10961,7 @@
         <v>131</v>
       </c>
       <c r="I168" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="J168" t="s">
         <v>17</v>
@@ -10967,18 +10970,18 @@
         <v>20</v>
       </c>
       <c r="L168" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="M168" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="N168" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B169" t="s">
         <v>129</v>
@@ -11002,7 +11005,7 @@
         <v>131</v>
       </c>
       <c r="I169" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="J169" t="s">
         <v>17</v>
@@ -11011,18 +11014,18 @@
         <v>20</v>
       </c>
       <c r="L169" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="M169" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="N169" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B170" t="s">
         <v>129</v>
@@ -11046,7 +11049,7 @@
         <v>131</v>
       </c>
       <c r="I170" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="J170" t="s">
         <v>17</v>
@@ -11055,18 +11058,18 @@
         <v>20</v>
       </c>
       <c r="L170" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="M170" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="N170" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B171" t="s">
         <v>129</v>
@@ -11090,7 +11093,7 @@
         <v>131</v>
       </c>
       <c r="I171" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="J171" t="s">
         <v>17</v>
@@ -11099,18 +11102,18 @@
         <v>20</v>
       </c>
       <c r="L171" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="M171" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="N171" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B172" t="s">
         <v>129</v>
@@ -11134,7 +11137,7 @@
         <v>131</v>
       </c>
       <c r="I172" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="J172" t="s">
         <v>17</v>
@@ -11143,18 +11146,18 @@
         <v>20</v>
       </c>
       <c r="L172" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="M172" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="N172" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B173" t="s">
         <v>129</v>
@@ -11178,7 +11181,7 @@
         <v>131</v>
       </c>
       <c r="I173" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="J173" t="s">
         <v>17</v>
@@ -11187,18 +11190,18 @@
         <v>20</v>
       </c>
       <c r="L173" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="M173" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="N173" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B174" t="s">
         <v>129</v>
@@ -11222,7 +11225,7 @@
         <v>131</v>
       </c>
       <c r="I174" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="J174" t="s">
         <v>17</v>
@@ -11231,18 +11234,18 @@
         <v>20</v>
       </c>
       <c r="L174" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="M174" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="N174" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B175" t="s">
         <v>129</v>
@@ -11266,7 +11269,7 @@
         <v>131</v>
       </c>
       <c r="I175" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="J175" t="s">
         <v>17</v>
@@ -11275,18 +11278,18 @@
         <v>20</v>
       </c>
       <c r="L175" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="M175" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="N175" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B176" t="s">
         <v>129</v>
@@ -11310,7 +11313,7 @@
         <v>131</v>
       </c>
       <c r="I176" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="J176" t="s">
         <v>17</v>
@@ -11319,18 +11322,18 @@
         <v>20</v>
       </c>
       <c r="L176" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="M176" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="N176" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B177" t="s">
         <v>129</v>
@@ -11354,7 +11357,7 @@
         <v>131</v>
       </c>
       <c r="I177" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="J177" t="s">
         <v>17</v>
@@ -11363,18 +11366,18 @@
         <v>20</v>
       </c>
       <c r="L177" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="M177" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="N177" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B178" t="s">
         <v>129</v>
@@ -11398,7 +11401,7 @@
         <v>131</v>
       </c>
       <c r="I178" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="J178" t="s">
         <v>17</v>
@@ -11407,18 +11410,18 @@
         <v>20</v>
       </c>
       <c r="L178" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="M178" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="N178" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B179" t="s">
         <v>129</v>
@@ -11442,7 +11445,7 @@
         <v>131</v>
       </c>
       <c r="I179" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="J179" t="s">
         <v>17</v>
@@ -11451,18 +11454,18 @@
         <v>20</v>
       </c>
       <c r="L179" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="M179" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="N179" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B180" t="s">
         <v>302</v>
@@ -11486,7 +11489,7 @@
         <v>131</v>
       </c>
       <c r="I180" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="J180" t="s">
         <v>17</v>
@@ -11495,18 +11498,18 @@
         <v>20</v>
       </c>
       <c r="L180" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="M180" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="N180" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B181" t="s">
         <v>129</v>
@@ -11530,7 +11533,7 @@
         <v>131</v>
       </c>
       <c r="I181" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="J181" t="s">
         <v>17</v>
@@ -11539,18 +11542,18 @@
         <v>20</v>
       </c>
       <c r="L181" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="M181" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="N181" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B182" t="s">
         <v>129</v>
@@ -11574,7 +11577,7 @@
         <v>131</v>
       </c>
       <c r="I182" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="J182" t="s">
         <v>17</v>
@@ -11583,18 +11586,18 @@
         <v>20</v>
       </c>
       <c r="L182" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="M182" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="N182" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B183" t="s">
         <v>129</v>
@@ -11618,7 +11621,7 @@
         <v>131</v>
       </c>
       <c r="I183" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="J183" t="s">
         <v>17</v>
@@ -11627,18 +11630,18 @@
         <v>20</v>
       </c>
       <c r="L183" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="M183" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="N183" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B184" t="s">
         <v>129</v>
@@ -11662,7 +11665,7 @@
         <v>131</v>
       </c>
       <c r="I184" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="J184" t="s">
         <v>17</v>
@@ -11671,21 +11674,21 @@
         <v>20</v>
       </c>
       <c r="L184" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="M184" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="N184" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B185" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C185" t="s">
         <v>16</v>
@@ -11706,7 +11709,7 @@
         <v>18</v>
       </c>
       <c r="I185" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="J185" t="s">
         <v>17</v>
@@ -11715,24 +11718,24 @@
         <v>20</v>
       </c>
       <c r="L185" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="M185" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="N185" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B186" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C186" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="D186" t="s">
         <v>17</v>
@@ -11750,7 +11753,7 @@
         <v>18</v>
       </c>
       <c r="I186" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="J186" t="s">
         <v>17</v>
@@ -11759,24 +11762,24 @@
         <v>20</v>
       </c>
       <c r="L186" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="M186" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="N186" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B187" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C187" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="D187" t="s">
         <v>17</v>
@@ -11794,7 +11797,7 @@
         <v>18</v>
       </c>
       <c r="I187" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="J187" t="s">
         <v>17</v>
@@ -11803,24 +11806,24 @@
         <v>20</v>
       </c>
       <c r="L187" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="M187" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="N187" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B188" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C188" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="D188" t="s">
         <v>17</v>
@@ -11838,7 +11841,7 @@
         <v>18</v>
       </c>
       <c r="I188" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="J188" t="s">
         <v>17</v>
@@ -11847,24 +11850,24 @@
         <v>20</v>
       </c>
       <c r="L188" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="M188" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="N188" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B189" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="C189" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="D189" t="s">
         <v>17</v>
@@ -11882,7 +11885,7 @@
         <v>18</v>
       </c>
       <c r="I189" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="J189" t="s">
         <v>17</v>
@@ -11891,21 +11894,21 @@
         <v>20</v>
       </c>
       <c r="L189" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="M189" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="N189" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B190" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C190" t="s">
         <v>16</v>
@@ -11926,7 +11929,7 @@
         <v>40</v>
       </c>
       <c r="I190" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="J190" t="b">
         <v>0</v>
@@ -11935,21 +11938,21 @@
         <v>20</v>
       </c>
       <c r="L190" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="M190" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="N190" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B191" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C191" t="s">
         <v>129</v>
@@ -11970,7 +11973,7 @@
         <v>40</v>
       </c>
       <c r="I191" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="J191" t="b">
         <v>1</v>
@@ -11979,21 +11982,21 @@
         <v>20</v>
       </c>
       <c r="L191" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="M191" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="N191" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B192" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C192" t="s">
         <v>16</v>
@@ -12014,7 +12017,7 @@
         <v>40</v>
       </c>
       <c r="I192" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="J192" t="b">
         <v>1</v>
@@ -12023,24 +12026,24 @@
         <v>20</v>
       </c>
       <c r="L192" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="M192" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="N192" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B193" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="C193" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="D193" t="s">
         <v>17</v>
@@ -12058,7 +12061,7 @@
         <v>18</v>
       </c>
       <c r="I193" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="J193" t="s">
         <v>17</v>
@@ -12067,24 +12070,24 @@
         <v>20</v>
       </c>
       <c r="L193" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="M193" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="N193" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B194" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="C194" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="D194" t="s">
         <v>17</v>
@@ -12102,7 +12105,7 @@
         <v>18</v>
       </c>
       <c r="I194" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="J194" t="s">
         <v>17</v>
@@ -12111,21 +12114,21 @@
         <v>20</v>
       </c>
       <c r="L194" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="M194" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="N194" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B195" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="C195" t="s">
         <v>38</v>
@@ -12146,7 +12149,7 @@
         <v>40</v>
       </c>
       <c r="I195" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="J195" t="b">
         <v>1</v>
@@ -12155,24 +12158,24 @@
         <v>20</v>
       </c>
       <c r="L195" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="M195" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="N195" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B196" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="C196" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="D196" t="s">
         <v>17</v>
@@ -12190,7 +12193,7 @@
         <v>18</v>
       </c>
       <c r="I196" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="J196" t="s">
         <v>17</v>
@@ -12199,24 +12202,24 @@
         <v>20</v>
       </c>
       <c r="L196" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="M196" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="N196" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B197" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="C197" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="D197" t="b">
         <v>0</v>
@@ -12234,7 +12237,7 @@
         <v>40</v>
       </c>
       <c r="I197" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="J197" t="b">
         <v>1</v>
@@ -12243,24 +12246,24 @@
         <v>20</v>
       </c>
       <c r="L197" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="M197" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="N197" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B198" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="C198" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="D198" t="b">
         <v>0</v>
@@ -12278,7 +12281,7 @@
         <v>40</v>
       </c>
       <c r="I198" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="J198" t="b">
         <v>1</v>
@@ -12287,24 +12290,24 @@
         <v>20</v>
       </c>
       <c r="L198" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="M198" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="N198" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B199" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="C199" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="D199" t="b">
         <v>0</v>
@@ -12322,7 +12325,7 @@
         <v>40</v>
       </c>
       <c r="I199" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="J199" t="b">
         <v>1</v>
@@ -12331,13 +12334,13 @@
         <v>20</v>
       </c>
       <c r="L199" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="M199" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="N199" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-grace-master.report.xlsx
+++ b/tools/importer/reports/import-grace-master.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3259" uniqueCount="1216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3663" uniqueCount="1365">
   <si>
     <t>_reportFile</t>
   </si>
@@ -2949,18 +2949,90 @@
     <t>https://grace.com/newsroom/press-releases/</t>
   </si>
   <si>
+    <t>products/activators-custom-organoborate-boron-compounds.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","cards-featured-content"]</t>
+  </si>
+  <si>
+    <t>["breadcrumb"]</t>
+  </si>
+  <si>
+    <t>products/activators-custom-organoborate-boron-compounds</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:00:44.463Z</t>
+  </si>
+  <si>
+    <t>Activators Custom Organoborate/Boron Compounds</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/activators-custom-organoborate-boron-compounds/</t>
+  </si>
+  <si>
+    <t>products/activcat-catalysts.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","video-overlay","cards-featured-content"]</t>
+  </si>
+  <si>
+    <t>products/activcat-catalysts</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:01:41.202Z</t>
+  </si>
+  <si>
+    <t>ActivCat® Catalysts</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/activcat-catalysts/</t>
+  </si>
+  <si>
     <t>products/adsorbents.report.json</t>
   </si>
   <si>
     <t>products/adsorbents</t>
   </si>
   <si>
-    <t>2026-08-09T12:22:45.796Z</t>
+    <t>2026-08-09T17:02:34.956Z</t>
+  </si>
+  <si>
+    <t>Adsorbents</t>
   </si>
   <si>
     <t>https://grace.com/products/adsorbents/</t>
   </si>
   <si>
+    <t>products/catalysts.report.json</t>
+  </si>
+  <si>
+    <t>products/catalysts</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:03:30.004Z</t>
+  </si>
+  <si>
+    <t>Catalysts</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/catalysts/</t>
+  </si>
+  <si>
+    <t>products/consista.report.json</t>
+  </si>
+  <si>
+    <t>products/consista</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:04:25.639Z</t>
+  </si>
+  <si>
+    <t>CONSISTA®</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/consista/</t>
+  </si>
+  <si>
     <t>products/davisil.report.json</t>
   </si>
   <si>
@@ -2970,7 +3042,7 @@
     <t>products/davisil</t>
   </si>
   <si>
-    <t>2026-08-09T09:12:08.931Z</t>
+    <t>2026-08-09T17:05:21.134Z</t>
   </si>
   <si>
     <t>DAVISIL®</t>
@@ -2979,6 +3051,36 @@
     <t>https://grace.com/products/davisil/</t>
   </si>
   <si>
+    <t>products/fine-chemicals.report.json</t>
+  </si>
+  <si>
+    <t>products/fine-chemicals</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:06:16.549Z</t>
+  </si>
+  <si>
+    <t>Fine Chemicals</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/fine-chemicals/</t>
+  </si>
+  <si>
+    <t>products/hyampp-catalysts-and-donors.report.json</t>
+  </si>
+  <si>
+    <t>products/hyampp-catalysts-and-donors</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:07:10.730Z</t>
+  </si>
+  <si>
+    <t>HYAMPP® Catalysts and Donors</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/hyampp-catalysts-and-donors/</t>
+  </si>
+  <si>
     <t>products/ludox.report.json</t>
   </si>
   <si>
@@ -2988,7 +3090,7 @@
     <t>products/ludox</t>
   </si>
   <si>
-    <t>2026-08-09T09:13:01.218Z</t>
+    <t>2026-08-09T16:59:48.932Z</t>
   </si>
   <si>
     <t>LUDOX®</t>
@@ -2997,6 +3099,147 @@
     <t>https://grace.com/products/ludox/</t>
   </si>
   <si>
+    <t>products/lynx-pe.report.json</t>
+  </si>
+  <si>
+    <t>products/lynx-pe</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:00:44.906Z</t>
+  </si>
+  <si>
+    <t>LYNX® PE</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/lynx-pe/</t>
+  </si>
+  <si>
+    <t>products/lynx-pp.report.json</t>
+  </si>
+  <si>
+    <t>products/lynx-pp</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:01:38.956Z</t>
+  </si>
+  <si>
+    <t>LYNX® PP</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/lynx-pp/</t>
+  </si>
+  <si>
+    <t>products/magnapore.report.json</t>
+  </si>
+  <si>
+    <t>products/magnapore</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:02:35.030Z</t>
+  </si>
+  <si>
+    <t>MAGNAPORE®</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/magnapore/</t>
+  </si>
+  <si>
+    <t>products/metallocenes.report.json</t>
+  </si>
+  <si>
+    <t>products/metallocenes</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:03:30.204Z</t>
+  </si>
+  <si>
+    <t>Metallocenes</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/metallocenes/</t>
+  </si>
+  <si>
+    <t>products/polytrak-catalysts.report.json</t>
+  </si>
+  <si>
+    <t>products/polytrak-catalysts</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:04:25.165Z</t>
+  </si>
+  <si>
+    <t>POLYTRAK® Catalysts</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/polytrak-catalysts/</t>
+  </si>
+  <si>
+    <t>products/product-stewardship.report.json</t>
+  </si>
+  <si>
+    <t>["table-two-column-content"]</t>
+  </si>
+  <si>
+    <t>products/product-stewardship</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:05:19.428Z</t>
+  </si>
+  <si>
+    <t>Product Stewardship</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/product-stewardship/</t>
+  </si>
+  <si>
+    <t>products/quality-management.report.json</t>
+  </si>
+  <si>
+    <t>products/quality-management</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:06:14.628Z</t>
+  </si>
+  <si>
+    <t>Quality</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/quality-management/</t>
+  </si>
+  <si>
+    <t>products/reflectn-digital-plant-simulator-software.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-horizontal-teaser","cards-featured-content","social-follow","banner-contact-split","table-two-column-content","table-two-column-content"]</t>
+  </si>
+  <si>
+    <t>products/reflectn-digital-plant-simulator-software</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:07:08.602Z</t>
+  </si>
+  <si>
+    <t>REFLECTN™ Digital Plant Simulator Software</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/reflectn-digital-plant-simulator-software/</t>
+  </si>
+  <si>
+    <t>products/shac.report.json</t>
+  </si>
+  <si>
+    <t>products/shac</t>
+  </si>
+  <si>
+    <t>2026-08-09T16:59:47.928Z</t>
+  </si>
+  <si>
+    <t>SHAC®</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/shac/</t>
+  </si>
+  <si>
     <t>products/shieldex.report.json</t>
   </si>
   <si>
@@ -3006,7 +3249,7 @@
     <t>products/shieldex</t>
   </si>
   <si>
-    <t>2026-08-09T09:13:53.991Z</t>
+    <t>2026-08-09T17:00:43.762Z</t>
   </si>
   <si>
     <t>SHIELDEX® Anti-Corrosive Pigments</t>
@@ -3015,13 +3258,136 @@
     <t>https://grace.com/products/shieldex/</t>
   </si>
   <si>
+    <t>products/silsol.report.json</t>
+  </si>
+  <si>
+    <t>products/silsol</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:18:15.873Z</t>
+  </si>
+  <si>
+    <t>SILSOL®</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/silsol/</t>
+  </si>
+  <si>
+    <t>products/syloid-mx-silica-series.report.json</t>
+  </si>
+  <si>
+    <t>products/syloid-mx-silica-series</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:02:34.204Z</t>
+  </si>
+  <si>
+    <t>SYLOID® MX Silica Matting Agents for Coatings</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/syloid-mx-silica-series/</t>
+  </si>
+  <si>
+    <t>products/syloid-rad-silica-series.report.json</t>
+  </si>
+  <si>
+    <t>products/syloid-rad-silica-series</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:03:27.843Z</t>
+  </si>
+  <si>
+    <t>SYLOID® RAD Silica Series</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/syloid-rad-silica-series/</t>
+  </si>
+  <si>
+    <t>products/syloid-silica.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","video-overlay","columns-horizontal-teaser","cards-featured-content"]</t>
+  </si>
+  <si>
+    <t>products/syloid-silica</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:04:21.827Z</t>
+  </si>
+  <si>
+    <t>SYLOID® Silica</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/syloid-silica/</t>
+  </si>
+  <si>
+    <t>products/syloid-xdp-f-silica.report.json</t>
+  </si>
+  <si>
+    <t>products/syloid-xdp-f-silica</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:05:16.627Z</t>
+  </si>
+  <si>
+    <t>SYLOID® XDP F Silica for Nutraceutical Formulators</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/syloid-xdp-f-silica/</t>
+  </si>
+  <si>
+    <t>products/sylopol-cr-catalysts.report.json</t>
+  </si>
+  <si>
+    <t>products/sylopol-cr-catalysts</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:06:10.948Z</t>
+  </si>
+  <si>
+    <t>SYLOPOL® CR Catalysts</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/sylopol-cr-catalysts/</t>
+  </si>
+  <si>
+    <t>products/sylopol-zn-catalysts.report.json</t>
+  </si>
+  <si>
+    <t>products/sylopol-zn-catalysts</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:07:05.103Z</t>
+  </si>
+  <si>
+    <t>SYLOPOL® ZN Catalysts</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/sylopol-zn-catalysts/</t>
+  </si>
+  <si>
+    <t>products/sylosiv.report.json</t>
+  </si>
+  <si>
+    <t>products/sylosiv</t>
+  </si>
+  <si>
+    <t>2026-08-09T16:59:49.450Z</t>
+  </si>
+  <si>
+    <t>SYLOSIV®</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/sylosiv/</t>
+  </si>
+  <si>
     <t>products/synthetic-silicas.report.json</t>
   </si>
   <si>
     <t>products/synthetic-silicas</t>
   </si>
   <si>
-    <t>2026-08-09T12:26:54.020Z</t>
+    <t>2026-08-09T17:00:44.459Z</t>
   </si>
   <si>
     <t>Synthetic Silicas</t>
@@ -3030,6 +3396,57 @@
     <t>https://grace.com/products/synthetic-silicas/</t>
   </si>
   <si>
+    <t>products/trisyl-silica.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","video-overlay","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq","columns-horizontal-teaser","cards-featured-content"]</t>
+  </si>
+  <si>
+    <t>products/trisyl-silica</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:02:39.636Z</t>
+  </si>
+  <si>
+    <t>TRISYL® Silica</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/trisyl-silica/</t>
+  </si>
+  <si>
+    <t>products/trisyl-xge-catalyst.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","video-overlay","accordion-faq"]</t>
+  </si>
+  <si>
+    <t>products/trisyl-xge-catalyst</t>
+  </si>
+  <si>
+    <t>2026-08-09T16:59:50.185Z</t>
+  </si>
+  <si>
+    <t>TRISYL® XGE Catalyst</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/TRISYL-XGE-Catalyst/</t>
+  </si>
+  <si>
+    <t>products/unipol-donors.report.json</t>
+  </si>
+  <si>
+    <t>products/unipol-donors</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:03:34.205Z</t>
+  </si>
+  <si>
+    <t>UNIPOL® Donors</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/unipol-donors/</t>
+  </si>
+  <si>
     <t>products/unipol-unippac-process-control-software.report.json</t>
   </si>
   <si>
@@ -3039,7 +3456,7 @@
     <t>products/unipol-unippac-process-control-software</t>
   </si>
   <si>
-    <t>2026-08-09T09:15:41.679Z</t>
+    <t>2026-08-09T17:04:30.232Z</t>
   </si>
   <si>
     <t>UNIPOL UNIPPAC® Process Control Software</t>
@@ -3048,6 +3465,39 @@
     <t>https://grace.com/products/unipol-unippac-process-control-software/</t>
   </si>
   <si>
+    <t>products/vydac.report.json</t>
+  </si>
+  <si>
+    <t>products/vydac</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:05:23.669Z</t>
+  </si>
+  <si>
+    <t>VYDAC®</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/vydac/</t>
+  </si>
+  <si>
+    <t>products/vyvid.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","video-overlay","cards-product","cards-featured-content"]</t>
+  </si>
+  <si>
+    <t>products/vyvid</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:06:19.129Z</t>
+  </si>
+  <si>
+    <t>VYVID™</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/vyvid/</t>
+  </si>
+  <si>
     <t>about-grace/leadership-team/anthony-yoo.report.json</t>
   </si>
   <si>
@@ -3186,7 +3636,7 @@
     <t>products/synthetic-silicas/classification</t>
   </si>
   <si>
-    <t>2026-08-09T09:14:47.548Z</t>
+    <t>2026-08-09T17:01:40.743Z</t>
   </si>
   <si>
     <t>Synthetic Amorphous Silica (SAS)</t>
@@ -3421,9 +3871,6 @@
   </si>
   <si>
     <t>newsroom/press-releases/2023-press-releases/grace-announces-start-up-two-more-unipol-pp-technology-lines.report.json</t>
-  </si>
-  <si>
-    <t>["breadcrumb"]</t>
   </si>
   <si>
     <t>newsroom/press-releases/2023-press-releases/grace-announces-start-up-two-more-unipol-pp-technology-lines</t>
@@ -4049,7 +4496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P232"/>
+  <dimension ref="A1:P260"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -13469,10 +13916,10 @@
         <v>978</v>
       </c>
       <c r="B189" t="s">
-        <v>19</v>
+        <v>979</v>
       </c>
       <c r="C189" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D189" t="s">
         <v>19</v>
@@ -13481,45 +13928,45 @@
         <v>19</v>
       </c>
       <c r="F189" t="s">
-        <v>323</v>
+        <v>19</v>
       </c>
       <c r="G189" t="s">
-        <v>324</v>
-      </c>
-      <c r="H189" t="s">
-        <v>19</v>
+        <v>19</v>
+      </c>
+      <c r="H189" t="b">
+        <v>0</v>
       </c>
       <c r="I189" t="s">
-        <v>19</v>
+        <v>980</v>
       </c>
       <c r="J189" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K189" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="L189" t="s">
         <v>19</v>
       </c>
       <c r="M189" t="s">
-        <v>326</v>
+        <v>22</v>
       </c>
       <c r="N189" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="O189" t="s">
-        <v>19</v>
+        <v>983</v>
       </c>
       <c r="P189" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
     </row>
     <row r="190" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="B190" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="C190" t="s">
         <v>18</v>
@@ -13540,13 +13987,13 @@
         <v>1</v>
       </c>
       <c r="I190" t="s">
-        <v>18</v>
+        <v>980</v>
       </c>
       <c r="J190" t="s">
         <v>20</v>
       </c>
       <c r="K190" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="L190" t="s">
         <v>19</v>
@@ -13555,30 +14002,30 @@
         <v>22</v>
       </c>
       <c r="N190" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="O190" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="P190" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
     </row>
     <row r="191" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="B191" t="s">
-        <v>989</v>
+        <v>18</v>
       </c>
       <c r="C191" t="s">
         <v>18</v>
       </c>
-      <c r="D191" t="s">
-        <v>19</v>
-      </c>
-      <c r="E191" t="s">
-        <v>19</v>
+      <c r="D191" t="b">
+        <v>0</v>
+      </c>
+      <c r="E191">
+        <v>4</v>
       </c>
       <c r="F191" t="s">
         <v>19</v>
@@ -13587,48 +14034,48 @@
         <v>19</v>
       </c>
       <c r="H191" t="b">
+        <v>0</v>
+      </c>
+      <c r="I191" t="s">
+        <v>41</v>
+      </c>
+      <c r="J191" t="s">
+        <v>42</v>
+      </c>
+      <c r="K191" t="s">
+        <v>992</v>
+      </c>
+      <c r="L191" t="b">
         <v>1</v>
       </c>
-      <c r="I191" t="s">
-        <v>18</v>
-      </c>
-      <c r="J191" t="s">
-        <v>20</v>
-      </c>
-      <c r="K191" t="s">
-        <v>990</v>
-      </c>
-      <c r="L191" t="s">
-        <v>19</v>
-      </c>
       <c r="M191" t="s">
         <v>22</v>
       </c>
       <c r="N191" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="O191" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="P191" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
     </row>
     <row r="192" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="B192" t="s">
-        <v>995</v>
+        <v>18</v>
       </c>
       <c r="C192" t="s">
         <v>18</v>
       </c>
-      <c r="D192" t="s">
-        <v>19</v>
-      </c>
-      <c r="E192" t="s">
-        <v>19</v>
+      <c r="D192" t="b">
+        <v>0</v>
+      </c>
+      <c r="E192">
+        <v>3</v>
       </c>
       <c r="F192" t="s">
         <v>19</v>
@@ -13637,48 +14084,48 @@
         <v>19</v>
       </c>
       <c r="H192" t="b">
+        <v>0</v>
+      </c>
+      <c r="I192" t="s">
+        <v>41</v>
+      </c>
+      <c r="J192" t="s">
+        <v>42</v>
+      </c>
+      <c r="K192" t="s">
+        <v>997</v>
+      </c>
+      <c r="L192" t="b">
         <v>1</v>
       </c>
-      <c r="I192" t="s">
-        <v>18</v>
-      </c>
-      <c r="J192" t="s">
-        <v>20</v>
-      </c>
-      <c r="K192" t="s">
-        <v>996</v>
-      </c>
-      <c r="L192" t="s">
-        <v>19</v>
-      </c>
       <c r="M192" t="s">
         <v>22</v>
       </c>
       <c r="N192" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="O192" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="P192" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="193" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B193" t="s">
-        <v>18</v>
+        <v>979</v>
       </c>
       <c r="C193" t="s">
         <v>18</v>
       </c>
-      <c r="D193" t="b">
-        <v>0</v>
-      </c>
-      <c r="E193">
-        <v>4</v>
+      <c r="D193" t="s">
+        <v>19</v>
+      </c>
+      <c r="E193" t="s">
+        <v>19</v>
       </c>
       <c r="F193" t="s">
         <v>19</v>
@@ -13687,39 +14134,39 @@
         <v>19</v>
       </c>
       <c r="H193" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I193" t="s">
-        <v>41</v>
+        <v>980</v>
       </c>
       <c r="J193" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K193" t="s">
-        <v>1001</v>
-      </c>
-      <c r="L193" t="b">
-        <v>1</v>
+        <v>1002</v>
+      </c>
+      <c r="L193" t="s">
+        <v>19</v>
       </c>
       <c r="M193" t="s">
         <v>22</v>
       </c>
       <c r="N193" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="O193" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="P193" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="194" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B194" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C194" t="s">
         <v>18</v>
@@ -13740,13 +14187,13 @@
         <v>1</v>
       </c>
       <c r="I194" t="s">
-        <v>18</v>
+        <v>980</v>
       </c>
       <c r="J194" t="s">
         <v>20</v>
       </c>
       <c r="K194" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="L194" t="s">
         <v>19</v>
@@ -13755,30 +14202,30 @@
         <v>22</v>
       </c>
       <c r="N194" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="O194" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="P194" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="195" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B195" t="s">
-        <v>1012</v>
+        <v>18</v>
       </c>
       <c r="C195" t="s">
-        <v>1013</v>
-      </c>
-      <c r="D195" t="s">
-        <v>19</v>
-      </c>
-      <c r="E195" t="s">
-        <v>19</v>
+        <v>18</v>
+      </c>
+      <c r="D195" t="b">
+        <v>0</v>
+      </c>
+      <c r="E195">
+        <v>4</v>
       </c>
       <c r="F195" t="s">
         <v>19</v>
@@ -13790,95 +14237,95 @@
         <v>0</v>
       </c>
       <c r="I195" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="J195" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="K195" t="s">
+        <v>1013</v>
+      </c>
+      <c r="L195" t="b">
+        <v>1</v>
+      </c>
+      <c r="M195" t="s">
+        <v>22</v>
+      </c>
+      <c r="N195" t="s">
         <v>1014</v>
       </c>
-      <c r="L195" t="s">
-        <v>19</v>
-      </c>
-      <c r="M195" t="s">
-        <v>22</v>
-      </c>
-      <c r="N195" t="s">
+      <c r="O195" t="s">
         <v>1015</v>
       </c>
-      <c r="O195" t="s">
+      <c r="P195" t="s">
         <v>1016</v>
-      </c>
-      <c r="P195" t="s">
-        <v>1017</v>
       </c>
     </row>
     <row r="196" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B196" t="s">
+        <v>979</v>
+      </c>
+      <c r="C196" t="s">
+        <v>18</v>
+      </c>
+      <c r="D196" t="s">
+        <v>19</v>
+      </c>
+      <c r="E196" t="s">
+        <v>19</v>
+      </c>
+      <c r="F196" t="s">
+        <v>19</v>
+      </c>
+      <c r="G196" t="s">
+        <v>19</v>
+      </c>
+      <c r="H196" t="b">
+        <v>1</v>
+      </c>
+      <c r="I196" t="s">
+        <v>980</v>
+      </c>
+      <c r="J196" t="s">
+        <v>20</v>
+      </c>
+      <c r="K196" t="s">
         <v>1018</v>
       </c>
-      <c r="B196" t="s">
+      <c r="L196" t="s">
+        <v>19</v>
+      </c>
+      <c r="M196" t="s">
+        <v>22</v>
+      </c>
+      <c r="N196" t="s">
         <v>1019</v>
       </c>
-      <c r="C196" t="s">
-        <v>18</v>
-      </c>
-      <c r="D196" t="b">
-        <v>0</v>
-      </c>
-      <c r="E196">
-        <v>0</v>
-      </c>
-      <c r="F196" t="s">
-        <v>19</v>
-      </c>
-      <c r="G196" t="s">
-        <v>19</v>
-      </c>
-      <c r="H196" t="b">
-        <v>0</v>
-      </c>
-      <c r="I196" t="s">
-        <v>66</v>
-      </c>
-      <c r="J196" t="s">
-        <v>42</v>
-      </c>
-      <c r="K196" t="s">
+      <c r="O196" t="s">
         <v>1020</v>
       </c>
-      <c r="L196" t="b">
-        <v>0</v>
-      </c>
-      <c r="M196" t="s">
-        <v>22</v>
-      </c>
-      <c r="N196" t="s">
+      <c r="P196" t="s">
         <v>1021</v>
-      </c>
-      <c r="O196" t="s">
-        <v>1022</v>
-      </c>
-      <c r="P196" t="s">
-        <v>1023</v>
       </c>
     </row>
     <row r="197" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="B197" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C197" t="s">
-        <v>129</v>
-      </c>
-      <c r="D197" t="b">
-        <v>0</v>
-      </c>
-      <c r="E197">
-        <v>2</v>
+        <v>18</v>
+      </c>
+      <c r="D197" t="s">
+        <v>19</v>
+      </c>
+      <c r="E197" t="s">
+        <v>19</v>
       </c>
       <c r="F197" t="s">
         <v>19</v>
@@ -13890,86 +14337,86 @@
         <v>1</v>
       </c>
       <c r="I197" t="s">
-        <v>66</v>
+        <v>980</v>
       </c>
       <c r="J197" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K197" t="s">
+        <v>1024</v>
+      </c>
+      <c r="L197" t="s">
+        <v>19</v>
+      </c>
+      <c r="M197" t="s">
+        <v>22</v>
+      </c>
+      <c r="N197" t="s">
+        <v>1025</v>
+      </c>
+      <c r="O197" t="s">
         <v>1026</v>
       </c>
-      <c r="L197" t="b">
-        <v>1</v>
-      </c>
-      <c r="M197" t="s">
-        <v>22</v>
-      </c>
-      <c r="N197" t="s">
+      <c r="P197" t="s">
         <v>1027</v>
-      </c>
-      <c r="O197" t="s">
-        <v>1028</v>
-      </c>
-      <c r="P197" t="s">
-        <v>1029</v>
       </c>
     </row>
     <row r="198" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B198" t="s">
+        <v>979</v>
+      </c>
+      <c r="C198" t="s">
+        <v>18</v>
+      </c>
+      <c r="D198" t="s">
+        <v>19</v>
+      </c>
+      <c r="E198" t="s">
+        <v>19</v>
+      </c>
+      <c r="F198" t="s">
+        <v>19</v>
+      </c>
+      <c r="G198" t="s">
+        <v>19</v>
+      </c>
+      <c r="H198" t="b">
+        <v>0</v>
+      </c>
+      <c r="I198" t="s">
+        <v>980</v>
+      </c>
+      <c r="J198" t="s">
+        <v>20</v>
+      </c>
+      <c r="K198" t="s">
+        <v>1029</v>
+      </c>
+      <c r="L198" t="s">
+        <v>19</v>
+      </c>
+      <c r="M198" t="s">
+        <v>22</v>
+      </c>
+      <c r="N198" t="s">
         <v>1030</v>
       </c>
-      <c r="B198" t="s">
+      <c r="O198" t="s">
         <v>1031</v>
       </c>
-      <c r="C198" t="s">
-        <v>18</v>
-      </c>
-      <c r="D198" t="b">
-        <v>0</v>
-      </c>
-      <c r="E198">
-        <v>4</v>
-      </c>
-      <c r="F198" t="s">
-        <v>19</v>
-      </c>
-      <c r="G198" t="s">
-        <v>19</v>
-      </c>
-      <c r="H198" t="b">
-        <v>1</v>
-      </c>
-      <c r="I198" t="s">
-        <v>66</v>
-      </c>
-      <c r="J198" t="s">
-        <v>42</v>
-      </c>
-      <c r="K198" t="s">
+      <c r="P198" t="s">
         <v>1032</v>
-      </c>
-      <c r="L198" t="b">
-        <v>1</v>
-      </c>
-      <c r="M198" t="s">
-        <v>22</v>
-      </c>
-      <c r="N198" t="s">
-        <v>1033</v>
-      </c>
-      <c r="O198" t="s">
-        <v>1034</v>
-      </c>
-      <c r="P198" t="s">
-        <v>1035</v>
       </c>
     </row>
     <row r="199" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="B199" t="s">
-        <v>1037</v>
+        <v>979</v>
       </c>
       <c r="C199" t="s">
         <v>18</v>
@@ -13987,16 +14434,16 @@
         <v>19</v>
       </c>
       <c r="H199" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I199" t="s">
-        <v>18</v>
+        <v>980</v>
       </c>
       <c r="J199" t="s">
         <v>20</v>
       </c>
       <c r="K199" t="s">
-        <v>1038</v>
+        <v>1034</v>
       </c>
       <c r="L199" t="s">
         <v>19</v>
@@ -14005,21 +14452,21 @@
         <v>22</v>
       </c>
       <c r="N199" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
       <c r="O199" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="P199" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="200" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="B200" t="s">
-        <v>1043</v>
+        <v>979</v>
       </c>
       <c r="C200" t="s">
         <v>18</v>
@@ -14037,16 +14484,16 @@
         <v>19</v>
       </c>
       <c r="H200" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I200" t="s">
-        <v>18</v>
+        <v>980</v>
       </c>
       <c r="J200" t="s">
         <v>20</v>
       </c>
       <c r="K200" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="L200" t="s">
         <v>19</v>
@@ -14055,30 +14502,30 @@
         <v>22</v>
       </c>
       <c r="N200" t="s">
-        <v>1045</v>
+        <v>1040</v>
       </c>
       <c r="O200" t="s">
-        <v>1046</v>
+        <v>1041</v>
       </c>
       <c r="P200" t="s">
-        <v>1047</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="201" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
       <c r="B201" t="s">
-        <v>1049</v>
+        <v>979</v>
       </c>
       <c r="C201" t="s">
-        <v>40</v>
-      </c>
-      <c r="D201" t="b">
-        <v>0</v>
-      </c>
-      <c r="E201">
-        <v>2</v>
+        <v>18</v>
+      </c>
+      <c r="D201" t="s">
+        <v>19</v>
+      </c>
+      <c r="E201" t="s">
+        <v>19</v>
       </c>
       <c r="F201" t="s">
         <v>19</v>
@@ -14090,36 +14537,36 @@
         <v>0</v>
       </c>
       <c r="I201" t="s">
-        <v>66</v>
+        <v>980</v>
       </c>
       <c r="J201" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K201" t="s">
-        <v>1050</v>
-      </c>
-      <c r="L201" t="b">
-        <v>1</v>
+        <v>1044</v>
+      </c>
+      <c r="L201" t="s">
+        <v>19</v>
       </c>
       <c r="M201" t="s">
         <v>22</v>
       </c>
       <c r="N201" t="s">
-        <v>1051</v>
+        <v>1045</v>
       </c>
       <c r="O201" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
       <c r="P201" t="s">
-        <v>1053</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="202" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>1054</v>
+        <v>1048</v>
       </c>
       <c r="B202" t="s">
-        <v>1055</v>
+        <v>979</v>
       </c>
       <c r="C202" t="s">
         <v>18</v>
@@ -14140,13 +14587,13 @@
         <v>0</v>
       </c>
       <c r="I202" t="s">
-        <v>18</v>
+        <v>980</v>
       </c>
       <c r="J202" t="s">
         <v>20</v>
       </c>
       <c r="K202" t="s">
-        <v>1056</v>
+        <v>1049</v>
       </c>
       <c r="L202" t="s">
         <v>19</v>
@@ -14155,30 +14602,30 @@
         <v>22</v>
       </c>
       <c r="N202" t="s">
-        <v>1057</v>
+        <v>1050</v>
       </c>
       <c r="O202" t="s">
-        <v>1058</v>
+        <v>1051</v>
       </c>
       <c r="P202" t="s">
-        <v>1059</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="203" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>1060</v>
+        <v>1053</v>
       </c>
       <c r="B203" t="s">
-        <v>1061</v>
+        <v>1054</v>
       </c>
       <c r="C203" t="s">
-        <v>1062</v>
+        <v>18</v>
       </c>
       <c r="D203" t="b">
         <v>0</v>
       </c>
       <c r="E203">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F203" t="s">
         <v>19</v>
@@ -14187,16 +14634,16 @@
         <v>19</v>
       </c>
       <c r="H203" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I203" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="J203" t="s">
         <v>42</v>
       </c>
       <c r="K203" t="s">
-        <v>1063</v>
+        <v>1055</v>
       </c>
       <c r="L203" t="b">
         <v>1</v>
@@ -14205,30 +14652,30 @@
         <v>22</v>
       </c>
       <c r="N203" t="s">
-        <v>1064</v>
+        <v>1056</v>
       </c>
       <c r="O203" t="s">
-        <v>1065</v>
+        <v>1057</v>
       </c>
       <c r="P203" t="s">
-        <v>1066</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="204" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>1067</v>
+        <v>1059</v>
       </c>
       <c r="B204" t="s">
-        <v>1068</v>
+        <v>18</v>
       </c>
       <c r="C204" t="s">
-        <v>1069</v>
+        <v>18</v>
       </c>
       <c r="D204" t="b">
         <v>0</v>
       </c>
       <c r="E204">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F204" t="s">
         <v>19</v>
@@ -14237,16 +14684,16 @@
         <v>19</v>
       </c>
       <c r="H204" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I204" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="J204" t="s">
         <v>42</v>
       </c>
       <c r="K204" t="s">
-        <v>1070</v>
+        <v>1060</v>
       </c>
       <c r="L204" t="b">
         <v>1</v>
@@ -14255,21 +14702,21 @@
         <v>22</v>
       </c>
       <c r="N204" t="s">
-        <v>1071</v>
+        <v>1061</v>
       </c>
       <c r="O204" t="s">
-        <v>1072</v>
+        <v>1062</v>
       </c>
       <c r="P204" t="s">
-        <v>1073</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="205" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>1074</v>
+        <v>1064</v>
       </c>
       <c r="B205" t="s">
-        <v>1075</v>
+        <v>1065</v>
       </c>
       <c r="C205" t="s">
         <v>18</v>
@@ -14287,7 +14734,7 @@
         <v>19</v>
       </c>
       <c r="H205" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I205" t="s">
         <v>18</v>
@@ -14296,7 +14743,7 @@
         <v>20</v>
       </c>
       <c r="K205" t="s">
-        <v>1076</v>
+        <v>1066</v>
       </c>
       <c r="L205" t="s">
         <v>19</v>
@@ -14305,21 +14752,21 @@
         <v>22</v>
       </c>
       <c r="N205" t="s">
-        <v>1077</v>
+        <v>1067</v>
       </c>
       <c r="O205" t="s">
-        <v>1078</v>
+        <v>1068</v>
       </c>
       <c r="P205" t="s">
-        <v>1079</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="206" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>1080</v>
+        <v>1070</v>
       </c>
       <c r="B206" t="s">
-        <v>1075</v>
+        <v>979</v>
       </c>
       <c r="C206" t="s">
         <v>18</v>
@@ -14340,13 +14787,13 @@
         <v>0</v>
       </c>
       <c r="I206" t="s">
-        <v>18</v>
+        <v>980</v>
       </c>
       <c r="J206" t="s">
         <v>20</v>
       </c>
       <c r="K206" t="s">
-        <v>1081</v>
+        <v>1071</v>
       </c>
       <c r="L206" t="s">
         <v>19</v>
@@ -14355,21 +14802,21 @@
         <v>22</v>
       </c>
       <c r="N206" t="s">
-        <v>1082</v>
+        <v>1072</v>
       </c>
       <c r="O206" t="s">
-        <v>1083</v>
+        <v>1073</v>
       </c>
       <c r="P206" t="s">
-        <v>1084</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="207" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>1085</v>
+        <v>1075</v>
       </c>
       <c r="B207" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C207" t="s">
         <v>18</v>
@@ -14387,16 +14834,16 @@
         <v>19</v>
       </c>
       <c r="H207" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I207" t="s">
-        <v>18</v>
+        <v>980</v>
       </c>
       <c r="J207" t="s">
         <v>20</v>
       </c>
       <c r="K207" t="s">
-        <v>1086</v>
+        <v>1077</v>
       </c>
       <c r="L207" t="s">
         <v>19</v>
@@ -14405,21 +14852,21 @@
         <v>22</v>
       </c>
       <c r="N207" t="s">
-        <v>1087</v>
+        <v>1078</v>
       </c>
       <c r="O207" t="s">
-        <v>1088</v>
+        <v>1079</v>
       </c>
       <c r="P207" t="s">
-        <v>1089</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="208" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>1090</v>
+        <v>1081</v>
       </c>
       <c r="B208" t="s">
-        <v>1075</v>
+        <v>1023</v>
       </c>
       <c r="C208" t="s">
         <v>18</v>
@@ -14437,16 +14884,16 @@
         <v>19</v>
       </c>
       <c r="H208" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I208" t="s">
-        <v>18</v>
+        <v>980</v>
       </c>
       <c r="J208" t="s">
         <v>20</v>
       </c>
       <c r="K208" t="s">
-        <v>1091</v>
+        <v>1082</v>
       </c>
       <c r="L208" t="s">
         <v>19</v>
@@ -14455,21 +14902,21 @@
         <v>22</v>
       </c>
       <c r="N208" t="s">
-        <v>1092</v>
+        <v>1083</v>
       </c>
       <c r="O208" t="s">
-        <v>1093</v>
+        <v>1084</v>
       </c>
       <c r="P208" t="s">
-        <v>1094</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="209" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>1095</v>
+        <v>1086</v>
       </c>
       <c r="B209" t="s">
-        <v>1075</v>
+        <v>1065</v>
       </c>
       <c r="C209" t="s">
         <v>18</v>
@@ -14487,16 +14934,16 @@
         <v>19</v>
       </c>
       <c r="H209" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I209" t="s">
-        <v>18</v>
+        <v>980</v>
       </c>
       <c r="J209" t="s">
         <v>20</v>
       </c>
       <c r="K209" t="s">
-        <v>1096</v>
+        <v>1087</v>
       </c>
       <c r="L209" t="s">
         <v>19</v>
@@ -14505,21 +14952,21 @@
         <v>22</v>
       </c>
       <c r="N209" t="s">
-        <v>1097</v>
+        <v>1088</v>
       </c>
       <c r="O209" t="s">
-        <v>1098</v>
+        <v>1089</v>
       </c>
       <c r="P209" t="s">
-        <v>1099</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="210" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>1100</v>
+        <v>1091</v>
       </c>
       <c r="B210" t="s">
-        <v>1075</v>
+        <v>1065</v>
       </c>
       <c r="C210" t="s">
         <v>18</v>
@@ -14537,7 +14984,7 @@
         <v>19</v>
       </c>
       <c r="H210" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I210" t="s">
         <v>18</v>
@@ -14546,7 +14993,7 @@
         <v>20</v>
       </c>
       <c r="K210" t="s">
-        <v>1101</v>
+        <v>1092</v>
       </c>
       <c r="L210" t="s">
         <v>19</v>
@@ -14555,21 +15002,21 @@
         <v>22</v>
       </c>
       <c r="N210" t="s">
-        <v>1102</v>
+        <v>1093</v>
       </c>
       <c r="O210" t="s">
-        <v>1103</v>
+        <v>1094</v>
       </c>
       <c r="P210" t="s">
-        <v>1104</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="211" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>1105</v>
+        <v>1096</v>
       </c>
       <c r="B211" t="s">
-        <v>1075</v>
+        <v>1097</v>
       </c>
       <c r="C211" t="s">
         <v>18</v>
@@ -14587,16 +15034,16 @@
         <v>19</v>
       </c>
       <c r="H211" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I211" t="s">
-        <v>18</v>
+        <v>980</v>
       </c>
       <c r="J211" t="s">
         <v>20</v>
       </c>
       <c r="K211" t="s">
-        <v>1106</v>
+        <v>1098</v>
       </c>
       <c r="L211" t="s">
         <v>19</v>
@@ -14605,21 +15052,21 @@
         <v>22</v>
       </c>
       <c r="N211" t="s">
-        <v>1107</v>
+        <v>1099</v>
       </c>
       <c r="O211" t="s">
-        <v>1108</v>
+        <v>1100</v>
       </c>
       <c r="P211" t="s">
-        <v>1109</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="212" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>1110</v>
+        <v>1102</v>
       </c>
       <c r="B212" t="s">
-        <v>1075</v>
+        <v>1065</v>
       </c>
       <c r="C212" t="s">
         <v>18</v>
@@ -14637,7 +15084,7 @@
         <v>19</v>
       </c>
       <c r="H212" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I212" t="s">
         <v>18</v>
@@ -14646,7 +15093,7 @@
         <v>20</v>
       </c>
       <c r="K212" t="s">
-        <v>1111</v>
+        <v>1103</v>
       </c>
       <c r="L212" t="s">
         <v>19</v>
@@ -14655,21 +15102,21 @@
         <v>22</v>
       </c>
       <c r="N212" t="s">
-        <v>1112</v>
+        <v>1104</v>
       </c>
       <c r="O212" t="s">
-        <v>1113</v>
+        <v>1105</v>
       </c>
       <c r="P212" t="s">
-        <v>1114</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="213" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>1115</v>
+        <v>1107</v>
       </c>
       <c r="B213" t="s">
-        <v>1075</v>
+        <v>979</v>
       </c>
       <c r="C213" t="s">
         <v>18</v>
@@ -14690,13 +15137,13 @@
         <v>0</v>
       </c>
       <c r="I213" t="s">
-        <v>18</v>
+        <v>980</v>
       </c>
       <c r="J213" t="s">
         <v>20</v>
       </c>
       <c r="K213" t="s">
-        <v>1116</v>
+        <v>1108</v>
       </c>
       <c r="L213" t="s">
         <v>19</v>
@@ -14705,21 +15152,21 @@
         <v>22</v>
       </c>
       <c r="N213" t="s">
-        <v>1117</v>
+        <v>1109</v>
       </c>
       <c r="O213" t="s">
-        <v>1118</v>
+        <v>1110</v>
       </c>
       <c r="P213" t="s">
-        <v>1119</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="214" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>1120</v>
+        <v>1112</v>
       </c>
       <c r="B214" t="s">
-        <v>1075</v>
+        <v>979</v>
       </c>
       <c r="C214" t="s">
         <v>18</v>
@@ -14740,13 +15187,13 @@
         <v>0</v>
       </c>
       <c r="I214" t="s">
-        <v>18</v>
+        <v>980</v>
       </c>
       <c r="J214" t="s">
         <v>20</v>
       </c>
       <c r="K214" t="s">
-        <v>1121</v>
+        <v>1113</v>
       </c>
       <c r="L214" t="s">
         <v>19</v>
@@ -14755,21 +15202,21 @@
         <v>22</v>
       </c>
       <c r="N214" t="s">
-        <v>1122</v>
+        <v>1114</v>
       </c>
       <c r="O214" t="s">
-        <v>1123</v>
+        <v>1115</v>
       </c>
       <c r="P214" t="s">
-        <v>1124</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="215" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>1125</v>
+        <v>1117</v>
       </c>
       <c r="B215" t="s">
-        <v>1075</v>
+        <v>1023</v>
       </c>
       <c r="C215" t="s">
         <v>18</v>
@@ -14787,16 +15234,16 @@
         <v>19</v>
       </c>
       <c r="H215" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I215" t="s">
-        <v>18</v>
+        <v>980</v>
       </c>
       <c r="J215" t="s">
         <v>20</v>
       </c>
       <c r="K215" t="s">
-        <v>1126</v>
+        <v>1118</v>
       </c>
       <c r="L215" t="s">
         <v>19</v>
@@ -14805,30 +15252,30 @@
         <v>22</v>
       </c>
       <c r="N215" t="s">
-        <v>1127</v>
+        <v>1119</v>
       </c>
       <c r="O215" t="s">
-        <v>1128</v>
+        <v>1120</v>
       </c>
       <c r="P215" t="s">
-        <v>1129</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="216" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>1130</v>
+        <v>1122</v>
       </c>
       <c r="B216" t="s">
-        <v>1075</v>
+        <v>18</v>
       </c>
       <c r="C216" t="s">
         <v>18</v>
       </c>
-      <c r="D216" t="s">
-        <v>19</v>
-      </c>
-      <c r="E216" t="s">
-        <v>19</v>
+      <c r="D216" t="b">
+        <v>0</v>
+      </c>
+      <c r="E216">
+        <v>4</v>
       </c>
       <c r="F216" t="s">
         <v>19</v>
@@ -14840,36 +15287,36 @@
         <v>0</v>
       </c>
       <c r="I216" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="J216" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="K216" t="s">
-        <v>1131</v>
-      </c>
-      <c r="L216" t="s">
-        <v>19</v>
+        <v>1123</v>
+      </c>
+      <c r="L216" t="b">
+        <v>1</v>
       </c>
       <c r="M216" t="s">
         <v>22</v>
       </c>
       <c r="N216" t="s">
-        <v>1132</v>
+        <v>1124</v>
       </c>
       <c r="O216" t="s">
-        <v>1133</v>
+        <v>1125</v>
       </c>
       <c r="P216" t="s">
-        <v>1134</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="217" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>1135</v>
+        <v>1127</v>
       </c>
       <c r="B217" t="s">
-        <v>1075</v>
+        <v>1128</v>
       </c>
       <c r="C217" t="s">
         <v>18</v>
@@ -14887,16 +15334,16 @@
         <v>19</v>
       </c>
       <c r="H217" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I217" t="s">
-        <v>1136</v>
+        <v>18</v>
       </c>
       <c r="J217" t="s">
         <v>20</v>
       </c>
       <c r="K217" t="s">
-        <v>1137</v>
+        <v>1129</v>
       </c>
       <c r="L217" t="s">
         <v>19</v>
@@ -14905,21 +15352,21 @@
         <v>22</v>
       </c>
       <c r="N217" t="s">
-        <v>1138</v>
+        <v>1130</v>
       </c>
       <c r="O217" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
       <c r="P217" t="s">
-        <v>1140</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="218" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>1141</v>
+        <v>1133</v>
       </c>
       <c r="B218" t="s">
-        <v>1075</v>
+        <v>1134</v>
       </c>
       <c r="C218" t="s">
         <v>18</v>
@@ -14937,16 +15384,16 @@
         <v>19</v>
       </c>
       <c r="H218" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I218" t="s">
-        <v>1136</v>
+        <v>980</v>
       </c>
       <c r="J218" t="s">
         <v>20</v>
       </c>
       <c r="K218" t="s">
-        <v>1142</v>
+        <v>1135</v>
       </c>
       <c r="L218" t="s">
         <v>19</v>
@@ -14955,21 +15402,21 @@
         <v>22</v>
       </c>
       <c r="N218" t="s">
-        <v>1143</v>
+        <v>1136</v>
       </c>
       <c r="O218" t="s">
-        <v>1144</v>
+        <v>1137</v>
       </c>
       <c r="P218" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="219" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>1146</v>
+        <v>1139</v>
       </c>
       <c r="B219" t="s">
-        <v>1075</v>
+        <v>979</v>
       </c>
       <c r="C219" t="s">
         <v>18</v>
@@ -14990,13 +15437,13 @@
         <v>0</v>
       </c>
       <c r="I219" t="s">
-        <v>1136</v>
+        <v>980</v>
       </c>
       <c r="J219" t="s">
         <v>20</v>
       </c>
       <c r="K219" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
       <c r="L219" t="s">
         <v>19</v>
@@ -15005,21 +15452,21 @@
         <v>22</v>
       </c>
       <c r="N219" t="s">
-        <v>1148</v>
+        <v>1141</v>
       </c>
       <c r="O219" t="s">
-        <v>1149</v>
+        <v>1142</v>
       </c>
       <c r="P219" t="s">
-        <v>1150</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="220" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>1151</v>
+        <v>1144</v>
       </c>
       <c r="B220" t="s">
-        <v>1075</v>
+        <v>1145</v>
       </c>
       <c r="C220" t="s">
         <v>18</v>
@@ -15037,16 +15484,16 @@
         <v>19</v>
       </c>
       <c r="H220" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I220" t="s">
-        <v>1136</v>
+        <v>18</v>
       </c>
       <c r="J220" t="s">
         <v>20</v>
       </c>
       <c r="K220" t="s">
-        <v>1152</v>
+        <v>1146</v>
       </c>
       <c r="L220" t="s">
         <v>19</v>
@@ -15055,21 +15502,21 @@
         <v>22</v>
       </c>
       <c r="N220" t="s">
-        <v>1153</v>
+        <v>1147</v>
       </c>
       <c r="O220" t="s">
-        <v>1154</v>
+        <v>1148</v>
       </c>
       <c r="P220" t="s">
-        <v>1155</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="221" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>1156</v>
+        <v>1150</v>
       </c>
       <c r="B221" t="s">
-        <v>1075</v>
+        <v>979</v>
       </c>
       <c r="C221" t="s">
         <v>18</v>
@@ -15087,16 +15534,16 @@
         <v>19</v>
       </c>
       <c r="H221" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I221" t="s">
-        <v>1136</v>
+        <v>980</v>
       </c>
       <c r="J221" t="s">
         <v>20</v>
       </c>
       <c r="K221" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="L221" t="s">
         <v>19</v>
@@ -15105,21 +15552,21 @@
         <v>22</v>
       </c>
       <c r="N221" t="s">
-        <v>1158</v>
+        <v>1152</v>
       </c>
       <c r="O221" t="s">
-        <v>1159</v>
+        <v>1153</v>
       </c>
       <c r="P221" t="s">
-        <v>1160</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="222" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>1161</v>
+        <v>1155</v>
       </c>
       <c r="B222" t="s">
-        <v>1075</v>
+        <v>1156</v>
       </c>
       <c r="C222" t="s">
         <v>18</v>
@@ -15137,7 +15584,7 @@
         <v>19</v>
       </c>
       <c r="H222" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I222" t="s">
         <v>18</v>
@@ -15146,7 +15593,7 @@
         <v>20</v>
       </c>
       <c r="K222" t="s">
-        <v>1162</v>
+        <v>1157</v>
       </c>
       <c r="L222" t="s">
         <v>19</v>
@@ -15155,80 +15602,80 @@
         <v>22</v>
       </c>
       <c r="N222" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="O222" t="s">
-        <v>1164</v>
+        <v>1159</v>
       </c>
       <c r="P222" t="s">
-        <v>1165</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="223" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B223" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C223" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D223" t="s">
+        <v>19</v>
+      </c>
+      <c r="E223" t="s">
+        <v>19</v>
+      </c>
+      <c r="F223" t="s">
+        <v>19</v>
+      </c>
+      <c r="G223" t="s">
+        <v>19</v>
+      </c>
+      <c r="H223" t="b">
+        <v>0</v>
+      </c>
+      <c r="I223" t="s">
+        <v>18</v>
+      </c>
+      <c r="J223" t="s">
+        <v>20</v>
+      </c>
+      <c r="K223" t="s">
+        <v>1164</v>
+      </c>
+      <c r="L223" t="s">
+        <v>19</v>
+      </c>
+      <c r="M223" t="s">
+        <v>22</v>
+      </c>
+      <c r="N223" t="s">
+        <v>1165</v>
+      </c>
+      <c r="O223" t="s">
         <v>1166</v>
       </c>
-      <c r="B223" t="s">
-        <v>19</v>
-      </c>
-      <c r="C223" t="s">
-        <v>19</v>
-      </c>
-      <c r="D223" t="s">
-        <v>19</v>
-      </c>
-      <c r="E223" t="s">
-        <v>19</v>
-      </c>
-      <c r="F223" t="s">
-        <v>323</v>
-      </c>
-      <c r="G223" t="s">
-        <v>324</v>
-      </c>
-      <c r="H223" t="s">
-        <v>19</v>
-      </c>
-      <c r="I223" t="s">
-        <v>19</v>
-      </c>
-      <c r="J223" t="s">
-        <v>19</v>
-      </c>
-      <c r="K223" t="s">
+      <c r="P223" t="s">
         <v>1167</v>
-      </c>
-      <c r="L223" t="s">
-        <v>19</v>
-      </c>
-      <c r="M223" t="s">
-        <v>326</v>
-      </c>
-      <c r="N223" t="s">
-        <v>1168</v>
-      </c>
-      <c r="O223" t="s">
-        <v>19</v>
-      </c>
-      <c r="P223" t="s">
-        <v>1169</v>
       </c>
     </row>
     <row r="224" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="B224" t="s">
-        <v>1075</v>
+        <v>1169</v>
       </c>
       <c r="C224" t="s">
         <v>18</v>
       </c>
-      <c r="D224" t="s">
-        <v>19</v>
-      </c>
-      <c r="E224" t="s">
-        <v>19</v>
+      <c r="D224" t="b">
+        <v>0</v>
+      </c>
+      <c r="E224">
+        <v>0</v>
       </c>
       <c r="F224" t="s">
         <v>19</v>
@@ -15240,28 +15687,28 @@
         <v>0</v>
       </c>
       <c r="I224" t="s">
-        <v>1136</v>
+        <v>66</v>
       </c>
       <c r="J224" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="K224" t="s">
+        <v>1170</v>
+      </c>
+      <c r="L224" t="b">
+        <v>0</v>
+      </c>
+      <c r="M224" t="s">
+        <v>22</v>
+      </c>
+      <c r="N224" t="s">
         <v>1171</v>
       </c>
-      <c r="L224" t="s">
-        <v>19</v>
-      </c>
-      <c r="M224" t="s">
-        <v>22</v>
-      </c>
-      <c r="N224" t="s">
+      <c r="O224" t="s">
         <v>1172</v>
       </c>
-      <c r="O224" t="s">
+      <c r="P224" t="s">
         <v>1173</v>
-      </c>
-      <c r="P224" t="s">
-        <v>1169</v>
       </c>
     </row>
     <row r="225" spans="1:16" x14ac:dyDescent="0.25">
@@ -15269,16 +15716,16 @@
         <v>1174</v>
       </c>
       <c r="B225" t="s">
-        <v>1075</v>
+        <v>1175</v>
       </c>
       <c r="C225" t="s">
-        <v>18</v>
-      </c>
-      <c r="D225" t="s">
-        <v>19</v>
-      </c>
-      <c r="E225" t="s">
-        <v>19</v>
+        <v>129</v>
+      </c>
+      <c r="D225" t="b">
+        <v>0</v>
+      </c>
+      <c r="E225">
+        <v>2</v>
       </c>
       <c r="F225" t="s">
         <v>19</v>
@@ -15287,48 +15734,48 @@
         <v>19</v>
       </c>
       <c r="H225" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I225" t="s">
-        <v>1136</v>
+        <v>66</v>
       </c>
       <c r="J225" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="K225" t="s">
-        <v>1175</v>
-      </c>
-      <c r="L225" t="s">
-        <v>19</v>
+        <v>1176</v>
+      </c>
+      <c r="L225" t="b">
+        <v>1</v>
       </c>
       <c r="M225" t="s">
         <v>22</v>
       </c>
       <c r="N225" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="O225" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="P225" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="226" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B226" t="s">
-        <v>1075</v>
+        <v>1181</v>
       </c>
       <c r="C226" t="s">
         <v>18</v>
       </c>
-      <c r="D226" t="s">
-        <v>19</v>
-      </c>
-      <c r="E226" t="s">
-        <v>19</v>
+      <c r="D226" t="b">
+        <v>0</v>
+      </c>
+      <c r="E226">
+        <v>4</v>
       </c>
       <c r="F226" t="s">
         <v>19</v>
@@ -15337,39 +15784,39 @@
         <v>19</v>
       </c>
       <c r="H226" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I226" t="s">
-        <v>1136</v>
+        <v>66</v>
       </c>
       <c r="J226" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="K226" t="s">
-        <v>1180</v>
-      </c>
-      <c r="L226" t="s">
-        <v>19</v>
+        <v>1182</v>
+      </c>
+      <c r="L226" t="b">
+        <v>1</v>
       </c>
       <c r="M226" t="s">
         <v>22</v>
       </c>
       <c r="N226" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="O226" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="P226" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="227" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="B227" t="s">
-        <v>1075</v>
+        <v>1187</v>
       </c>
       <c r="C227" t="s">
         <v>18</v>
@@ -15387,16 +15834,16 @@
         <v>19</v>
       </c>
       <c r="H227" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I227" t="s">
-        <v>1136</v>
+        <v>18</v>
       </c>
       <c r="J227" t="s">
         <v>20</v>
       </c>
       <c r="K227" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="L227" t="s">
         <v>19</v>
@@ -15405,21 +15852,21 @@
         <v>22</v>
       </c>
       <c r="N227" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="O227" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="P227" t="s">
-        <v>1188</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="228" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
       <c r="B228" t="s">
-        <v>1075</v>
+        <v>1193</v>
       </c>
       <c r="C228" t="s">
         <v>18</v>
@@ -15437,16 +15884,16 @@
         <v>19</v>
       </c>
       <c r="H228" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I228" t="s">
-        <v>1136</v>
+        <v>18</v>
       </c>
       <c r="J228" t="s">
         <v>20</v>
       </c>
       <c r="K228" t="s">
-        <v>1190</v>
+        <v>1194</v>
       </c>
       <c r="L228" t="s">
         <v>19</v>
@@ -15455,30 +15902,30 @@
         <v>22</v>
       </c>
       <c r="N228" t="s">
-        <v>1191</v>
+        <v>1195</v>
       </c>
       <c r="O228" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="P228" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="229" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="B229" t="s">
-        <v>1075</v>
+        <v>1199</v>
       </c>
       <c r="C229" t="s">
-        <v>18</v>
-      </c>
-      <c r="D229" t="s">
-        <v>19</v>
-      </c>
-      <c r="E229" t="s">
-        <v>19</v>
+        <v>40</v>
+      </c>
+      <c r="D229" t="b">
+        <v>0</v>
+      </c>
+      <c r="E229">
+        <v>2</v>
       </c>
       <c r="F229" t="s">
         <v>19</v>
@@ -15490,45 +15937,45 @@
         <v>0</v>
       </c>
       <c r="I229" t="s">
-        <v>1136</v>
+        <v>66</v>
       </c>
       <c r="J229" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="K229" t="s">
-        <v>1195</v>
-      </c>
-      <c r="L229" t="s">
-        <v>19</v>
+        <v>1200</v>
+      </c>
+      <c r="L229" t="b">
+        <v>1</v>
       </c>
       <c r="M229" t="s">
         <v>22</v>
       </c>
       <c r="N229" t="s">
-        <v>1196</v>
+        <v>1201</v>
       </c>
       <c r="O229" t="s">
-        <v>1197</v>
+        <v>1202</v>
       </c>
       <c r="P229" t="s">
-        <v>1198</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="230" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>1199</v>
+        <v>1204</v>
       </c>
       <c r="B230" t="s">
-        <v>18</v>
+        <v>1205</v>
       </c>
       <c r="C230" t="s">
         <v>18</v>
       </c>
-      <c r="D230" t="b">
-        <v>0</v>
-      </c>
-      <c r="E230">
-        <v>14</v>
+      <c r="D230" t="s">
+        <v>19</v>
+      </c>
+      <c r="E230" t="s">
+        <v>19</v>
       </c>
       <c r="F230" t="s">
         <v>19</v>
@@ -15540,45 +15987,45 @@
         <v>0</v>
       </c>
       <c r="I230" t="s">
-        <v>41</v>
+        <v>980</v>
       </c>
       <c r="J230" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K230" t="s">
-        <v>1200</v>
-      </c>
-      <c r="L230" t="b">
-        <v>0</v>
+        <v>1206</v>
+      </c>
+      <c r="L230" t="s">
+        <v>19</v>
       </c>
       <c r="M230" t="s">
         <v>22</v>
       </c>
       <c r="N230" t="s">
-        <v>1201</v>
+        <v>1207</v>
       </c>
       <c r="O230" t="s">
-        <v>1202</v>
+        <v>1208</v>
       </c>
       <c r="P230" t="s">
-        <v>1203</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="231" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>1204</v>
+        <v>1210</v>
       </c>
       <c r="B231" t="s">
-        <v>1075</v>
+        <v>1211</v>
       </c>
       <c r="C231" t="s">
-        <v>18</v>
-      </c>
-      <c r="D231" t="s">
-        <v>19</v>
-      </c>
-      <c r="E231" t="s">
-        <v>19</v>
+        <v>1212</v>
+      </c>
+      <c r="D231" t="b">
+        <v>0</v>
+      </c>
+      <c r="E231">
+        <v>10</v>
       </c>
       <c r="F231" t="s">
         <v>19</v>
@@ -15587,48 +16034,48 @@
         <v>19</v>
       </c>
       <c r="H231" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I231" t="s">
-        <v>1136</v>
+        <v>66</v>
       </c>
       <c r="J231" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="K231" t="s">
-        <v>1205</v>
-      </c>
-      <c r="L231" t="s">
-        <v>19</v>
+        <v>1213</v>
+      </c>
+      <c r="L231" t="b">
+        <v>1</v>
       </c>
       <c r="M231" t="s">
         <v>22</v>
       </c>
       <c r="N231" t="s">
-        <v>1206</v>
+        <v>1214</v>
       </c>
       <c r="O231" t="s">
-        <v>1207</v>
+        <v>1215</v>
       </c>
       <c r="P231" t="s">
-        <v>1208</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="232" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>1209</v>
+        <v>1217</v>
       </c>
       <c r="B232" t="s">
-        <v>1210</v>
+        <v>1218</v>
       </c>
       <c r="C232" t="s">
-        <v>1211</v>
+        <v>1219</v>
       </c>
       <c r="D232" t="b">
         <v>0</v>
       </c>
       <c r="E232">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F232" t="s">
         <v>19</v>
@@ -15637,7 +16084,7 @@
         <v>19</v>
       </c>
       <c r="H232" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I232" t="s">
         <v>66</v>
@@ -15646,7 +16093,7 @@
         <v>42</v>
       </c>
       <c r="K232" t="s">
-        <v>1212</v>
+        <v>1220</v>
       </c>
       <c r="L232" t="b">
         <v>1</v>
@@ -15655,13 +16102,1413 @@
         <v>22</v>
       </c>
       <c r="N232" t="s">
-        <v>1213</v>
+        <v>1221</v>
       </c>
       <c r="O232" t="s">
-        <v>1214</v>
+        <v>1222</v>
       </c>
       <c r="P232" t="s">
-        <v>1215</v>
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="233" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B233" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C233" t="s">
+        <v>18</v>
+      </c>
+      <c r="D233" t="s">
+        <v>19</v>
+      </c>
+      <c r="E233" t="s">
+        <v>19</v>
+      </c>
+      <c r="F233" t="s">
+        <v>19</v>
+      </c>
+      <c r="G233" t="s">
+        <v>19</v>
+      </c>
+      <c r="H233" t="b">
+        <v>0</v>
+      </c>
+      <c r="I233" t="s">
+        <v>18</v>
+      </c>
+      <c r="J233" t="s">
+        <v>20</v>
+      </c>
+      <c r="K233" t="s">
+        <v>1226</v>
+      </c>
+      <c r="L233" t="s">
+        <v>19</v>
+      </c>
+      <c r="M233" t="s">
+        <v>22</v>
+      </c>
+      <c r="N233" t="s">
+        <v>1227</v>
+      </c>
+      <c r="O233" t="s">
+        <v>1228</v>
+      </c>
+      <c r="P233" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="234" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B234" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C234" t="s">
+        <v>18</v>
+      </c>
+      <c r="D234" t="s">
+        <v>19</v>
+      </c>
+      <c r="E234" t="s">
+        <v>19</v>
+      </c>
+      <c r="F234" t="s">
+        <v>19</v>
+      </c>
+      <c r="G234" t="s">
+        <v>19</v>
+      </c>
+      <c r="H234" t="b">
+        <v>0</v>
+      </c>
+      <c r="I234" t="s">
+        <v>18</v>
+      </c>
+      <c r="J234" t="s">
+        <v>20</v>
+      </c>
+      <c r="K234" t="s">
+        <v>1231</v>
+      </c>
+      <c r="L234" t="s">
+        <v>19</v>
+      </c>
+      <c r="M234" t="s">
+        <v>22</v>
+      </c>
+      <c r="N234" t="s">
+        <v>1232</v>
+      </c>
+      <c r="O234" t="s">
+        <v>1233</v>
+      </c>
+      <c r="P234" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="235" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B235" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C235" t="s">
+        <v>18</v>
+      </c>
+      <c r="D235" t="s">
+        <v>19</v>
+      </c>
+      <c r="E235" t="s">
+        <v>19</v>
+      </c>
+      <c r="F235" t="s">
+        <v>19</v>
+      </c>
+      <c r="G235" t="s">
+        <v>19</v>
+      </c>
+      <c r="H235" t="b">
+        <v>0</v>
+      </c>
+      <c r="I235" t="s">
+        <v>18</v>
+      </c>
+      <c r="J235" t="s">
+        <v>20</v>
+      </c>
+      <c r="K235" t="s">
+        <v>1236</v>
+      </c>
+      <c r="L235" t="s">
+        <v>19</v>
+      </c>
+      <c r="M235" t="s">
+        <v>22</v>
+      </c>
+      <c r="N235" t="s">
+        <v>1237</v>
+      </c>
+      <c r="O235" t="s">
+        <v>1238</v>
+      </c>
+      <c r="P235" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="236" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B236" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C236" t="s">
+        <v>18</v>
+      </c>
+      <c r="D236" t="s">
+        <v>19</v>
+      </c>
+      <c r="E236" t="s">
+        <v>19</v>
+      </c>
+      <c r="F236" t="s">
+        <v>19</v>
+      </c>
+      <c r="G236" t="s">
+        <v>19</v>
+      </c>
+      <c r="H236" t="b">
+        <v>0</v>
+      </c>
+      <c r="I236" t="s">
+        <v>18</v>
+      </c>
+      <c r="J236" t="s">
+        <v>20</v>
+      </c>
+      <c r="K236" t="s">
+        <v>1241</v>
+      </c>
+      <c r="L236" t="s">
+        <v>19</v>
+      </c>
+      <c r="M236" t="s">
+        <v>22</v>
+      </c>
+      <c r="N236" t="s">
+        <v>1242</v>
+      </c>
+      <c r="O236" t="s">
+        <v>1243</v>
+      </c>
+      <c r="P236" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="237" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B237" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C237" t="s">
+        <v>18</v>
+      </c>
+      <c r="D237" t="s">
+        <v>19</v>
+      </c>
+      <c r="E237" t="s">
+        <v>19</v>
+      </c>
+      <c r="F237" t="s">
+        <v>19</v>
+      </c>
+      <c r="G237" t="s">
+        <v>19</v>
+      </c>
+      <c r="H237" t="b">
+        <v>0</v>
+      </c>
+      <c r="I237" t="s">
+        <v>18</v>
+      </c>
+      <c r="J237" t="s">
+        <v>20</v>
+      </c>
+      <c r="K237" t="s">
+        <v>1246</v>
+      </c>
+      <c r="L237" t="s">
+        <v>19</v>
+      </c>
+      <c r="M237" t="s">
+        <v>22</v>
+      </c>
+      <c r="N237" t="s">
+        <v>1247</v>
+      </c>
+      <c r="O237" t="s">
+        <v>1248</v>
+      </c>
+      <c r="P237" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="238" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B238" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C238" t="s">
+        <v>18</v>
+      </c>
+      <c r="D238" t="s">
+        <v>19</v>
+      </c>
+      <c r="E238" t="s">
+        <v>19</v>
+      </c>
+      <c r="F238" t="s">
+        <v>19</v>
+      </c>
+      <c r="G238" t="s">
+        <v>19</v>
+      </c>
+      <c r="H238" t="b">
+        <v>0</v>
+      </c>
+      <c r="I238" t="s">
+        <v>18</v>
+      </c>
+      <c r="J238" t="s">
+        <v>20</v>
+      </c>
+      <c r="K238" t="s">
+        <v>1251</v>
+      </c>
+      <c r="L238" t="s">
+        <v>19</v>
+      </c>
+      <c r="M238" t="s">
+        <v>22</v>
+      </c>
+      <c r="N238" t="s">
+        <v>1252</v>
+      </c>
+      <c r="O238" t="s">
+        <v>1253</v>
+      </c>
+      <c r="P238" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="239" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B239" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C239" t="s">
+        <v>18</v>
+      </c>
+      <c r="D239" t="s">
+        <v>19</v>
+      </c>
+      <c r="E239" t="s">
+        <v>19</v>
+      </c>
+      <c r="F239" t="s">
+        <v>19</v>
+      </c>
+      <c r="G239" t="s">
+        <v>19</v>
+      </c>
+      <c r="H239" t="b">
+        <v>0</v>
+      </c>
+      <c r="I239" t="s">
+        <v>18</v>
+      </c>
+      <c r="J239" t="s">
+        <v>20</v>
+      </c>
+      <c r="K239" t="s">
+        <v>1256</v>
+      </c>
+      <c r="L239" t="s">
+        <v>19</v>
+      </c>
+      <c r="M239" t="s">
+        <v>22</v>
+      </c>
+      <c r="N239" t="s">
+        <v>1257</v>
+      </c>
+      <c r="O239" t="s">
+        <v>1258</v>
+      </c>
+      <c r="P239" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="240" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B240" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C240" t="s">
+        <v>18</v>
+      </c>
+      <c r="D240" t="s">
+        <v>19</v>
+      </c>
+      <c r="E240" t="s">
+        <v>19</v>
+      </c>
+      <c r="F240" t="s">
+        <v>19</v>
+      </c>
+      <c r="G240" t="s">
+        <v>19</v>
+      </c>
+      <c r="H240" t="b">
+        <v>0</v>
+      </c>
+      <c r="I240" t="s">
+        <v>18</v>
+      </c>
+      <c r="J240" t="s">
+        <v>20</v>
+      </c>
+      <c r="K240" t="s">
+        <v>1261</v>
+      </c>
+      <c r="L240" t="s">
+        <v>19</v>
+      </c>
+      <c r="M240" t="s">
+        <v>22</v>
+      </c>
+      <c r="N240" t="s">
+        <v>1262</v>
+      </c>
+      <c r="O240" t="s">
+        <v>1263</v>
+      </c>
+      <c r="P240" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="241" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B241" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C241" t="s">
+        <v>18</v>
+      </c>
+      <c r="D241" t="s">
+        <v>19</v>
+      </c>
+      <c r="E241" t="s">
+        <v>19</v>
+      </c>
+      <c r="F241" t="s">
+        <v>19</v>
+      </c>
+      <c r="G241" t="s">
+        <v>19</v>
+      </c>
+      <c r="H241" t="b">
+        <v>0</v>
+      </c>
+      <c r="I241" t="s">
+        <v>18</v>
+      </c>
+      <c r="J241" t="s">
+        <v>20</v>
+      </c>
+      <c r="K241" t="s">
+        <v>1266</v>
+      </c>
+      <c r="L241" t="s">
+        <v>19</v>
+      </c>
+      <c r="M241" t="s">
+        <v>22</v>
+      </c>
+      <c r="N241" t="s">
+        <v>1267</v>
+      </c>
+      <c r="O241" t="s">
+        <v>1268</v>
+      </c>
+      <c r="P241" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="242" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B242" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C242" t="s">
+        <v>18</v>
+      </c>
+      <c r="D242" t="s">
+        <v>19</v>
+      </c>
+      <c r="E242" t="s">
+        <v>19</v>
+      </c>
+      <c r="F242" t="s">
+        <v>19</v>
+      </c>
+      <c r="G242" t="s">
+        <v>19</v>
+      </c>
+      <c r="H242" t="b">
+        <v>0</v>
+      </c>
+      <c r="I242" t="s">
+        <v>18</v>
+      </c>
+      <c r="J242" t="s">
+        <v>20</v>
+      </c>
+      <c r="K242" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L242" t="s">
+        <v>19</v>
+      </c>
+      <c r="M242" t="s">
+        <v>22</v>
+      </c>
+      <c r="N242" t="s">
+        <v>1272</v>
+      </c>
+      <c r="O242" t="s">
+        <v>1273</v>
+      </c>
+      <c r="P242" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="243" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B243" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C243" t="s">
+        <v>18</v>
+      </c>
+      <c r="D243" t="s">
+        <v>19</v>
+      </c>
+      <c r="E243" t="s">
+        <v>19</v>
+      </c>
+      <c r="F243" t="s">
+        <v>19</v>
+      </c>
+      <c r="G243" t="s">
+        <v>19</v>
+      </c>
+      <c r="H243" t="b">
+        <v>0</v>
+      </c>
+      <c r="I243" t="s">
+        <v>18</v>
+      </c>
+      <c r="J243" t="s">
+        <v>20</v>
+      </c>
+      <c r="K243" t="s">
+        <v>1276</v>
+      </c>
+      <c r="L243" t="s">
+        <v>19</v>
+      </c>
+      <c r="M243" t="s">
+        <v>22</v>
+      </c>
+      <c r="N243" t="s">
+        <v>1277</v>
+      </c>
+      <c r="O243" t="s">
+        <v>1278</v>
+      </c>
+      <c r="P243" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="244" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B244" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C244" t="s">
+        <v>18</v>
+      </c>
+      <c r="D244" t="s">
+        <v>19</v>
+      </c>
+      <c r="E244" t="s">
+        <v>19</v>
+      </c>
+      <c r="F244" t="s">
+        <v>19</v>
+      </c>
+      <c r="G244" t="s">
+        <v>19</v>
+      </c>
+      <c r="H244" t="b">
+        <v>0</v>
+      </c>
+      <c r="I244" t="s">
+        <v>18</v>
+      </c>
+      <c r="J244" t="s">
+        <v>20</v>
+      </c>
+      <c r="K244" t="s">
+        <v>1281</v>
+      </c>
+      <c r="L244" t="s">
+        <v>19</v>
+      </c>
+      <c r="M244" t="s">
+        <v>22</v>
+      </c>
+      <c r="N244" t="s">
+        <v>1282</v>
+      </c>
+      <c r="O244" t="s">
+        <v>1283</v>
+      </c>
+      <c r="P244" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="245" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B245" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C245" t="s">
+        <v>18</v>
+      </c>
+      <c r="D245" t="s">
+        <v>19</v>
+      </c>
+      <c r="E245" t="s">
+        <v>19</v>
+      </c>
+      <c r="F245" t="s">
+        <v>19</v>
+      </c>
+      <c r="G245" t="s">
+        <v>19</v>
+      </c>
+      <c r="H245" t="b">
+        <v>0</v>
+      </c>
+      <c r="I245" t="s">
+        <v>980</v>
+      </c>
+      <c r="J245" t="s">
+        <v>20</v>
+      </c>
+      <c r="K245" t="s">
+        <v>1286</v>
+      </c>
+      <c r="L245" t="s">
+        <v>19</v>
+      </c>
+      <c r="M245" t="s">
+        <v>22</v>
+      </c>
+      <c r="N245" t="s">
+        <v>1287</v>
+      </c>
+      <c r="O245" t="s">
+        <v>1288</v>
+      </c>
+      <c r="P245" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="246" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B246" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C246" t="s">
+        <v>18</v>
+      </c>
+      <c r="D246" t="s">
+        <v>19</v>
+      </c>
+      <c r="E246" t="s">
+        <v>19</v>
+      </c>
+      <c r="F246" t="s">
+        <v>19</v>
+      </c>
+      <c r="G246" t="s">
+        <v>19</v>
+      </c>
+      <c r="H246" t="b">
+        <v>0</v>
+      </c>
+      <c r="I246" t="s">
+        <v>980</v>
+      </c>
+      <c r="J246" t="s">
+        <v>20</v>
+      </c>
+      <c r="K246" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L246" t="s">
+        <v>19</v>
+      </c>
+      <c r="M246" t="s">
+        <v>22</v>
+      </c>
+      <c r="N246" t="s">
+        <v>1292</v>
+      </c>
+      <c r="O246" t="s">
+        <v>1293</v>
+      </c>
+      <c r="P246" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="247" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B247" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C247" t="s">
+        <v>18</v>
+      </c>
+      <c r="D247" t="s">
+        <v>19</v>
+      </c>
+      <c r="E247" t="s">
+        <v>19</v>
+      </c>
+      <c r="F247" t="s">
+        <v>19</v>
+      </c>
+      <c r="G247" t="s">
+        <v>19</v>
+      </c>
+      <c r="H247" t="b">
+        <v>0</v>
+      </c>
+      <c r="I247" t="s">
+        <v>980</v>
+      </c>
+      <c r="J247" t="s">
+        <v>20</v>
+      </c>
+      <c r="K247" t="s">
+        <v>1296</v>
+      </c>
+      <c r="L247" t="s">
+        <v>19</v>
+      </c>
+      <c r="M247" t="s">
+        <v>22</v>
+      </c>
+      <c r="N247" t="s">
+        <v>1297</v>
+      </c>
+      <c r="O247" t="s">
+        <v>1298</v>
+      </c>
+      <c r="P247" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="248" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B248" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C248" t="s">
+        <v>18</v>
+      </c>
+      <c r="D248" t="s">
+        <v>19</v>
+      </c>
+      <c r="E248" t="s">
+        <v>19</v>
+      </c>
+      <c r="F248" t="s">
+        <v>19</v>
+      </c>
+      <c r="G248" t="s">
+        <v>19</v>
+      </c>
+      <c r="H248" t="b">
+        <v>0</v>
+      </c>
+      <c r="I248" t="s">
+        <v>980</v>
+      </c>
+      <c r="J248" t="s">
+        <v>20</v>
+      </c>
+      <c r="K248" t="s">
+        <v>1301</v>
+      </c>
+      <c r="L248" t="s">
+        <v>19</v>
+      </c>
+      <c r="M248" t="s">
+        <v>22</v>
+      </c>
+      <c r="N248" t="s">
+        <v>1302</v>
+      </c>
+      <c r="O248" t="s">
+        <v>1303</v>
+      </c>
+      <c r="P248" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="249" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B249" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C249" t="s">
+        <v>18</v>
+      </c>
+      <c r="D249" t="s">
+        <v>19</v>
+      </c>
+      <c r="E249" t="s">
+        <v>19</v>
+      </c>
+      <c r="F249" t="s">
+        <v>19</v>
+      </c>
+      <c r="G249" t="s">
+        <v>19</v>
+      </c>
+      <c r="H249" t="b">
+        <v>0</v>
+      </c>
+      <c r="I249" t="s">
+        <v>980</v>
+      </c>
+      <c r="J249" t="s">
+        <v>20</v>
+      </c>
+      <c r="K249" t="s">
+        <v>1306</v>
+      </c>
+      <c r="L249" t="s">
+        <v>19</v>
+      </c>
+      <c r="M249" t="s">
+        <v>22</v>
+      </c>
+      <c r="N249" t="s">
+        <v>1307</v>
+      </c>
+      <c r="O249" t="s">
+        <v>1308</v>
+      </c>
+      <c r="P249" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="250" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B250" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C250" t="s">
+        <v>18</v>
+      </c>
+      <c r="D250" t="s">
+        <v>19</v>
+      </c>
+      <c r="E250" t="s">
+        <v>19</v>
+      </c>
+      <c r="F250" t="s">
+        <v>19</v>
+      </c>
+      <c r="G250" t="s">
+        <v>19</v>
+      </c>
+      <c r="H250" t="b">
+        <v>0</v>
+      </c>
+      <c r="I250" t="s">
+        <v>18</v>
+      </c>
+      <c r="J250" t="s">
+        <v>20</v>
+      </c>
+      <c r="K250" t="s">
+        <v>1311</v>
+      </c>
+      <c r="L250" t="s">
+        <v>19</v>
+      </c>
+      <c r="M250" t="s">
+        <v>22</v>
+      </c>
+      <c r="N250" t="s">
+        <v>1312</v>
+      </c>
+      <c r="O250" t="s">
+        <v>1313</v>
+      </c>
+      <c r="P250" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="251" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B251" t="s">
+        <v>19</v>
+      </c>
+      <c r="C251" t="s">
+        <v>19</v>
+      </c>
+      <c r="D251" t="s">
+        <v>19</v>
+      </c>
+      <c r="E251" t="s">
+        <v>19</v>
+      </c>
+      <c r="F251" t="s">
+        <v>323</v>
+      </c>
+      <c r="G251" t="s">
+        <v>324</v>
+      </c>
+      <c r="H251" t="s">
+        <v>19</v>
+      </c>
+      <c r="I251" t="s">
+        <v>19</v>
+      </c>
+      <c r="J251" t="s">
+        <v>19</v>
+      </c>
+      <c r="K251" t="s">
+        <v>1316</v>
+      </c>
+      <c r="L251" t="s">
+        <v>19</v>
+      </c>
+      <c r="M251" t="s">
+        <v>326</v>
+      </c>
+      <c r="N251" t="s">
+        <v>1317</v>
+      </c>
+      <c r="O251" t="s">
+        <v>19</v>
+      </c>
+      <c r="P251" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="252" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B252" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C252" t="s">
+        <v>18</v>
+      </c>
+      <c r="D252" t="s">
+        <v>19</v>
+      </c>
+      <c r="E252" t="s">
+        <v>19</v>
+      </c>
+      <c r="F252" t="s">
+        <v>19</v>
+      </c>
+      <c r="G252" t="s">
+        <v>19</v>
+      </c>
+      <c r="H252" t="b">
+        <v>0</v>
+      </c>
+      <c r="I252" t="s">
+        <v>980</v>
+      </c>
+      <c r="J252" t="s">
+        <v>20</v>
+      </c>
+      <c r="K252" t="s">
+        <v>1320</v>
+      </c>
+      <c r="L252" t="s">
+        <v>19</v>
+      </c>
+      <c r="M252" t="s">
+        <v>22</v>
+      </c>
+      <c r="N252" t="s">
+        <v>1321</v>
+      </c>
+      <c r="O252" t="s">
+        <v>1322</v>
+      </c>
+      <c r="P252" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="253" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B253" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C253" t="s">
+        <v>18</v>
+      </c>
+      <c r="D253" t="s">
+        <v>19</v>
+      </c>
+      <c r="E253" t="s">
+        <v>19</v>
+      </c>
+      <c r="F253" t="s">
+        <v>19</v>
+      </c>
+      <c r="G253" t="s">
+        <v>19</v>
+      </c>
+      <c r="H253" t="b">
+        <v>0</v>
+      </c>
+      <c r="I253" t="s">
+        <v>980</v>
+      </c>
+      <c r="J253" t="s">
+        <v>20</v>
+      </c>
+      <c r="K253" t="s">
+        <v>1324</v>
+      </c>
+      <c r="L253" t="s">
+        <v>19</v>
+      </c>
+      <c r="M253" t="s">
+        <v>22</v>
+      </c>
+      <c r="N253" t="s">
+        <v>1325</v>
+      </c>
+      <c r="O253" t="s">
+        <v>1326</v>
+      </c>
+      <c r="P253" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="254" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B254" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C254" t="s">
+        <v>18</v>
+      </c>
+      <c r="D254" t="s">
+        <v>19</v>
+      </c>
+      <c r="E254" t="s">
+        <v>19</v>
+      </c>
+      <c r="F254" t="s">
+        <v>19</v>
+      </c>
+      <c r="G254" t="s">
+        <v>19</v>
+      </c>
+      <c r="H254" t="b">
+        <v>0</v>
+      </c>
+      <c r="I254" t="s">
+        <v>980</v>
+      </c>
+      <c r="J254" t="s">
+        <v>20</v>
+      </c>
+      <c r="K254" t="s">
+        <v>1329</v>
+      </c>
+      <c r="L254" t="s">
+        <v>19</v>
+      </c>
+      <c r="M254" t="s">
+        <v>22</v>
+      </c>
+      <c r="N254" t="s">
+        <v>1330</v>
+      </c>
+      <c r="O254" t="s">
+        <v>1331</v>
+      </c>
+      <c r="P254" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="255" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B255" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C255" t="s">
+        <v>18</v>
+      </c>
+      <c r="D255" t="s">
+        <v>19</v>
+      </c>
+      <c r="E255" t="s">
+        <v>19</v>
+      </c>
+      <c r="F255" t="s">
+        <v>19</v>
+      </c>
+      <c r="G255" t="s">
+        <v>19</v>
+      </c>
+      <c r="H255" t="b">
+        <v>0</v>
+      </c>
+      <c r="I255" t="s">
+        <v>980</v>
+      </c>
+      <c r="J255" t="s">
+        <v>20</v>
+      </c>
+      <c r="K255" t="s">
+        <v>1334</v>
+      </c>
+      <c r="L255" t="s">
+        <v>19</v>
+      </c>
+      <c r="M255" t="s">
+        <v>22</v>
+      </c>
+      <c r="N255" t="s">
+        <v>1335</v>
+      </c>
+      <c r="O255" t="s">
+        <v>1336</v>
+      </c>
+      <c r="P255" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="256" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B256" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C256" t="s">
+        <v>18</v>
+      </c>
+      <c r="D256" t="s">
+        <v>19</v>
+      </c>
+      <c r="E256" t="s">
+        <v>19</v>
+      </c>
+      <c r="F256" t="s">
+        <v>19</v>
+      </c>
+      <c r="G256" t="s">
+        <v>19</v>
+      </c>
+      <c r="H256" t="b">
+        <v>0</v>
+      </c>
+      <c r="I256" t="s">
+        <v>980</v>
+      </c>
+      <c r="J256" t="s">
+        <v>20</v>
+      </c>
+      <c r="K256" t="s">
+        <v>1339</v>
+      </c>
+      <c r="L256" t="s">
+        <v>19</v>
+      </c>
+      <c r="M256" t="s">
+        <v>22</v>
+      </c>
+      <c r="N256" t="s">
+        <v>1340</v>
+      </c>
+      <c r="O256" t="s">
+        <v>1341</v>
+      </c>
+      <c r="P256" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="257" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B257" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C257" t="s">
+        <v>18</v>
+      </c>
+      <c r="D257" t="s">
+        <v>19</v>
+      </c>
+      <c r="E257" t="s">
+        <v>19</v>
+      </c>
+      <c r="F257" t="s">
+        <v>19</v>
+      </c>
+      <c r="G257" t="s">
+        <v>19</v>
+      </c>
+      <c r="H257" t="b">
+        <v>0</v>
+      </c>
+      <c r="I257" t="s">
+        <v>980</v>
+      </c>
+      <c r="J257" t="s">
+        <v>20</v>
+      </c>
+      <c r="K257" t="s">
+        <v>1344</v>
+      </c>
+      <c r="L257" t="s">
+        <v>19</v>
+      </c>
+      <c r="M257" t="s">
+        <v>22</v>
+      </c>
+      <c r="N257" t="s">
+        <v>1345</v>
+      </c>
+      <c r="O257" t="s">
+        <v>1346</v>
+      </c>
+      <c r="P257" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="258" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B258" t="s">
+        <v>18</v>
+      </c>
+      <c r="C258" t="s">
+        <v>18</v>
+      </c>
+      <c r="D258" t="b">
+        <v>0</v>
+      </c>
+      <c r="E258">
+        <v>14</v>
+      </c>
+      <c r="F258" t="s">
+        <v>19</v>
+      </c>
+      <c r="G258" t="s">
+        <v>19</v>
+      </c>
+      <c r="H258" t="b">
+        <v>0</v>
+      </c>
+      <c r="I258" t="s">
+        <v>41</v>
+      </c>
+      <c r="J258" t="s">
+        <v>42</v>
+      </c>
+      <c r="K258" t="s">
+        <v>1349</v>
+      </c>
+      <c r="L258" t="b">
+        <v>0</v>
+      </c>
+      <c r="M258" t="s">
+        <v>22</v>
+      </c>
+      <c r="N258" t="s">
+        <v>1350</v>
+      </c>
+      <c r="O258" t="s">
+        <v>1351</v>
+      </c>
+      <c r="P258" t="s">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="259" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B259" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C259" t="s">
+        <v>18</v>
+      </c>
+      <c r="D259" t="s">
+        <v>19</v>
+      </c>
+      <c r="E259" t="s">
+        <v>19</v>
+      </c>
+      <c r="F259" t="s">
+        <v>19</v>
+      </c>
+      <c r="G259" t="s">
+        <v>19</v>
+      </c>
+      <c r="H259" t="b">
+        <v>0</v>
+      </c>
+      <c r="I259" t="s">
+        <v>980</v>
+      </c>
+      <c r="J259" t="s">
+        <v>20</v>
+      </c>
+      <c r="K259" t="s">
+        <v>1354</v>
+      </c>
+      <c r="L259" t="s">
+        <v>19</v>
+      </c>
+      <c r="M259" t="s">
+        <v>22</v>
+      </c>
+      <c r="N259" t="s">
+        <v>1355</v>
+      </c>
+      <c r="O259" t="s">
+        <v>1356</v>
+      </c>
+      <c r="P259" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="260" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B260" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C260" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D260" t="b">
+        <v>0</v>
+      </c>
+      <c r="E260">
+        <v>4</v>
+      </c>
+      <c r="F260" t="s">
+        <v>19</v>
+      </c>
+      <c r="G260" t="s">
+        <v>19</v>
+      </c>
+      <c r="H260" t="b">
+        <v>0</v>
+      </c>
+      <c r="I260" t="s">
+        <v>66</v>
+      </c>
+      <c r="J260" t="s">
+        <v>42</v>
+      </c>
+      <c r="K260" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L260" t="b">
+        <v>1</v>
+      </c>
+      <c r="M260" t="s">
+        <v>22</v>
+      </c>
+      <c r="N260" t="s">
+        <v>1362</v>
+      </c>
+      <c r="O260" t="s">
+        <v>1363</v>
+      </c>
+      <c r="P260" t="s">
+        <v>1364</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-grace-master.report.xlsx
+++ b/tools/importer/reports/import-grace-master.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3663" uniqueCount="1365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3663" uniqueCount="1367">
   <si>
     <t>_reportFile</t>
   </si>
@@ -2955,682 +2955,688 @@
     <t>["hero-banner","cards-featured-content"]</t>
   </si>
   <si>
+    <t>["template","contactus","contactus-tagline","breadcrumb"]</t>
+  </si>
+  <si>
+    <t>products/activators-custom-organoborate-boron-compounds</t>
+  </si>
+  <si>
+    <t>2026-08-09T21:24:21.589Z</t>
+  </si>
+  <si>
+    <t>Activators Custom Organoborate/Boron Compounds</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/activators-custom-organoborate-boron-compounds/</t>
+  </si>
+  <si>
+    <t>products/activcat-catalysts.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","video-overlay","cards-featured-content"]</t>
+  </si>
+  <si>
+    <t>products/activcat-catalysts</t>
+  </si>
+  <si>
+    <t>2026-08-09T21:25:15.988Z</t>
+  </si>
+  <si>
+    <t>ActivCat® Catalysts</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/activcat-catalysts/</t>
+  </si>
+  <si>
+    <t>products/adsorbents.report.json</t>
+  </si>
+  <si>
+    <t>products/adsorbents</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:02:34.956Z</t>
+  </si>
+  <si>
+    <t>Adsorbents</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/adsorbents/</t>
+  </si>
+  <si>
+    <t>products/catalysts.report.json</t>
+  </si>
+  <si>
+    <t>products/catalysts</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:03:30.004Z</t>
+  </si>
+  <si>
+    <t>Catalysts</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/catalysts/</t>
+  </si>
+  <si>
+    <t>products/consista.report.json</t>
+  </si>
+  <si>
+    <t>products/consista</t>
+  </si>
+  <si>
+    <t>2026-08-09T21:26:10.006Z</t>
+  </si>
+  <si>
+    <t>CONSISTA®</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/consista/</t>
+  </si>
+  <si>
+    <t>products/davisil.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","table-two-column-content","table-two-column-content","cards-featured-content"]</t>
+  </si>
+  <si>
+    <t>["template","contactus","breadcrumb"]</t>
+  </si>
+  <si>
+    <t>products/davisil</t>
+  </si>
+  <si>
+    <t>2026-08-09T21:27:03.670Z</t>
+  </si>
+  <si>
+    <t>DAVISIL®</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/davisil/</t>
+  </si>
+  <si>
+    <t>products/fine-chemicals.report.json</t>
+  </si>
+  <si>
+    <t>products/fine-chemicals</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:06:16.549Z</t>
+  </si>
+  <si>
+    <t>Fine Chemicals</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/fine-chemicals/</t>
+  </si>
+  <si>
+    <t>products/hyampp-catalysts-and-donors.report.json</t>
+  </si>
+  <si>
+    <t>products/hyampp-catalysts-and-donors</t>
+  </si>
+  <si>
+    <t>2026-08-09T21:27:58.166Z</t>
+  </si>
+  <si>
+    <t>HYAMPP® Catalysts and Donors</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/hyampp-catalysts-and-donors/</t>
+  </si>
+  <si>
+    <t>products/ludox.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-horizontal-teaser","cards-featured-content"]</t>
+  </si>
+  <si>
+    <t>products/ludox</t>
+  </si>
+  <si>
+    <t>2026-08-09T21:28:50.808Z</t>
+  </si>
+  <si>
+    <t>LUDOX®</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/ludox/</t>
+  </si>
+  <si>
+    <t>products/lynx-pe.report.json</t>
+  </si>
+  <si>
+    <t>products/lynx-pe</t>
+  </si>
+  <si>
+    <t>2026-08-09T21:29:43.704Z</t>
+  </si>
+  <si>
+    <t>LYNX® PE</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/lynx-pe/</t>
+  </si>
+  <si>
+    <t>products/lynx-pp.report.json</t>
+  </si>
+  <si>
+    <t>products/lynx-pp</t>
+  </si>
+  <si>
+    <t>2026-08-09T21:30:37.237Z</t>
+  </si>
+  <si>
+    <t>LYNX® PP</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/lynx-pp/</t>
+  </si>
+  <si>
+    <t>products/magnapore.report.json</t>
+  </si>
+  <si>
+    <t>products/magnapore</t>
+  </si>
+  <si>
+    <t>2026-08-09T21:31:30.171Z</t>
+  </si>
+  <si>
+    <t>MAGNAPORE®</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/magnapore/</t>
+  </si>
+  <si>
+    <t>products/metallocenes.report.json</t>
+  </si>
+  <si>
+    <t>products/metallocenes</t>
+  </si>
+  <si>
+    <t>2026-08-09T21:32:23.242Z</t>
+  </si>
+  <si>
+    <t>Metallocenes</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/metallocenes/</t>
+  </si>
+  <si>
+    <t>products/polytrak-catalysts.report.json</t>
+  </si>
+  <si>
+    <t>products/polytrak-catalysts</t>
+  </si>
+  <si>
+    <t>2026-08-09T21:33:17.355Z</t>
+  </si>
+  <si>
+    <t>POLYTRAK® Catalysts</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/polytrak-catalysts/</t>
+  </si>
+  <si>
+    <t>products/product-stewardship.report.json</t>
+  </si>
+  <si>
+    <t>["table-two-column-content"]</t>
+  </si>
+  <si>
+    <t>products/product-stewardship</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:05:19.428Z</t>
+  </si>
+  <si>
+    <t>Product Stewardship</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/product-stewardship/</t>
+  </si>
+  <si>
+    <t>products/quality-management.report.json</t>
+  </si>
+  <si>
+    <t>products/quality-management</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:06:14.628Z</t>
+  </si>
+  <si>
+    <t>Quality</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/quality-management/</t>
+  </si>
+  <si>
+    <t>products/reflectn-digital-plant-simulator-software.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-horizontal-teaser","cards-featured-content","social-follow","banner-contact-split","table-two-column-content","table-two-column-content"]</t>
+  </si>
+  <si>
+    <t>products/reflectn-digital-plant-simulator-software</t>
+  </si>
+  <si>
+    <t>2026-08-09T21:34:51.783Z</t>
+  </si>
+  <si>
+    <t>REFLECTN™ Digital Plant Simulator Software</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/reflectn-digital-plant-simulator-software/</t>
+  </si>
+  <si>
+    <t>products/shac.report.json</t>
+  </si>
+  <si>
+    <t>products/shac</t>
+  </si>
+  <si>
+    <t>2026-08-09T21:35:45.479Z</t>
+  </si>
+  <si>
+    <t>SHAC®</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/shac/</t>
+  </si>
+  <si>
+    <t>products/shieldex.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-brochure-promo","columns-horizontal-teaser-featured","cards-featured-content"]</t>
+  </si>
+  <si>
+    <t>products/shieldex</t>
+  </si>
+  <si>
+    <t>2026-08-09T21:36:39.463Z</t>
+  </si>
+  <si>
+    <t>SHIELDEX® Anti-Corrosive Pigments</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/shieldex/</t>
+  </si>
+  <si>
+    <t>products/silsol.report.json</t>
+  </si>
+  <si>
+    <t>products/silsol</t>
+  </si>
+  <si>
+    <t>2026-08-09T21:37:32.632Z</t>
+  </si>
+  <si>
+    <t>SILSOL®</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/silsol/</t>
+  </si>
+  <si>
+    <t>products/syloid-mx-silica-series.report.json</t>
+  </si>
+  <si>
+    <t>products/syloid-mx-silica-series</t>
+  </si>
+  <si>
+    <t>2026-08-09T21:38:26.743Z</t>
+  </si>
+  <si>
+    <t>SYLOID® MX Silica Matting Agents for Coatings</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/syloid-mx-silica-series/</t>
+  </si>
+  <si>
+    <t>products/syloid-rad-silica-series.report.json</t>
+  </si>
+  <si>
+    <t>products/syloid-rad-silica-series</t>
+  </si>
+  <si>
+    <t>2026-08-09T21:39:20.631Z</t>
+  </si>
+  <si>
+    <t>SYLOID® RAD Silica Series</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/syloid-rad-silica-series/</t>
+  </si>
+  <si>
+    <t>products/syloid-silica.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","video-overlay","columns-horizontal-teaser","cards-featured-content"]</t>
+  </si>
+  <si>
+    <t>products/syloid-silica</t>
+  </si>
+  <si>
+    <t>2026-08-09T21:40:13.804Z</t>
+  </si>
+  <si>
+    <t>SYLOID® Silica</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/syloid-silica/</t>
+  </si>
+  <si>
+    <t>products/syloid-xdp-f-silica.report.json</t>
+  </si>
+  <si>
+    <t>products/syloid-xdp-f-silica</t>
+  </si>
+  <si>
+    <t>2026-08-09T21:42:17.894Z</t>
+  </si>
+  <si>
+    <t>SYLOID® XDP F Silica for Nutraceutical Formulators</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/syloid-xdp-f-silica/</t>
+  </si>
+  <si>
+    <t>products/sylopol-cr-catalysts.report.json</t>
+  </si>
+  <si>
+    <t>products/sylopol-cr-catalysts</t>
+  </si>
+  <si>
+    <t>2026-08-09T21:43:11.737Z</t>
+  </si>
+  <si>
+    <t>SYLOPOL® CR Catalysts</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/sylopol-cr-catalysts/</t>
+  </si>
+  <si>
+    <t>products/sylopol-zn-catalysts.report.json</t>
+  </si>
+  <si>
+    <t>products/sylopol-zn-catalysts</t>
+  </si>
+  <si>
+    <t>2026-08-09T21:44:04.621Z</t>
+  </si>
+  <si>
+    <t>SYLOPOL® ZN Catalysts</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/sylopol-zn-catalysts/</t>
+  </si>
+  <si>
+    <t>products/sylosiv.report.json</t>
+  </si>
+  <si>
+    <t>products/sylosiv</t>
+  </si>
+  <si>
+    <t>2026-08-09T21:44:59.032Z</t>
+  </si>
+  <si>
+    <t>SYLOSIV®</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/sylosiv/</t>
+  </si>
+  <si>
+    <t>products/synthetic-silicas.report.json</t>
+  </si>
+  <si>
+    <t>products/synthetic-silicas</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:00:44.459Z</t>
+  </si>
+  <si>
+    <t>Synthetic Silicas</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/synthetic-silicas/</t>
+  </si>
+  <si>
+    <t>products/trisyl-silica.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","video-overlay","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq","columns-horizontal-teaser","cards-featured-content"]</t>
+  </si>
+  <si>
+    <t>products/trisyl-silica</t>
+  </si>
+  <si>
+    <t>2026-08-09T21:45:52.611Z</t>
+  </si>
+  <si>
+    <t>TRISYL® Silica</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/trisyl-silica/</t>
+  </si>
+  <si>
+    <t>products/trisyl-xge-catalyst.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","video-overlay","cards-product","accordion-faq"]</t>
+  </si>
+  <si>
+    <t>products/trisyl-xge-catalyst</t>
+  </si>
+  <si>
+    <t>2026-08-09T21:52:01.687Z</t>
+  </si>
+  <si>
+    <t>TRISYL® XGE Catalyst</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/TRISYL-XGE-Catalyst/</t>
+  </si>
+  <si>
+    <t>products/unipol-donors.report.json</t>
+  </si>
+  <si>
+    <t>products/unipol-donors</t>
+  </si>
+  <si>
+    <t>2026-08-09T21:47:54.805Z</t>
+  </si>
+  <si>
+    <t>UNIPOL® Donors</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/unipol-donors/</t>
+  </si>
+  <si>
+    <t>products/unipol-unippac-process-control-software.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","cards-solution-grid","columns-horizontal-teaser","cards-featured-content"]</t>
+  </si>
+  <si>
+    <t>products/unipol-unippac-process-control-software</t>
+  </si>
+  <si>
+    <t>2026-08-09T21:48:48.234Z</t>
+  </si>
+  <si>
+    <t>UNIPOL UNIPPAC® Process Control Software</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/unipol-unippac-process-control-software/</t>
+  </si>
+  <si>
+    <t>products/vydac.report.json</t>
+  </si>
+  <si>
+    <t>products/vydac</t>
+  </si>
+  <si>
+    <t>2026-08-09T21:49:41.758Z</t>
+  </si>
+  <si>
+    <t>VYDAC®</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/vydac/</t>
+  </si>
+  <si>
+    <t>products/vyvid.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","video-overlay","cards-product","cards-featured-content"]</t>
+  </si>
+  <si>
+    <t>products/vyvid</t>
+  </si>
+  <si>
+    <t>2026-08-09T21:50:37.007Z</t>
+  </si>
+  <si>
+    <t>VYVID™</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/vyvid/</t>
+  </si>
+  <si>
+    <t>about-grace/leadership-team/anthony-yoo.report.json</t>
+  </si>
+  <si>
+    <t>["columns-profile-detail"]</t>
+  </si>
+  <si>
+    <t>["banner-cta","cards-featured-content"]</t>
+  </si>
+  <si>
+    <t>about-grace/leadership-team/anthony-yoo</t>
+  </si>
+  <si>
+    <t>2026-08-05T16:32:51.597Z</t>
+  </si>
+  <si>
+    <t>Anthony Yoo</t>
+  </si>
+  <si>
+    <t>https://grace.com/about-grace/leadership-team/anthony-yoo/</t>
+  </si>
+  <si>
+    <t>about-grace/locations/aiken.report.json</t>
+  </si>
+  <si>
+    <t>["columns-location-detail","columns-location-detail"]</t>
+  </si>
+  <si>
+    <t>about-grace/locations/aiken</t>
+  </si>
+  <si>
+    <t>2026-08-05T20:52:27.772Z</t>
+  </si>
+  <si>
+    <t>Aiken, SC, USA</t>
+  </si>
+  <si>
+    <t>https://grace.com/about-grace/locations/aiken/</t>
+  </si>
+  <si>
+    <t>industries/coatings/wood.report.json</t>
+  </si>
+  <si>
+    <t>["featured-product-selector"]</t>
+  </si>
+  <si>
+    <t>industries/coatings/wood</t>
+  </si>
+  <si>
+    <t>2026-08-05T17:05:39.728Z</t>
+  </si>
+  <si>
+    <t>Wood</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/coatings/wood/</t>
+  </si>
+  <si>
+    <t>industries/food-beverage/beer.report.json</t>
+  </si>
+  <si>
+    <t>["cards-product","table-product-comparison","cards-featured-content"]</t>
+  </si>
+  <si>
+    <t>industries/food-beverage/beer</t>
+  </si>
+  <si>
+    <t>2026-08-05T20:55:57.459Z</t>
+  </si>
+  <si>
+    <t>Beer</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/food-beverage/beer/</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/polypropylene-catalysts.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","cards-icon-grid","columns-horizontal-teaser-featured","cards-product","cards-featured-content"]</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/polypropylene-catalysts</t>
+  </si>
+  <si>
+    <t>2026-08-09T09:15:39.863Z</t>
+  </si>
+  <si>
+    <t>Polypropylene Catalysts</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/plastics-and-polymers/polypropylene-catalysts/</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/catalagram-archive.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","custom-widget-news-archive"]</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/catalagram-archive</t>
+  </si>
+  <si>
+    <t>2026-08-09T09:11:15.811Z</t>
+  </si>
+  <si>
+    <t>Catalagram Archive</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/refining-technologies/catalagram-archive/</t>
+  </si>
+  <si>
+    <t>people-and-careers/benefits/us-employee-benefits-summary.report.json</t>
+  </si>
+  <si>
+    <t>["accordion-nested"]</t>
+  </si>
+  <si>
+    <t>people-and-careers/benefits/us-employee-benefits-summary</t>
+  </si>
+  <si>
+    <t>2026-08-05T16:53:46.074Z</t>
+  </si>
+  <si>
+    <t>U.S. Employee Benefits Summary</t>
+  </si>
+  <si>
+    <t>https://grace.com/people-and-careers/benefits/us-employee-benefits-summary/</t>
+  </si>
+  <si>
+    <t>products/synthetic-silicas/classification.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-image-teaser"]</t>
+  </si>
+  <si>
     <t>["breadcrumb"]</t>
-  </si>
-  <si>
-    <t>products/activators-custom-organoborate-boron-compounds</t>
-  </si>
-  <si>
-    <t>2026-08-09T17:00:44.463Z</t>
-  </si>
-  <si>
-    <t>Activators Custom Organoborate/Boron Compounds</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/activators-custom-organoborate-boron-compounds/</t>
-  </si>
-  <si>
-    <t>products/activcat-catalysts.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","video-overlay","cards-featured-content"]</t>
-  </si>
-  <si>
-    <t>products/activcat-catalysts</t>
-  </si>
-  <si>
-    <t>2026-08-09T17:01:41.202Z</t>
-  </si>
-  <si>
-    <t>ActivCat® Catalysts</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/activcat-catalysts/</t>
-  </si>
-  <si>
-    <t>products/adsorbents.report.json</t>
-  </si>
-  <si>
-    <t>products/adsorbents</t>
-  </si>
-  <si>
-    <t>2026-08-09T17:02:34.956Z</t>
-  </si>
-  <si>
-    <t>Adsorbents</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/adsorbents/</t>
-  </si>
-  <si>
-    <t>products/catalysts.report.json</t>
-  </si>
-  <si>
-    <t>products/catalysts</t>
-  </si>
-  <si>
-    <t>2026-08-09T17:03:30.004Z</t>
-  </si>
-  <si>
-    <t>Catalysts</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/catalysts/</t>
-  </si>
-  <si>
-    <t>products/consista.report.json</t>
-  </si>
-  <si>
-    <t>products/consista</t>
-  </si>
-  <si>
-    <t>2026-08-09T17:04:25.639Z</t>
-  </si>
-  <si>
-    <t>CONSISTA®</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/consista/</t>
-  </si>
-  <si>
-    <t>products/davisil.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","table-two-column-content","table-two-column-content","cards-featured-content"]</t>
-  </si>
-  <si>
-    <t>products/davisil</t>
-  </si>
-  <si>
-    <t>2026-08-09T17:05:21.134Z</t>
-  </si>
-  <si>
-    <t>DAVISIL®</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/davisil/</t>
-  </si>
-  <si>
-    <t>products/fine-chemicals.report.json</t>
-  </si>
-  <si>
-    <t>products/fine-chemicals</t>
-  </si>
-  <si>
-    <t>2026-08-09T17:06:16.549Z</t>
-  </si>
-  <si>
-    <t>Fine Chemicals</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/fine-chemicals/</t>
-  </si>
-  <si>
-    <t>products/hyampp-catalysts-and-donors.report.json</t>
-  </si>
-  <si>
-    <t>products/hyampp-catalysts-and-donors</t>
-  </si>
-  <si>
-    <t>2026-08-09T17:07:10.730Z</t>
-  </si>
-  <si>
-    <t>HYAMPP® Catalysts and Donors</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/hyampp-catalysts-and-donors/</t>
-  </si>
-  <si>
-    <t>products/ludox.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","columns-horizontal-teaser","cards-featured-content"]</t>
-  </si>
-  <si>
-    <t>products/ludox</t>
-  </si>
-  <si>
-    <t>2026-08-09T16:59:48.932Z</t>
-  </si>
-  <si>
-    <t>LUDOX®</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/ludox/</t>
-  </si>
-  <si>
-    <t>products/lynx-pe.report.json</t>
-  </si>
-  <si>
-    <t>products/lynx-pe</t>
-  </si>
-  <si>
-    <t>2026-08-09T17:00:44.906Z</t>
-  </si>
-  <si>
-    <t>LYNX® PE</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/lynx-pe/</t>
-  </si>
-  <si>
-    <t>products/lynx-pp.report.json</t>
-  </si>
-  <si>
-    <t>products/lynx-pp</t>
-  </si>
-  <si>
-    <t>2026-08-09T17:01:38.956Z</t>
-  </si>
-  <si>
-    <t>LYNX® PP</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/lynx-pp/</t>
-  </si>
-  <si>
-    <t>products/magnapore.report.json</t>
-  </si>
-  <si>
-    <t>products/magnapore</t>
-  </si>
-  <si>
-    <t>2026-08-09T17:02:35.030Z</t>
-  </si>
-  <si>
-    <t>MAGNAPORE®</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/magnapore/</t>
-  </si>
-  <si>
-    <t>products/metallocenes.report.json</t>
-  </si>
-  <si>
-    <t>products/metallocenes</t>
-  </si>
-  <si>
-    <t>2026-08-09T17:03:30.204Z</t>
-  </si>
-  <si>
-    <t>Metallocenes</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/metallocenes/</t>
-  </si>
-  <si>
-    <t>products/polytrak-catalysts.report.json</t>
-  </si>
-  <si>
-    <t>products/polytrak-catalysts</t>
-  </si>
-  <si>
-    <t>2026-08-09T17:04:25.165Z</t>
-  </si>
-  <si>
-    <t>POLYTRAK® Catalysts</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/polytrak-catalysts/</t>
-  </si>
-  <si>
-    <t>products/product-stewardship.report.json</t>
-  </si>
-  <si>
-    <t>["table-two-column-content"]</t>
-  </si>
-  <si>
-    <t>products/product-stewardship</t>
-  </si>
-  <si>
-    <t>2026-08-09T17:05:19.428Z</t>
-  </si>
-  <si>
-    <t>Product Stewardship</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/product-stewardship/</t>
-  </si>
-  <si>
-    <t>products/quality-management.report.json</t>
-  </si>
-  <si>
-    <t>products/quality-management</t>
-  </si>
-  <si>
-    <t>2026-08-09T17:06:14.628Z</t>
-  </si>
-  <si>
-    <t>Quality</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/quality-management/</t>
-  </si>
-  <si>
-    <t>products/reflectn-digital-plant-simulator-software.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","columns-horizontal-teaser","cards-featured-content","social-follow","banner-contact-split","table-two-column-content","table-two-column-content"]</t>
-  </si>
-  <si>
-    <t>products/reflectn-digital-plant-simulator-software</t>
-  </si>
-  <si>
-    <t>2026-08-09T17:07:08.602Z</t>
-  </si>
-  <si>
-    <t>REFLECTN™ Digital Plant Simulator Software</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/reflectn-digital-plant-simulator-software/</t>
-  </si>
-  <si>
-    <t>products/shac.report.json</t>
-  </si>
-  <si>
-    <t>products/shac</t>
-  </si>
-  <si>
-    <t>2026-08-09T16:59:47.928Z</t>
-  </si>
-  <si>
-    <t>SHAC®</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/shac/</t>
-  </si>
-  <si>
-    <t>products/shieldex.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","columns-brochure-promo","columns-horizontal-teaser-featured","cards-featured-content"]</t>
-  </si>
-  <si>
-    <t>products/shieldex</t>
-  </si>
-  <si>
-    <t>2026-08-09T17:00:43.762Z</t>
-  </si>
-  <si>
-    <t>SHIELDEX® Anti-Corrosive Pigments</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/shieldex/</t>
-  </si>
-  <si>
-    <t>products/silsol.report.json</t>
-  </si>
-  <si>
-    <t>products/silsol</t>
-  </si>
-  <si>
-    <t>2026-08-09T17:18:15.873Z</t>
-  </si>
-  <si>
-    <t>SILSOL®</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/silsol/</t>
-  </si>
-  <si>
-    <t>products/syloid-mx-silica-series.report.json</t>
-  </si>
-  <si>
-    <t>products/syloid-mx-silica-series</t>
-  </si>
-  <si>
-    <t>2026-08-09T17:02:34.204Z</t>
-  </si>
-  <si>
-    <t>SYLOID® MX Silica Matting Agents for Coatings</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/syloid-mx-silica-series/</t>
-  </si>
-  <si>
-    <t>products/syloid-rad-silica-series.report.json</t>
-  </si>
-  <si>
-    <t>products/syloid-rad-silica-series</t>
-  </si>
-  <si>
-    <t>2026-08-09T17:03:27.843Z</t>
-  </si>
-  <si>
-    <t>SYLOID® RAD Silica Series</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/syloid-rad-silica-series/</t>
-  </si>
-  <si>
-    <t>products/syloid-silica.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","video-overlay","columns-horizontal-teaser","cards-featured-content"]</t>
-  </si>
-  <si>
-    <t>products/syloid-silica</t>
-  </si>
-  <si>
-    <t>2026-08-09T17:04:21.827Z</t>
-  </si>
-  <si>
-    <t>SYLOID® Silica</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/syloid-silica/</t>
-  </si>
-  <si>
-    <t>products/syloid-xdp-f-silica.report.json</t>
-  </si>
-  <si>
-    <t>products/syloid-xdp-f-silica</t>
-  </si>
-  <si>
-    <t>2026-08-09T17:05:16.627Z</t>
-  </si>
-  <si>
-    <t>SYLOID® XDP F Silica for Nutraceutical Formulators</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/syloid-xdp-f-silica/</t>
-  </si>
-  <si>
-    <t>products/sylopol-cr-catalysts.report.json</t>
-  </si>
-  <si>
-    <t>products/sylopol-cr-catalysts</t>
-  </si>
-  <si>
-    <t>2026-08-09T17:06:10.948Z</t>
-  </si>
-  <si>
-    <t>SYLOPOL® CR Catalysts</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/sylopol-cr-catalysts/</t>
-  </si>
-  <si>
-    <t>products/sylopol-zn-catalysts.report.json</t>
-  </si>
-  <si>
-    <t>products/sylopol-zn-catalysts</t>
-  </si>
-  <si>
-    <t>2026-08-09T17:07:05.103Z</t>
-  </si>
-  <si>
-    <t>SYLOPOL® ZN Catalysts</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/sylopol-zn-catalysts/</t>
-  </si>
-  <si>
-    <t>products/sylosiv.report.json</t>
-  </si>
-  <si>
-    <t>products/sylosiv</t>
-  </si>
-  <si>
-    <t>2026-08-09T16:59:49.450Z</t>
-  </si>
-  <si>
-    <t>SYLOSIV®</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/sylosiv/</t>
-  </si>
-  <si>
-    <t>products/synthetic-silicas.report.json</t>
-  </si>
-  <si>
-    <t>products/synthetic-silicas</t>
-  </si>
-  <si>
-    <t>2026-08-09T17:00:44.459Z</t>
-  </si>
-  <si>
-    <t>Synthetic Silicas</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/synthetic-silicas/</t>
-  </si>
-  <si>
-    <t>products/trisyl-silica.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","video-overlay","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq","columns-horizontal-teaser","cards-featured-content"]</t>
-  </si>
-  <si>
-    <t>products/trisyl-silica</t>
-  </si>
-  <si>
-    <t>2026-08-09T17:02:39.636Z</t>
-  </si>
-  <si>
-    <t>TRISYL® Silica</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/trisyl-silica/</t>
-  </si>
-  <si>
-    <t>products/trisyl-xge-catalyst.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","video-overlay","accordion-faq"]</t>
-  </si>
-  <si>
-    <t>products/trisyl-xge-catalyst</t>
-  </si>
-  <si>
-    <t>2026-08-09T16:59:50.185Z</t>
-  </si>
-  <si>
-    <t>TRISYL® XGE Catalyst</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/TRISYL-XGE-Catalyst/</t>
-  </si>
-  <si>
-    <t>products/unipol-donors.report.json</t>
-  </si>
-  <si>
-    <t>products/unipol-donors</t>
-  </si>
-  <si>
-    <t>2026-08-09T17:03:34.205Z</t>
-  </si>
-  <si>
-    <t>UNIPOL® Donors</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/unipol-donors/</t>
-  </si>
-  <si>
-    <t>products/unipol-unippac-process-control-software.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","cards-solution-grid","columns-horizontal-teaser","cards-featured-content"]</t>
-  </si>
-  <si>
-    <t>products/unipol-unippac-process-control-software</t>
-  </si>
-  <si>
-    <t>2026-08-09T17:04:30.232Z</t>
-  </si>
-  <si>
-    <t>UNIPOL UNIPPAC® Process Control Software</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/unipol-unippac-process-control-software/</t>
-  </si>
-  <si>
-    <t>products/vydac.report.json</t>
-  </si>
-  <si>
-    <t>products/vydac</t>
-  </si>
-  <si>
-    <t>2026-08-09T17:05:23.669Z</t>
-  </si>
-  <si>
-    <t>VYDAC®</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/vydac/</t>
-  </si>
-  <si>
-    <t>products/vyvid.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","video-overlay","cards-product","cards-featured-content"]</t>
-  </si>
-  <si>
-    <t>products/vyvid</t>
-  </si>
-  <si>
-    <t>2026-08-09T17:06:19.129Z</t>
-  </si>
-  <si>
-    <t>VYVID™</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/vyvid/</t>
-  </si>
-  <si>
-    <t>about-grace/leadership-team/anthony-yoo.report.json</t>
-  </si>
-  <si>
-    <t>["columns-profile-detail"]</t>
-  </si>
-  <si>
-    <t>["banner-cta","cards-featured-content"]</t>
-  </si>
-  <si>
-    <t>about-grace/leadership-team/anthony-yoo</t>
-  </si>
-  <si>
-    <t>2026-08-05T16:32:51.597Z</t>
-  </si>
-  <si>
-    <t>Anthony Yoo</t>
-  </si>
-  <si>
-    <t>https://grace.com/about-grace/leadership-team/anthony-yoo/</t>
-  </si>
-  <si>
-    <t>about-grace/locations/aiken.report.json</t>
-  </si>
-  <si>
-    <t>["columns-location-detail","columns-location-detail"]</t>
-  </si>
-  <si>
-    <t>about-grace/locations/aiken</t>
-  </si>
-  <si>
-    <t>2026-08-05T20:52:27.772Z</t>
-  </si>
-  <si>
-    <t>Aiken, SC, USA</t>
-  </si>
-  <si>
-    <t>https://grace.com/about-grace/locations/aiken/</t>
-  </si>
-  <si>
-    <t>industries/coatings/wood.report.json</t>
-  </si>
-  <si>
-    <t>["featured-product-selector"]</t>
-  </si>
-  <si>
-    <t>industries/coatings/wood</t>
-  </si>
-  <si>
-    <t>2026-08-05T17:05:39.728Z</t>
-  </si>
-  <si>
-    <t>Wood</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/coatings/wood/</t>
-  </si>
-  <si>
-    <t>industries/food-beverage/beer.report.json</t>
-  </si>
-  <si>
-    <t>["cards-product","table-product-comparison","cards-featured-content"]</t>
-  </si>
-  <si>
-    <t>industries/food-beverage/beer</t>
-  </si>
-  <si>
-    <t>2026-08-05T20:55:57.459Z</t>
-  </si>
-  <si>
-    <t>Beer</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/food-beverage/beer/</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/polypropylene-catalysts.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","cards-icon-grid","columns-horizontal-teaser-featured","cards-product","cards-featured-content"]</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/polypropylene-catalysts</t>
-  </si>
-  <si>
-    <t>2026-08-09T09:15:39.863Z</t>
-  </si>
-  <si>
-    <t>Polypropylene Catalysts</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/plastics-and-polymers/polypropylene-catalysts/</t>
-  </si>
-  <si>
-    <t>industries/refining-technologies/catalagram-archive.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","custom-widget-news-archive"]</t>
-  </si>
-  <si>
-    <t>industries/refining-technologies/catalagram-archive</t>
-  </si>
-  <si>
-    <t>2026-08-09T09:11:15.811Z</t>
-  </si>
-  <si>
-    <t>Catalagram Archive</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/refining-technologies/catalagram-archive/</t>
-  </si>
-  <si>
-    <t>people-and-careers/benefits/us-employee-benefits-summary.report.json</t>
-  </si>
-  <si>
-    <t>["accordion-nested"]</t>
-  </si>
-  <si>
-    <t>people-and-careers/benefits/us-employee-benefits-summary</t>
-  </si>
-  <si>
-    <t>2026-08-05T16:53:46.074Z</t>
-  </si>
-  <si>
-    <t>U.S. Employee Benefits Summary</t>
-  </si>
-  <si>
-    <t>https://grace.com/people-and-careers/benefits/us-employee-benefits-summary/</t>
-  </si>
-  <si>
-    <t>products/synthetic-silicas/classification.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","columns-image-teaser"]</t>
   </si>
   <si>
     <t>products/synthetic-silicas/classification</t>
@@ -14187,13 +14193,13 @@
         <v>1</v>
       </c>
       <c r="I194" t="s">
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="J194" t="s">
         <v>20</v>
       </c>
       <c r="K194" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="L194" t="s">
         <v>19</v>
@@ -14202,18 +14208,18 @@
         <v>22</v>
       </c>
       <c r="N194" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="O194" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="P194" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="195" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B195" t="s">
         <v>18</v>
@@ -14243,7 +14249,7 @@
         <v>42</v>
       </c>
       <c r="K195" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="L195" t="b">
         <v>1</v>
@@ -14252,18 +14258,18 @@
         <v>22</v>
       </c>
       <c r="N195" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="O195" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="P195" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="196" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B196" t="s">
         <v>979</v>
@@ -14293,7 +14299,7 @@
         <v>20</v>
       </c>
       <c r="K196" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="L196" t="s">
         <v>19</v>
@@ -14302,21 +14308,21 @@
         <v>22</v>
       </c>
       <c r="N196" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="O196" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="P196" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="197" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B197" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="C197" t="s">
         <v>18</v>
@@ -14343,7 +14349,7 @@
         <v>20</v>
       </c>
       <c r="K197" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="L197" t="s">
         <v>19</v>
@@ -14352,18 +14358,18 @@
         <v>22</v>
       </c>
       <c r="N197" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="O197" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="P197" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="198" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B198" t="s">
         <v>979</v>
@@ -14393,7 +14399,7 @@
         <v>20</v>
       </c>
       <c r="K198" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="L198" t="s">
         <v>19</v>
@@ -14402,18 +14408,18 @@
         <v>22</v>
       </c>
       <c r="N198" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="O198" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="P198" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="199" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B199" t="s">
         <v>979</v>
@@ -14443,7 +14449,7 @@
         <v>20</v>
       </c>
       <c r="K199" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="L199" t="s">
         <v>19</v>
@@ -14452,18 +14458,18 @@
         <v>22</v>
       </c>
       <c r="N199" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="O199" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="P199" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="200" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B200" t="s">
         <v>979</v>
@@ -14493,7 +14499,7 @@
         <v>20</v>
       </c>
       <c r="K200" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="L200" t="s">
         <v>19</v>
@@ -14502,18 +14508,18 @@
         <v>22</v>
       </c>
       <c r="N200" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="O200" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="P200" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="201" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B201" t="s">
         <v>979</v>
@@ -14543,7 +14549,7 @@
         <v>20</v>
       </c>
       <c r="K201" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="L201" t="s">
         <v>19</v>
@@ -14552,18 +14558,18 @@
         <v>22</v>
       </c>
       <c r="N201" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="O201" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="P201" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="202" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B202" t="s">
         <v>979</v>
@@ -14593,7 +14599,7 @@
         <v>20</v>
       </c>
       <c r="K202" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="L202" t="s">
         <v>19</v>
@@ -14602,21 +14608,21 @@
         <v>22</v>
       </c>
       <c r="N202" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="O202" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="P202" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="203" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B203" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="C203" t="s">
         <v>18</v>
@@ -14643,7 +14649,7 @@
         <v>42</v>
       </c>
       <c r="K203" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="L203" t="b">
         <v>1</v>
@@ -14652,18 +14658,18 @@
         <v>22</v>
       </c>
       <c r="N203" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="O203" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="P203" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="204" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B204" t="s">
         <v>18</v>
@@ -14693,7 +14699,7 @@
         <v>42</v>
       </c>
       <c r="K204" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="L204" t="b">
         <v>1</v>
@@ -14702,21 +14708,21 @@
         <v>22</v>
       </c>
       <c r="N204" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="O204" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="P204" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="205" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B205" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C205" t="s">
         <v>18</v>
@@ -14737,13 +14743,13 @@
         <v>1</v>
       </c>
       <c r="I205" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="J205" t="s">
         <v>20</v>
       </c>
       <c r="K205" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="L205" t="s">
         <v>19</v>
@@ -14752,18 +14758,18 @@
         <v>22</v>
       </c>
       <c r="N205" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="O205" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="P205" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="206" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B206" t="s">
         <v>979</v>
@@ -14793,7 +14799,7 @@
         <v>20</v>
       </c>
       <c r="K206" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="L206" t="s">
         <v>19</v>
@@ -14802,21 +14808,21 @@
         <v>22</v>
       </c>
       <c r="N206" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="O206" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="P206" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="207" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B207" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="C207" t="s">
         <v>18</v>
@@ -14843,7 +14849,7 @@
         <v>20</v>
       </c>
       <c r="K207" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="L207" t="s">
         <v>19</v>
@@ -14852,21 +14858,21 @@
         <v>22</v>
       </c>
       <c r="N207" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="O207" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="P207" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="208" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B208" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="C208" t="s">
         <v>18</v>
@@ -14893,7 +14899,7 @@
         <v>20</v>
       </c>
       <c r="K208" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="L208" t="s">
         <v>19</v>
@@ -14902,21 +14908,21 @@
         <v>22</v>
       </c>
       <c r="N208" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="O208" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="P208" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="209" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B209" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C209" t="s">
         <v>18</v>
@@ -14943,7 +14949,7 @@
         <v>20</v>
       </c>
       <c r="K209" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="L209" t="s">
         <v>19</v>
@@ -14952,21 +14958,21 @@
         <v>22</v>
       </c>
       <c r="N209" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="O209" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="P209" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="210" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B210" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C210" t="s">
         <v>18</v>
@@ -14987,13 +14993,13 @@
         <v>1</v>
       </c>
       <c r="I210" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="J210" t="s">
         <v>20</v>
       </c>
       <c r="K210" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="L210" t="s">
         <v>19</v>
@@ -15002,21 +15008,21 @@
         <v>22</v>
       </c>
       <c r="N210" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="O210" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="P210" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="211" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B211" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="C211" t="s">
         <v>18</v>
@@ -15043,7 +15049,7 @@
         <v>20</v>
       </c>
       <c r="K211" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="L211" t="s">
         <v>19</v>
@@ -15052,21 +15058,21 @@
         <v>22</v>
       </c>
       <c r="N211" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="O211" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="P211" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="212" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B212" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C212" t="s">
         <v>18</v>
@@ -15087,13 +15093,13 @@
         <v>1</v>
       </c>
       <c r="I212" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="J212" t="s">
         <v>20</v>
       </c>
       <c r="K212" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="L212" t="s">
         <v>19</v>
@@ -15102,18 +15108,18 @@
         <v>22</v>
       </c>
       <c r="N212" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="O212" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="P212" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="213" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B213" t="s">
         <v>979</v>
@@ -15143,7 +15149,7 @@
         <v>20</v>
       </c>
       <c r="K213" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="L213" t="s">
         <v>19</v>
@@ -15152,18 +15158,18 @@
         <v>22</v>
       </c>
       <c r="N213" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="O213" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="P213" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="214" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B214" t="s">
         <v>979</v>
@@ -15193,7 +15199,7 @@
         <v>20</v>
       </c>
       <c r="K214" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="L214" t="s">
         <v>19</v>
@@ -15202,21 +15208,21 @@
         <v>22</v>
       </c>
       <c r="N214" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="O214" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="P214" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="215" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B215" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="C215" t="s">
         <v>18</v>
@@ -15243,7 +15249,7 @@
         <v>20</v>
       </c>
       <c r="K215" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="L215" t="s">
         <v>19</v>
@@ -15252,18 +15258,18 @@
         <v>22</v>
       </c>
       <c r="N215" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="O215" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="P215" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="216" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B216" t="s">
         <v>18</v>
@@ -15293,7 +15299,7 @@
         <v>42</v>
       </c>
       <c r="K216" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="L216" t="b">
         <v>1</v>
@@ -15302,21 +15308,21 @@
         <v>22</v>
       </c>
       <c r="N216" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="O216" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="P216" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="217" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B217" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="C217" t="s">
         <v>18</v>
@@ -15337,13 +15343,13 @@
         <v>1</v>
       </c>
       <c r="I217" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="J217" t="s">
         <v>20</v>
       </c>
       <c r="K217" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="L217" t="s">
         <v>19</v>
@@ -15352,21 +15358,21 @@
         <v>22</v>
       </c>
       <c r="N217" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="O217" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="P217" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="218" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B218" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="C218" t="s">
         <v>18</v>
@@ -15393,7 +15399,7 @@
         <v>20</v>
       </c>
       <c r="K218" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="L218" t="s">
         <v>19</v>
@@ -15402,18 +15408,18 @@
         <v>22</v>
       </c>
       <c r="N218" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="O218" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="P218" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="219" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B219" t="s">
         <v>979</v>
@@ -15443,7 +15449,7 @@
         <v>20</v>
       </c>
       <c r="K219" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="L219" t="s">
         <v>19</v>
@@ -15452,21 +15458,21 @@
         <v>22</v>
       </c>
       <c r="N219" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="O219" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="P219" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="220" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B220" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="C220" t="s">
         <v>18</v>
@@ -15487,13 +15493,13 @@
         <v>1</v>
       </c>
       <c r="I220" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="J220" t="s">
         <v>20</v>
       </c>
       <c r="K220" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="L220" t="s">
         <v>19</v>
@@ -15502,18 +15508,18 @@
         <v>22</v>
       </c>
       <c r="N220" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="O220" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="P220" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="221" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B221" t="s">
         <v>979</v>
@@ -15543,7 +15549,7 @@
         <v>20</v>
       </c>
       <c r="K221" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="L221" t="s">
         <v>19</v>
@@ -15552,21 +15558,21 @@
         <v>22</v>
       </c>
       <c r="N221" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="O221" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="P221" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="222" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B222" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="C222" t="s">
         <v>18</v>
@@ -15587,13 +15593,13 @@
         <v>1</v>
       </c>
       <c r="I222" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="J222" t="s">
         <v>20</v>
       </c>
       <c r="K222" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="L222" t="s">
         <v>19</v>
@@ -15602,24 +15608,24 @@
         <v>22</v>
       </c>
       <c r="N222" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="O222" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="P222" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="223" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B223" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="C223" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="D223" t="s">
         <v>19</v>
@@ -15643,7 +15649,7 @@
         <v>20</v>
       </c>
       <c r="K223" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="L223" t="s">
         <v>19</v>
@@ -15652,21 +15658,21 @@
         <v>22</v>
       </c>
       <c r="N223" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="O223" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="P223" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="224" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B224" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="C224" t="s">
         <v>18</v>
@@ -15693,7 +15699,7 @@
         <v>42</v>
       </c>
       <c r="K224" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="L224" t="b">
         <v>0</v>
@@ -15702,21 +15708,21 @@
         <v>22</v>
       </c>
       <c r="N224" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="O224" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="P224" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="225" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="B225" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="C225" t="s">
         <v>129</v>
@@ -15743,7 +15749,7 @@
         <v>42</v>
       </c>
       <c r="K225" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="L225" t="b">
         <v>1</v>
@@ -15752,21 +15758,21 @@
         <v>22</v>
       </c>
       <c r="N225" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="O225" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="P225" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="226" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B226" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="C226" t="s">
         <v>18</v>
@@ -15793,7 +15799,7 @@
         <v>42</v>
       </c>
       <c r="K226" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="L226" t="b">
         <v>1</v>
@@ -15802,21 +15808,21 @@
         <v>22</v>
       </c>
       <c r="N226" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="O226" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="P226" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="227" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B227" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="C227" t="s">
         <v>18</v>
@@ -15843,7 +15849,7 @@
         <v>20</v>
       </c>
       <c r="K227" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="L227" t="s">
         <v>19</v>
@@ -15852,21 +15858,21 @@
         <v>22</v>
       </c>
       <c r="N227" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="O227" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="P227" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="228" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="B228" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="C228" t="s">
         <v>18</v>
@@ -15893,7 +15899,7 @@
         <v>20</v>
       </c>
       <c r="K228" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="L228" t="s">
         <v>19</v>
@@ -15902,21 +15908,21 @@
         <v>22</v>
       </c>
       <c r="N228" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="O228" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="P228" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="229" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B229" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="C229" t="s">
         <v>40</v>
@@ -15943,7 +15949,7 @@
         <v>42</v>
       </c>
       <c r="K229" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="L229" t="b">
         <v>1</v>
@@ -15952,21 +15958,21 @@
         <v>22</v>
       </c>
       <c r="N229" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="O229" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="P229" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="230" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B230" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="C230" t="s">
         <v>18</v>
@@ -15987,13 +15993,13 @@
         <v>0</v>
       </c>
       <c r="I230" t="s">
-        <v>980</v>
+        <v>1207</v>
       </c>
       <c r="J230" t="s">
         <v>20</v>
       </c>
       <c r="K230" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="L230" t="s">
         <v>19</v>
@@ -16002,24 +16008,24 @@
         <v>22</v>
       </c>
       <c r="N230" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="O230" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="P230" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="231" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="B231" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="C231" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="D231" t="b">
         <v>0</v>
@@ -16043,7 +16049,7 @@
         <v>42</v>
       </c>
       <c r="K231" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="L231" t="b">
         <v>1</v>
@@ -16052,24 +16058,24 @@
         <v>22</v>
       </c>
       <c r="N231" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="O231" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="P231" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="232" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="B232" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="C232" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="D232" t="b">
         <v>0</v>
@@ -16093,7 +16099,7 @@
         <v>42</v>
       </c>
       <c r="K232" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="L232" t="b">
         <v>1</v>
@@ -16102,21 +16108,21 @@
         <v>22</v>
       </c>
       <c r="N232" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="O232" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="P232" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="233" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="B233" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C233" t="s">
         <v>18</v>
@@ -16143,7 +16149,7 @@
         <v>20</v>
       </c>
       <c r="K233" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="L233" t="s">
         <v>19</v>
@@ -16152,21 +16158,21 @@
         <v>22</v>
       </c>
       <c r="N233" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="O233" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="P233" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="234" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="B234" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C234" t="s">
         <v>18</v>
@@ -16193,7 +16199,7 @@
         <v>20</v>
       </c>
       <c r="K234" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="L234" t="s">
         <v>19</v>
@@ -16202,21 +16208,21 @@
         <v>22</v>
       </c>
       <c r="N234" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="O234" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="P234" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="235" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="B235" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C235" t="s">
         <v>18</v>
@@ -16243,7 +16249,7 @@
         <v>20</v>
       </c>
       <c r="K235" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="L235" t="s">
         <v>19</v>
@@ -16252,21 +16258,21 @@
         <v>22</v>
       </c>
       <c r="N235" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="O235" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="P235" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="236" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="B236" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C236" t="s">
         <v>18</v>
@@ -16293,7 +16299,7 @@
         <v>20</v>
       </c>
       <c r="K236" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="L236" t="s">
         <v>19</v>
@@ -16302,21 +16308,21 @@
         <v>22</v>
       </c>
       <c r="N236" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="O236" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="P236" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="237" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="B237" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C237" t="s">
         <v>18</v>
@@ -16343,7 +16349,7 @@
         <v>20</v>
       </c>
       <c r="K237" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="L237" t="s">
         <v>19</v>
@@ -16352,21 +16358,21 @@
         <v>22</v>
       </c>
       <c r="N237" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="O237" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="P237" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="238" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="B238" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C238" t="s">
         <v>18</v>
@@ -16393,7 +16399,7 @@
         <v>20</v>
       </c>
       <c r="K238" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="L238" t="s">
         <v>19</v>
@@ -16402,21 +16408,21 @@
         <v>22</v>
       </c>
       <c r="N238" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="O238" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="P238" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="239" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="B239" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C239" t="s">
         <v>18</v>
@@ -16443,7 +16449,7 @@
         <v>20</v>
       </c>
       <c r="K239" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="L239" t="s">
         <v>19</v>
@@ -16452,21 +16458,21 @@
         <v>22</v>
       </c>
       <c r="N239" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="O239" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="P239" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="240" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="B240" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C240" t="s">
         <v>18</v>
@@ -16493,7 +16499,7 @@
         <v>20</v>
       </c>
       <c r="K240" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="L240" t="s">
         <v>19</v>
@@ -16502,21 +16508,21 @@
         <v>22</v>
       </c>
       <c r="N240" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="O240" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="P240" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="241" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="B241" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C241" t="s">
         <v>18</v>
@@ -16543,7 +16549,7 @@
         <v>20</v>
       </c>
       <c r="K241" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="L241" t="s">
         <v>19</v>
@@ -16552,21 +16558,21 @@
         <v>22</v>
       </c>
       <c r="N241" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="O241" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="P241" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="242" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="B242" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C242" t="s">
         <v>18</v>
@@ -16593,7 +16599,7 @@
         <v>20</v>
       </c>
       <c r="K242" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="L242" t="s">
         <v>19</v>
@@ -16602,21 +16608,21 @@
         <v>22</v>
       </c>
       <c r="N242" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="O242" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="P242" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="243" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="B243" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C243" t="s">
         <v>18</v>
@@ -16643,7 +16649,7 @@
         <v>20</v>
       </c>
       <c r="K243" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="L243" t="s">
         <v>19</v>
@@ -16652,21 +16658,21 @@
         <v>22</v>
       </c>
       <c r="N243" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="O243" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="P243" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="244" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="B244" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C244" t="s">
         <v>18</v>
@@ -16693,7 +16699,7 @@
         <v>20</v>
       </c>
       <c r="K244" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="L244" t="s">
         <v>19</v>
@@ -16702,21 +16708,21 @@
         <v>22</v>
       </c>
       <c r="N244" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="O244" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="P244" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="245" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="B245" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C245" t="s">
         <v>18</v>
@@ -16737,13 +16743,13 @@
         <v>0</v>
       </c>
       <c r="I245" t="s">
-        <v>980</v>
+        <v>1207</v>
       </c>
       <c r="J245" t="s">
         <v>20</v>
       </c>
       <c r="K245" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="L245" t="s">
         <v>19</v>
@@ -16752,21 +16758,21 @@
         <v>22</v>
       </c>
       <c r="N245" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="O245" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="P245" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="246" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="B246" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C246" t="s">
         <v>18</v>
@@ -16787,13 +16793,13 @@
         <v>0</v>
       </c>
       <c r="I246" t="s">
-        <v>980</v>
+        <v>1207</v>
       </c>
       <c r="J246" t="s">
         <v>20</v>
       </c>
       <c r="K246" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="L246" t="s">
         <v>19</v>
@@ -16802,21 +16808,21 @@
         <v>22</v>
       </c>
       <c r="N246" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="O246" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="P246" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="247" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="B247" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C247" t="s">
         <v>18</v>
@@ -16837,13 +16843,13 @@
         <v>0</v>
       </c>
       <c r="I247" t="s">
-        <v>980</v>
+        <v>1207</v>
       </c>
       <c r="J247" t="s">
         <v>20</v>
       </c>
       <c r="K247" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="L247" t="s">
         <v>19</v>
@@ -16852,21 +16858,21 @@
         <v>22</v>
       </c>
       <c r="N247" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="O247" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="P247" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="248" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="B248" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C248" t="s">
         <v>18</v>
@@ -16887,13 +16893,13 @@
         <v>0</v>
       </c>
       <c r="I248" t="s">
-        <v>980</v>
+        <v>1207</v>
       </c>
       <c r="J248" t="s">
         <v>20</v>
       </c>
       <c r="K248" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="L248" t="s">
         <v>19</v>
@@ -16902,21 +16908,21 @@
         <v>22</v>
       </c>
       <c r="N248" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="O248" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="P248" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="249" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="B249" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C249" t="s">
         <v>18</v>
@@ -16937,13 +16943,13 @@
         <v>0</v>
       </c>
       <c r="I249" t="s">
-        <v>980</v>
+        <v>1207</v>
       </c>
       <c r="J249" t="s">
         <v>20</v>
       </c>
       <c r="K249" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="L249" t="s">
         <v>19</v>
@@ -16952,21 +16958,21 @@
         <v>22</v>
       </c>
       <c r="N249" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="O249" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="P249" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="250" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="B250" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C250" t="s">
         <v>18</v>
@@ -16993,7 +16999,7 @@
         <v>20</v>
       </c>
       <c r="K250" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="L250" t="s">
         <v>19</v>
@@ -17002,18 +17008,18 @@
         <v>22</v>
       </c>
       <c r="N250" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="O250" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="P250" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="251" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="B251" t="s">
         <v>19</v>
@@ -17043,7 +17049,7 @@
         <v>19</v>
       </c>
       <c r="K251" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="L251" t="s">
         <v>19</v>
@@ -17052,21 +17058,21 @@
         <v>326</v>
       </c>
       <c r="N251" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="O251" t="s">
         <v>19</v>
       </c>
       <c r="P251" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="252" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="B252" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C252" t="s">
         <v>18</v>
@@ -17087,36 +17093,36 @@
         <v>0</v>
       </c>
       <c r="I252" t="s">
-        <v>980</v>
+        <v>1207</v>
       </c>
       <c r="J252" t="s">
         <v>20</v>
       </c>
       <c r="K252" t="s">
+        <v>1322</v>
+      </c>
+      <c r="L252" t="s">
+        <v>19</v>
+      </c>
+      <c r="M252" t="s">
+        <v>22</v>
+      </c>
+      <c r="N252" t="s">
+        <v>1323</v>
+      </c>
+      <c r="O252" t="s">
+        <v>1324</v>
+      </c>
+      <c r="P252" t="s">
         <v>1320</v>
-      </c>
-      <c r="L252" t="s">
-        <v>19</v>
-      </c>
-      <c r="M252" t="s">
-        <v>22</v>
-      </c>
-      <c r="N252" t="s">
-        <v>1321</v>
-      </c>
-      <c r="O252" t="s">
-        <v>1322</v>
-      </c>
-      <c r="P252" t="s">
-        <v>1318</v>
       </c>
     </row>
     <row r="253" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="B253" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C253" t="s">
         <v>18</v>
@@ -17137,13 +17143,13 @@
         <v>0</v>
       </c>
       <c r="I253" t="s">
-        <v>980</v>
+        <v>1207</v>
       </c>
       <c r="J253" t="s">
         <v>20</v>
       </c>
       <c r="K253" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="L253" t="s">
         <v>19</v>
@@ -17152,21 +17158,21 @@
         <v>22</v>
       </c>
       <c r="N253" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="O253" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="P253" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="254" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="B254" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C254" t="s">
         <v>18</v>
@@ -17187,13 +17193,13 @@
         <v>0</v>
       </c>
       <c r="I254" t="s">
-        <v>980</v>
+        <v>1207</v>
       </c>
       <c r="J254" t="s">
         <v>20</v>
       </c>
       <c r="K254" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="L254" t="s">
         <v>19</v>
@@ -17202,21 +17208,21 @@
         <v>22</v>
       </c>
       <c r="N254" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="O254" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="P254" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="255" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="B255" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C255" t="s">
         <v>18</v>
@@ -17237,13 +17243,13 @@
         <v>0</v>
       </c>
       <c r="I255" t="s">
-        <v>980</v>
+        <v>1207</v>
       </c>
       <c r="J255" t="s">
         <v>20</v>
       </c>
       <c r="K255" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="L255" t="s">
         <v>19</v>
@@ -17252,21 +17258,21 @@
         <v>22</v>
       </c>
       <c r="N255" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="O255" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="P255" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="256" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="B256" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C256" t="s">
         <v>18</v>
@@ -17287,13 +17293,13 @@
         <v>0</v>
       </c>
       <c r="I256" t="s">
-        <v>980</v>
+        <v>1207</v>
       </c>
       <c r="J256" t="s">
         <v>20</v>
       </c>
       <c r="K256" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="L256" t="s">
         <v>19</v>
@@ -17302,21 +17308,21 @@
         <v>22</v>
       </c>
       <c r="N256" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="O256" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="P256" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="257" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="B257" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C257" t="s">
         <v>18</v>
@@ -17337,13 +17343,13 @@
         <v>0</v>
       </c>
       <c r="I257" t="s">
-        <v>980</v>
+        <v>1207</v>
       </c>
       <c r="J257" t="s">
         <v>20</v>
       </c>
       <c r="K257" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="L257" t="s">
         <v>19</v>
@@ -17352,18 +17358,18 @@
         <v>22</v>
       </c>
       <c r="N257" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="O257" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="P257" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="258" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="B258" t="s">
         <v>18</v>
@@ -17393,7 +17399,7 @@
         <v>42</v>
       </c>
       <c r="K258" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="L258" t="b">
         <v>0</v>
@@ -17402,21 +17408,21 @@
         <v>22</v>
       </c>
       <c r="N258" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="O258" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="P258" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="259" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="B259" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C259" t="s">
         <v>18</v>
@@ -17437,13 +17443,13 @@
         <v>0</v>
       </c>
       <c r="I259" t="s">
-        <v>980</v>
+        <v>1207</v>
       </c>
       <c r="J259" t="s">
         <v>20</v>
       </c>
       <c r="K259" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="L259" t="s">
         <v>19</v>
@@ -17452,24 +17458,24 @@
         <v>22</v>
       </c>
       <c r="N259" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="O259" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="P259" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="260" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="B260" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="C260" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="D260" t="b">
         <v>0</v>
@@ -17493,7 +17499,7 @@
         <v>42</v>
       </c>
       <c r="K260" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="L260" t="b">
         <v>1</v>
@@ -17502,13 +17508,13 @@
         <v>22</v>
       </c>
       <c r="N260" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="O260" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="P260" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-grace-master.report.xlsx
+++ b/tools/importer/reports/import-grace-master.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3663" uniqueCount="1367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3664" uniqueCount="1366">
   <si>
     <t>_reportFile</t>
   </si>
@@ -2979,7 +2979,7 @@
     <t>products/activcat-catalysts</t>
   </si>
   <si>
-    <t>2026-08-09T21:25:15.988Z</t>
+    <t>2026-08-11T20:12:48.960Z</t>
   </si>
   <si>
     <t>ActivCat® Catalysts</t>
@@ -3024,7 +3024,7 @@
     <t>products/consista</t>
   </si>
   <si>
-    <t>2026-08-09T21:26:10.006Z</t>
+    <t>2026-08-11T20:07:35.632Z</t>
   </si>
   <si>
     <t>CONSISTA®</t>
@@ -3093,7 +3093,7 @@
     <t>products/ludox</t>
   </si>
   <si>
-    <t>2026-08-09T21:28:50.808Z</t>
+    <t>2026-08-11T16:54:11.193Z</t>
   </si>
   <si>
     <t>LUDOX®</t>
@@ -3153,10 +3153,7 @@
     <t>products/metallocenes</t>
   </si>
   <si>
-    <t>2026-08-09T21:32:23.242Z</t>
-  </si>
-  <si>
-    <t>Metallocenes</t>
+    <t>2026-08-11T20:16:13.549Z</t>
   </si>
   <si>
     <t>https://grace.com/products/metallocenes/</t>
@@ -3252,7 +3249,7 @@
     <t>products/shieldex</t>
   </si>
   <si>
-    <t>2026-08-09T21:36:39.463Z</t>
+    <t>2026-08-11T20:09:01.782Z</t>
   </si>
   <si>
     <t>SHIELDEX® Anti-Corrosive Pigments</t>
@@ -14522,10 +14519,10 @@
         <v>1044</v>
       </c>
       <c r="B201" t="s">
-        <v>979</v>
+        <v>19</v>
       </c>
       <c r="C201" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D201" t="s">
         <v>19</v>
@@ -14534,19 +14531,19 @@
         <v>19</v>
       </c>
       <c r="F201" t="s">
-        <v>19</v>
+        <v>323</v>
       </c>
       <c r="G201" t="s">
-        <v>19</v>
-      </c>
-      <c r="H201" t="b">
-        <v>0</v>
+        <v>324</v>
+      </c>
+      <c r="H201" t="s">
+        <v>19</v>
       </c>
       <c r="I201" t="s">
-        <v>980</v>
+        <v>19</v>
       </c>
       <c r="J201" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K201" t="s">
         <v>1045</v>
@@ -14555,21 +14552,21 @@
         <v>19</v>
       </c>
       <c r="M201" t="s">
-        <v>22</v>
+        <v>326</v>
       </c>
       <c r="N201" t="s">
         <v>1046</v>
       </c>
       <c r="O201" t="s">
+        <v>19</v>
+      </c>
+      <c r="P201" t="s">
         <v>1047</v>
-      </c>
-      <c r="P201" t="s">
-        <v>1048</v>
       </c>
     </row>
     <row r="202" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B202" t="s">
         <v>979</v>
@@ -14599,30 +14596,30 @@
         <v>20</v>
       </c>
       <c r="K202" t="s">
+        <v>1049</v>
+      </c>
+      <c r="L202" t="s">
+        <v>19</v>
+      </c>
+      <c r="M202" t="s">
+        <v>22</v>
+      </c>
+      <c r="N202" t="s">
         <v>1050</v>
       </c>
-      <c r="L202" t="s">
-        <v>19</v>
-      </c>
-      <c r="M202" t="s">
-        <v>22</v>
-      </c>
-      <c r="N202" t="s">
+      <c r="O202" t="s">
         <v>1051</v>
       </c>
-      <c r="O202" t="s">
+      <c r="P202" t="s">
         <v>1052</v>
-      </c>
-      <c r="P202" t="s">
-        <v>1053</v>
       </c>
     </row>
     <row r="203" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B203" t="s">
         <v>1054</v>
-      </c>
-      <c r="B203" t="s">
-        <v>1055</v>
       </c>
       <c r="C203" t="s">
         <v>18</v>
@@ -14649,7 +14646,7 @@
         <v>42</v>
       </c>
       <c r="K203" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="L203" t="b">
         <v>1</v>
@@ -14658,18 +14655,18 @@
         <v>22</v>
       </c>
       <c r="N203" t="s">
+        <v>1056</v>
+      </c>
+      <c r="O203" t="s">
         <v>1057</v>
       </c>
-      <c r="O203" t="s">
+      <c r="P203" t="s">
         <v>1058</v>
-      </c>
-      <c r="P203" t="s">
-        <v>1059</v>
       </c>
     </row>
     <row r="204" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B204" t="s">
         <v>18</v>
@@ -14699,7 +14696,7 @@
         <v>42</v>
       </c>
       <c r="K204" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="L204" t="b">
         <v>1</v>
@@ -14708,21 +14705,21 @@
         <v>22</v>
       </c>
       <c r="N204" t="s">
+        <v>1061</v>
+      </c>
+      <c r="O204" t="s">
         <v>1062</v>
       </c>
-      <c r="O204" t="s">
+      <c r="P204" t="s">
         <v>1063</v>
-      </c>
-      <c r="P204" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="205" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B205" t="s">
         <v>1065</v>
-      </c>
-      <c r="B205" t="s">
-        <v>1066</v>
       </c>
       <c r="C205" t="s">
         <v>18</v>
@@ -14749,27 +14746,27 @@
         <v>20</v>
       </c>
       <c r="K205" t="s">
+        <v>1066</v>
+      </c>
+      <c r="L205" t="s">
+        <v>19</v>
+      </c>
+      <c r="M205" t="s">
+        <v>22</v>
+      </c>
+      <c r="N205" t="s">
         <v>1067</v>
       </c>
-      <c r="L205" t="s">
-        <v>19</v>
-      </c>
-      <c r="M205" t="s">
-        <v>22</v>
-      </c>
-      <c r="N205" t="s">
+      <c r="O205" t="s">
         <v>1068</v>
       </c>
-      <c r="O205" t="s">
+      <c r="P205" t="s">
         <v>1069</v>
-      </c>
-      <c r="P205" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="206" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="B206" t="s">
         <v>979</v>
@@ -14799,30 +14796,30 @@
         <v>20</v>
       </c>
       <c r="K206" t="s">
+        <v>1071</v>
+      </c>
+      <c r="L206" t="s">
+        <v>19</v>
+      </c>
+      <c r="M206" t="s">
+        <v>22</v>
+      </c>
+      <c r="N206" t="s">
         <v>1072</v>
       </c>
-      <c r="L206" t="s">
-        <v>19</v>
-      </c>
-      <c r="M206" t="s">
-        <v>22</v>
-      </c>
-      <c r="N206" t="s">
+      <c r="O206" t="s">
         <v>1073</v>
       </c>
-      <c r="O206" t="s">
+      <c r="P206" t="s">
         <v>1074</v>
-      </c>
-      <c r="P206" t="s">
-        <v>1075</v>
       </c>
     </row>
     <row r="207" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B207" t="s">
         <v>1076</v>
-      </c>
-      <c r="B207" t="s">
-        <v>1077</v>
       </c>
       <c r="C207" t="s">
         <v>18</v>
@@ -14849,27 +14846,27 @@
         <v>20</v>
       </c>
       <c r="K207" t="s">
+        <v>1077</v>
+      </c>
+      <c r="L207" t="s">
+        <v>19</v>
+      </c>
+      <c r="M207" t="s">
+        <v>22</v>
+      </c>
+      <c r="N207" t="s">
         <v>1078</v>
       </c>
-      <c r="L207" t="s">
-        <v>19</v>
-      </c>
-      <c r="M207" t="s">
-        <v>22</v>
-      </c>
-      <c r="N207" t="s">
+      <c r="O207" t="s">
         <v>1079</v>
       </c>
-      <c r="O207" t="s">
+      <c r="P207" t="s">
         <v>1080</v>
-      </c>
-      <c r="P207" t="s">
-        <v>1081</v>
       </c>
     </row>
     <row r="208" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B208" t="s">
         <v>1024</v>
@@ -14899,30 +14896,30 @@
         <v>20</v>
       </c>
       <c r="K208" t="s">
+        <v>1082</v>
+      </c>
+      <c r="L208" t="s">
+        <v>19</v>
+      </c>
+      <c r="M208" t="s">
+        <v>22</v>
+      </c>
+      <c r="N208" t="s">
         <v>1083</v>
       </c>
-      <c r="L208" t="s">
-        <v>19</v>
-      </c>
-      <c r="M208" t="s">
-        <v>22</v>
-      </c>
-      <c r="N208" t="s">
+      <c r="O208" t="s">
         <v>1084</v>
       </c>
-      <c r="O208" t="s">
+      <c r="P208" t="s">
         <v>1085</v>
-      </c>
-      <c r="P208" t="s">
-        <v>1086</v>
       </c>
     </row>
     <row r="209" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="B209" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="C209" t="s">
         <v>18</v>
@@ -14949,30 +14946,30 @@
         <v>20</v>
       </c>
       <c r="K209" t="s">
+        <v>1087</v>
+      </c>
+      <c r="L209" t="s">
+        <v>19</v>
+      </c>
+      <c r="M209" t="s">
+        <v>22</v>
+      </c>
+      <c r="N209" t="s">
         <v>1088</v>
       </c>
-      <c r="L209" t="s">
-        <v>19</v>
-      </c>
-      <c r="M209" t="s">
-        <v>22</v>
-      </c>
-      <c r="N209" t="s">
+      <c r="O209" t="s">
         <v>1089</v>
       </c>
-      <c r="O209" t="s">
+      <c r="P209" t="s">
         <v>1090</v>
-      </c>
-      <c r="P209" t="s">
-        <v>1091</v>
       </c>
     </row>
     <row r="210" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B210" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="C210" t="s">
         <v>18</v>
@@ -14999,30 +14996,30 @@
         <v>20</v>
       </c>
       <c r="K210" t="s">
+        <v>1092</v>
+      </c>
+      <c r="L210" t="s">
+        <v>19</v>
+      </c>
+      <c r="M210" t="s">
+        <v>22</v>
+      </c>
+      <c r="N210" t="s">
         <v>1093</v>
       </c>
-      <c r="L210" t="s">
-        <v>19</v>
-      </c>
-      <c r="M210" t="s">
-        <v>22</v>
-      </c>
-      <c r="N210" t="s">
+      <c r="O210" t="s">
         <v>1094</v>
       </c>
-      <c r="O210" t="s">
+      <c r="P210" t="s">
         <v>1095</v>
-      </c>
-      <c r="P210" t="s">
-        <v>1096</v>
       </c>
     </row>
     <row r="211" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B211" t="s">
         <v>1097</v>
-      </c>
-      <c r="B211" t="s">
-        <v>1098</v>
       </c>
       <c r="C211" t="s">
         <v>18</v>
@@ -15049,30 +15046,30 @@
         <v>20</v>
       </c>
       <c r="K211" t="s">
+        <v>1098</v>
+      </c>
+      <c r="L211" t="s">
+        <v>19</v>
+      </c>
+      <c r="M211" t="s">
+        <v>22</v>
+      </c>
+      <c r="N211" t="s">
         <v>1099</v>
       </c>
-      <c r="L211" t="s">
-        <v>19</v>
-      </c>
-      <c r="M211" t="s">
-        <v>22</v>
-      </c>
-      <c r="N211" t="s">
+      <c r="O211" t="s">
         <v>1100</v>
       </c>
-      <c r="O211" t="s">
+      <c r="P211" t="s">
         <v>1101</v>
-      </c>
-      <c r="P211" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="212" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="B212" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="C212" t="s">
         <v>18</v>
@@ -15099,27 +15096,27 @@
         <v>20</v>
       </c>
       <c r="K212" t="s">
+        <v>1103</v>
+      </c>
+      <c r="L212" t="s">
+        <v>19</v>
+      </c>
+      <c r="M212" t="s">
+        <v>22</v>
+      </c>
+      <c r="N212" t="s">
         <v>1104</v>
       </c>
-      <c r="L212" t="s">
-        <v>19</v>
-      </c>
-      <c r="M212" t="s">
-        <v>22</v>
-      </c>
-      <c r="N212" t="s">
+      <c r="O212" t="s">
         <v>1105</v>
       </c>
-      <c r="O212" t="s">
+      <c r="P212" t="s">
         <v>1106</v>
-      </c>
-      <c r="P212" t="s">
-        <v>1107</v>
       </c>
     </row>
     <row r="213" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="B213" t="s">
         <v>979</v>
@@ -15149,27 +15146,27 @@
         <v>20</v>
       </c>
       <c r="K213" t="s">
+        <v>1108</v>
+      </c>
+      <c r="L213" t="s">
+        <v>19</v>
+      </c>
+      <c r="M213" t="s">
+        <v>22</v>
+      </c>
+      <c r="N213" t="s">
         <v>1109</v>
       </c>
-      <c r="L213" t="s">
-        <v>19</v>
-      </c>
-      <c r="M213" t="s">
-        <v>22</v>
-      </c>
-      <c r="N213" t="s">
+      <c r="O213" t="s">
         <v>1110</v>
       </c>
-      <c r="O213" t="s">
+      <c r="P213" t="s">
         <v>1111</v>
-      </c>
-      <c r="P213" t="s">
-        <v>1112</v>
       </c>
     </row>
     <row r="214" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B214" t="s">
         <v>979</v>
@@ -15199,27 +15196,27 @@
         <v>20</v>
       </c>
       <c r="K214" t="s">
+        <v>1113</v>
+      </c>
+      <c r="L214" t="s">
+        <v>19</v>
+      </c>
+      <c r="M214" t="s">
+        <v>22</v>
+      </c>
+      <c r="N214" t="s">
         <v>1114</v>
       </c>
-      <c r="L214" t="s">
-        <v>19</v>
-      </c>
-      <c r="M214" t="s">
-        <v>22</v>
-      </c>
-      <c r="N214" t="s">
+      <c r="O214" t="s">
         <v>1115</v>
       </c>
-      <c r="O214" t="s">
+      <c r="P214" t="s">
         <v>1116</v>
-      </c>
-      <c r="P214" t="s">
-        <v>1117</v>
       </c>
     </row>
     <row r="215" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="B215" t="s">
         <v>1024</v>
@@ -15249,27 +15246,27 @@
         <v>20</v>
       </c>
       <c r="K215" t="s">
+        <v>1118</v>
+      </c>
+      <c r="L215" t="s">
+        <v>19</v>
+      </c>
+      <c r="M215" t="s">
+        <v>22</v>
+      </c>
+      <c r="N215" t="s">
         <v>1119</v>
       </c>
-      <c r="L215" t="s">
-        <v>19</v>
-      </c>
-      <c r="M215" t="s">
-        <v>22</v>
-      </c>
-      <c r="N215" t="s">
+      <c r="O215" t="s">
         <v>1120</v>
       </c>
-      <c r="O215" t="s">
+      <c r="P215" t="s">
         <v>1121</v>
-      </c>
-      <c r="P215" t="s">
-        <v>1122</v>
       </c>
     </row>
     <row r="216" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B216" t="s">
         <v>18</v>
@@ -15299,7 +15296,7 @@
         <v>42</v>
       </c>
       <c r="K216" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="L216" t="b">
         <v>1</v>
@@ -15308,21 +15305,21 @@
         <v>22</v>
       </c>
       <c r="N216" t="s">
+        <v>1124</v>
+      </c>
+      <c r="O216" t="s">
         <v>1125</v>
       </c>
-      <c r="O216" t="s">
+      <c r="P216" t="s">
         <v>1126</v>
-      </c>
-      <c r="P216" t="s">
-        <v>1127</v>
       </c>
     </row>
     <row r="217" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B217" t="s">
         <v>1128</v>
-      </c>
-      <c r="B217" t="s">
-        <v>1129</v>
       </c>
       <c r="C217" t="s">
         <v>18</v>
@@ -15349,30 +15346,30 @@
         <v>20</v>
       </c>
       <c r="K217" t="s">
+        <v>1129</v>
+      </c>
+      <c r="L217" t="s">
+        <v>19</v>
+      </c>
+      <c r="M217" t="s">
+        <v>22</v>
+      </c>
+      <c r="N217" t="s">
         <v>1130</v>
       </c>
-      <c r="L217" t="s">
-        <v>19</v>
-      </c>
-      <c r="M217" t="s">
-        <v>22</v>
-      </c>
-      <c r="N217" t="s">
+      <c r="O217" t="s">
         <v>1131</v>
       </c>
-      <c r="O217" t="s">
+      <c r="P217" t="s">
         <v>1132</v>
-      </c>
-      <c r="P217" t="s">
-        <v>1133</v>
       </c>
     </row>
     <row r="218" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B218" t="s">
         <v>1134</v>
-      </c>
-      <c r="B218" t="s">
-        <v>1135</v>
       </c>
       <c r="C218" t="s">
         <v>18</v>
@@ -15399,27 +15396,27 @@
         <v>20</v>
       </c>
       <c r="K218" t="s">
+        <v>1135</v>
+      </c>
+      <c r="L218" t="s">
+        <v>19</v>
+      </c>
+      <c r="M218" t="s">
+        <v>22</v>
+      </c>
+      <c r="N218" t="s">
         <v>1136</v>
       </c>
-      <c r="L218" t="s">
-        <v>19</v>
-      </c>
-      <c r="M218" t="s">
-        <v>22</v>
-      </c>
-      <c r="N218" t="s">
+      <c r="O218" t="s">
         <v>1137</v>
       </c>
-      <c r="O218" t="s">
+      <c r="P218" t="s">
         <v>1138</v>
-      </c>
-      <c r="P218" t="s">
-        <v>1139</v>
       </c>
     </row>
     <row r="219" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="B219" t="s">
         <v>979</v>
@@ -15449,30 +15446,30 @@
         <v>20</v>
       </c>
       <c r="K219" t="s">
+        <v>1140</v>
+      </c>
+      <c r="L219" t="s">
+        <v>19</v>
+      </c>
+      <c r="M219" t="s">
+        <v>22</v>
+      </c>
+      <c r="N219" t="s">
         <v>1141</v>
       </c>
-      <c r="L219" t="s">
-        <v>19</v>
-      </c>
-      <c r="M219" t="s">
-        <v>22</v>
-      </c>
-      <c r="N219" t="s">
+      <c r="O219" t="s">
         <v>1142</v>
       </c>
-      <c r="O219" t="s">
+      <c r="P219" t="s">
         <v>1143</v>
-      </c>
-      <c r="P219" t="s">
-        <v>1144</v>
       </c>
     </row>
     <row r="220" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B220" t="s">
         <v>1145</v>
-      </c>
-      <c r="B220" t="s">
-        <v>1146</v>
       </c>
       <c r="C220" t="s">
         <v>18</v>
@@ -15499,27 +15496,27 @@
         <v>20</v>
       </c>
       <c r="K220" t="s">
+        <v>1146</v>
+      </c>
+      <c r="L220" t="s">
+        <v>19</v>
+      </c>
+      <c r="M220" t="s">
+        <v>22</v>
+      </c>
+      <c r="N220" t="s">
         <v>1147</v>
       </c>
-      <c r="L220" t="s">
-        <v>19</v>
-      </c>
-      <c r="M220" t="s">
-        <v>22</v>
-      </c>
-      <c r="N220" t="s">
+      <c r="O220" t="s">
         <v>1148</v>
       </c>
-      <c r="O220" t="s">
+      <c r="P220" t="s">
         <v>1149</v>
-      </c>
-      <c r="P220" t="s">
-        <v>1150</v>
       </c>
     </row>
     <row r="221" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="B221" t="s">
         <v>979</v>
@@ -15549,30 +15546,30 @@
         <v>20</v>
       </c>
       <c r="K221" t="s">
+        <v>1151</v>
+      </c>
+      <c r="L221" t="s">
+        <v>19</v>
+      </c>
+      <c r="M221" t="s">
+        <v>22</v>
+      </c>
+      <c r="N221" t="s">
         <v>1152</v>
       </c>
-      <c r="L221" t="s">
-        <v>19</v>
-      </c>
-      <c r="M221" t="s">
-        <v>22</v>
-      </c>
-      <c r="N221" t="s">
+      <c r="O221" t="s">
         <v>1153</v>
       </c>
-      <c r="O221" t="s">
+      <c r="P221" t="s">
         <v>1154</v>
-      </c>
-      <c r="P221" t="s">
-        <v>1155</v>
       </c>
     </row>
     <row r="222" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B222" t="s">
         <v>1156</v>
-      </c>
-      <c r="B222" t="s">
-        <v>1157</v>
       </c>
       <c r="C222" t="s">
         <v>18</v>
@@ -15599,33 +15596,33 @@
         <v>20</v>
       </c>
       <c r="K222" t="s">
+        <v>1157</v>
+      </c>
+      <c r="L222" t="s">
+        <v>19</v>
+      </c>
+      <c r="M222" t="s">
+        <v>22</v>
+      </c>
+      <c r="N222" t="s">
         <v>1158</v>
       </c>
-      <c r="L222" t="s">
-        <v>19</v>
-      </c>
-      <c r="M222" t="s">
-        <v>22</v>
-      </c>
-      <c r="N222" t="s">
+      <c r="O222" t="s">
         <v>1159</v>
       </c>
-      <c r="O222" t="s">
+      <c r="P222" t="s">
         <v>1160</v>
-      </c>
-      <c r="P222" t="s">
-        <v>1161</v>
       </c>
     </row>
     <row r="223" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B223" t="s">
         <v>1162</v>
       </c>
-      <c r="B223" t="s">
+      <c r="C223" t="s">
         <v>1163</v>
-      </c>
-      <c r="C223" t="s">
-        <v>1164</v>
       </c>
       <c r="D223" t="s">
         <v>19</v>
@@ -15649,30 +15646,30 @@
         <v>20</v>
       </c>
       <c r="K223" t="s">
+        <v>1164</v>
+      </c>
+      <c r="L223" t="s">
+        <v>19</v>
+      </c>
+      <c r="M223" t="s">
+        <v>22</v>
+      </c>
+      <c r="N223" t="s">
         <v>1165</v>
       </c>
-      <c r="L223" t="s">
-        <v>19</v>
-      </c>
-      <c r="M223" t="s">
-        <v>22</v>
-      </c>
-      <c r="N223" t="s">
+      <c r="O223" t="s">
         <v>1166</v>
       </c>
-      <c r="O223" t="s">
+      <c r="P223" t="s">
         <v>1167</v>
-      </c>
-      <c r="P223" t="s">
-        <v>1168</v>
       </c>
     </row>
     <row r="224" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B224" t="s">
         <v>1169</v>
-      </c>
-      <c r="B224" t="s">
-        <v>1170</v>
       </c>
       <c r="C224" t="s">
         <v>18</v>
@@ -15699,7 +15696,7 @@
         <v>42</v>
       </c>
       <c r="K224" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="L224" t="b">
         <v>0</v>
@@ -15708,21 +15705,21 @@
         <v>22</v>
       </c>
       <c r="N224" t="s">
+        <v>1171</v>
+      </c>
+      <c r="O224" t="s">
         <v>1172</v>
       </c>
-      <c r="O224" t="s">
+      <c r="P224" t="s">
         <v>1173</v>
-      </c>
-      <c r="P224" t="s">
-        <v>1174</v>
       </c>
     </row>
     <row r="225" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B225" t="s">
         <v>1175</v>
-      </c>
-      <c r="B225" t="s">
-        <v>1176</v>
       </c>
       <c r="C225" t="s">
         <v>129</v>
@@ -15749,7 +15746,7 @@
         <v>42</v>
       </c>
       <c r="K225" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="L225" t="b">
         <v>1</v>
@@ -15758,21 +15755,21 @@
         <v>22</v>
       </c>
       <c r="N225" t="s">
+        <v>1177</v>
+      </c>
+      <c r="O225" t="s">
         <v>1178</v>
       </c>
-      <c r="O225" t="s">
+      <c r="P225" t="s">
         <v>1179</v>
-      </c>
-      <c r="P225" t="s">
-        <v>1180</v>
       </c>
     </row>
     <row r="226" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B226" t="s">
         <v>1181</v>
-      </c>
-      <c r="B226" t="s">
-        <v>1182</v>
       </c>
       <c r="C226" t="s">
         <v>18</v>
@@ -15799,7 +15796,7 @@
         <v>42</v>
       </c>
       <c r="K226" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L226" t="b">
         <v>1</v>
@@ -15808,21 +15805,21 @@
         <v>22</v>
       </c>
       <c r="N226" t="s">
+        <v>1183</v>
+      </c>
+      <c r="O226" t="s">
         <v>1184</v>
       </c>
-      <c r="O226" t="s">
+      <c r="P226" t="s">
         <v>1185</v>
-      </c>
-      <c r="P226" t="s">
-        <v>1186</v>
       </c>
     </row>
     <row r="227" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B227" t="s">
         <v>1187</v>
-      </c>
-      <c r="B227" t="s">
-        <v>1188</v>
       </c>
       <c r="C227" t="s">
         <v>18</v>
@@ -15849,30 +15846,30 @@
         <v>20</v>
       </c>
       <c r="K227" t="s">
+        <v>1188</v>
+      </c>
+      <c r="L227" t="s">
+        <v>19</v>
+      </c>
+      <c r="M227" t="s">
+        <v>22</v>
+      </c>
+      <c r="N227" t="s">
         <v>1189</v>
       </c>
-      <c r="L227" t="s">
-        <v>19</v>
-      </c>
-      <c r="M227" t="s">
-        <v>22</v>
-      </c>
-      <c r="N227" t="s">
+      <c r="O227" t="s">
         <v>1190</v>
       </c>
-      <c r="O227" t="s">
+      <c r="P227" t="s">
         <v>1191</v>
-      </c>
-      <c r="P227" t="s">
-        <v>1192</v>
       </c>
     </row>
     <row r="228" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B228" t="s">
         <v>1193</v>
-      </c>
-      <c r="B228" t="s">
-        <v>1194</v>
       </c>
       <c r="C228" t="s">
         <v>18</v>
@@ -15899,30 +15896,30 @@
         <v>20</v>
       </c>
       <c r="K228" t="s">
+        <v>1194</v>
+      </c>
+      <c r="L228" t="s">
+        <v>19</v>
+      </c>
+      <c r="M228" t="s">
+        <v>22</v>
+      </c>
+      <c r="N228" t="s">
         <v>1195</v>
       </c>
-      <c r="L228" t="s">
-        <v>19</v>
-      </c>
-      <c r="M228" t="s">
-        <v>22</v>
-      </c>
-      <c r="N228" t="s">
+      <c r="O228" t="s">
         <v>1196</v>
       </c>
-      <c r="O228" t="s">
+      <c r="P228" t="s">
         <v>1197</v>
-      </c>
-      <c r="P228" t="s">
-        <v>1198</v>
       </c>
     </row>
     <row r="229" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B229" t="s">
         <v>1199</v>
-      </c>
-      <c r="B229" t="s">
-        <v>1200</v>
       </c>
       <c r="C229" t="s">
         <v>40</v>
@@ -15949,7 +15946,7 @@
         <v>42</v>
       </c>
       <c r="K229" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="L229" t="b">
         <v>1</v>
@@ -15958,21 +15955,21 @@
         <v>22</v>
       </c>
       <c r="N229" t="s">
+        <v>1201</v>
+      </c>
+      <c r="O229" t="s">
         <v>1202</v>
       </c>
-      <c r="O229" t="s">
+      <c r="P229" t="s">
         <v>1203</v>
-      </c>
-      <c r="P229" t="s">
-        <v>1204</v>
       </c>
     </row>
     <row r="230" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B230" t="s">
         <v>1205</v>
-      </c>
-      <c r="B230" t="s">
-        <v>1206</v>
       </c>
       <c r="C230" t="s">
         <v>18</v>
@@ -15993,39 +15990,39 @@
         <v>0</v>
       </c>
       <c r="I230" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="J230" t="s">
         <v>20</v>
       </c>
       <c r="K230" t="s">
+        <v>1207</v>
+      </c>
+      <c r="L230" t="s">
+        <v>19</v>
+      </c>
+      <c r="M230" t="s">
+        <v>22</v>
+      </c>
+      <c r="N230" t="s">
         <v>1208</v>
       </c>
-      <c r="L230" t="s">
-        <v>19</v>
-      </c>
-      <c r="M230" t="s">
-        <v>22</v>
-      </c>
-      <c r="N230" t="s">
+      <c r="O230" t="s">
         <v>1209</v>
       </c>
-      <c r="O230" t="s">
+      <c r="P230" t="s">
         <v>1210</v>
-      </c>
-      <c r="P230" t="s">
-        <v>1211</v>
       </c>
     </row>
     <row r="231" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B231" t="s">
         <v>1212</v>
       </c>
-      <c r="B231" t="s">
+      <c r="C231" t="s">
         <v>1213</v>
-      </c>
-      <c r="C231" t="s">
-        <v>1214</v>
       </c>
       <c r="D231" t="b">
         <v>0</v>
@@ -16049,7 +16046,7 @@
         <v>42</v>
       </c>
       <c r="K231" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="L231" t="b">
         <v>1</v>
@@ -16058,24 +16055,24 @@
         <v>22</v>
       </c>
       <c r="N231" t="s">
+        <v>1215</v>
+      </c>
+      <c r="O231" t="s">
         <v>1216</v>
       </c>
-      <c r="O231" t="s">
+      <c r="P231" t="s">
         <v>1217</v>
-      </c>
-      <c r="P231" t="s">
-        <v>1218</v>
       </c>
     </row>
     <row r="232" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B232" t="s">
         <v>1219</v>
       </c>
-      <c r="B232" t="s">
+      <c r="C232" t="s">
         <v>1220</v>
-      </c>
-      <c r="C232" t="s">
-        <v>1221</v>
       </c>
       <c r="D232" t="b">
         <v>0</v>
@@ -16099,7 +16096,7 @@
         <v>42</v>
       </c>
       <c r="K232" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="L232" t="b">
         <v>1</v>
@@ -16108,21 +16105,21 @@
         <v>22</v>
       </c>
       <c r="N232" t="s">
+        <v>1222</v>
+      </c>
+      <c r="O232" t="s">
         <v>1223</v>
       </c>
-      <c r="O232" t="s">
+      <c r="P232" t="s">
         <v>1224</v>
-      </c>
-      <c r="P232" t="s">
-        <v>1225</v>
       </c>
     </row>
     <row r="233" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B233" t="s">
         <v>1226</v>
-      </c>
-      <c r="B233" t="s">
-        <v>1227</v>
       </c>
       <c r="C233" t="s">
         <v>18</v>
@@ -16149,30 +16146,30 @@
         <v>20</v>
       </c>
       <c r="K233" t="s">
+        <v>1227</v>
+      </c>
+      <c r="L233" t="s">
+        <v>19</v>
+      </c>
+      <c r="M233" t="s">
+        <v>22</v>
+      </c>
+      <c r="N233" t="s">
         <v>1228</v>
       </c>
-      <c r="L233" t="s">
-        <v>19</v>
-      </c>
-      <c r="M233" t="s">
-        <v>22</v>
-      </c>
-      <c r="N233" t="s">
+      <c r="O233" t="s">
         <v>1229</v>
       </c>
-      <c r="O233" t="s">
+      <c r="P233" t="s">
         <v>1230</v>
-      </c>
-      <c r="P233" t="s">
-        <v>1231</v>
       </c>
     </row>
     <row r="234" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="B234" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C234" t="s">
         <v>18</v>
@@ -16199,30 +16196,30 @@
         <v>20</v>
       </c>
       <c r="K234" t="s">
+        <v>1232</v>
+      </c>
+      <c r="L234" t="s">
+        <v>19</v>
+      </c>
+      <c r="M234" t="s">
+        <v>22</v>
+      </c>
+      <c r="N234" t="s">
         <v>1233</v>
       </c>
-      <c r="L234" t="s">
-        <v>19</v>
-      </c>
-      <c r="M234" t="s">
-        <v>22</v>
-      </c>
-      <c r="N234" t="s">
+      <c r="O234" t="s">
         <v>1234</v>
       </c>
-      <c r="O234" t="s">
+      <c r="P234" t="s">
         <v>1235</v>
-      </c>
-      <c r="P234" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="235" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="B235" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C235" t="s">
         <v>18</v>
@@ -16249,30 +16246,30 @@
         <v>20</v>
       </c>
       <c r="K235" t="s">
+        <v>1237</v>
+      </c>
+      <c r="L235" t="s">
+        <v>19</v>
+      </c>
+      <c r="M235" t="s">
+        <v>22</v>
+      </c>
+      <c r="N235" t="s">
         <v>1238</v>
       </c>
-      <c r="L235" t="s">
-        <v>19</v>
-      </c>
-      <c r="M235" t="s">
-        <v>22</v>
-      </c>
-      <c r="N235" t="s">
+      <c r="O235" t="s">
         <v>1239</v>
       </c>
-      <c r="O235" t="s">
+      <c r="P235" t="s">
         <v>1240</v>
-      </c>
-      <c r="P235" t="s">
-        <v>1241</v>
       </c>
     </row>
     <row r="236" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="B236" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C236" t="s">
         <v>18</v>
@@ -16299,30 +16296,30 @@
         <v>20</v>
       </c>
       <c r="K236" t="s">
+        <v>1242</v>
+      </c>
+      <c r="L236" t="s">
+        <v>19</v>
+      </c>
+      <c r="M236" t="s">
+        <v>22</v>
+      </c>
+      <c r="N236" t="s">
         <v>1243</v>
       </c>
-      <c r="L236" t="s">
-        <v>19</v>
-      </c>
-      <c r="M236" t="s">
-        <v>22</v>
-      </c>
-      <c r="N236" t="s">
+      <c r="O236" t="s">
         <v>1244</v>
       </c>
-      <c r="O236" t="s">
+      <c r="P236" t="s">
         <v>1245</v>
-      </c>
-      <c r="P236" t="s">
-        <v>1246</v>
       </c>
     </row>
     <row r="237" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="B237" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C237" t="s">
         <v>18</v>
@@ -16349,30 +16346,30 @@
         <v>20</v>
       </c>
       <c r="K237" t="s">
+        <v>1247</v>
+      </c>
+      <c r="L237" t="s">
+        <v>19</v>
+      </c>
+      <c r="M237" t="s">
+        <v>22</v>
+      </c>
+      <c r="N237" t="s">
         <v>1248</v>
       </c>
-      <c r="L237" t="s">
-        <v>19</v>
-      </c>
-      <c r="M237" t="s">
-        <v>22</v>
-      </c>
-      <c r="N237" t="s">
+      <c r="O237" t="s">
         <v>1249</v>
       </c>
-      <c r="O237" t="s">
+      <c r="P237" t="s">
         <v>1250</v>
-      </c>
-      <c r="P237" t="s">
-        <v>1251</v>
       </c>
     </row>
     <row r="238" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="B238" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C238" t="s">
         <v>18</v>
@@ -16399,30 +16396,30 @@
         <v>20</v>
       </c>
       <c r="K238" t="s">
+        <v>1252</v>
+      </c>
+      <c r="L238" t="s">
+        <v>19</v>
+      </c>
+      <c r="M238" t="s">
+        <v>22</v>
+      </c>
+      <c r="N238" t="s">
         <v>1253</v>
       </c>
-      <c r="L238" t="s">
-        <v>19</v>
-      </c>
-      <c r="M238" t="s">
-        <v>22</v>
-      </c>
-      <c r="N238" t="s">
+      <c r="O238" t="s">
         <v>1254</v>
       </c>
-      <c r="O238" t="s">
+      <c r="P238" t="s">
         <v>1255</v>
-      </c>
-      <c r="P238" t="s">
-        <v>1256</v>
       </c>
     </row>
     <row r="239" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="B239" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C239" t="s">
         <v>18</v>
@@ -16449,30 +16446,30 @@
         <v>20</v>
       </c>
       <c r="K239" t="s">
+        <v>1257</v>
+      </c>
+      <c r="L239" t="s">
+        <v>19</v>
+      </c>
+      <c r="M239" t="s">
+        <v>22</v>
+      </c>
+      <c r="N239" t="s">
         <v>1258</v>
       </c>
-      <c r="L239" t="s">
-        <v>19</v>
-      </c>
-      <c r="M239" t="s">
-        <v>22</v>
-      </c>
-      <c r="N239" t="s">
+      <c r="O239" t="s">
         <v>1259</v>
       </c>
-      <c r="O239" t="s">
+      <c r="P239" t="s">
         <v>1260</v>
-      </c>
-      <c r="P239" t="s">
-        <v>1261</v>
       </c>
     </row>
     <row r="240" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B240" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C240" t="s">
         <v>18</v>
@@ -16499,30 +16496,30 @@
         <v>20</v>
       </c>
       <c r="K240" t="s">
+        <v>1262</v>
+      </c>
+      <c r="L240" t="s">
+        <v>19</v>
+      </c>
+      <c r="M240" t="s">
+        <v>22</v>
+      </c>
+      <c r="N240" t="s">
         <v>1263</v>
       </c>
-      <c r="L240" t="s">
-        <v>19</v>
-      </c>
-      <c r="M240" t="s">
-        <v>22</v>
-      </c>
-      <c r="N240" t="s">
+      <c r="O240" t="s">
         <v>1264</v>
       </c>
-      <c r="O240" t="s">
+      <c r="P240" t="s">
         <v>1265</v>
-      </c>
-      <c r="P240" t="s">
-        <v>1266</v>
       </c>
     </row>
     <row r="241" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="B241" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C241" t="s">
         <v>18</v>
@@ -16549,30 +16546,30 @@
         <v>20</v>
       </c>
       <c r="K241" t="s">
+        <v>1267</v>
+      </c>
+      <c r="L241" t="s">
+        <v>19</v>
+      </c>
+      <c r="M241" t="s">
+        <v>22</v>
+      </c>
+      <c r="N241" t="s">
         <v>1268</v>
       </c>
-      <c r="L241" t="s">
-        <v>19</v>
-      </c>
-      <c r="M241" t="s">
-        <v>22</v>
-      </c>
-      <c r="N241" t="s">
+      <c r="O241" t="s">
         <v>1269</v>
       </c>
-      <c r="O241" t="s">
+      <c r="P241" t="s">
         <v>1270</v>
-      </c>
-      <c r="P241" t="s">
-        <v>1271</v>
       </c>
     </row>
     <row r="242" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="B242" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C242" t="s">
         <v>18</v>
@@ -16599,30 +16596,30 @@
         <v>20</v>
       </c>
       <c r="K242" t="s">
+        <v>1272</v>
+      </c>
+      <c r="L242" t="s">
+        <v>19</v>
+      </c>
+      <c r="M242" t="s">
+        <v>22</v>
+      </c>
+      <c r="N242" t="s">
         <v>1273</v>
       </c>
-      <c r="L242" t="s">
-        <v>19</v>
-      </c>
-      <c r="M242" t="s">
-        <v>22</v>
-      </c>
-      <c r="N242" t="s">
+      <c r="O242" t="s">
         <v>1274</v>
       </c>
-      <c r="O242" t="s">
+      <c r="P242" t="s">
         <v>1275</v>
-      </c>
-      <c r="P242" t="s">
-        <v>1276</v>
       </c>
     </row>
     <row r="243" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="B243" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C243" t="s">
         <v>18</v>
@@ -16649,30 +16646,30 @@
         <v>20</v>
       </c>
       <c r="K243" t="s">
+        <v>1277</v>
+      </c>
+      <c r="L243" t="s">
+        <v>19</v>
+      </c>
+      <c r="M243" t="s">
+        <v>22</v>
+      </c>
+      <c r="N243" t="s">
         <v>1278</v>
       </c>
-      <c r="L243" t="s">
-        <v>19</v>
-      </c>
-      <c r="M243" t="s">
-        <v>22</v>
-      </c>
-      <c r="N243" t="s">
+      <c r="O243" t="s">
         <v>1279</v>
       </c>
-      <c r="O243" t="s">
+      <c r="P243" t="s">
         <v>1280</v>
-      </c>
-      <c r="P243" t="s">
-        <v>1281</v>
       </c>
     </row>
     <row r="244" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="B244" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C244" t="s">
         <v>18</v>
@@ -16699,30 +16696,30 @@
         <v>20</v>
       </c>
       <c r="K244" t="s">
+        <v>1282</v>
+      </c>
+      <c r="L244" t="s">
+        <v>19</v>
+      </c>
+      <c r="M244" t="s">
+        <v>22</v>
+      </c>
+      <c r="N244" t="s">
         <v>1283</v>
       </c>
-      <c r="L244" t="s">
-        <v>19</v>
-      </c>
-      <c r="M244" t="s">
-        <v>22</v>
-      </c>
-      <c r="N244" t="s">
+      <c r="O244" t="s">
         <v>1284</v>
       </c>
-      <c r="O244" t="s">
+      <c r="P244" t="s">
         <v>1285</v>
-      </c>
-      <c r="P244" t="s">
-        <v>1286</v>
       </c>
     </row>
     <row r="245" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="B245" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C245" t="s">
         <v>18</v>
@@ -16743,36 +16740,36 @@
         <v>0</v>
       </c>
       <c r="I245" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="J245" t="s">
         <v>20</v>
       </c>
       <c r="K245" t="s">
+        <v>1287</v>
+      </c>
+      <c r="L245" t="s">
+        <v>19</v>
+      </c>
+      <c r="M245" t="s">
+        <v>22</v>
+      </c>
+      <c r="N245" t="s">
         <v>1288</v>
       </c>
-      <c r="L245" t="s">
-        <v>19</v>
-      </c>
-      <c r="M245" t="s">
-        <v>22</v>
-      </c>
-      <c r="N245" t="s">
+      <c r="O245" t="s">
         <v>1289</v>
       </c>
-      <c r="O245" t="s">
+      <c r="P245" t="s">
         <v>1290</v>
-      </c>
-      <c r="P245" t="s">
-        <v>1291</v>
       </c>
     </row>
     <row r="246" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B246" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C246" t="s">
         <v>18</v>
@@ -16793,36 +16790,36 @@
         <v>0</v>
       </c>
       <c r="I246" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="J246" t="s">
         <v>20</v>
       </c>
       <c r="K246" t="s">
+        <v>1292</v>
+      </c>
+      <c r="L246" t="s">
+        <v>19</v>
+      </c>
+      <c r="M246" t="s">
+        <v>22</v>
+      </c>
+      <c r="N246" t="s">
         <v>1293</v>
       </c>
-      <c r="L246" t="s">
-        <v>19</v>
-      </c>
-      <c r="M246" t="s">
-        <v>22</v>
-      </c>
-      <c r="N246" t="s">
+      <c r="O246" t="s">
         <v>1294</v>
       </c>
-      <c r="O246" t="s">
+      <c r="P246" t="s">
         <v>1295</v>
-      </c>
-      <c r="P246" t="s">
-        <v>1296</v>
       </c>
     </row>
     <row r="247" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="B247" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C247" t="s">
         <v>18</v>
@@ -16843,36 +16840,36 @@
         <v>0</v>
       </c>
       <c r="I247" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="J247" t="s">
         <v>20</v>
       </c>
       <c r="K247" t="s">
+        <v>1297</v>
+      </c>
+      <c r="L247" t="s">
+        <v>19</v>
+      </c>
+      <c r="M247" t="s">
+        <v>22</v>
+      </c>
+      <c r="N247" t="s">
         <v>1298</v>
       </c>
-      <c r="L247" t="s">
-        <v>19</v>
-      </c>
-      <c r="M247" t="s">
-        <v>22</v>
-      </c>
-      <c r="N247" t="s">
+      <c r="O247" t="s">
         <v>1299</v>
       </c>
-      <c r="O247" t="s">
+      <c r="P247" t="s">
         <v>1300</v>
-      </c>
-      <c r="P247" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="248" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="B248" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C248" t="s">
         <v>18</v>
@@ -16893,36 +16890,36 @@
         <v>0</v>
       </c>
       <c r="I248" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="J248" t="s">
         <v>20</v>
       </c>
       <c r="K248" t="s">
+        <v>1302</v>
+      </c>
+      <c r="L248" t="s">
+        <v>19</v>
+      </c>
+      <c r="M248" t="s">
+        <v>22</v>
+      </c>
+      <c r="N248" t="s">
         <v>1303</v>
       </c>
-      <c r="L248" t="s">
-        <v>19</v>
-      </c>
-      <c r="M248" t="s">
-        <v>22</v>
-      </c>
-      <c r="N248" t="s">
+      <c r="O248" t="s">
         <v>1304</v>
       </c>
-      <c r="O248" t="s">
+      <c r="P248" t="s">
         <v>1305</v>
-      </c>
-      <c r="P248" t="s">
-        <v>1306</v>
       </c>
     </row>
     <row r="249" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="B249" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C249" t="s">
         <v>18</v>
@@ -16943,36 +16940,36 @@
         <v>0</v>
       </c>
       <c r="I249" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="J249" t="s">
         <v>20</v>
       </c>
       <c r="K249" t="s">
+        <v>1307</v>
+      </c>
+      <c r="L249" t="s">
+        <v>19</v>
+      </c>
+      <c r="M249" t="s">
+        <v>22</v>
+      </c>
+      <c r="N249" t="s">
         <v>1308</v>
       </c>
-      <c r="L249" t="s">
-        <v>19</v>
-      </c>
-      <c r="M249" t="s">
-        <v>22</v>
-      </c>
-      <c r="N249" t="s">
+      <c r="O249" t="s">
         <v>1309</v>
       </c>
-      <c r="O249" t="s">
+      <c r="P249" t="s">
         <v>1310</v>
-      </c>
-      <c r="P249" t="s">
-        <v>1311</v>
       </c>
     </row>
     <row r="250" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="B250" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C250" t="s">
         <v>18</v>
@@ -16999,27 +16996,27 @@
         <v>20</v>
       </c>
       <c r="K250" t="s">
+        <v>1312</v>
+      </c>
+      <c r="L250" t="s">
+        <v>19</v>
+      </c>
+      <c r="M250" t="s">
+        <v>22</v>
+      </c>
+      <c r="N250" t="s">
         <v>1313</v>
       </c>
-      <c r="L250" t="s">
-        <v>19</v>
-      </c>
-      <c r="M250" t="s">
-        <v>22</v>
-      </c>
-      <c r="N250" t="s">
+      <c r="O250" t="s">
         <v>1314</v>
       </c>
-      <c r="O250" t="s">
+      <c r="P250" t="s">
         <v>1315</v>
-      </c>
-      <c r="P250" t="s">
-        <v>1316</v>
       </c>
     </row>
     <row r="251" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="B251" t="s">
         <v>19</v>
@@ -17049,7 +17046,7 @@
         <v>19</v>
       </c>
       <c r="K251" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="L251" t="s">
         <v>19</v>
@@ -17058,21 +17055,21 @@
         <v>326</v>
       </c>
       <c r="N251" t="s">
+        <v>1318</v>
+      </c>
+      <c r="O251" t="s">
+        <v>19</v>
+      </c>
+      <c r="P251" t="s">
         <v>1319</v>
-      </c>
-      <c r="O251" t="s">
-        <v>19</v>
-      </c>
-      <c r="P251" t="s">
-        <v>1320</v>
       </c>
     </row>
     <row r="252" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="B252" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C252" t="s">
         <v>18</v>
@@ -17093,36 +17090,36 @@
         <v>0</v>
       </c>
       <c r="I252" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="J252" t="s">
         <v>20</v>
       </c>
       <c r="K252" t="s">
+        <v>1321</v>
+      </c>
+      <c r="L252" t="s">
+        <v>19</v>
+      </c>
+      <c r="M252" t="s">
+        <v>22</v>
+      </c>
+      <c r="N252" t="s">
         <v>1322</v>
       </c>
-      <c r="L252" t="s">
-        <v>19</v>
-      </c>
-      <c r="M252" t="s">
-        <v>22</v>
-      </c>
-      <c r="N252" t="s">
+      <c r="O252" t="s">
         <v>1323</v>
       </c>
-      <c r="O252" t="s">
-        <v>1324</v>
-      </c>
       <c r="P252" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="253" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="B253" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C253" t="s">
         <v>18</v>
@@ -17143,36 +17140,36 @@
         <v>0</v>
       </c>
       <c r="I253" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="J253" t="s">
         <v>20</v>
       </c>
       <c r="K253" t="s">
+        <v>1325</v>
+      </c>
+      <c r="L253" t="s">
+        <v>19</v>
+      </c>
+      <c r="M253" t="s">
+        <v>22</v>
+      </c>
+      <c r="N253" t="s">
         <v>1326</v>
       </c>
-      <c r="L253" t="s">
-        <v>19</v>
-      </c>
-      <c r="M253" t="s">
-        <v>22</v>
-      </c>
-      <c r="N253" t="s">
+      <c r="O253" t="s">
         <v>1327</v>
       </c>
-      <c r="O253" t="s">
+      <c r="P253" t="s">
         <v>1328</v>
-      </c>
-      <c r="P253" t="s">
-        <v>1329</v>
       </c>
     </row>
     <row r="254" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="B254" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C254" t="s">
         <v>18</v>
@@ -17193,36 +17190,36 @@
         <v>0</v>
       </c>
       <c r="I254" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="J254" t="s">
         <v>20</v>
       </c>
       <c r="K254" t="s">
+        <v>1330</v>
+      </c>
+      <c r="L254" t="s">
+        <v>19</v>
+      </c>
+      <c r="M254" t="s">
+        <v>22</v>
+      </c>
+      <c r="N254" t="s">
         <v>1331</v>
       </c>
-      <c r="L254" t="s">
-        <v>19</v>
-      </c>
-      <c r="M254" t="s">
-        <v>22</v>
-      </c>
-      <c r="N254" t="s">
+      <c r="O254" t="s">
         <v>1332</v>
       </c>
-      <c r="O254" t="s">
+      <c r="P254" t="s">
         <v>1333</v>
-      </c>
-      <c r="P254" t="s">
-        <v>1334</v>
       </c>
     </row>
     <row r="255" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="B255" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C255" t="s">
         <v>18</v>
@@ -17243,36 +17240,36 @@
         <v>0</v>
       </c>
       <c r="I255" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="J255" t="s">
         <v>20</v>
       </c>
       <c r="K255" t="s">
+        <v>1335</v>
+      </c>
+      <c r="L255" t="s">
+        <v>19</v>
+      </c>
+      <c r="M255" t="s">
+        <v>22</v>
+      </c>
+      <c r="N255" t="s">
         <v>1336</v>
       </c>
-      <c r="L255" t="s">
-        <v>19</v>
-      </c>
-      <c r="M255" t="s">
-        <v>22</v>
-      </c>
-      <c r="N255" t="s">
+      <c r="O255" t="s">
         <v>1337</v>
       </c>
-      <c r="O255" t="s">
+      <c r="P255" t="s">
         <v>1338</v>
-      </c>
-      <c r="P255" t="s">
-        <v>1339</v>
       </c>
     </row>
     <row r="256" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="B256" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C256" t="s">
         <v>18</v>
@@ -17293,36 +17290,36 @@
         <v>0</v>
       </c>
       <c r="I256" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="J256" t="s">
         <v>20</v>
       </c>
       <c r="K256" t="s">
+        <v>1340</v>
+      </c>
+      <c r="L256" t="s">
+        <v>19</v>
+      </c>
+      <c r="M256" t="s">
+        <v>22</v>
+      </c>
+      <c r="N256" t="s">
         <v>1341</v>
       </c>
-      <c r="L256" t="s">
-        <v>19</v>
-      </c>
-      <c r="M256" t="s">
-        <v>22</v>
-      </c>
-      <c r="N256" t="s">
+      <c r="O256" t="s">
         <v>1342</v>
       </c>
-      <c r="O256" t="s">
+      <c r="P256" t="s">
         <v>1343</v>
-      </c>
-      <c r="P256" t="s">
-        <v>1344</v>
       </c>
     </row>
     <row r="257" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="B257" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C257" t="s">
         <v>18</v>
@@ -17343,33 +17340,33 @@
         <v>0</v>
       </c>
       <c r="I257" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="J257" t="s">
         <v>20</v>
       </c>
       <c r="K257" t="s">
+        <v>1345</v>
+      </c>
+      <c r="L257" t="s">
+        <v>19</v>
+      </c>
+      <c r="M257" t="s">
+        <v>22</v>
+      </c>
+      <c r="N257" t="s">
         <v>1346</v>
       </c>
-      <c r="L257" t="s">
-        <v>19</v>
-      </c>
-      <c r="M257" t="s">
-        <v>22</v>
-      </c>
-      <c r="N257" t="s">
+      <c r="O257" t="s">
         <v>1347</v>
       </c>
-      <c r="O257" t="s">
+      <c r="P257" t="s">
         <v>1348</v>
-      </c>
-      <c r="P257" t="s">
-        <v>1349</v>
       </c>
     </row>
     <row r="258" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="B258" t="s">
         <v>18</v>
@@ -17399,7 +17396,7 @@
         <v>42</v>
       </c>
       <c r="K258" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="L258" t="b">
         <v>0</v>
@@ -17408,21 +17405,21 @@
         <v>22</v>
       </c>
       <c r="N258" t="s">
+        <v>1351</v>
+      </c>
+      <c r="O258" t="s">
         <v>1352</v>
       </c>
-      <c r="O258" t="s">
+      <c r="P258" t="s">
         <v>1353</v>
-      </c>
-      <c r="P258" t="s">
-        <v>1354</v>
       </c>
     </row>
     <row r="259" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="B259" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C259" t="s">
         <v>18</v>
@@ -17443,39 +17440,39 @@
         <v>0</v>
       </c>
       <c r="I259" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="J259" t="s">
         <v>20</v>
       </c>
       <c r="K259" t="s">
+        <v>1355</v>
+      </c>
+      <c r="L259" t="s">
+        <v>19</v>
+      </c>
+      <c r="M259" t="s">
+        <v>22</v>
+      </c>
+      <c r="N259" t="s">
         <v>1356</v>
       </c>
-      <c r="L259" t="s">
-        <v>19</v>
-      </c>
-      <c r="M259" t="s">
-        <v>22</v>
-      </c>
-      <c r="N259" t="s">
+      <c r="O259" t="s">
         <v>1357</v>
       </c>
-      <c r="O259" t="s">
+      <c r="P259" t="s">
         <v>1358</v>
-      </c>
-      <c r="P259" t="s">
-        <v>1359</v>
       </c>
     </row>
     <row r="260" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B260" t="s">
         <v>1360</v>
       </c>
-      <c r="B260" t="s">
+      <c r="C260" t="s">
         <v>1361</v>
-      </c>
-      <c r="C260" t="s">
-        <v>1362</v>
       </c>
       <c r="D260" t="b">
         <v>0</v>
@@ -17499,7 +17496,7 @@
         <v>42</v>
       </c>
       <c r="K260" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="L260" t="b">
         <v>1</v>
@@ -17508,13 +17505,13 @@
         <v>22</v>
       </c>
       <c r="N260" t="s">
+        <v>1363</v>
+      </c>
+      <c r="O260" t="s">
         <v>1364</v>
       </c>
-      <c r="O260" t="s">
+      <c r="P260" t="s">
         <v>1365</v>
-      </c>
-      <c r="P260" t="s">
-        <v>1366</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-grace-master.report.xlsx
+++ b/tools/importer/reports/import-grace-master.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3664" uniqueCount="1366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3663" uniqueCount="1367">
   <si>
     <t>_reportFile</t>
   </si>
@@ -3153,7 +3153,10 @@
     <t>products/metallocenes</t>
   </si>
   <si>
-    <t>2026-08-11T20:16:13.549Z</t>
+    <t>2026-08-11T23:25:00.988Z</t>
+  </si>
+  <si>
+    <t>Metallocenes</t>
   </si>
   <si>
     <t>https://grace.com/products/metallocenes/</t>
@@ -3165,7 +3168,7 @@
     <t>products/polytrak-catalysts</t>
   </si>
   <si>
-    <t>2026-08-09T21:33:17.355Z</t>
+    <t>2026-08-11T23:25:53.875Z</t>
   </si>
   <si>
     <t>POLYTRAK® Catalysts</t>
@@ -3372,7 +3375,7 @@
     <t>products/sylosiv</t>
   </si>
   <si>
-    <t>2026-08-09T21:44:59.032Z</t>
+    <t>2026-08-11T23:26:48.052Z</t>
   </si>
   <si>
     <t>SYLOSIV®</t>
@@ -14519,10 +14522,10 @@
         <v>1044</v>
       </c>
       <c r="B201" t="s">
-        <v>19</v>
+        <v>979</v>
       </c>
       <c r="C201" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D201" t="s">
         <v>19</v>
@@ -14531,19 +14534,19 @@
         <v>19</v>
       </c>
       <c r="F201" t="s">
-        <v>323</v>
+        <v>19</v>
       </c>
       <c r="G201" t="s">
-        <v>324</v>
-      </c>
-      <c r="H201" t="s">
-        <v>19</v>
+        <v>19</v>
+      </c>
+      <c r="H201" t="b">
+        <v>0</v>
       </c>
       <c r="I201" t="s">
-        <v>19</v>
+        <v>980</v>
       </c>
       <c r="J201" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K201" t="s">
         <v>1045</v>
@@ -14552,21 +14555,21 @@
         <v>19</v>
       </c>
       <c r="M201" t="s">
-        <v>326</v>
+        <v>22</v>
       </c>
       <c r="N201" t="s">
         <v>1046</v>
       </c>
       <c r="O201" t="s">
-        <v>19</v>
+        <v>1047</v>
       </c>
       <c r="P201" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="202" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B202" t="s">
         <v>979</v>
@@ -14596,7 +14599,7 @@
         <v>20</v>
       </c>
       <c r="K202" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="L202" t="s">
         <v>19</v>
@@ -14605,21 +14608,21 @@
         <v>22</v>
       </c>
       <c r="N202" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="O202" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="P202" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="203" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B203" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="C203" t="s">
         <v>18</v>
@@ -14646,7 +14649,7 @@
         <v>42</v>
       </c>
       <c r="K203" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="L203" t="b">
         <v>1</v>
@@ -14655,18 +14658,18 @@
         <v>22</v>
       </c>
       <c r="N203" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="O203" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="P203" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="204" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B204" t="s">
         <v>18</v>
@@ -14696,7 +14699,7 @@
         <v>42</v>
       </c>
       <c r="K204" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="L204" t="b">
         <v>1</v>
@@ -14705,21 +14708,21 @@
         <v>22</v>
       </c>
       <c r="N204" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="O204" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="P204" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="205" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B205" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C205" t="s">
         <v>18</v>
@@ -14746,7 +14749,7 @@
         <v>20</v>
       </c>
       <c r="K205" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="L205" t="s">
         <v>19</v>
@@ -14755,18 +14758,18 @@
         <v>22</v>
       </c>
       <c r="N205" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="O205" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="P205" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="206" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B206" t="s">
         <v>979</v>
@@ -14796,7 +14799,7 @@
         <v>20</v>
       </c>
       <c r="K206" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="L206" t="s">
         <v>19</v>
@@ -14805,21 +14808,21 @@
         <v>22</v>
       </c>
       <c r="N206" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="O206" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="P206" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="207" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B207" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="C207" t="s">
         <v>18</v>
@@ -14846,7 +14849,7 @@
         <v>20</v>
       </c>
       <c r="K207" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="L207" t="s">
         <v>19</v>
@@ -14855,18 +14858,18 @@
         <v>22</v>
       </c>
       <c r="N207" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="O207" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="P207" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="208" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B208" t="s">
         <v>1024</v>
@@ -14896,7 +14899,7 @@
         <v>20</v>
       </c>
       <c r="K208" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="L208" t="s">
         <v>19</v>
@@ -14905,21 +14908,21 @@
         <v>22</v>
       </c>
       <c r="N208" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="O208" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="P208" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="209" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B209" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C209" t="s">
         <v>18</v>
@@ -14946,7 +14949,7 @@
         <v>20</v>
       </c>
       <c r="K209" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="L209" t="s">
         <v>19</v>
@@ -14955,21 +14958,21 @@
         <v>22</v>
       </c>
       <c r="N209" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="O209" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="P209" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="210" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B210" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C210" t="s">
         <v>18</v>
@@ -14996,7 +14999,7 @@
         <v>20</v>
       </c>
       <c r="K210" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="L210" t="s">
         <v>19</v>
@@ -15005,21 +15008,21 @@
         <v>22</v>
       </c>
       <c r="N210" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="O210" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="P210" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="211" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B211" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="C211" t="s">
         <v>18</v>
@@ -15046,7 +15049,7 @@
         <v>20</v>
       </c>
       <c r="K211" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="L211" t="s">
         <v>19</v>
@@ -15055,21 +15058,21 @@
         <v>22</v>
       </c>
       <c r="N211" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="O211" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="P211" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="212" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B212" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C212" t="s">
         <v>18</v>
@@ -15096,7 +15099,7 @@
         <v>20</v>
       </c>
       <c r="K212" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="L212" t="s">
         <v>19</v>
@@ -15105,18 +15108,18 @@
         <v>22</v>
       </c>
       <c r="N212" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="O212" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="P212" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="213" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B213" t="s">
         <v>979</v>
@@ -15146,7 +15149,7 @@
         <v>20</v>
       </c>
       <c r="K213" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="L213" t="s">
         <v>19</v>
@@ -15155,18 +15158,18 @@
         <v>22</v>
       </c>
       <c r="N213" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="O213" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="P213" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="214" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B214" t="s">
         <v>979</v>
@@ -15196,7 +15199,7 @@
         <v>20</v>
       </c>
       <c r="K214" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="L214" t="s">
         <v>19</v>
@@ -15205,18 +15208,18 @@
         <v>22</v>
       </c>
       <c r="N214" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="O214" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="P214" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="215" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B215" t="s">
         <v>1024</v>
@@ -15246,7 +15249,7 @@
         <v>20</v>
       </c>
       <c r="K215" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="L215" t="s">
         <v>19</v>
@@ -15255,18 +15258,18 @@
         <v>22</v>
       </c>
       <c r="N215" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="O215" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="P215" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="216" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B216" t="s">
         <v>18</v>
@@ -15296,7 +15299,7 @@
         <v>42</v>
       </c>
       <c r="K216" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="L216" t="b">
         <v>1</v>
@@ -15305,21 +15308,21 @@
         <v>22</v>
       </c>
       <c r="N216" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="O216" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="P216" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="217" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B217" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="C217" t="s">
         <v>18</v>
@@ -15346,7 +15349,7 @@
         <v>20</v>
       </c>
       <c r="K217" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="L217" t="s">
         <v>19</v>
@@ -15355,21 +15358,21 @@
         <v>22</v>
       </c>
       <c r="N217" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="O217" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="P217" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="218" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B218" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="C218" t="s">
         <v>18</v>
@@ -15396,7 +15399,7 @@
         <v>20</v>
       </c>
       <c r="K218" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="L218" t="s">
         <v>19</v>
@@ -15405,18 +15408,18 @@
         <v>22</v>
       </c>
       <c r="N218" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="O218" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="P218" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="219" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B219" t="s">
         <v>979</v>
@@ -15446,7 +15449,7 @@
         <v>20</v>
       </c>
       <c r="K219" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="L219" t="s">
         <v>19</v>
@@ -15455,21 +15458,21 @@
         <v>22</v>
       </c>
       <c r="N219" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="O219" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="P219" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="220" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B220" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="C220" t="s">
         <v>18</v>
@@ -15496,7 +15499,7 @@
         <v>20</v>
       </c>
       <c r="K220" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="L220" t="s">
         <v>19</v>
@@ -15505,18 +15508,18 @@
         <v>22</v>
       </c>
       <c r="N220" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="O220" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="P220" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="221" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B221" t="s">
         <v>979</v>
@@ -15546,7 +15549,7 @@
         <v>20</v>
       </c>
       <c r="K221" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="L221" t="s">
         <v>19</v>
@@ -15555,21 +15558,21 @@
         <v>22</v>
       </c>
       <c r="N221" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="O221" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="P221" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="222" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B222" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="C222" t="s">
         <v>18</v>
@@ -15596,7 +15599,7 @@
         <v>20</v>
       </c>
       <c r="K222" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="L222" t="s">
         <v>19</v>
@@ -15605,24 +15608,24 @@
         <v>22</v>
       </c>
       <c r="N222" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="O222" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="P222" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="223" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B223" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="C223" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="D223" t="s">
         <v>19</v>
@@ -15646,7 +15649,7 @@
         <v>20</v>
       </c>
       <c r="K223" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="L223" t="s">
         <v>19</v>
@@ -15655,21 +15658,21 @@
         <v>22</v>
       </c>
       <c r="N223" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="O223" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="P223" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="224" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B224" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="C224" t="s">
         <v>18</v>
@@ -15696,7 +15699,7 @@
         <v>42</v>
       </c>
       <c r="K224" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="L224" t="b">
         <v>0</v>
@@ -15705,21 +15708,21 @@
         <v>22</v>
       </c>
       <c r="N224" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="O224" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="P224" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="225" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="B225" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="C225" t="s">
         <v>129</v>
@@ -15746,7 +15749,7 @@
         <v>42</v>
       </c>
       <c r="K225" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="L225" t="b">
         <v>1</v>
@@ -15755,21 +15758,21 @@
         <v>22</v>
       </c>
       <c r="N225" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="O225" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="P225" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="226" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B226" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="C226" t="s">
         <v>18</v>
@@ -15796,7 +15799,7 @@
         <v>42</v>
       </c>
       <c r="K226" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="L226" t="b">
         <v>1</v>
@@ -15805,21 +15808,21 @@
         <v>22</v>
       </c>
       <c r="N226" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="O226" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="P226" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="227" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B227" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="C227" t="s">
         <v>18</v>
@@ -15846,7 +15849,7 @@
         <v>20</v>
       </c>
       <c r="K227" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="L227" t="s">
         <v>19</v>
@@ -15855,21 +15858,21 @@
         <v>22</v>
       </c>
       <c r="N227" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="O227" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="P227" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="228" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="B228" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="C228" t="s">
         <v>18</v>
@@ -15896,7 +15899,7 @@
         <v>20</v>
       </c>
       <c r="K228" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="L228" t="s">
         <v>19</v>
@@ -15905,21 +15908,21 @@
         <v>22</v>
       </c>
       <c r="N228" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="O228" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="P228" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="229" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B229" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="C229" t="s">
         <v>40</v>
@@ -15946,7 +15949,7 @@
         <v>42</v>
       </c>
       <c r="K229" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="L229" t="b">
         <v>1</v>
@@ -15955,21 +15958,21 @@
         <v>22</v>
       </c>
       <c r="N229" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="O229" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="P229" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="230" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B230" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="C230" t="s">
         <v>18</v>
@@ -15990,13 +15993,13 @@
         <v>0</v>
       </c>
       <c r="I230" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="J230" t="s">
         <v>20</v>
       </c>
       <c r="K230" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="L230" t="s">
         <v>19</v>
@@ -16005,24 +16008,24 @@
         <v>22</v>
       </c>
       <c r="N230" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="O230" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="P230" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="231" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="B231" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="C231" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="D231" t="b">
         <v>0</v>
@@ -16046,7 +16049,7 @@
         <v>42</v>
       </c>
       <c r="K231" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="L231" t="b">
         <v>1</v>
@@ -16055,24 +16058,24 @@
         <v>22</v>
       </c>
       <c r="N231" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="O231" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="P231" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="232" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B232" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="C232" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="D232" t="b">
         <v>0</v>
@@ -16096,7 +16099,7 @@
         <v>42</v>
       </c>
       <c r="K232" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="L232" t="b">
         <v>1</v>
@@ -16105,21 +16108,21 @@
         <v>22</v>
       </c>
       <c r="N232" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="O232" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="P232" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="233" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B233" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C233" t="s">
         <v>18</v>
@@ -16146,7 +16149,7 @@
         <v>20</v>
       </c>
       <c r="K233" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="L233" t="s">
         <v>19</v>
@@ -16155,21 +16158,21 @@
         <v>22</v>
       </c>
       <c r="N233" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="O233" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="P233" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="234" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B234" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C234" t="s">
         <v>18</v>
@@ -16196,7 +16199,7 @@
         <v>20</v>
       </c>
       <c r="K234" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="L234" t="s">
         <v>19</v>
@@ -16205,21 +16208,21 @@
         <v>22</v>
       </c>
       <c r="N234" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="O234" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="P234" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="235" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B235" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C235" t="s">
         <v>18</v>
@@ -16246,7 +16249,7 @@
         <v>20</v>
       </c>
       <c r="K235" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="L235" t="s">
         <v>19</v>
@@ -16255,21 +16258,21 @@
         <v>22</v>
       </c>
       <c r="N235" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="O235" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="P235" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="236" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B236" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C236" t="s">
         <v>18</v>
@@ -16296,7 +16299,7 @@
         <v>20</v>
       </c>
       <c r="K236" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="L236" t="s">
         <v>19</v>
@@ -16305,21 +16308,21 @@
         <v>22</v>
       </c>
       <c r="N236" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="O236" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="P236" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="237" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B237" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C237" t="s">
         <v>18</v>
@@ -16346,7 +16349,7 @@
         <v>20</v>
       </c>
       <c r="K237" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="L237" t="s">
         <v>19</v>
@@ -16355,21 +16358,21 @@
         <v>22</v>
       </c>
       <c r="N237" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="O237" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="P237" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="238" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="B238" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C238" t="s">
         <v>18</v>
@@ -16396,7 +16399,7 @@
         <v>20</v>
       </c>
       <c r="K238" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="L238" t="s">
         <v>19</v>
@@ -16405,21 +16408,21 @@
         <v>22</v>
       </c>
       <c r="N238" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="O238" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="P238" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="239" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B239" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C239" t="s">
         <v>18</v>
@@ -16446,7 +16449,7 @@
         <v>20</v>
       </c>
       <c r="K239" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="L239" t="s">
         <v>19</v>
@@ -16455,21 +16458,21 @@
         <v>22</v>
       </c>
       <c r="N239" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="O239" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="P239" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="240" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="B240" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C240" t="s">
         <v>18</v>
@@ -16496,7 +16499,7 @@
         <v>20</v>
       </c>
       <c r="K240" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="L240" t="s">
         <v>19</v>
@@ -16505,21 +16508,21 @@
         <v>22</v>
       </c>
       <c r="N240" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="O240" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="P240" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="241" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="B241" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C241" t="s">
         <v>18</v>
@@ -16546,7 +16549,7 @@
         <v>20</v>
       </c>
       <c r="K241" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="L241" t="s">
         <v>19</v>
@@ -16555,21 +16558,21 @@
         <v>22</v>
       </c>
       <c r="N241" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="O241" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="P241" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="242" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="B242" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C242" t="s">
         <v>18</v>
@@ -16596,7 +16599,7 @@
         <v>20</v>
       </c>
       <c r="K242" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="L242" t="s">
         <v>19</v>
@@ -16605,21 +16608,21 @@
         <v>22</v>
       </c>
       <c r="N242" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="O242" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="P242" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="243" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B243" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C243" t="s">
         <v>18</v>
@@ -16646,7 +16649,7 @@
         <v>20</v>
       </c>
       <c r="K243" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="L243" t="s">
         <v>19</v>
@@ -16655,21 +16658,21 @@
         <v>22</v>
       </c>
       <c r="N243" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="O243" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="P243" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="244" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B244" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C244" t="s">
         <v>18</v>
@@ -16696,7 +16699,7 @@
         <v>20</v>
       </c>
       <c r="K244" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="L244" t="s">
         <v>19</v>
@@ -16705,21 +16708,21 @@
         <v>22</v>
       </c>
       <c r="N244" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="O244" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="P244" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="245" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B245" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C245" t="s">
         <v>18</v>
@@ -16740,13 +16743,13 @@
         <v>0</v>
       </c>
       <c r="I245" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="J245" t="s">
         <v>20</v>
       </c>
       <c r="K245" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="L245" t="s">
         <v>19</v>
@@ -16755,21 +16758,21 @@
         <v>22</v>
       </c>
       <c r="N245" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="O245" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="P245" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="246" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="B246" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C246" t="s">
         <v>18</v>
@@ -16790,13 +16793,13 @@
         <v>0</v>
       </c>
       <c r="I246" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="J246" t="s">
         <v>20</v>
       </c>
       <c r="K246" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="L246" t="s">
         <v>19</v>
@@ -16805,21 +16808,21 @@
         <v>22</v>
       </c>
       <c r="N246" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="O246" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="P246" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="247" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="B247" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C247" t="s">
         <v>18</v>
@@ -16840,13 +16843,13 @@
         <v>0</v>
       </c>
       <c r="I247" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="J247" t="s">
         <v>20</v>
       </c>
       <c r="K247" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="L247" t="s">
         <v>19</v>
@@ -16855,21 +16858,21 @@
         <v>22</v>
       </c>
       <c r="N247" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="O247" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="P247" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="248" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="B248" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C248" t="s">
         <v>18</v>
@@ -16890,13 +16893,13 @@
         <v>0</v>
       </c>
       <c r="I248" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="J248" t="s">
         <v>20</v>
       </c>
       <c r="K248" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="L248" t="s">
         <v>19</v>
@@ -16905,21 +16908,21 @@
         <v>22</v>
       </c>
       <c r="N248" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="O248" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="P248" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="249" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="B249" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C249" t="s">
         <v>18</v>
@@ -16940,13 +16943,13 @@
         <v>0</v>
       </c>
       <c r="I249" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="J249" t="s">
         <v>20</v>
       </c>
       <c r="K249" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="L249" t="s">
         <v>19</v>
@@ -16955,21 +16958,21 @@
         <v>22</v>
       </c>
       <c r="N249" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="O249" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="P249" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="250" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="B250" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C250" t="s">
         <v>18</v>
@@ -16996,7 +16999,7 @@
         <v>20</v>
       </c>
       <c r="K250" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="L250" t="s">
         <v>19</v>
@@ -17005,18 +17008,18 @@
         <v>22</v>
       </c>
       <c r="N250" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="O250" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="P250" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="251" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="B251" t="s">
         <v>19</v>
@@ -17046,7 +17049,7 @@
         <v>19</v>
       </c>
       <c r="K251" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="L251" t="s">
         <v>19</v>
@@ -17055,21 +17058,21 @@
         <v>326</v>
       </c>
       <c r="N251" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="O251" t="s">
         <v>19</v>
       </c>
       <c r="P251" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="252" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B252" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C252" t="s">
         <v>18</v>
@@ -17090,13 +17093,13 @@
         <v>0</v>
       </c>
       <c r="I252" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="J252" t="s">
         <v>20</v>
       </c>
       <c r="K252" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="L252" t="s">
         <v>19</v>
@@ -17105,21 +17108,21 @@
         <v>22</v>
       </c>
       <c r="N252" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="O252" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="P252" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="253" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B253" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C253" t="s">
         <v>18</v>
@@ -17140,13 +17143,13 @@
         <v>0</v>
       </c>
       <c r="I253" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="J253" t="s">
         <v>20</v>
       </c>
       <c r="K253" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="L253" t="s">
         <v>19</v>
@@ -17155,21 +17158,21 @@
         <v>22</v>
       </c>
       <c r="N253" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="O253" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="P253" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="254" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="B254" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C254" t="s">
         <v>18</v>
@@ -17190,13 +17193,13 @@
         <v>0</v>
       </c>
       <c r="I254" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="J254" t="s">
         <v>20</v>
       </c>
       <c r="K254" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="L254" t="s">
         <v>19</v>
@@ -17205,21 +17208,21 @@
         <v>22</v>
       </c>
       <c r="N254" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="O254" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="P254" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="255" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="B255" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C255" t="s">
         <v>18</v>
@@ -17240,13 +17243,13 @@
         <v>0</v>
       </c>
       <c r="I255" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="J255" t="s">
         <v>20</v>
       </c>
       <c r="K255" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="L255" t="s">
         <v>19</v>
@@ -17255,21 +17258,21 @@
         <v>22</v>
       </c>
       <c r="N255" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="O255" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="P255" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="256" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="B256" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C256" t="s">
         <v>18</v>
@@ -17290,13 +17293,13 @@
         <v>0</v>
       </c>
       <c r="I256" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="J256" t="s">
         <v>20</v>
       </c>
       <c r="K256" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="L256" t="s">
         <v>19</v>
@@ -17305,21 +17308,21 @@
         <v>22</v>
       </c>
       <c r="N256" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="O256" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="P256" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="257" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B257" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C257" t="s">
         <v>18</v>
@@ -17340,13 +17343,13 @@
         <v>0</v>
       </c>
       <c r="I257" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="J257" t="s">
         <v>20</v>
       </c>
       <c r="K257" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="L257" t="s">
         <v>19</v>
@@ -17355,18 +17358,18 @@
         <v>22</v>
       </c>
       <c r="N257" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="O257" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="P257" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="258" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B258" t="s">
         <v>18</v>
@@ -17396,7 +17399,7 @@
         <v>42</v>
       </c>
       <c r="K258" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="L258" t="b">
         <v>0</v>
@@ -17405,21 +17408,21 @@
         <v>22</v>
       </c>
       <c r="N258" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="O258" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="P258" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="259" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="B259" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C259" t="s">
         <v>18</v>
@@ -17440,13 +17443,13 @@
         <v>0</v>
       </c>
       <c r="I259" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="J259" t="s">
         <v>20</v>
       </c>
       <c r="K259" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="L259" t="s">
         <v>19</v>
@@ -17455,24 +17458,24 @@
         <v>22</v>
       </c>
       <c r="N259" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="O259" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="P259" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="260" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B260" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="C260" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="D260" t="b">
         <v>0</v>
@@ -17496,7 +17499,7 @@
         <v>42</v>
       </c>
       <c r="K260" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="L260" t="b">
         <v>1</v>
@@ -17505,13 +17508,13 @@
         <v>22</v>
       </c>
       <c r="N260" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="O260" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="P260" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-grace-master.report.xlsx
+++ b/tools/importer/reports/import-grace-master.report.xlsx
@@ -184,7 +184,7 @@
     <t>industries</t>
   </si>
   <si>
-    <t>2026-08-13T13:25:28.088Z</t>
+    <t>2026-08-13T19:41:36.954Z</t>
   </si>
   <si>
     <t>Industries</t>
@@ -406,7 +406,7 @@
     <t>industries/agriculture</t>
   </si>
   <si>
-    <t>2026-08-13T14:41:59.447Z</t>
+    <t>2026-08-13T19:51:26.890Z</t>
   </si>
   <si>
     <t>Agriculture</t>
@@ -424,7 +424,7 @@
     <t>industries/biofuels</t>
   </si>
   <si>
-    <t>2026-08-13T14:51:55.168Z</t>
+    <t>2026-08-13T20:01:18.343Z</t>
   </si>
   <si>
     <t>Biofuels</t>
@@ -442,7 +442,7 @@
     <t>industries/chemical-processing</t>
   </si>
   <si>
-    <t>2026-08-13T13:45:15.502Z</t>
+    <t>2026-08-13T20:01:39.575Z</t>
   </si>
   <si>
     <t>Chemical Processing</t>
@@ -460,7 +460,7 @@
     <t>industries/coatings</t>
   </si>
   <si>
-    <t>2026-08-13T14:08:35.990Z</t>
+    <t>2026-08-13T19:42:33.595Z</t>
   </si>
   <si>
     <t>Coatings</t>
@@ -475,7 +475,7 @@
     <t>industries/food-beverage</t>
   </si>
   <si>
-    <t>2026-08-13T14:47:22.546Z</t>
+    <t>2026-08-13T19:56:49.090Z</t>
   </si>
   <si>
     <t>Food and Beverage</t>
@@ -493,7 +493,7 @@
     <t>industries/general-industrial</t>
   </si>
   <si>
-    <t>2026-08-13T14:13:58.101Z</t>
+    <t>2026-08-13T19:47:59.907Z</t>
   </si>
   <si>
     <t>General Industrial</t>
@@ -511,7 +511,7 @@
     <t>industries/nutraceutical-solutions</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:33.678Z</t>
+    <t>2026-08-13T19:46:04.850Z</t>
   </si>
   <si>
     <t>Nutraceutical Solutions</t>
@@ -529,7 +529,7 @@
     <t>industries/personal-care</t>
   </si>
   <si>
-    <t>2026-08-13T14:44:39.659Z</t>
+    <t>2026-08-13T19:54:08.546Z</t>
   </si>
   <si>
     <t>Personal Care</t>
@@ -547,7 +547,7 @@
     <t>industries/pharmaceutical-solutions</t>
   </si>
   <si>
-    <t>2026-08-13T14:20:19.429Z</t>
+    <t>2026-08-13T19:54:22.804Z</t>
   </si>
   <si>
     <t>Pharmaceutical Solutions</t>
@@ -565,7 +565,7 @@
     <t>industries/plastics-and-polymers</t>
   </si>
   <si>
-    <t>2026-08-13T13:48:53.297Z</t>
+    <t>2026-08-13T19:43:23.544Z</t>
   </si>
   <si>
     <t>Plastics and Polymers</t>
@@ -583,7 +583,7 @@
     <t>industries/refining-technologies</t>
   </si>
   <si>
-    <t>2026-08-13T13:26:22.518Z</t>
+    <t>2026-08-13T19:42:35.543Z</t>
   </si>
   <si>
     <t>Refining Technologies</t>
@@ -3738,7 +3738,7 @@
     <t>industries/agriculture/agriculture-cdmo</t>
   </si>
   <si>
-    <t>2026-08-13T14:42:53.244Z</t>
+    <t>2026-08-13T19:52:22.111Z</t>
   </si>
   <si>
     <t>Agriculture CDMO</t>
@@ -3756,7 +3756,7 @@
     <t>industries/agriculture/animal-feed-agricultural-active-solutions</t>
   </si>
   <si>
-    <t>2026-08-13T14:43:46.430Z</t>
+    <t>2026-08-13T19:53:15.424Z</t>
   </si>
   <si>
     <t>Animal Feed and Agricultural Active Solutions</t>
@@ -3774,7 +3774,7 @@
     <t>industries/biofuels/biodiesel</t>
   </si>
   <si>
-    <t>2026-08-13T14:56:24.480Z</t>
+    <t>2026-08-13T20:05:44.319Z</t>
   </si>
   <si>
     <t>Biomass-based Diesel</t>
@@ -3789,7 +3789,7 @@
     <t>industries/biofuels/bioethanol</t>
   </si>
   <si>
-    <t>2026-08-13T14:55:31.709Z</t>
+    <t>2026-08-13T20:04:51.052Z</t>
   </si>
   <si>
     <t>Bioethanol</t>
@@ -3804,7 +3804,7 @@
     <t>industries/biofuels/biomass-based-diesel</t>
   </si>
   <si>
-    <t>2026-08-13T14:52:47.948Z</t>
+    <t>2026-08-13T20:02:11.273Z</t>
   </si>
   <si>
     <t>https://grace.com/industries/biofuels/biomass-based-diesel/</t>
@@ -3819,7 +3819,7 @@
     <t>industries/chemical-processing/catalyst-supports</t>
   </si>
   <si>
-    <t>2026-08-13T13:47:04.034Z</t>
+    <t>2026-08-13T19:41:35.387Z</t>
   </si>
   <si>
     <t>Catalyst Supports</t>
@@ -3834,7 +3834,7 @@
     <t>industries/chemical-processing/custom-development</t>
   </si>
   <si>
-    <t>2026-08-13T13:47:59.217Z</t>
+    <t>2026-08-13T19:42:30.244Z</t>
   </si>
   <si>
     <t>Custom Development</t>
@@ -3849,7 +3849,7 @@
     <t>industries/chemical-processing/hydrogenation-catalysts</t>
   </si>
   <si>
-    <t>2026-08-13T13:46:10.288Z</t>
+    <t>2026-08-13T20:02:32.750Z</t>
   </si>
   <si>
     <t>Hydrogenation Catalysts</t>
@@ -3867,7 +3867,7 @@
     <t>industries/coatings/architectural</t>
   </si>
   <si>
-    <t>2026-08-13T14:11:16.658Z</t>
+    <t>2026-08-13T19:45:15.395Z</t>
   </si>
   <si>
     <t>Architectural</t>
@@ -3882,7 +3882,7 @@
     <t>industries/coatings/coil</t>
   </si>
   <si>
-    <t>2026-08-13T14:10:24.136Z</t>
+    <t>2026-08-13T19:44:21.745Z</t>
   </si>
   <si>
     <t>Coil</t>
@@ -3897,7 +3897,7 @@
     <t>industries/coatings/general-industrial-coatings</t>
   </si>
   <si>
-    <t>2026-08-13T14:13:04.481Z</t>
+    <t>2026-08-13T19:47:04.958Z</t>
   </si>
   <si>
     <t>General Industrial Coatings</t>
@@ -3912,7 +3912,7 @@
     <t>industries/coatings/inks-paper</t>
   </si>
   <si>
-    <t>2026-08-13T14:12:10.609Z</t>
+    <t>2026-08-13T19:46:10.699Z</t>
   </si>
   <si>
     <t>Inks and Paper</t>
@@ -3927,7 +3927,7 @@
     <t>industries/coatings/wood</t>
   </si>
   <si>
-    <t>2026-08-13T14:09:28.758Z</t>
+    <t>2026-08-13T19:43:28.497Z</t>
   </si>
   <si>
     <t>Wood</t>
@@ -3945,7 +3945,7 @@
     <t>industries/food-beverage/beer</t>
   </si>
   <si>
-    <t>2026-08-13T14:48:17.644Z</t>
+    <t>2026-08-13T19:57:44.067Z</t>
   </si>
   <si>
     <t>Beer</t>
@@ -3966,7 +3966,7 @@
     <t>industries/food-beverage/beverage</t>
   </si>
   <si>
-    <t>2026-08-13T14:51:00.719Z</t>
+    <t>2026-08-13T20:00:25.398Z</t>
   </si>
   <si>
     <t>Beverage</t>
@@ -3981,7 +3981,7 @@
     <t>industries/food-beverage/edible-oil-refining</t>
   </si>
   <si>
-    <t>2026-08-13T14:49:11.585Z</t>
+    <t>2026-08-13T19:58:39.248Z</t>
   </si>
   <si>
     <t>Edible Oil Refining</t>
@@ -3999,7 +3999,7 @@
     <t>industries/food-beverage/food-processing</t>
   </si>
   <si>
-    <t>2026-08-13T14:50:05.235Z</t>
+    <t>2026-08-13T19:59:32.496Z</t>
   </si>
   <si>
     <t>Food Processing</t>
@@ -4017,7 +4017,7 @@
     <t>industries/general-industrial/colloidal-silica-in-catalysts</t>
   </si>
   <si>
-    <t>2026-08-13T14:16:42.744Z</t>
+    <t>2026-08-13T19:50:42.947Z</t>
   </si>
   <si>
     <t>Colloidal Silica in Catalysts</t>
@@ -4035,7 +4035,7 @@
     <t>industries/general-industrial/construction</t>
   </si>
   <si>
-    <t>2026-08-13T14:19:25.286Z</t>
+    <t>2026-08-13T19:53:29.000Z</t>
   </si>
   <si>
     <t>Construction</t>
@@ -4050,7 +4050,7 @@
     <t>industries/general-industrial/investment-casting-binders</t>
   </si>
   <si>
-    <t>2026-08-13T14:17:35.830Z</t>
+    <t>2026-08-13T19:51:38.395Z</t>
   </si>
   <si>
     <t>Investment Casting Binders</t>
@@ -4065,7 +4065,7 @@
     <t>industries/general-industrial/process-adsorbents</t>
   </si>
   <si>
-    <t>2026-08-13T14:14:54.168Z</t>
+    <t>2026-08-13T19:48:54.336Z</t>
   </si>
   <si>
     <t>Process Adsorbents</t>
@@ -4080,7 +4080,7 @@
     <t>industries/general-industrial/refractory-additives</t>
   </si>
   <si>
-    <t>2026-08-13T14:18:29.843Z</t>
+    <t>2026-08-13T19:52:34.615Z</t>
   </si>
   <si>
     <t>Refractory Additives</t>
@@ -4095,7 +4095,7 @@
     <t>industries/general-industrial/static-adsorbents</t>
   </si>
   <si>
-    <t>2026-08-13T14:15:47.645Z</t>
+    <t>2026-08-13T19:49:47.540Z</t>
   </si>
   <si>
     <t>Static Adsorbents</t>
@@ -4110,7 +4110,7 @@
     <t>industries/nutraceutical-solutions/cbd-purification-formulation-delivery</t>
   </si>
   <si>
-    <t>2026-08-13T14:39:17.520Z</t>
+    <t>2026-08-13T19:48:43.394Z</t>
   </si>
   <si>
     <t>CBD Purfication, Formulation and Delivery</t>
@@ -4125,7 +4125,7 @@
     <t>industries/nutraceutical-solutions/lipid-purification-formulation-delivery</t>
   </si>
   <si>
-    <t>2026-08-13T14:38:22.842Z</t>
+    <t>2026-08-13T19:47:49.988Z</t>
   </si>
   <si>
     <t>Lipid Purfication, Formulation and Delivery</t>
@@ -4140,7 +4140,7 @@
     <t>industries/nutraceutical-solutions/nutraceutical-cdmo</t>
   </si>
   <si>
-    <t>2026-08-13T14:40:10.426Z</t>
+    <t>2026-08-13T19:49:38.195Z</t>
   </si>
   <si>
     <t>Nutraceutical CDMO</t>
@@ -4161,7 +4161,7 @@
     <t>industries/nutraceutical-solutions/traditional-herbal-medicine</t>
   </si>
   <si>
-    <t>2026-08-13T14:41:03.476Z</t>
+    <t>2026-08-13T19:50:32.595Z</t>
   </si>
   <si>
     <t>Traditional Herbal Medicine (THM) and Botanical Solutions</t>
@@ -4176,7 +4176,7 @@
     <t>industries/nutraceutical-solutions/vitamin-purification-formulation-delivery</t>
   </si>
   <si>
-    <t>2026-08-13T14:37:29.817Z</t>
+    <t>2026-08-13T19:46:57.529Z</t>
   </si>
   <si>
     <t>Vitamin Purification, Formulation and Delivery</t>
@@ -4194,7 +4194,7 @@
     <t>industries/personal-care/cosmetics</t>
   </si>
   <si>
-    <t>2026-08-13T14:46:29.941Z</t>
+    <t>2026-08-13T19:55:55.928Z</t>
   </si>
   <si>
     <t>Cosmetics</t>
@@ -4212,7 +4212,7 @@
     <t>industries/personal-care/toothpaste</t>
   </si>
   <si>
-    <t>2026-08-13T14:45:33.742Z</t>
+    <t>2026-08-13T19:55:02.740Z</t>
   </si>
   <si>
     <t>Toothpaste</t>
@@ -4227,7 +4227,7 @@
     <t>industries/pharmaceutical-solutions/fine-chemicals</t>
   </si>
   <si>
-    <t>2026-08-13T14:21:13.167Z</t>
+    <t>2026-08-13T19:55:17.636Z</t>
   </si>
   <si>
     <t>https://grace.com/industries/pharmaceutical-solutions/fine-chemicals/</t>
@@ -4239,7 +4239,7 @@
     <t>industries/pharmaceutical-solutions/packaging-adsorbents</t>
   </si>
   <si>
-    <t>2026-08-13T14:35:38.290Z</t>
+    <t>2026-08-13T19:45:11.197Z</t>
   </si>
   <si>
     <t>Packaging Adsorbents</t>
@@ -4254,7 +4254,7 @@
     <t>industries/pharmaceutical-solutions/purification-formulation-delivery</t>
   </si>
   <si>
-    <t>2026-08-13T14:31:59.527Z</t>
+    <t>2026-08-13T19:41:36.288Z</t>
   </si>
   <si>
     <t>Purification, Formulation and Delivery</t>
@@ -4269,7 +4269,7 @@
     <t>industries/plastics-and-polymers/custom-catalysts</t>
   </si>
   <si>
-    <t>2026-08-13T14:04:07.542Z</t>
+    <t>2026-08-13T19:58:45.156Z</t>
   </si>
   <si>
     <t>Custom Catalysts</t>
@@ -4284,7 +4284,7 @@
     <t>industries/plastics-and-polymers/plastic-additives</t>
   </si>
   <si>
-    <t>2026-08-13T14:05:01.197Z</t>
+    <t>2026-08-13T19:59:39.301Z</t>
   </si>
   <si>
     <t>Plastic Additives</t>
@@ -4299,7 +4299,7 @@
     <t>industries/plastics-and-polymers/polyethylene-catalysts</t>
   </si>
   <si>
-    <t>2026-08-13T13:49:45.993Z</t>
+    <t>2026-08-13T19:44:18.296Z</t>
   </si>
   <si>
     <t>Polyethylene Catalysts</t>
@@ -4317,7 +4317,7 @@
     <t>industries/plastics-and-polymers/polypropylene-catalysts</t>
   </si>
   <si>
-    <t>2026-08-13T13:55:09.865Z</t>
+    <t>2026-08-13T19:49:42.396Z</t>
   </si>
   <si>
     <t>Polypropylene Catalysts</t>
@@ -4332,7 +4332,7 @@
     <t>industries/plastics-and-polymers/tire-and-rubber-additives</t>
   </si>
   <si>
-    <t>2026-08-13T14:07:41.728Z</t>
+    <t>2026-08-13T19:41:37.430Z</t>
   </si>
   <si>
     <t>Tire and Rubber Additives</t>
@@ -4347,7 +4347,7 @@
     <t>industries/plastics-and-polymers/unipol-pp-process-technology</t>
   </si>
   <si>
-    <t>2026-08-13T13:58:46.541Z</t>
+    <t>2026-08-13T19:53:21.697Z</t>
   </si>
   <si>
     <t>UNIPOL® Polypropylene Process and Related Polypropylene Product Technology</t>
@@ -4365,7 +4365,7 @@
     <t>industries/refining-technologies/catalagram-archive</t>
   </si>
   <si>
-    <t>2026-08-13T13:44:22.893Z</t>
+    <t>2026-08-13T20:00:45.898Z</t>
   </si>
   <si>
     <t>Catalagram Archive</t>
@@ -4383,7 +4383,7 @@
     <t>industries/refining-technologies/fcc-additive-solutions</t>
   </si>
   <si>
-    <t>2026-08-13T13:35:22.383Z</t>
+    <t>2026-08-13T19:51:44.172Z</t>
   </si>
   <si>
     <t>FCC Additive Solutions</t>
@@ -4401,7 +4401,7 @@
     <t>industries/refining-technologies/fcc-catalyst-application</t>
   </si>
   <si>
-    <t>2026-08-13T13:27:15.540Z</t>
+    <t>2026-08-13T19:43:32.402Z</t>
   </si>
   <si>
     <t>FCC Catalyst Solutions</t>
@@ -4419,7 +4419,7 @@
     <t>industries/refining-technologies/hydroprocessing</t>
   </si>
   <si>
-    <t>2026-08-13T13:40:47.223Z</t>
+    <t>2026-08-13T19:57:09.242Z</t>
   </si>
   <si>
     <t>Hydroprocessing</t>
@@ -4437,7 +4437,7 @@
     <t>industries/refining-technologies/value-creation</t>
   </si>
   <si>
-    <t>2026-08-13T13:31:46.882Z</t>
+    <t>2026-08-13T19:48:07.544Z</t>
   </si>
   <si>
     <t>Value Creation</t>
@@ -4491,7 +4491,7 @@
     <t>industries/biofuels/biomass-based-diesel/first-generation-biodiesel</t>
   </si>
   <si>
-    <t>2026-08-13T14:53:41.646Z</t>
+    <t>2026-08-13T20:03:05.293Z</t>
   </si>
   <si>
     <t>First Generation Biodiesel</t>
@@ -4509,7 +4509,7 @@
     <t>industries/biofuels/biomass-based-diesel/renewable-diesel</t>
   </si>
   <si>
-    <t>2026-08-13T14:54:35.912Z</t>
+    <t>2026-08-13T20:03:58.046Z</t>
   </si>
   <si>
     <t>Renewable Diesel</t>
@@ -4524,7 +4524,7 @@
     <t>industries/pharmaceutical-solutions/fine-chemicals/consultative-services</t>
   </si>
   <si>
-    <t>2026-08-13T14:25:42.628Z</t>
+    <t>2026-08-13T19:59:47.535Z</t>
   </si>
   <si>
     <t>Consultative Services</t>
@@ -4539,7 +4539,7 @@
     <t>industries/pharmaceutical-solutions/fine-chemicals/custom-apis</t>
   </si>
   <si>
-    <t>2026-08-13T14:22:06.860Z</t>
+    <t>2026-08-13T19:56:12.157Z</t>
   </si>
   <si>
     <t>Custom APIs</t>
@@ -4554,7 +4554,7 @@
     <t>industries/pharmaceutical-solutions/fine-chemicals/facilities</t>
   </si>
   <si>
-    <t>2026-08-13T14:28:24.292Z</t>
+    <t>2026-08-13T20:02:28.188Z</t>
   </si>
   <si>
     <t>Facilities</t>
@@ -4572,7 +4572,7 @@
     <t>industries/pharmaceutical-solutions/fine-chemicals/fcms-case-study</t>
   </si>
   <si>
-    <t>2026-08-13T14:31:05.453Z</t>
+    <t>2026-08-13T20:05:08.894Z</t>
   </si>
   <si>
     <t>FCMS Case Study</t>
@@ -4587,7 +4587,7 @@
     <t>industries/pharmaceutical-solutions/fine-chemicals/generic-apis</t>
   </si>
   <si>
-    <t>2026-08-13T14:23:56.626Z</t>
+    <t>2026-08-13T19:57:59.050Z</t>
   </si>
   <si>
     <t>Generic APIs</t>
@@ -4602,7 +4602,7 @@
     <t>industries/pharmaceutical-solutions/fine-chemicals/integrated-scale-up</t>
   </si>
   <si>
-    <t>2026-08-13T14:24:49.550Z</t>
+    <t>2026-08-13T19:58:53.146Z</t>
   </si>
   <si>
     <t>Integrated Scale-Up</t>
@@ -4617,7 +4617,7 @@
     <t>industries/pharmaceutical-solutions/fine-chemicals/rsms-and-intermediates</t>
   </si>
   <si>
-    <t>2026-08-13T14:23:00.133Z</t>
+    <t>2026-08-13T19:57:06.256Z</t>
   </si>
   <si>
     <t>RSMs and Intermediates</t>
@@ -4632,7 +4632,7 @@
     <t>industries/pharmaceutical-solutions/purification-formulation-delivery/active-ingredient-delivery</t>
   </si>
   <si>
-    <t>2026-08-13T14:34:43.931Z</t>
+    <t>2026-08-13T19:44:18.004Z</t>
   </si>
   <si>
     <t>Active Ingredient Delivery</t>
@@ -4650,7 +4650,7 @@
     <t>industries/pharmaceutical-solutions/purification-formulation-delivery/chromatography</t>
   </si>
   <si>
-    <t>2026-08-13T14:32:55.749Z</t>
+    <t>2026-08-13T19:42:31.146Z</t>
   </si>
   <si>
     <t>Chromatography</t>
@@ -4668,7 +4668,7 @@
     <t>industries/pharmaceutical-solutions/purification-formulation-delivery/excipients</t>
   </si>
   <si>
-    <t>2026-08-13T14:33:50.126Z</t>
+    <t>2026-08-13T19:43:24.551Z</t>
   </si>
   <si>
     <t>Excipients</t>
@@ -4686,7 +4686,7 @@
     <t>industries/plastics-and-polymers/plastic-additives/silica-anti-blocking-agents</t>
   </si>
   <si>
-    <t>2026-08-13T14:05:57.086Z</t>
+    <t>2026-08-13T20:00:31.750Z</t>
   </si>
   <si>
     <t>Silica Anti-blocking Agents</t>
@@ -4704,7 +4704,7 @@
     <t>industries/plastics-and-polymers/plastic-additives/titanium-dioxide-extenders</t>
   </si>
   <si>
-    <t>2026-08-13T14:06:49.411Z</t>
+    <t>2026-08-13T20:01:24.650Z</t>
   </si>
   <si>
     <t>Titanium Dioxide Extenders</t>
@@ -4719,7 +4719,7 @@
     <t>industries/plastics-and-polymers/polyethylene-catalysts/pe-catalyst-components-and-supports</t>
   </si>
   <si>
-    <t>2026-08-13T13:50:39.994Z</t>
+    <t>2026-08-13T19:45:11.697Z</t>
   </si>
   <si>
     <t>PE Catalyst Components and Supports</t>
@@ -4734,7 +4734,7 @@
     <t>industries/plastics-and-polymers/polyethylene-catalysts/pe-gas-phase</t>
   </si>
   <si>
-    <t>2026-08-13T13:52:29.916Z</t>
+    <t>2026-08-13T19:46:59.894Z</t>
   </si>
   <si>
     <t>PE Gas Phase</t>
@@ -4749,7 +4749,7 @@
     <t>industries/plastics-and-polymers/polyethylene-catalysts/pe-hybrid</t>
   </si>
   <si>
-    <t>2026-08-13T13:54:16.910Z</t>
+    <t>2026-08-13T19:48:48.943Z</t>
   </si>
   <si>
     <t>PE Hybrid</t>
@@ -4764,7 +4764,7 @@
     <t>industries/plastics-and-polymers/polyethylene-catalysts/pe-slurry</t>
   </si>
   <si>
-    <t>2026-08-13T13:51:34.883Z</t>
+    <t>2026-08-13T19:46:06.442Z</t>
   </si>
   <si>
     <t>PE Slurry</t>
@@ -4779,7 +4779,7 @@
     <t>industries/plastics-and-polymers/polyethylene-catalysts/pe-solution</t>
   </si>
   <si>
-    <t>2026-08-13T13:53:22.153Z</t>
+    <t>2026-08-13T19:47:55.263Z</t>
   </si>
   <si>
     <t>PE Solution</t>
@@ -4794,7 +4794,7 @@
     <t>industries/plastics-and-polymers/polypropylene-catalysts/pp-bulk</t>
   </si>
   <si>
-    <t>2026-08-13T13:56:03.344Z</t>
+    <t>2026-08-13T19:50:37.896Z</t>
   </si>
   <si>
     <t>PP Bulk</t>
@@ -4809,7 +4809,7 @@
     <t>industries/plastics-and-polymers/polypropylene-catalysts/pp-gas-phase</t>
   </si>
   <si>
-    <t>2026-08-13T13:56:59.266Z</t>
+    <t>2026-08-13T19:51:33.076Z</t>
   </si>
   <si>
     <t>PP Gas Phase</t>
@@ -4824,7 +4824,7 @@
     <t>industries/plastics-and-polymers/polypropylene-catalysts/pp-slurry</t>
   </si>
   <si>
-    <t>2026-08-13T13:57:52.978Z</t>
+    <t>2026-08-13T19:52:27.600Z</t>
   </si>
   <si>
     <t>PP Slurry</t>
@@ -4851,7 +4851,7 @@
     <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-performance</t>
   </si>
   <si>
-    <t>2026-08-13T14:01:28.916Z</t>
+    <t>2026-08-13T19:56:03.555Z</t>
   </si>
   <si>
     <t>UNIPOL® PP Performance</t>
@@ -4866,7 +4866,7 @@
     <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-process</t>
   </si>
   <si>
-    <t>2026-08-13T13:59:39.220Z</t>
+    <t>2026-08-13T19:54:14.694Z</t>
   </si>
   <si>
     <t>UNIPOL® PP Process</t>
@@ -4878,7 +4878,7 @@
     <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-products</t>
   </si>
   <si>
-    <t>2026-08-13T14:00:33.027Z</t>
+    <t>2026-08-13T19:55:09.606Z</t>
   </si>
   <si>
     <t>UNIPOL® PP Products</t>
@@ -4893,7 +4893,7 @@
     <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-services</t>
   </si>
   <si>
-    <t>2026-08-13T14:02:21.259Z</t>
+    <t>2026-08-13T19:56:57.071Z</t>
   </si>
   <si>
     <t>UNIPOL® PP Services</t>
@@ -4911,7 +4911,7 @@
     <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-technology-ppartner-program</t>
   </si>
   <si>
-    <t>2026-08-13T14:03:15.155Z</t>
+    <t>2026-08-13T19:57:50.862Z</t>
   </si>
   <si>
     <t>PPartner Program™ Services</t>
@@ -4926,7 +4926,7 @@
     <t>industries/refining-technologies/fcc-additive-solutions/combustion-promoter</t>
   </si>
   <si>
-    <t>2026-08-13T13:39:53.699Z</t>
+    <t>2026-08-13T19:56:15.995Z</t>
   </si>
   <si>
     <t>Combustion Promoter</t>
@@ -4941,7 +4941,7 @@
     <t>industries/refining-technologies/fcc-additive-solutions/gasoline-sulphur-reduction</t>
   </si>
   <si>
-    <t>2026-08-13T13:37:09.353Z</t>
+    <t>2026-08-13T19:53:33.634Z</t>
   </si>
   <si>
     <t>Gasoline Sulphur Reduction</t>
@@ -4956,7 +4956,7 @@
     <t>industries/refining-technologies/fcc-additive-solutions/light-olefins</t>
   </si>
   <si>
-    <t>2026-08-13T13:38:02.794Z</t>
+    <t>2026-08-13T19:54:28.018Z</t>
   </si>
   <si>
     <t>Light Olefins</t>
@@ -4971,7 +4971,7 @@
     <t>industries/refining-technologies/fcc-additive-solutions/nox-reduction</t>
   </si>
   <si>
-    <t>2026-08-13T13:38:59.015Z</t>
+    <t>2026-08-13T19:55:21.295Z</t>
   </si>
   <si>
     <t>NOx Reduction</t>
@@ -4986,7 +4986,7 @@
     <t>industries/refining-technologies/fcc-additive-solutions/sox-reduction</t>
   </si>
   <si>
-    <t>2026-08-13T13:36:16.426Z</t>
+    <t>2026-08-13T19:52:38.394Z</t>
   </si>
   <si>
     <t>SOx Reduction</t>
@@ -5001,7 +5001,7 @@
     <t>industries/refining-technologies/fcc-catalyst-application/butylene-selectivity</t>
   </si>
   <si>
-    <t>2026-08-13T13:29:00.795Z</t>
+    <t>2026-08-13T19:45:23.237Z</t>
   </si>
   <si>
     <t>Butylene Selectivity</t>
@@ -5016,7 +5016,7 @@
     <t>industries/refining-technologies/fcc-catalyst-application/light-feed-performance</t>
   </si>
   <si>
-    <t>2026-08-13T13:30:51.955Z</t>
+    <t>2026-08-13T19:47:12.911Z</t>
   </si>
   <si>
     <t>Light Feed Performance</t>
@@ -5031,7 +5031,7 @@
     <t>industries/refining-technologies/fcc-catalyst-application/maximize-propylene</t>
   </si>
   <si>
-    <t>2026-08-13T13:28:08.086Z</t>
+    <t>2026-08-13T19:44:27.444Z</t>
   </si>
   <si>
     <t>Maximize Propylene</t>
@@ -5046,7 +5046,7 @@
     <t>industries/refining-technologies/fcc-catalyst-application/resid-conversion</t>
   </si>
   <si>
-    <t>2026-08-13T13:29:57.305Z</t>
+    <t>2026-08-13T19:46:18.270Z</t>
   </si>
   <si>
     <t>Resid Conversion</t>
@@ -5064,7 +5064,7 @@
     <t>industries/refining-technologies/hydroprocessing/distillate-hydrotreating-solutions</t>
   </si>
   <si>
-    <t>2026-08-13T13:43:28.071Z</t>
+    <t>2026-08-13T19:59:51.448Z</t>
   </si>
   <si>
     <t>Distillate Hydrotreating Solutions</t>
@@ -5079,7 +5079,7 @@
     <t>industries/refining-technologies/hydroprocessing/resid-hydrocracking-solutions</t>
   </si>
   <si>
-    <t>2026-08-13T13:42:32.849Z</t>
+    <t>2026-08-13T19:58:56.694Z</t>
   </si>
   <si>
     <t>Resid Hydrocracking Solutions</t>
@@ -5094,7 +5094,7 @@
     <t>industries/refining-technologies/hydroprocessing/resid-hydrotreating-solutions</t>
   </si>
   <si>
-    <t>2026-08-13T13:41:39.610Z</t>
+    <t>2026-08-13T19:58:02.950Z</t>
   </si>
   <si>
     <t>Resid Hydrotreating Solutions</t>
@@ -5112,7 +5112,7 @@
     <t>industries/refining-technologies/value-creation/specialized-evaluation-tools</t>
   </si>
   <si>
-    <t>2026-08-13T13:33:32.981Z</t>
+    <t>2026-08-13T19:49:56.303Z</t>
   </si>
   <si>
     <t>Specialized Evaluation Tools</t>
@@ -5127,7 +5127,7 @@
     <t>industries/refining-technologies/value-creation/sustainability</t>
   </si>
   <si>
-    <t>2026-08-13T13:34:28.963Z</t>
+    <t>2026-08-13T19:50:49.692Z</t>
   </si>
   <si>
     <t>Sustainable Solutions for FCC</t>
@@ -5145,7 +5145,7 @@
     <t>industries/refining-technologies/value-creation/technical-service-expertise</t>
   </si>
   <si>
-    <t>2026-08-13T13:32:39.987Z</t>
+    <t>2026-08-13T19:49:02.103Z</t>
   </si>
   <si>
     <t>Technical Service Expertise</t>
@@ -5559,7 +5559,7 @@
     <t>industries/pharmaceutical-solutions/fine-chemicals/consultative-services/quality-and-compliance</t>
   </si>
   <si>
-    <t>2026-08-13T14:27:28.701Z</t>
+    <t>2026-08-13T20:01:35.443Z</t>
   </si>
   <si>
     <t>Quality and Compliance</t>
@@ -5574,7 +5574,7 @@
     <t>industries/pharmaceutical-solutions/fine-chemicals/consultative-services/r-d</t>
   </si>
   <si>
-    <t>2026-08-13T14:26:35.626Z</t>
+    <t>2026-08-13T20:00:41.014Z</t>
   </si>
   <si>
     <t>R&amp;D</t>
@@ -5592,7 +5592,7 @@
     <t>industries/pharmaceutical-solutions/fine-chemicals/facilities/south-haven</t>
   </si>
   <si>
-    <t>2026-08-13T14:29:17.753Z</t>
+    <t>2026-08-13T20:03:21.541Z</t>
   </si>
   <si>
     <t>South Haven</t>
@@ -5607,7 +5607,7 @@
     <t>industries/pharmaceutical-solutions/fine-chemicals/facilities/tyrone</t>
   </si>
   <si>
-    <t>2026-08-13T14:30:12.247Z</t>
+    <t>2026-08-13T20:04:15.119Z</t>
   </si>
   <si>
     <t>Tyrone</t>

--- a/tools/importer/reports/import-grace-master.report.xlsx
+++ b/tools/importer/reports/import-grace-master.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5101" uniqueCount="1867">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5101" uniqueCount="1868">
   <si>
     <t>_reportFile</t>
   </si>
@@ -3732,13 +3732,13 @@
     <t>industries/agriculture/agriculture-cdmo.report.json</t>
   </si>
   <si>
-    <t>["hero-banner","columns-horizontal-teaser-featured","accordion-faq","cards-product"]</t>
+    <t>["hero-banner","columns-horizontal-teaser-featured","accordion-faq","cards-category-grid"]</t>
   </si>
   <si>
     <t>industries/agriculture/agriculture-cdmo</t>
   </si>
   <si>
-    <t>2026-08-13T19:52:22.111Z</t>
+    <t>2026-08-13T21:47:29.126Z</t>
   </si>
   <si>
     <t>Agriculture CDMO</t>
@@ -3750,13 +3750,13 @@
     <t>industries/agriculture/animal-feed-agricultural-active-solutions.report.json</t>
   </si>
   <si>
-    <t>["hero-banner","columns-horizontal-teaser-featured","cards-product"]</t>
+    <t>["hero-banner","columns-horizontal-teaser-featured","cards-category-grid"]</t>
   </si>
   <si>
     <t>industries/agriculture/animal-feed-agricultural-active-solutions</t>
   </si>
   <si>
-    <t>2026-08-13T19:53:15.424Z</t>
+    <t>2026-08-13T21:48:22.397Z</t>
   </si>
   <si>
     <t>Animal Feed and Agricultural Active Solutions</t>
@@ -5058,13 +5058,16 @@
     <t>industries/refining-technologies/hydroprocessing/distillate-hydrotreating-solutions.report.json</t>
   </si>
   <si>
+    <t>["hero-banner","cards-category-grid"]</t>
+  </si>
+  <si>
     <t>["template","contactus","breadcrumb","breadcrumb-title"]</t>
   </si>
   <si>
     <t>industries/refining-technologies/hydroprocessing/distillate-hydrotreating-solutions</t>
   </si>
   <si>
-    <t>2026-08-13T19:59:51.448Z</t>
+    <t>2026-08-13T21:46:36.990Z</t>
   </si>
   <si>
     <t>Distillate Hydrotreating Solutions</t>
@@ -5079,7 +5082,7 @@
     <t>industries/refining-technologies/hydroprocessing/resid-hydrocracking-solutions</t>
   </si>
   <si>
-    <t>2026-08-13T19:58:56.694Z</t>
+    <t>2026-08-13T21:45:43.655Z</t>
   </si>
   <si>
     <t>Resid Hydrocracking Solutions</t>
@@ -5094,7 +5097,7 @@
     <t>industries/refining-technologies/hydroprocessing/resid-hydrotreating-solutions</t>
   </si>
   <si>
-    <t>2026-08-13T19:58:02.950Z</t>
+    <t>2026-08-13T21:44:50.934Z</t>
   </si>
   <si>
     <t>Resid Hydrotreating Solutions</t>
@@ -21922,7 +21925,7 @@
         <v>1680</v>
       </c>
       <c r="B319" t="s">
-        <v>1517</v>
+        <v>1681</v>
       </c>
       <c r="C319" t="s">
         <v>18</v>
@@ -21943,13 +21946,13 @@
         <v>0</v>
       </c>
       <c r="I319" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="J319" t="s">
         <v>20</v>
       </c>
       <c r="K319" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="L319" t="s">
         <v>19</v>
@@ -21958,21 +21961,21 @@
         <v>22</v>
       </c>
       <c r="N319" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="O319" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="P319" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="320" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="B320" t="s">
-        <v>1517</v>
+        <v>1681</v>
       </c>
       <c r="C320" t="s">
         <v>18</v>
@@ -21993,13 +21996,13 @@
         <v>0</v>
       </c>
       <c r="I320" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="J320" t="s">
         <v>20</v>
       </c>
       <c r="K320" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="L320" t="s">
         <v>19</v>
@@ -22008,21 +22011,21 @@
         <v>22</v>
       </c>
       <c r="N320" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="O320" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="P320" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="321" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="B321" t="s">
-        <v>1517</v>
+        <v>1681</v>
       </c>
       <c r="C321" t="s">
         <v>18</v>
@@ -22043,13 +22046,13 @@
         <v>0</v>
       </c>
       <c r="I321" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="J321" t="s">
         <v>20</v>
       </c>
       <c r="K321" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="L321" t="s">
         <v>19</v>
@@ -22058,21 +22061,21 @@
         <v>22</v>
       </c>
       <c r="N321" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="O321" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="P321" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="322" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="B322" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="C322" t="s">
         <v>18</v>
@@ -22099,7 +22102,7 @@
         <v>20</v>
       </c>
       <c r="K322" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="L322" t="s">
         <v>19</v>
@@ -22108,18 +22111,18 @@
         <v>22</v>
       </c>
       <c r="N322" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="O322" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="P322" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="323" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="B323" t="s">
         <v>1466</v>
@@ -22149,7 +22152,7 @@
         <v>20</v>
       </c>
       <c r="K323" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="L323" t="s">
         <v>19</v>
@@ -22158,21 +22161,21 @@
         <v>22</v>
       </c>
       <c r="N323" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="O323" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="P323" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="324" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B324" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="C324" t="s">
         <v>18</v>
@@ -22199,7 +22202,7 @@
         <v>20</v>
       </c>
       <c r="K324" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="L324" t="s">
         <v>19</v>
@@ -22208,18 +22211,18 @@
         <v>22</v>
       </c>
       <c r="N324" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="O324" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="P324" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="325" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="B325" t="s">
         <v>1517</v>
@@ -22249,7 +22252,7 @@
         <v>20</v>
       </c>
       <c r="K325" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="L325" t="s">
         <v>19</v>
@@ -22258,18 +22261,18 @@
         <v>22</v>
       </c>
       <c r="N325" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="O325" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="P325" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="326" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="B326" t="s">
         <v>1517</v>
@@ -22299,7 +22302,7 @@
         <v>20</v>
       </c>
       <c r="K326" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="L326" t="s">
         <v>19</v>
@@ -22308,18 +22311,18 @@
         <v>22</v>
       </c>
       <c r="N326" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="O326" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="P326" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="327" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="B327" t="s">
         <v>1517</v>
@@ -22349,7 +22352,7 @@
         <v>20</v>
       </c>
       <c r="K327" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="L327" t="s">
         <v>19</v>
@@ -22358,18 +22361,18 @@
         <v>22</v>
       </c>
       <c r="N327" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="O327" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="P327" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="328" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="B328" t="s">
         <v>1517</v>
@@ -22399,7 +22402,7 @@
         <v>20</v>
       </c>
       <c r="K328" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="L328" t="s">
         <v>19</v>
@@ -22408,18 +22411,18 @@
         <v>22</v>
       </c>
       <c r="N328" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="O328" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="P328" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="329" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="B329" t="s">
         <v>1517</v>
@@ -22449,7 +22452,7 @@
         <v>20</v>
       </c>
       <c r="K329" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="L329" t="s">
         <v>19</v>
@@ -22458,18 +22461,18 @@
         <v>22</v>
       </c>
       <c r="N329" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="O329" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="P329" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="330" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="B330" t="s">
         <v>1517</v>
@@ -22499,7 +22502,7 @@
         <v>20</v>
       </c>
       <c r="K330" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="L330" t="s">
         <v>19</v>
@@ -22508,18 +22511,18 @@
         <v>22</v>
       </c>
       <c r="N330" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="O330" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="P330" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="331" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="B331" t="s">
         <v>1517</v>
@@ -22549,7 +22552,7 @@
         <v>20</v>
       </c>
       <c r="K331" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="L331" t="s">
         <v>19</v>
@@ -22558,18 +22561,18 @@
         <v>22</v>
       </c>
       <c r="N331" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="O331" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="P331" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="332" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="B332" t="s">
         <v>1517</v>
@@ -22599,7 +22602,7 @@
         <v>20</v>
       </c>
       <c r="K332" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="L332" t="s">
         <v>19</v>
@@ -22608,18 +22611,18 @@
         <v>22</v>
       </c>
       <c r="N332" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="O332" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="P332" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="333" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="B333" t="s">
         <v>1517</v>
@@ -22649,7 +22652,7 @@
         <v>20</v>
       </c>
       <c r="K333" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="L333" t="s">
         <v>19</v>
@@ -22658,18 +22661,18 @@
         <v>22</v>
       </c>
       <c r="N333" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="O333" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="P333" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="334" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="B334" t="s">
         <v>1517</v>
@@ -22699,7 +22702,7 @@
         <v>20</v>
       </c>
       <c r="K334" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="L334" t="s">
         <v>19</v>
@@ -22708,18 +22711,18 @@
         <v>22</v>
       </c>
       <c r="N334" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="O334" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="P334" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="335" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B335" t="s">
         <v>1517</v>
@@ -22749,7 +22752,7 @@
         <v>20</v>
       </c>
       <c r="K335" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="L335" t="s">
         <v>19</v>
@@ -22758,18 +22761,18 @@
         <v>22</v>
       </c>
       <c r="N335" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="O335" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="P335" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="336" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="B336" t="s">
         <v>1517</v>
@@ -22799,7 +22802,7 @@
         <v>20</v>
       </c>
       <c r="K336" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="L336" t="s">
         <v>19</v>
@@ -22808,18 +22811,18 @@
         <v>22</v>
       </c>
       <c r="N336" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="O336" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="P336" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="337" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="B337" t="s">
         <v>1517</v>
@@ -22849,7 +22852,7 @@
         <v>20</v>
       </c>
       <c r="K337" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="L337" t="s">
         <v>19</v>
@@ -22858,18 +22861,18 @@
         <v>22</v>
       </c>
       <c r="N337" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="O337" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="P337" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="338" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="B338" t="s">
         <v>1517</v>
@@ -22899,7 +22902,7 @@
         <v>20</v>
       </c>
       <c r="K338" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="L338" t="s">
         <v>19</v>
@@ -22908,18 +22911,18 @@
         <v>22</v>
       </c>
       <c r="N338" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="O338" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="P338" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="339" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="B339" t="s">
         <v>1517</v>
@@ -22949,7 +22952,7 @@
         <v>20</v>
       </c>
       <c r="K339" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="L339" t="s">
         <v>19</v>
@@ -22958,18 +22961,18 @@
         <v>22</v>
       </c>
       <c r="N339" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="O339" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="P339" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="340" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="B340" t="s">
         <v>1517</v>
@@ -22999,7 +23002,7 @@
         <v>20</v>
       </c>
       <c r="K340" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="L340" t="s">
         <v>19</v>
@@ -23008,18 +23011,18 @@
         <v>22</v>
       </c>
       <c r="N340" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="O340" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="P340" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="341" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="B341" t="s">
         <v>1517</v>
@@ -23049,7 +23052,7 @@
         <v>20</v>
       </c>
       <c r="K341" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="L341" t="s">
         <v>19</v>
@@ -23058,18 +23061,18 @@
         <v>22</v>
       </c>
       <c r="N341" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="O341" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="P341" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="342" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="B342" t="s">
         <v>1517</v>
@@ -23099,7 +23102,7 @@
         <v>20</v>
       </c>
       <c r="K342" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="L342" t="s">
         <v>19</v>
@@ -23108,18 +23111,18 @@
         <v>22</v>
       </c>
       <c r="N342" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="O342" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="P342" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="343" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="B343" t="s">
         <v>19</v>
@@ -23149,7 +23152,7 @@
         <v>19</v>
       </c>
       <c r="K343" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="L343" t="s">
         <v>19</v>
@@ -23158,18 +23161,18 @@
         <v>391</v>
       </c>
       <c r="N343" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="O343" t="s">
         <v>19</v>
       </c>
       <c r="P343" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="344" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="B344" t="s">
         <v>1517</v>
@@ -23199,7 +23202,7 @@
         <v>20</v>
       </c>
       <c r="K344" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="L344" t="s">
         <v>19</v>
@@ -23208,18 +23211,18 @@
         <v>22</v>
       </c>
       <c r="N344" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="O344" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="P344" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="345" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B345" t="s">
         <v>1517</v>
@@ -23249,7 +23252,7 @@
         <v>20</v>
       </c>
       <c r="K345" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="L345" t="s">
         <v>19</v>
@@ -23258,18 +23261,18 @@
         <v>22</v>
       </c>
       <c r="N345" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="O345" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="P345" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="346" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="B346" t="s">
         <v>1517</v>
@@ -23299,7 +23302,7 @@
         <v>20</v>
       </c>
       <c r="K346" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="L346" t="s">
         <v>19</v>
@@ -23308,18 +23311,18 @@
         <v>22</v>
       </c>
       <c r="N346" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="O346" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="P346" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="347" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="B347" t="s">
         <v>1517</v>
@@ -23349,7 +23352,7 @@
         <v>20</v>
       </c>
       <c r="K347" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="L347" t="s">
         <v>19</v>
@@ -23358,18 +23361,18 @@
         <v>22</v>
       </c>
       <c r="N347" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="O347" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="P347" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="348" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="B348" t="s">
         <v>1517</v>
@@ -23399,7 +23402,7 @@
         <v>20</v>
       </c>
       <c r="K348" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="L348" t="s">
         <v>19</v>
@@ -23408,18 +23411,18 @@
         <v>22</v>
       </c>
       <c r="N348" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="O348" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="P348" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="349" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="B349" t="s">
         <v>1517</v>
@@ -23449,7 +23452,7 @@
         <v>20</v>
       </c>
       <c r="K349" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="L349" t="s">
         <v>19</v>
@@ -23458,18 +23461,18 @@
         <v>22</v>
       </c>
       <c r="N349" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="O349" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="P349" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="350" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="B350" t="s">
         <v>18</v>
@@ -23499,7 +23502,7 @@
         <v>42</v>
       </c>
       <c r="K350" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="L350" t="b">
         <v>0</v>
@@ -23508,18 +23511,18 @@
         <v>22</v>
       </c>
       <c r="N350" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="O350" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="P350" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="351" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="B351" t="s">
         <v>1517</v>
@@ -23549,7 +23552,7 @@
         <v>20</v>
       </c>
       <c r="K351" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="L351" t="s">
         <v>19</v>
@@ -23558,18 +23561,18 @@
         <v>22</v>
       </c>
       <c r="N351" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="O351" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="P351" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="352" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="B352" t="s">
         <v>135</v>
@@ -23599,7 +23602,7 @@
         <v>20</v>
       </c>
       <c r="K352" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="L352" t="s">
         <v>19</v>
@@ -23608,18 +23611,18 @@
         <v>22</v>
       </c>
       <c r="N352" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="O352" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="P352" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="353" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="B353" t="s">
         <v>1326</v>
@@ -23649,7 +23652,7 @@
         <v>20</v>
       </c>
       <c r="K353" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="L353" t="s">
         <v>19</v>
@@ -23658,21 +23661,21 @@
         <v>22</v>
       </c>
       <c r="N353" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="O353" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="P353" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="354" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="B354" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="C354" t="s">
         <v>18</v>
@@ -23699,7 +23702,7 @@
         <v>20</v>
       </c>
       <c r="K354" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="L354" t="s">
         <v>19</v>
@@ -23708,21 +23711,21 @@
         <v>22</v>
       </c>
       <c r="N354" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="O354" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="P354" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="355" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B355" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="C355" t="s">
         <v>18</v>
@@ -23749,7 +23752,7 @@
         <v>20</v>
       </c>
       <c r="K355" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="L355" t="s">
         <v>19</v>
@@ -23758,13 +23761,13 @@
         <v>22</v>
       </c>
       <c r="N355" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="O355" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="P355" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-grace-master.report.xlsx
+++ b/tools/importer/reports/import-grace-master.report.xlsx
@@ -583,7 +583,7 @@
     <t>industries/refining-technologies</t>
   </si>
   <si>
-    <t>2026-08-13T19:42:35.543Z</t>
+    <t>2026-08-14T08:52:40.610Z</t>
   </si>
   <si>
     <t>Refining Technologies</t>
@@ -4377,13 +4377,13 @@
     <t>industries/refining-technologies/fcc-additive-solutions.report.json</t>
   </si>
   <si>
-    <t>["hero-banner","columns-horizontal-teaser-featured","cards-featured-content","banner-resource-download"]</t>
+    <t>["hero-banner","columns-horizontal-teaser-featured","cards-category-grid","cards-featured-content","banner-resource-download"]</t>
   </si>
   <si>
     <t>industries/refining-technologies/fcc-additive-solutions</t>
   </si>
   <si>
-    <t>2026-08-13T19:51:44.172Z</t>
+    <t>2026-08-14T09:00:42.616Z</t>
   </si>
   <si>
     <t>FCC Additive Solutions</t>
@@ -4395,13 +4395,10 @@
     <t>industries/refining-technologies/fcc-catalyst-application.report.json</t>
   </si>
   <si>
-    <t>["hero-banner","video-overlay","columns-horizontal-teaser-featured","cards-featured-content","banner-resource-download"]</t>
-  </si>
-  <si>
     <t>industries/refining-technologies/fcc-catalyst-application</t>
   </si>
   <si>
-    <t>2026-08-13T19:43:32.402Z</t>
+    <t>2026-08-14T08:59:49.380Z</t>
   </si>
   <si>
     <t>FCC Catalyst Solutions</t>
@@ -4413,724 +4410,727 @@
     <t>industries/refining-technologies/hydroprocessing.report.json</t>
   </si>
   <si>
+    <t>["hero-banner","cards-category-grid","cards-featured-content","banner-resource-download"]</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/hydroprocessing</t>
+  </si>
+  <si>
+    <t>2026-08-14T08:58:02.910Z</t>
+  </si>
+  <si>
+    <t>Hydroprocessing</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/refining-technologies/hydroprocessing/</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/value-creation.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","video-overlay","columns-image-teaser","cards-category-grid","cards-featured-content","banner-resource-download"]</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/value-creation</t>
+  </si>
+  <si>
+    <t>2026-08-14T08:58:56.509Z</t>
+  </si>
+  <si>
+    <t>Value Creation</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/refining-technologies/value-creation/</t>
+  </si>
+  <si>
+    <t>people-and-careers/benefits/us-employee-benefits-summary.report.json</t>
+  </si>
+  <si>
+    <t>["accordion-nested"]</t>
+  </si>
+  <si>
+    <t>people-and-careers/benefits/us-employee-benefits-summary</t>
+  </si>
+  <si>
+    <t>2026-08-05T16:53:46.074Z</t>
+  </si>
+  <si>
+    <t>U.S. Employee Benefits Summary</t>
+  </si>
+  <si>
+    <t>https://grace.com/people-and-careers/benefits/us-employee-benefits-summary/</t>
+  </si>
+  <si>
+    <t>products/synthetic-silicas/classification.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-image-teaser"]</t>
+  </si>
+  <si>
+    <t>["breadcrumb"]</t>
+  </si>
+  <si>
+    <t>products/synthetic-silicas/classification</t>
+  </si>
+  <si>
+    <t>2026-08-09T17:01:40.743Z</t>
+  </si>
+  <si>
+    <t>Synthetic Amorphous Silica (SAS)</t>
+  </si>
+  <si>
+    <t>https://grace.com/products/synthetic-silicas/classification/</t>
+  </si>
+  <si>
+    <t>industries/biofuels/biomass-based-diesel/first-generation-biodiesel.report.json</t>
+  </si>
+  <si>
+    <t>industries/biofuels/biomass-based-diesel/first-generation-biodiesel</t>
+  </si>
+  <si>
+    <t>2026-08-13T20:03:05.293Z</t>
+  </si>
+  <si>
+    <t>First Generation Biodiesel</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/biofuels/biomass-based-diesel/first-generation-biodiesel/</t>
+  </si>
+  <si>
+    <t>industries/biofuels/biomass-based-diesel/renewable-diesel.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","video-overlay","quote-highlight","cards-product","columns-horizontal-teaser-featured","cards-featured-content"]</t>
+  </si>
+  <si>
+    <t>industries/biofuels/biomass-based-diesel/renewable-diesel</t>
+  </si>
+  <si>
+    <t>2026-08-13T20:03:58.046Z</t>
+  </si>
+  <si>
+    <t>Renewable Diesel</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/biofuels/biomass-based-diesel/renewable-diesel/</t>
+  </si>
+  <si>
+    <t>industries/pharmaceutical-solutions/fine-chemicals/consultative-services.report.json</t>
+  </si>
+  <si>
+    <t>industries/pharmaceutical-solutions/fine-chemicals/consultative-services</t>
+  </si>
+  <si>
+    <t>2026-08-13T19:59:47.535Z</t>
+  </si>
+  <si>
+    <t>Consultative Services</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/pharmaceutical-solutions/fine-chemicals/consultative-services/</t>
+  </si>
+  <si>
+    <t>industries/pharmaceutical-solutions/fine-chemicals/custom-apis.report.json</t>
+  </si>
+  <si>
+    <t>industries/pharmaceutical-solutions/fine-chemicals/custom-apis</t>
+  </si>
+  <si>
+    <t>2026-08-13T19:56:12.157Z</t>
+  </si>
+  <si>
+    <t>Custom APIs</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/pharmaceutical-solutions/fine-chemicals/custom-apis/</t>
+  </si>
+  <si>
+    <t>industries/pharmaceutical-solutions/fine-chemicals/facilities.report.json</t>
+  </si>
+  <si>
+    <t>industries/pharmaceutical-solutions/fine-chemicals/facilities</t>
+  </si>
+  <si>
+    <t>2026-08-13T20:02:28.188Z</t>
+  </si>
+  <si>
+    <t>Facilities</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/pharmaceutical-solutions/fine-chemicals/facilities/</t>
+  </si>
+  <si>
+    <t>industries/pharmaceutical-solutions/fine-chemicals/fcms-case-study.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner"]</t>
+  </si>
+  <si>
+    <t>industries/pharmaceutical-solutions/fine-chemicals/fcms-case-study</t>
+  </si>
+  <si>
+    <t>2026-08-13T20:05:08.894Z</t>
+  </si>
+  <si>
+    <t>FCMS Case Study</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/pharmaceutical-solutions/fine-chemicals/fcms-case-study/</t>
+  </si>
+  <si>
+    <t>industries/pharmaceutical-solutions/fine-chemicals/generic-apis.report.json</t>
+  </si>
+  <si>
+    <t>industries/pharmaceutical-solutions/fine-chemicals/generic-apis</t>
+  </si>
+  <si>
+    <t>2026-08-13T19:57:59.050Z</t>
+  </si>
+  <si>
+    <t>Generic APIs</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/pharmaceutical-solutions/fine-chemicals/generic-apis/</t>
+  </si>
+  <si>
+    <t>industries/pharmaceutical-solutions/fine-chemicals/integrated-scale-up.report.json</t>
+  </si>
+  <si>
+    <t>industries/pharmaceutical-solutions/fine-chemicals/integrated-scale-up</t>
+  </si>
+  <si>
+    <t>2026-08-13T19:58:53.146Z</t>
+  </si>
+  <si>
+    <t>Integrated Scale-Up</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/pharmaceutical-solutions/fine-chemicals/integrated-scale-up/</t>
+  </si>
+  <si>
+    <t>industries/pharmaceutical-solutions/fine-chemicals/rsms-and-intermediates.report.json</t>
+  </si>
+  <si>
+    <t>industries/pharmaceutical-solutions/fine-chemicals/rsms-and-intermediates</t>
+  </si>
+  <si>
+    <t>2026-08-13T19:57:06.256Z</t>
+  </si>
+  <si>
+    <t>RSMs and Intermediates</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/pharmaceutical-solutions/fine-chemicals/rsms-and-intermediates/</t>
+  </si>
+  <si>
+    <t>industries/pharmaceutical-solutions/purification-formulation-delivery/active-ingredient-delivery.report.json</t>
+  </si>
+  <si>
+    <t>industries/pharmaceutical-solutions/purification-formulation-delivery/active-ingredient-delivery</t>
+  </si>
+  <si>
+    <t>2026-08-13T19:44:18.004Z</t>
+  </si>
+  <si>
+    <t>Active Ingredient Delivery</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/pharmaceutical-solutions/purification-formulation-delivery/active-ingredient-delivery/</t>
+  </si>
+  <si>
+    <t>industries/pharmaceutical-solutions/purification-formulation-delivery/chromatography.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","video-overlay","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq","columns-horizontal-teaser-featured","cards-category-grid","cards-featured-content"]</t>
+  </si>
+  <si>
+    <t>industries/pharmaceutical-solutions/purification-formulation-delivery/chromatography</t>
+  </si>
+  <si>
+    <t>2026-08-13T19:42:31.146Z</t>
+  </si>
+  <si>
+    <t>Chromatography</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/pharmaceutical-solutions/purification-formulation-delivery/chromatography/</t>
+  </si>
+  <si>
+    <t>industries/pharmaceutical-solutions/purification-formulation-delivery/excipients.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","video-overlay","accordion-faq","columns-horizontal-teaser-featured","cards-category-grid","cards-featured-content"]</t>
+  </si>
+  <si>
+    <t>industries/pharmaceutical-solutions/purification-formulation-delivery/excipients</t>
+  </si>
+  <si>
+    <t>2026-08-13T19:43:24.551Z</t>
+  </si>
+  <si>
+    <t>Excipients</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/pharmaceutical-solutions/purification-formulation-delivery/excipients/</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/plastic-additives/silica-anti-blocking-agents.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","accordion-faq","table-three-column","table-three-column","table-three-column","cards-featured-content"]</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/plastic-additives/silica-anti-blocking-agents</t>
+  </si>
+  <si>
+    <t>2026-08-13T20:00:31.750Z</t>
+  </si>
+  <si>
+    <t>Silica Anti-blocking Agents</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/plastics-and-polymers/plastic-additives/silica-anti-blocking-agents/</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/plastic-additives/titanium-dioxide-extenders.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-brochure-promo","columns-image-teaser","cards-featured-content"]</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/plastic-additives/titanium-dioxide-extenders</t>
+  </si>
+  <si>
+    <t>2026-08-13T20:01:24.650Z</t>
+  </si>
+  <si>
+    <t>Titanium Dioxide Extenders</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/plastics-and-polymers/plastic-additives/titanium-dioxide-extenders/</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/polyethylene-catalysts/pe-catalyst-components-and-supports.report.json</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/polyethylene-catalysts/pe-catalyst-components-and-supports</t>
+  </si>
+  <si>
+    <t>2026-08-13T19:45:11.697Z</t>
+  </si>
+  <si>
+    <t>PE Catalyst Components and Supports</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/plastics-and-polymers/polyethylene-catalysts/pe-catalyst-components-and-supports/</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/polyethylene-catalysts/pe-gas-phase.report.json</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/polyethylene-catalysts/pe-gas-phase</t>
+  </si>
+  <si>
+    <t>2026-08-14T07:38:11.436Z</t>
+  </si>
+  <si>
+    <t>PE Gas Phase</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/plastics-and-polymers/polyethylene-catalysts/pe-gas-phase/</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/polyethylene-catalysts/pe-hybrid.report.json</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/polyethylene-catalysts/pe-hybrid</t>
+  </si>
+  <si>
+    <t>2026-08-13T19:48:48.943Z</t>
+  </si>
+  <si>
+    <t>PE Hybrid</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/plastics-and-polymers/polyethylene-catalysts/pe-hybrid/</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/polyethylene-catalysts/pe-slurry.report.json</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/polyethylene-catalysts/pe-slurry</t>
+  </si>
+  <si>
+    <t>2026-08-14T07:37:18.651Z</t>
+  </si>
+  <si>
+    <t>PE Slurry</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/plastics-and-polymers/polyethylene-catalysts/pe-slurry/</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/polyethylene-catalysts/pe-solution.report.json</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/polyethylene-catalysts/pe-solution</t>
+  </si>
+  <si>
+    <t>2026-08-13T19:47:55.263Z</t>
+  </si>
+  <si>
+    <t>PE Solution</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/plastics-and-polymers/polyethylene-catalysts/pe-solution/</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/polypropylene-catalysts/pp-bulk.report.json</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/polypropylene-catalysts/pp-bulk</t>
+  </si>
+  <si>
+    <t>2026-08-14T07:39:04.089Z</t>
+  </si>
+  <si>
+    <t>PP Bulk</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/plastics-and-polymers/polypropylene-catalysts/pp-bulk/</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/polypropylene-catalysts/pp-gas-phase.report.json</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/polypropylene-catalysts/pp-gas-phase</t>
+  </si>
+  <si>
+    <t>2026-08-14T07:39:57.483Z</t>
+  </si>
+  <si>
+    <t>PP Gas Phase</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/plastics-and-polymers/polypropylene-catalysts/pp-gas-phase/</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/polypropylene-catalysts/pp-slurry.report.json</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/polypropylene-catalysts/pp-slurry</t>
+  </si>
+  <si>
+    <t>2026-08-13T19:52:27.600Z</t>
+  </si>
+  <si>
+    <t>PP Slurry</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/plastics-and-polymers/polypropylene-catalysts/pp-slurry/</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/unipol--pp-process-technology/unipol-pp-process.report.json</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/unipol--pp-process-technology/unipol-pp-process</t>
+  </si>
+  <si>
+    <t>2026-08-13T01:34:30.899Z</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/plastics-and-polymers/unipol--pp-process-technology/unipol-pp-process/</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-performance.report.json</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-performance</t>
+  </si>
+  <si>
+    <t>2026-08-13T19:56:03.555Z</t>
+  </si>
+  <si>
+    <t>UNIPOL® PP Performance</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/plastics-and-polymers/unipol--pp-process-technology/unipol-pp-performance/</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-process.report.json</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-process</t>
+  </si>
+  <si>
+    <t>2026-08-13T19:54:14.694Z</t>
+  </si>
+  <si>
+    <t>UNIPOL® PP Process</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-products.report.json</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-products</t>
+  </si>
+  <si>
+    <t>2026-08-13T19:55:09.606Z</t>
+  </si>
+  <si>
+    <t>UNIPOL® PP Products</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/plastics-and-polymers/unipol--pp-process-technology/unipol-pp-products/</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-services.report.json</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-services</t>
+  </si>
+  <si>
+    <t>2026-08-13T19:56:57.071Z</t>
+  </si>
+  <si>
+    <t>UNIPOL® PP Services</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/plastics-and-polymers/unipol--pp-process-technology/unipol-pp-services/</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-technology-ppartner-program.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","video-overlay","quote-testimonial","columns-horizontal-teaser-featured","cards-category-grid"]</t>
+  </si>
+  <si>
+    <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-technology-ppartner-program</t>
+  </si>
+  <si>
+    <t>2026-08-13T19:57:50.862Z</t>
+  </si>
+  <si>
+    <t>PPartner Program™ Services</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/plastics-and-polymers/unipol--pp-process-technology/unipol-pp-technology-ppartner-program/</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/fcc-additive-solutions/combustion-promoter.report.json</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/fcc-additive-solutions/combustion-promoter</t>
+  </si>
+  <si>
+    <t>2026-08-14T08:57:10.011Z</t>
+  </si>
+  <si>
+    <t>Combustion Promoter</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/refining-technologies/fcc-additive-solutions/combustion-promoter/</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/fcc-additive-solutions/gasoline-sulphur-reduction.report.json</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/fcc-additive-solutions/gasoline-sulphur-reduction</t>
+  </si>
+  <si>
+    <t>2026-08-14T08:55:23.031Z</t>
+  </si>
+  <si>
+    <t>Gasoline Sulphur Reduction</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/refining-technologies/fcc-additive-solutions/gasoline-sulphur-reduction/</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/fcc-additive-solutions/light-olefins.report.json</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/fcc-additive-solutions/light-olefins</t>
+  </si>
+  <si>
+    <t>2026-08-14T08:54:28.613Z</t>
+  </si>
+  <si>
+    <t>Light Olefins</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/refining-technologies/fcc-additive-solutions/light-olefins/</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/fcc-additive-solutions/nox-reduction.report.json</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/fcc-additive-solutions/nox-reduction</t>
+  </si>
+  <si>
+    <t>2026-08-14T08:53:34.688Z</t>
+  </si>
+  <si>
+    <t>NOx Reduction</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/refining-technologies/fcc-additive-solutions/nox-reduction/</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/fcc-additive-solutions/sox-reduction.report.json</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/fcc-additive-solutions/sox-reduction</t>
+  </si>
+  <si>
+    <t>2026-08-14T08:56:16.531Z</t>
+  </si>
+  <si>
+    <t>SOx Reduction</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/refining-technologies/fcc-additive-solutions/sox-reduction/</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/fcc-catalyst-application/butylene-selectivity.report.json</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/fcc-catalyst-application/butylene-selectivity</t>
+  </si>
+  <si>
+    <t>2026-08-14T09:04:15.024Z</t>
+  </si>
+  <si>
+    <t>Butylene Selectivity</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/refining-technologies/fcc-catalyst-application/butylene-selectivity/</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/fcc-catalyst-application/light-feed-performance.report.json</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/fcc-catalyst-application/light-feed-performance</t>
+  </si>
+  <si>
+    <t>2026-08-14T09:02:28.927Z</t>
+  </si>
+  <si>
+    <t>Light Feed Performance</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/refining-technologies/fcc-catalyst-application/light-feed-performance/</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/fcc-catalyst-application/maximize-propylene.report.json</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/fcc-catalyst-application/maximize-propylene</t>
+  </si>
+  <si>
+    <t>2026-08-14T09:01:36.416Z</t>
+  </si>
+  <si>
+    <t>Maximize Propylene</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/refining-technologies/fcc-catalyst-application/maximize-propylene/</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/fcc-catalyst-application/resid-conversion.report.json</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/fcc-catalyst-application/resid-conversion</t>
+  </si>
+  <si>
+    <t>2026-08-14T09:03:22.033Z</t>
+  </si>
+  <si>
+    <t>Resid Conversion</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/refining-technologies/fcc-catalyst-application/resid-conversion/</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/hydroprocessing/distillate-hydrotreating-solutions.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","cards-category-grid"]</t>
+  </si>
+  <si>
+    <t>["template","contactus","breadcrumb","breadcrumb-title"]</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/hydroprocessing/distillate-hydrotreating-solutions</t>
+  </si>
+  <si>
+    <t>2026-08-13T21:46:36.990Z</t>
+  </si>
+  <si>
+    <t>Distillate Hydrotreating Solutions</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/refining-technologies/hydroprocessing/distillate-hydrotreating-solutions/</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/hydroprocessing/resid-hydrocracking-solutions.report.json</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/hydroprocessing/resid-hydrocracking-solutions</t>
+  </si>
+  <si>
+    <t>2026-08-13T21:45:43.655Z</t>
+  </si>
+  <si>
+    <t>Resid Hydrocracking Solutions</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/refining-technologies/hydroprocessing/resid-hydrocracking-solutions/</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/hydroprocessing/resid-hydrotreating-solutions.report.json</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/hydroprocessing/resid-hydrotreating-solutions</t>
+  </si>
+  <si>
+    <t>2026-08-13T21:44:50.934Z</t>
+  </si>
+  <si>
+    <t>Resid Hydrotreating Solutions</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/refining-technologies/hydroprocessing/resid-hydrotreating-solutions/</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/value-creation/specialized-evaluation-tools.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","video-overlay","cards-featured-content","banner-resource-download"]</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/value-creation/specialized-evaluation-tools</t>
+  </si>
+  <si>
+    <t>2026-08-14T09:06:56.441Z</t>
+  </si>
+  <si>
+    <t>Specialized Evaluation Tools</t>
+  </si>
+  <si>
+    <t>https://grace.com/industries/refining-technologies/value-creation/specialized-evaluation-tools/</t>
+  </si>
+  <si>
+    <t>industries/refining-technologies/value-creation/sustainability.report.json</t>
+  </si>
+  <si>
     <t>["hero-banner","cards-featured-content","banner-resource-download"]</t>
   </si>
   <si>
-    <t>industries/refining-technologies/hydroprocessing</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:57:09.242Z</t>
-  </si>
-  <si>
-    <t>Hydroprocessing</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/refining-technologies/hydroprocessing/</t>
-  </si>
-  <si>
-    <t>industries/refining-technologies/value-creation.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","video-overlay","columns-image-teaser","cards-featured-content","banner-resource-download"]</t>
-  </si>
-  <si>
-    <t>industries/refining-technologies/value-creation</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:48:07.544Z</t>
-  </si>
-  <si>
-    <t>Value Creation</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/refining-technologies/value-creation/</t>
-  </si>
-  <si>
-    <t>people-and-careers/benefits/us-employee-benefits-summary.report.json</t>
-  </si>
-  <si>
-    <t>["accordion-nested"]</t>
-  </si>
-  <si>
-    <t>people-and-careers/benefits/us-employee-benefits-summary</t>
-  </si>
-  <si>
-    <t>2026-08-05T16:53:46.074Z</t>
-  </si>
-  <si>
-    <t>U.S. Employee Benefits Summary</t>
-  </si>
-  <si>
-    <t>https://grace.com/people-and-careers/benefits/us-employee-benefits-summary/</t>
-  </si>
-  <si>
-    <t>products/synthetic-silicas/classification.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","columns-image-teaser"]</t>
-  </si>
-  <si>
-    <t>["breadcrumb"]</t>
-  </si>
-  <si>
-    <t>products/synthetic-silicas/classification</t>
-  </si>
-  <si>
-    <t>2026-08-09T17:01:40.743Z</t>
-  </si>
-  <si>
-    <t>Synthetic Amorphous Silica (SAS)</t>
-  </si>
-  <si>
-    <t>https://grace.com/products/synthetic-silicas/classification/</t>
-  </si>
-  <si>
-    <t>industries/biofuels/biomass-based-diesel/first-generation-biodiesel.report.json</t>
-  </si>
-  <si>
-    <t>industries/biofuels/biomass-based-diesel/first-generation-biodiesel</t>
-  </si>
-  <si>
-    <t>2026-08-13T20:03:05.293Z</t>
-  </si>
-  <si>
-    <t>First Generation Biodiesel</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/biofuels/biomass-based-diesel/first-generation-biodiesel/</t>
-  </si>
-  <si>
-    <t>industries/biofuels/biomass-based-diesel/renewable-diesel.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","video-overlay","quote-highlight","cards-product","columns-horizontal-teaser-featured","cards-featured-content"]</t>
-  </si>
-  <si>
-    <t>industries/biofuels/biomass-based-diesel/renewable-diesel</t>
-  </si>
-  <si>
-    <t>2026-08-13T20:03:58.046Z</t>
-  </si>
-  <si>
-    <t>Renewable Diesel</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/biofuels/biomass-based-diesel/renewable-diesel/</t>
-  </si>
-  <si>
-    <t>industries/pharmaceutical-solutions/fine-chemicals/consultative-services.report.json</t>
-  </si>
-  <si>
-    <t>industries/pharmaceutical-solutions/fine-chemicals/consultative-services</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:59:47.535Z</t>
-  </si>
-  <si>
-    <t>Consultative Services</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/pharmaceutical-solutions/fine-chemicals/consultative-services/</t>
-  </si>
-  <si>
-    <t>industries/pharmaceutical-solutions/fine-chemicals/custom-apis.report.json</t>
-  </si>
-  <si>
-    <t>industries/pharmaceutical-solutions/fine-chemicals/custom-apis</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:56:12.157Z</t>
-  </si>
-  <si>
-    <t>Custom APIs</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/pharmaceutical-solutions/fine-chemicals/custom-apis/</t>
-  </si>
-  <si>
-    <t>industries/pharmaceutical-solutions/fine-chemicals/facilities.report.json</t>
-  </si>
-  <si>
-    <t>industries/pharmaceutical-solutions/fine-chemicals/facilities</t>
-  </si>
-  <si>
-    <t>2026-08-13T20:02:28.188Z</t>
-  </si>
-  <si>
-    <t>Facilities</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/pharmaceutical-solutions/fine-chemicals/facilities/</t>
-  </si>
-  <si>
-    <t>industries/pharmaceutical-solutions/fine-chemicals/fcms-case-study.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner"]</t>
-  </si>
-  <si>
-    <t>industries/pharmaceutical-solutions/fine-chemicals/fcms-case-study</t>
-  </si>
-  <si>
-    <t>2026-08-13T20:05:08.894Z</t>
-  </si>
-  <si>
-    <t>FCMS Case Study</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/pharmaceutical-solutions/fine-chemicals/fcms-case-study/</t>
-  </si>
-  <si>
-    <t>industries/pharmaceutical-solutions/fine-chemicals/generic-apis.report.json</t>
-  </si>
-  <si>
-    <t>industries/pharmaceutical-solutions/fine-chemicals/generic-apis</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:57:59.050Z</t>
-  </si>
-  <si>
-    <t>Generic APIs</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/pharmaceutical-solutions/fine-chemicals/generic-apis/</t>
-  </si>
-  <si>
-    <t>industries/pharmaceutical-solutions/fine-chemicals/integrated-scale-up.report.json</t>
-  </si>
-  <si>
-    <t>industries/pharmaceutical-solutions/fine-chemicals/integrated-scale-up</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:58:53.146Z</t>
-  </si>
-  <si>
-    <t>Integrated Scale-Up</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/pharmaceutical-solutions/fine-chemicals/integrated-scale-up/</t>
-  </si>
-  <si>
-    <t>industries/pharmaceutical-solutions/fine-chemicals/rsms-and-intermediates.report.json</t>
-  </si>
-  <si>
-    <t>industries/pharmaceutical-solutions/fine-chemicals/rsms-and-intermediates</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:57:06.256Z</t>
-  </si>
-  <si>
-    <t>RSMs and Intermediates</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/pharmaceutical-solutions/fine-chemicals/rsms-and-intermediates/</t>
-  </si>
-  <si>
-    <t>industries/pharmaceutical-solutions/purification-formulation-delivery/active-ingredient-delivery.report.json</t>
-  </si>
-  <si>
-    <t>industries/pharmaceutical-solutions/purification-formulation-delivery/active-ingredient-delivery</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:44:18.004Z</t>
-  </si>
-  <si>
-    <t>Active Ingredient Delivery</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/pharmaceutical-solutions/purification-formulation-delivery/active-ingredient-delivery/</t>
-  </si>
-  <si>
-    <t>industries/pharmaceutical-solutions/purification-formulation-delivery/chromatography.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","video-overlay","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq","columns-horizontal-teaser-featured","cards-category-grid","cards-featured-content"]</t>
-  </si>
-  <si>
-    <t>industries/pharmaceutical-solutions/purification-formulation-delivery/chromatography</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:42:31.146Z</t>
-  </si>
-  <si>
-    <t>Chromatography</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/pharmaceutical-solutions/purification-formulation-delivery/chromatography/</t>
-  </si>
-  <si>
-    <t>industries/pharmaceutical-solutions/purification-formulation-delivery/excipients.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","video-overlay","accordion-faq","columns-horizontal-teaser-featured","cards-category-grid","cards-featured-content"]</t>
-  </si>
-  <si>
-    <t>industries/pharmaceutical-solutions/purification-formulation-delivery/excipients</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:43:24.551Z</t>
-  </si>
-  <si>
-    <t>Excipients</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/pharmaceutical-solutions/purification-formulation-delivery/excipients/</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/plastic-additives/silica-anti-blocking-agents.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","accordion-faq","table-three-column","table-three-column","table-three-column","cards-featured-content"]</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/plastic-additives/silica-anti-blocking-agents</t>
-  </si>
-  <si>
-    <t>2026-08-13T20:00:31.750Z</t>
-  </si>
-  <si>
-    <t>Silica Anti-blocking Agents</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/plastics-and-polymers/plastic-additives/silica-anti-blocking-agents/</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/plastic-additives/titanium-dioxide-extenders.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","columns-brochure-promo","columns-image-teaser","cards-featured-content"]</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/plastic-additives/titanium-dioxide-extenders</t>
-  </si>
-  <si>
-    <t>2026-08-13T20:01:24.650Z</t>
-  </si>
-  <si>
-    <t>Titanium Dioxide Extenders</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/plastics-and-polymers/plastic-additives/titanium-dioxide-extenders/</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/polyethylene-catalysts/pe-catalyst-components-and-supports.report.json</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/polyethylene-catalysts/pe-catalyst-components-and-supports</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:45:11.697Z</t>
-  </si>
-  <si>
-    <t>PE Catalyst Components and Supports</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/plastics-and-polymers/polyethylene-catalysts/pe-catalyst-components-and-supports/</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/polyethylene-catalysts/pe-gas-phase.report.json</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/polyethylene-catalysts/pe-gas-phase</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:46:59.894Z</t>
-  </si>
-  <si>
-    <t>PE Gas Phase</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/plastics-and-polymers/polyethylene-catalysts/pe-gas-phase/</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/polyethylene-catalysts/pe-hybrid.report.json</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/polyethylene-catalysts/pe-hybrid</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:48:48.943Z</t>
-  </si>
-  <si>
-    <t>PE Hybrid</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/plastics-and-polymers/polyethylene-catalysts/pe-hybrid/</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/polyethylene-catalysts/pe-slurry.report.json</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/polyethylene-catalysts/pe-slurry</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:46:06.442Z</t>
-  </si>
-  <si>
-    <t>PE Slurry</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/plastics-and-polymers/polyethylene-catalysts/pe-slurry/</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/polyethylene-catalysts/pe-solution.report.json</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/polyethylene-catalysts/pe-solution</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:47:55.263Z</t>
-  </si>
-  <si>
-    <t>PE Solution</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/plastics-and-polymers/polyethylene-catalysts/pe-solution/</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/polypropylene-catalysts/pp-bulk.report.json</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/polypropylene-catalysts/pp-bulk</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:50:37.896Z</t>
-  </si>
-  <si>
-    <t>PP Bulk</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/plastics-and-polymers/polypropylene-catalysts/pp-bulk/</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/polypropylene-catalysts/pp-gas-phase.report.json</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/polypropylene-catalysts/pp-gas-phase</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:51:33.076Z</t>
-  </si>
-  <si>
-    <t>PP Gas Phase</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/plastics-and-polymers/polypropylene-catalysts/pp-gas-phase/</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/polypropylene-catalysts/pp-slurry.report.json</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/polypropylene-catalysts/pp-slurry</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:52:27.600Z</t>
-  </si>
-  <si>
-    <t>PP Slurry</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/plastics-and-polymers/polypropylene-catalysts/pp-slurry/</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/unipol--pp-process-technology/unipol-pp-process.report.json</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/unipol--pp-process-technology/unipol-pp-process</t>
-  </si>
-  <si>
-    <t>2026-08-13T01:34:30.899Z</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/plastics-and-polymers/unipol--pp-process-technology/unipol-pp-process/</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-performance.report.json</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-performance</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:56:03.555Z</t>
-  </si>
-  <si>
-    <t>UNIPOL® PP Performance</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/plastics-and-polymers/unipol--pp-process-technology/unipol-pp-performance/</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-process.report.json</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-process</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:54:14.694Z</t>
-  </si>
-  <si>
-    <t>UNIPOL® PP Process</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-products.report.json</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-products</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:55:09.606Z</t>
-  </si>
-  <si>
-    <t>UNIPOL® PP Products</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/plastics-and-polymers/unipol--pp-process-technology/unipol-pp-products/</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-services.report.json</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-services</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:56:57.071Z</t>
-  </si>
-  <si>
-    <t>UNIPOL® PP Services</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/plastics-and-polymers/unipol--pp-process-technology/unipol-pp-services/</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-technology-ppartner-program.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","video-overlay","quote-testimonial","columns-horizontal-teaser-featured","cards-category-grid"]</t>
-  </si>
-  <si>
-    <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-technology-ppartner-program</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:57:50.862Z</t>
-  </si>
-  <si>
-    <t>PPartner Program™ Services</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/plastics-and-polymers/unipol--pp-process-technology/unipol-pp-technology-ppartner-program/</t>
-  </si>
-  <si>
-    <t>industries/refining-technologies/fcc-additive-solutions/combustion-promoter.report.json</t>
-  </si>
-  <si>
-    <t>industries/refining-technologies/fcc-additive-solutions/combustion-promoter</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:56:15.995Z</t>
-  </si>
-  <si>
-    <t>Combustion Promoter</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/refining-technologies/fcc-additive-solutions/combustion-promoter/</t>
-  </si>
-  <si>
-    <t>industries/refining-technologies/fcc-additive-solutions/gasoline-sulphur-reduction.report.json</t>
-  </si>
-  <si>
-    <t>industries/refining-technologies/fcc-additive-solutions/gasoline-sulphur-reduction</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:53:33.634Z</t>
-  </si>
-  <si>
-    <t>Gasoline Sulphur Reduction</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/refining-technologies/fcc-additive-solutions/gasoline-sulphur-reduction/</t>
-  </si>
-  <si>
-    <t>industries/refining-technologies/fcc-additive-solutions/light-olefins.report.json</t>
-  </si>
-  <si>
-    <t>industries/refining-technologies/fcc-additive-solutions/light-olefins</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:54:28.018Z</t>
-  </si>
-  <si>
-    <t>Light Olefins</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/refining-technologies/fcc-additive-solutions/light-olefins/</t>
-  </si>
-  <si>
-    <t>industries/refining-technologies/fcc-additive-solutions/nox-reduction.report.json</t>
-  </si>
-  <si>
-    <t>industries/refining-technologies/fcc-additive-solutions/nox-reduction</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:55:21.295Z</t>
-  </si>
-  <si>
-    <t>NOx Reduction</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/refining-technologies/fcc-additive-solutions/nox-reduction/</t>
-  </si>
-  <si>
-    <t>industries/refining-technologies/fcc-additive-solutions/sox-reduction.report.json</t>
-  </si>
-  <si>
-    <t>industries/refining-technologies/fcc-additive-solutions/sox-reduction</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:52:38.394Z</t>
-  </si>
-  <si>
-    <t>SOx Reduction</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/refining-technologies/fcc-additive-solutions/sox-reduction/</t>
-  </si>
-  <si>
-    <t>industries/refining-technologies/fcc-catalyst-application/butylene-selectivity.report.json</t>
-  </si>
-  <si>
-    <t>industries/refining-technologies/fcc-catalyst-application/butylene-selectivity</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:45:23.237Z</t>
-  </si>
-  <si>
-    <t>Butylene Selectivity</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/refining-technologies/fcc-catalyst-application/butylene-selectivity/</t>
-  </si>
-  <si>
-    <t>industries/refining-technologies/fcc-catalyst-application/light-feed-performance.report.json</t>
-  </si>
-  <si>
-    <t>industries/refining-technologies/fcc-catalyst-application/light-feed-performance</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:47:12.911Z</t>
-  </si>
-  <si>
-    <t>Light Feed Performance</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/refining-technologies/fcc-catalyst-application/light-feed-performance/</t>
-  </si>
-  <si>
-    <t>industries/refining-technologies/fcc-catalyst-application/maximize-propylene.report.json</t>
-  </si>
-  <si>
-    <t>industries/refining-technologies/fcc-catalyst-application/maximize-propylene</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:44:27.444Z</t>
-  </si>
-  <si>
-    <t>Maximize Propylene</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/refining-technologies/fcc-catalyst-application/maximize-propylene/</t>
-  </si>
-  <si>
-    <t>industries/refining-technologies/fcc-catalyst-application/resid-conversion.report.json</t>
-  </si>
-  <si>
-    <t>industries/refining-technologies/fcc-catalyst-application/resid-conversion</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:46:18.270Z</t>
-  </si>
-  <si>
-    <t>Resid Conversion</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/refining-technologies/fcc-catalyst-application/resid-conversion/</t>
-  </si>
-  <si>
-    <t>industries/refining-technologies/hydroprocessing/distillate-hydrotreating-solutions.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","cards-category-grid"]</t>
-  </si>
-  <si>
-    <t>["template","contactus","breadcrumb","breadcrumb-title"]</t>
-  </si>
-  <si>
-    <t>industries/refining-technologies/hydroprocessing/distillate-hydrotreating-solutions</t>
-  </si>
-  <si>
-    <t>2026-08-13T21:46:36.990Z</t>
-  </si>
-  <si>
-    <t>Distillate Hydrotreating Solutions</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/refining-technologies/hydroprocessing/distillate-hydrotreating-solutions/</t>
-  </si>
-  <si>
-    <t>industries/refining-technologies/hydroprocessing/resid-hydrocracking-solutions.report.json</t>
-  </si>
-  <si>
-    <t>industries/refining-technologies/hydroprocessing/resid-hydrocracking-solutions</t>
-  </si>
-  <si>
-    <t>2026-08-13T21:45:43.655Z</t>
-  </si>
-  <si>
-    <t>Resid Hydrocracking Solutions</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/refining-technologies/hydroprocessing/resid-hydrocracking-solutions/</t>
-  </si>
-  <si>
-    <t>industries/refining-technologies/hydroprocessing/resid-hydrotreating-solutions.report.json</t>
-  </si>
-  <si>
-    <t>industries/refining-technologies/hydroprocessing/resid-hydrotreating-solutions</t>
-  </si>
-  <si>
-    <t>2026-08-13T21:44:50.934Z</t>
-  </si>
-  <si>
-    <t>Resid Hydrotreating Solutions</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/refining-technologies/hydroprocessing/resid-hydrotreating-solutions/</t>
-  </si>
-  <si>
-    <t>industries/refining-technologies/value-creation/specialized-evaluation-tools.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","video-overlay","cards-featured-content","banner-resource-download"]</t>
-  </si>
-  <si>
-    <t>industries/refining-technologies/value-creation/specialized-evaluation-tools</t>
-  </si>
-  <si>
-    <t>2026-08-13T19:49:56.303Z</t>
-  </si>
-  <si>
-    <t>Specialized Evaluation Tools</t>
-  </si>
-  <si>
-    <t>https://grace.com/industries/refining-technologies/value-creation/specialized-evaluation-tools/</t>
-  </si>
-  <si>
-    <t>industries/refining-technologies/value-creation/sustainability.report.json</t>
-  </si>
-  <si>
     <t>industries/refining-technologies/value-creation/sustainability</t>
   </si>
   <si>
-    <t>2026-08-13T19:50:49.692Z</t>
+    <t>2026-08-14T09:06:02.821Z</t>
   </si>
   <si>
     <t>Sustainable Solutions for FCC</t>
@@ -5148,7 +5148,7 @@
     <t>industries/refining-technologies/value-creation/technical-service-expertise</t>
   </si>
   <si>
-    <t>2026-08-13T19:49:02.103Z</t>
+    <t>2026-08-14T09:05:08.778Z</t>
   </si>
   <si>
     <t>Technical Service Expertise</t>
@@ -19825,7 +19825,7 @@
         <v>1459</v>
       </c>
       <c r="B277" t="s">
-        <v>1460</v>
+        <v>188</v>
       </c>
       <c r="C277" t="s">
         <v>18</v>
@@ -19852,30 +19852,30 @@
         <v>20</v>
       </c>
       <c r="K277" t="s">
+        <v>1460</v>
+      </c>
+      <c r="L277" t="s">
+        <v>19</v>
+      </c>
+      <c r="M277" t="s">
+        <v>22</v>
+      </c>
+      <c r="N277" t="s">
         <v>1461</v>
       </c>
-      <c r="L277" t="s">
-        <v>19</v>
-      </c>
-      <c r="M277" t="s">
-        <v>22</v>
-      </c>
-      <c r="N277" t="s">
+      <c r="O277" t="s">
         <v>1462</v>
       </c>
-      <c r="O277" t="s">
+      <c r="P277" t="s">
         <v>1463</v>
-      </c>
-      <c r="P277" t="s">
-        <v>1464</v>
       </c>
     </row>
     <row r="278" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B278" t="s">
         <v>1465</v>
-      </c>
-      <c r="B278" t="s">
-        <v>1466</v>
       </c>
       <c r="C278" t="s">
         <v>18</v>
@@ -19902,30 +19902,30 @@
         <v>20</v>
       </c>
       <c r="K278" t="s">
+        <v>1466</v>
+      </c>
+      <c r="L278" t="s">
+        <v>19</v>
+      </c>
+      <c r="M278" t="s">
+        <v>22</v>
+      </c>
+      <c r="N278" t="s">
         <v>1467</v>
       </c>
-      <c r="L278" t="s">
-        <v>19</v>
-      </c>
-      <c r="M278" t="s">
-        <v>22</v>
-      </c>
-      <c r="N278" t="s">
+      <c r="O278" t="s">
         <v>1468</v>
       </c>
-      <c r="O278" t="s">
+      <c r="P278" t="s">
         <v>1469</v>
-      </c>
-      <c r="P278" t="s">
-        <v>1470</v>
       </c>
     </row>
     <row r="279" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
+        <v>1470</v>
+      </c>
+      <c r="B279" t="s">
         <v>1471</v>
-      </c>
-      <c r="B279" t="s">
-        <v>1472</v>
       </c>
       <c r="C279" t="s">
         <v>18</v>
@@ -19952,30 +19952,30 @@
         <v>20</v>
       </c>
       <c r="K279" t="s">
+        <v>1472</v>
+      </c>
+      <c r="L279" t="s">
+        <v>19</v>
+      </c>
+      <c r="M279" t="s">
+        <v>22</v>
+      </c>
+      <c r="N279" t="s">
         <v>1473</v>
       </c>
-      <c r="L279" t="s">
-        <v>19</v>
-      </c>
-      <c r="M279" t="s">
-        <v>22</v>
-      </c>
-      <c r="N279" t="s">
+      <c r="O279" t="s">
         <v>1474</v>
       </c>
-      <c r="O279" t="s">
+      <c r="P279" t="s">
         <v>1475</v>
-      </c>
-      <c r="P279" t="s">
-        <v>1476</v>
       </c>
     </row>
     <row r="280" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B280" t="s">
         <v>1477</v>
-      </c>
-      <c r="B280" t="s">
-        <v>1478</v>
       </c>
       <c r="C280" t="s">
         <v>40</v>
@@ -20002,7 +20002,7 @@
         <v>42</v>
       </c>
       <c r="K280" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="L280" t="b">
         <v>1</v>
@@ -20011,21 +20011,21 @@
         <v>22</v>
       </c>
       <c r="N280" t="s">
+        <v>1479</v>
+      </c>
+      <c r="O280" t="s">
         <v>1480</v>
       </c>
-      <c r="O280" t="s">
+      <c r="P280" t="s">
         <v>1481</v>
-      </c>
-      <c r="P280" t="s">
-        <v>1482</v>
       </c>
     </row>
     <row r="281" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
+        <v>1482</v>
+      </c>
+      <c r="B281" t="s">
         <v>1483</v>
-      </c>
-      <c r="B281" t="s">
-        <v>1484</v>
       </c>
       <c r="C281" t="s">
         <v>18</v>
@@ -20046,33 +20046,33 @@
         <v>0</v>
       </c>
       <c r="I281" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="J281" t="s">
         <v>20</v>
       </c>
       <c r="K281" t="s">
+        <v>1485</v>
+      </c>
+      <c r="L281" t="s">
+        <v>19</v>
+      </c>
+      <c r="M281" t="s">
+        <v>22</v>
+      </c>
+      <c r="N281" t="s">
         <v>1486</v>
       </c>
-      <c r="L281" t="s">
-        <v>19</v>
-      </c>
-      <c r="M281" t="s">
-        <v>22</v>
-      </c>
-      <c r="N281" t="s">
+      <c r="O281" t="s">
         <v>1487</v>
       </c>
-      <c r="O281" t="s">
+      <c r="P281" t="s">
         <v>1488</v>
-      </c>
-      <c r="P281" t="s">
-        <v>1489</v>
       </c>
     </row>
     <row r="282" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="B282" t="s">
         <v>1338</v>
@@ -20102,30 +20102,30 @@
         <v>20</v>
       </c>
       <c r="K282" t="s">
+        <v>1490</v>
+      </c>
+      <c r="L282" t="s">
+        <v>19</v>
+      </c>
+      <c r="M282" t="s">
+        <v>22</v>
+      </c>
+      <c r="N282" t="s">
         <v>1491</v>
       </c>
-      <c r="L282" t="s">
-        <v>19</v>
-      </c>
-      <c r="M282" t="s">
-        <v>22</v>
-      </c>
-      <c r="N282" t="s">
+      <c r="O282" t="s">
         <v>1492</v>
       </c>
-      <c r="O282" t="s">
+      <c r="P282" t="s">
         <v>1493</v>
-      </c>
-      <c r="P282" t="s">
-        <v>1494</v>
       </c>
     </row>
     <row r="283" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B283" t="s">
         <v>1495</v>
-      </c>
-      <c r="B283" t="s">
-        <v>1496</v>
       </c>
       <c r="C283" t="s">
         <v>18</v>
@@ -20152,27 +20152,27 @@
         <v>20</v>
       </c>
       <c r="K283" t="s">
+        <v>1496</v>
+      </c>
+      <c r="L283" t="s">
+        <v>19</v>
+      </c>
+      <c r="M283" t="s">
+        <v>22</v>
+      </c>
+      <c r="N283" t="s">
         <v>1497</v>
       </c>
-      <c r="L283" t="s">
-        <v>19</v>
-      </c>
-      <c r="M283" t="s">
-        <v>22</v>
-      </c>
-      <c r="N283" t="s">
+      <c r="O283" t="s">
         <v>1498</v>
       </c>
-      <c r="O283" t="s">
+      <c r="P283" t="s">
         <v>1499</v>
-      </c>
-      <c r="P283" t="s">
-        <v>1500</v>
       </c>
     </row>
     <row r="284" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="B284" t="s">
         <v>135</v>
@@ -20202,27 +20202,27 @@
         <v>20</v>
       </c>
       <c r="K284" t="s">
+        <v>1501</v>
+      </c>
+      <c r="L284" t="s">
+        <v>19</v>
+      </c>
+      <c r="M284" t="s">
+        <v>22</v>
+      </c>
+      <c r="N284" t="s">
         <v>1502</v>
       </c>
-      <c r="L284" t="s">
-        <v>19</v>
-      </c>
-      <c r="M284" t="s">
-        <v>22</v>
-      </c>
-      <c r="N284" t="s">
+      <c r="O284" t="s">
         <v>1503</v>
       </c>
-      <c r="O284" t="s">
+      <c r="P284" t="s">
         <v>1504</v>
-      </c>
-      <c r="P284" t="s">
-        <v>1505</v>
       </c>
     </row>
     <row r="285" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="B285" t="s">
         <v>135</v>
@@ -20252,27 +20252,27 @@
         <v>20</v>
       </c>
       <c r="K285" t="s">
+        <v>1506</v>
+      </c>
+      <c r="L285" t="s">
+        <v>19</v>
+      </c>
+      <c r="M285" t="s">
+        <v>22</v>
+      </c>
+      <c r="N285" t="s">
         <v>1507</v>
       </c>
-      <c r="L285" t="s">
-        <v>19</v>
-      </c>
-      <c r="M285" t="s">
-        <v>22</v>
-      </c>
-      <c r="N285" t="s">
+      <c r="O285" t="s">
         <v>1508</v>
       </c>
-      <c r="O285" t="s">
+      <c r="P285" t="s">
         <v>1509</v>
-      </c>
-      <c r="P285" t="s">
-        <v>1510</v>
       </c>
     </row>
     <row r="286" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="B286" t="s">
         <v>135</v>
@@ -20302,30 +20302,30 @@
         <v>20</v>
       </c>
       <c r="K286" t="s">
+        <v>1511</v>
+      </c>
+      <c r="L286" t="s">
+        <v>19</v>
+      </c>
+      <c r="M286" t="s">
+        <v>22</v>
+      </c>
+      <c r="N286" t="s">
         <v>1512</v>
       </c>
-      <c r="L286" t="s">
-        <v>19</v>
-      </c>
-      <c r="M286" t="s">
-        <v>22</v>
-      </c>
-      <c r="N286" t="s">
+      <c r="O286" t="s">
         <v>1513</v>
       </c>
-      <c r="O286" t="s">
+      <c r="P286" t="s">
         <v>1514</v>
-      </c>
-      <c r="P286" t="s">
-        <v>1515</v>
       </c>
     </row>
     <row r="287" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
+        <v>1515</v>
+      </c>
+      <c r="B287" t="s">
         <v>1516</v>
-      </c>
-      <c r="B287" t="s">
-        <v>1517</v>
       </c>
       <c r="C287" t="s">
         <v>18</v>
@@ -20352,27 +20352,27 @@
         <v>20</v>
       </c>
       <c r="K287" t="s">
+        <v>1517</v>
+      </c>
+      <c r="L287" t="s">
+        <v>19</v>
+      </c>
+      <c r="M287" t="s">
+        <v>22</v>
+      </c>
+      <c r="N287" t="s">
         <v>1518</v>
       </c>
-      <c r="L287" t="s">
-        <v>19</v>
-      </c>
-      <c r="M287" t="s">
-        <v>22</v>
-      </c>
-      <c r="N287" t="s">
+      <c r="O287" t="s">
         <v>1519</v>
       </c>
-      <c r="O287" t="s">
+      <c r="P287" t="s">
         <v>1520</v>
-      </c>
-      <c r="P287" t="s">
-        <v>1521</v>
       </c>
     </row>
     <row r="288" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="B288" t="s">
         <v>135</v>
@@ -20402,27 +20402,27 @@
         <v>20</v>
       </c>
       <c r="K288" t="s">
+        <v>1522</v>
+      </c>
+      <c r="L288" t="s">
+        <v>19</v>
+      </c>
+      <c r="M288" t="s">
+        <v>22</v>
+      </c>
+      <c r="N288" t="s">
         <v>1523</v>
       </c>
-      <c r="L288" t="s">
-        <v>19</v>
-      </c>
-      <c r="M288" t="s">
-        <v>22</v>
-      </c>
-      <c r="N288" t="s">
+      <c r="O288" t="s">
         <v>1524</v>
       </c>
-      <c r="O288" t="s">
+      <c r="P288" t="s">
         <v>1525</v>
-      </c>
-      <c r="P288" t="s">
-        <v>1526</v>
       </c>
     </row>
     <row r="289" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B289" t="s">
         <v>135</v>
@@ -20452,27 +20452,27 @@
         <v>20</v>
       </c>
       <c r="K289" t="s">
+        <v>1527</v>
+      </c>
+      <c r="L289" t="s">
+        <v>19</v>
+      </c>
+      <c r="M289" t="s">
+        <v>22</v>
+      </c>
+      <c r="N289" t="s">
         <v>1528</v>
       </c>
-      <c r="L289" t="s">
-        <v>19</v>
-      </c>
-      <c r="M289" t="s">
-        <v>22</v>
-      </c>
-      <c r="N289" t="s">
+      <c r="O289" t="s">
         <v>1529</v>
       </c>
-      <c r="O289" t="s">
+      <c r="P289" t="s">
         <v>1530</v>
-      </c>
-      <c r="P289" t="s">
-        <v>1531</v>
       </c>
     </row>
     <row r="290" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B290" t="s">
         <v>135</v>
@@ -20502,27 +20502,27 @@
         <v>20</v>
       </c>
       <c r="K290" t="s">
+        <v>1532</v>
+      </c>
+      <c r="L290" t="s">
+        <v>19</v>
+      </c>
+      <c r="M290" t="s">
+        <v>22</v>
+      </c>
+      <c r="N290" t="s">
         <v>1533</v>
       </c>
-      <c r="L290" t="s">
-        <v>19</v>
-      </c>
-      <c r="M290" t="s">
-        <v>22</v>
-      </c>
-      <c r="N290" t="s">
+      <c r="O290" t="s">
         <v>1534</v>
       </c>
-      <c r="O290" t="s">
+      <c r="P290" t="s">
         <v>1535</v>
-      </c>
-      <c r="P290" t="s">
-        <v>1536</v>
       </c>
     </row>
     <row r="291" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="B291" t="s">
         <v>135</v>
@@ -20552,30 +20552,30 @@
         <v>20</v>
       </c>
       <c r="K291" t="s">
+        <v>1537</v>
+      </c>
+      <c r="L291" t="s">
+        <v>19</v>
+      </c>
+      <c r="M291" t="s">
+        <v>22</v>
+      </c>
+      <c r="N291" t="s">
         <v>1538</v>
       </c>
-      <c r="L291" t="s">
-        <v>19</v>
-      </c>
-      <c r="M291" t="s">
-        <v>22</v>
-      </c>
-      <c r="N291" t="s">
+      <c r="O291" t="s">
         <v>1539</v>
       </c>
-      <c r="O291" t="s">
+      <c r="P291" t="s">
         <v>1540</v>
-      </c>
-      <c r="P291" t="s">
-        <v>1541</v>
       </c>
     </row>
     <row r="292" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
+        <v>1541</v>
+      </c>
+      <c r="B292" t="s">
         <v>1542</v>
-      </c>
-      <c r="B292" t="s">
-        <v>1543</v>
       </c>
       <c r="C292" t="s">
         <v>18</v>
@@ -20602,30 +20602,30 @@
         <v>20</v>
       </c>
       <c r="K292" t="s">
+        <v>1543</v>
+      </c>
+      <c r="L292" t="s">
+        <v>19</v>
+      </c>
+      <c r="M292" t="s">
+        <v>22</v>
+      </c>
+      <c r="N292" t="s">
         <v>1544</v>
       </c>
-      <c r="L292" t="s">
-        <v>19</v>
-      </c>
-      <c r="M292" t="s">
-        <v>22</v>
-      </c>
-      <c r="N292" t="s">
+      <c r="O292" t="s">
         <v>1545</v>
       </c>
-      <c r="O292" t="s">
+      <c r="P292" t="s">
         <v>1546</v>
-      </c>
-      <c r="P292" t="s">
-        <v>1547</v>
       </c>
     </row>
     <row r="293" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
+        <v>1547</v>
+      </c>
+      <c r="B293" t="s">
         <v>1548</v>
-      </c>
-      <c r="B293" t="s">
-        <v>1549</v>
       </c>
       <c r="C293" t="s">
         <v>18</v>
@@ -20652,30 +20652,30 @@
         <v>20</v>
       </c>
       <c r="K293" t="s">
+        <v>1549</v>
+      </c>
+      <c r="L293" t="s">
+        <v>19</v>
+      </c>
+      <c r="M293" t="s">
+        <v>22</v>
+      </c>
+      <c r="N293" t="s">
         <v>1550</v>
       </c>
-      <c r="L293" t="s">
-        <v>19</v>
-      </c>
-      <c r="M293" t="s">
-        <v>22</v>
-      </c>
-      <c r="N293" t="s">
+      <c r="O293" t="s">
         <v>1551</v>
       </c>
-      <c r="O293" t="s">
+      <c r="P293" t="s">
         <v>1552</v>
-      </c>
-      <c r="P293" t="s">
-        <v>1553</v>
       </c>
     </row>
     <row r="294" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
+        <v>1553</v>
+      </c>
+      <c r="B294" t="s">
         <v>1554</v>
-      </c>
-      <c r="B294" t="s">
-        <v>1555</v>
       </c>
       <c r="C294" t="s">
         <v>18</v>
@@ -20702,30 +20702,30 @@
         <v>20</v>
       </c>
       <c r="K294" t="s">
+        <v>1555</v>
+      </c>
+      <c r="L294" t="s">
+        <v>19</v>
+      </c>
+      <c r="M294" t="s">
+        <v>22</v>
+      </c>
+      <c r="N294" t="s">
         <v>1556</v>
       </c>
-      <c r="L294" t="s">
-        <v>19</v>
-      </c>
-      <c r="M294" t="s">
-        <v>22</v>
-      </c>
-      <c r="N294" t="s">
+      <c r="O294" t="s">
         <v>1557</v>
       </c>
-      <c r="O294" t="s">
+      <c r="P294" t="s">
         <v>1558</v>
-      </c>
-      <c r="P294" t="s">
-        <v>1559</v>
       </c>
     </row>
     <row r="295" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B295" t="s">
         <v>1560</v>
-      </c>
-      <c r="B295" t="s">
-        <v>1561</v>
       </c>
       <c r="C295" t="s">
         <v>18</v>
@@ -20752,27 +20752,27 @@
         <v>20</v>
       </c>
       <c r="K295" t="s">
+        <v>1561</v>
+      </c>
+      <c r="L295" t="s">
+        <v>19</v>
+      </c>
+      <c r="M295" t="s">
+        <v>22</v>
+      </c>
+      <c r="N295" t="s">
         <v>1562</v>
       </c>
-      <c r="L295" t="s">
-        <v>19</v>
-      </c>
-      <c r="M295" t="s">
-        <v>22</v>
-      </c>
-      <c r="N295" t="s">
+      <c r="O295" t="s">
         <v>1563</v>
       </c>
-      <c r="O295" t="s">
+      <c r="P295" t="s">
         <v>1564</v>
-      </c>
-      <c r="P295" t="s">
-        <v>1565</v>
       </c>
     </row>
     <row r="296" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="B296" t="s">
         <v>1044</v>
@@ -20802,30 +20802,30 @@
         <v>20</v>
       </c>
       <c r="K296" t="s">
+        <v>1566</v>
+      </c>
+      <c r="L296" t="s">
+        <v>19</v>
+      </c>
+      <c r="M296" t="s">
+        <v>22</v>
+      </c>
+      <c r="N296" t="s">
         <v>1567</v>
       </c>
-      <c r="L296" t="s">
-        <v>19</v>
-      </c>
-      <c r="M296" t="s">
-        <v>22</v>
-      </c>
-      <c r="N296" t="s">
+      <c r="O296" t="s">
         <v>1568</v>
       </c>
-      <c r="O296" t="s">
+      <c r="P296" t="s">
         <v>1569</v>
-      </c>
-      <c r="P296" t="s">
-        <v>1570</v>
       </c>
     </row>
     <row r="297" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="B297" t="s">
-        <v>1338</v>
+        <v>135</v>
       </c>
       <c r="C297" t="s">
         <v>18</v>
@@ -20852,27 +20852,27 @@
         <v>20</v>
       </c>
       <c r="K297" t="s">
+        <v>1571</v>
+      </c>
+      <c r="L297" t="s">
+        <v>19</v>
+      </c>
+      <c r="M297" t="s">
+        <v>22</v>
+      </c>
+      <c r="N297" t="s">
         <v>1572</v>
       </c>
-      <c r="L297" t="s">
-        <v>19</v>
-      </c>
-      <c r="M297" t="s">
-        <v>22</v>
-      </c>
-      <c r="N297" t="s">
+      <c r="O297" t="s">
         <v>1573</v>
       </c>
-      <c r="O297" t="s">
+      <c r="P297" t="s">
         <v>1574</v>
-      </c>
-      <c r="P297" t="s">
-        <v>1575</v>
       </c>
     </row>
     <row r="298" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="B298" t="s">
         <v>1044</v>
@@ -20902,30 +20902,30 @@
         <v>20</v>
       </c>
       <c r="K298" t="s">
+        <v>1576</v>
+      </c>
+      <c r="L298" t="s">
+        <v>19</v>
+      </c>
+      <c r="M298" t="s">
+        <v>22</v>
+      </c>
+      <c r="N298" t="s">
         <v>1577</v>
       </c>
-      <c r="L298" t="s">
-        <v>19</v>
-      </c>
-      <c r="M298" t="s">
-        <v>22</v>
-      </c>
-      <c r="N298" t="s">
+      <c r="O298" t="s">
         <v>1578</v>
       </c>
-      <c r="O298" t="s">
+      <c r="P298" t="s">
         <v>1579</v>
-      </c>
-      <c r="P298" t="s">
-        <v>1580</v>
       </c>
     </row>
     <row r="299" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="B299" t="s">
-        <v>1338</v>
+        <v>135</v>
       </c>
       <c r="C299" t="s">
         <v>18</v>
@@ -20952,27 +20952,27 @@
         <v>20</v>
       </c>
       <c r="K299" t="s">
+        <v>1581</v>
+      </c>
+      <c r="L299" t="s">
+        <v>19</v>
+      </c>
+      <c r="M299" t="s">
+        <v>22</v>
+      </c>
+      <c r="N299" t="s">
         <v>1582</v>
       </c>
-      <c r="L299" t="s">
-        <v>19</v>
-      </c>
-      <c r="M299" t="s">
-        <v>22</v>
-      </c>
-      <c r="N299" t="s">
+      <c r="O299" t="s">
         <v>1583</v>
       </c>
-      <c r="O299" t="s">
+      <c r="P299" t="s">
         <v>1584</v>
-      </c>
-      <c r="P299" t="s">
-        <v>1585</v>
       </c>
     </row>
     <row r="300" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="B300" t="s">
         <v>1338</v>
@@ -21002,30 +21002,30 @@
         <v>20</v>
       </c>
       <c r="K300" t="s">
+        <v>1586</v>
+      </c>
+      <c r="L300" t="s">
+        <v>19</v>
+      </c>
+      <c r="M300" t="s">
+        <v>22</v>
+      </c>
+      <c r="N300" t="s">
         <v>1587</v>
       </c>
-      <c r="L300" t="s">
-        <v>19</v>
-      </c>
-      <c r="M300" t="s">
-        <v>22</v>
-      </c>
-      <c r="N300" t="s">
+      <c r="O300" t="s">
         <v>1588</v>
       </c>
-      <c r="O300" t="s">
+      <c r="P300" t="s">
         <v>1589</v>
-      </c>
-      <c r="P300" t="s">
-        <v>1590</v>
       </c>
     </row>
     <row r="301" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="B301" t="s">
-        <v>1338</v>
+        <v>135</v>
       </c>
       <c r="C301" t="s">
         <v>18</v>
@@ -21052,30 +21052,30 @@
         <v>20</v>
       </c>
       <c r="K301" t="s">
+        <v>1591</v>
+      </c>
+      <c r="L301" t="s">
+        <v>19</v>
+      </c>
+      <c r="M301" t="s">
+        <v>22</v>
+      </c>
+      <c r="N301" t="s">
         <v>1592</v>
       </c>
-      <c r="L301" t="s">
-        <v>19</v>
-      </c>
-      <c r="M301" t="s">
-        <v>22</v>
-      </c>
-      <c r="N301" t="s">
+      <c r="O301" t="s">
         <v>1593</v>
       </c>
-      <c r="O301" t="s">
+      <c r="P301" t="s">
         <v>1594</v>
-      </c>
-      <c r="P301" t="s">
-        <v>1595</v>
       </c>
     </row>
     <row r="302" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="B302" t="s">
-        <v>1338</v>
+        <v>135</v>
       </c>
       <c r="C302" t="s">
         <v>18</v>
@@ -21102,27 +21102,27 @@
         <v>20</v>
       </c>
       <c r="K302" t="s">
+        <v>1596</v>
+      </c>
+      <c r="L302" t="s">
+        <v>19</v>
+      </c>
+      <c r="M302" t="s">
+        <v>22</v>
+      </c>
+      <c r="N302" t="s">
         <v>1597</v>
       </c>
-      <c r="L302" t="s">
-        <v>19</v>
-      </c>
-      <c r="M302" t="s">
-        <v>22</v>
-      </c>
-      <c r="N302" t="s">
+      <c r="O302" t="s">
         <v>1598</v>
       </c>
-      <c r="O302" t="s">
+      <c r="P302" t="s">
         <v>1599</v>
-      </c>
-      <c r="P302" t="s">
-        <v>1600</v>
       </c>
     </row>
     <row r="303" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="B303" t="s">
         <v>1338</v>
@@ -21152,27 +21152,27 @@
         <v>20</v>
       </c>
       <c r="K303" t="s">
+        <v>1601</v>
+      </c>
+      <c r="L303" t="s">
+        <v>19</v>
+      </c>
+      <c r="M303" t="s">
+        <v>22</v>
+      </c>
+      <c r="N303" t="s">
         <v>1602</v>
       </c>
-      <c r="L303" t="s">
-        <v>19</v>
-      </c>
-      <c r="M303" t="s">
-        <v>22</v>
-      </c>
-      <c r="N303" t="s">
+      <c r="O303" t="s">
         <v>1603</v>
       </c>
-      <c r="O303" t="s">
+      <c r="P303" t="s">
         <v>1604</v>
-      </c>
-      <c r="P303" t="s">
-        <v>1605</v>
       </c>
     </row>
     <row r="304" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="B304" t="s">
         <v>19</v>
@@ -21202,7 +21202,7 @@
         <v>19</v>
       </c>
       <c r="K304" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="L304" t="s">
         <v>19</v>
@@ -21211,18 +21211,18 @@
         <v>391</v>
       </c>
       <c r="N304" t="s">
+        <v>1607</v>
+      </c>
+      <c r="O304" t="s">
+        <v>19</v>
+      </c>
+      <c r="P304" t="s">
         <v>1608</v>
-      </c>
-      <c r="O304" t="s">
-        <v>19</v>
-      </c>
-      <c r="P304" t="s">
-        <v>1609</v>
       </c>
     </row>
     <row r="305" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="B305" t="s">
         <v>1338</v>
@@ -21252,27 +21252,27 @@
         <v>20</v>
       </c>
       <c r="K305" t="s">
+        <v>1610</v>
+      </c>
+      <c r="L305" t="s">
+        <v>19</v>
+      </c>
+      <c r="M305" t="s">
+        <v>22</v>
+      </c>
+      <c r="N305" t="s">
         <v>1611</v>
       </c>
-      <c r="L305" t="s">
-        <v>19</v>
-      </c>
-      <c r="M305" t="s">
-        <v>22</v>
-      </c>
-      <c r="N305" t="s">
+      <c r="O305" t="s">
         <v>1612</v>
       </c>
-      <c r="O305" t="s">
+      <c r="P305" t="s">
         <v>1613</v>
-      </c>
-      <c r="P305" t="s">
-        <v>1614</v>
       </c>
     </row>
     <row r="306" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="B306" t="s">
         <v>1338</v>
@@ -21302,27 +21302,27 @@
         <v>20</v>
       </c>
       <c r="K306" t="s">
+        <v>1615</v>
+      </c>
+      <c r="L306" t="s">
+        <v>19</v>
+      </c>
+      <c r="M306" t="s">
+        <v>22</v>
+      </c>
+      <c r="N306" t="s">
         <v>1616</v>
       </c>
-      <c r="L306" t="s">
-        <v>19</v>
-      </c>
-      <c r="M306" t="s">
-        <v>22</v>
-      </c>
-      <c r="N306" t="s">
+      <c r="O306" t="s">
         <v>1617</v>
       </c>
-      <c r="O306" t="s">
-        <v>1618</v>
-      </c>
       <c r="P306" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="307" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="B307" t="s">
         <v>1338</v>
@@ -21352,27 +21352,27 @@
         <v>20</v>
       </c>
       <c r="K307" t="s">
+        <v>1619</v>
+      </c>
+      <c r="L307" t="s">
+        <v>19</v>
+      </c>
+      <c r="M307" t="s">
+        <v>22</v>
+      </c>
+      <c r="N307" t="s">
         <v>1620</v>
       </c>
-      <c r="L307" t="s">
-        <v>19</v>
-      </c>
-      <c r="M307" t="s">
-        <v>22</v>
-      </c>
-      <c r="N307" t="s">
+      <c r="O307" t="s">
         <v>1621</v>
       </c>
-      <c r="O307" t="s">
+      <c r="P307" t="s">
         <v>1622</v>
-      </c>
-      <c r="P307" t="s">
-        <v>1623</v>
       </c>
     </row>
     <row r="308" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B308" t="s">
         <v>1338</v>
@@ -21402,30 +21402,30 @@
         <v>20</v>
       </c>
       <c r="K308" t="s">
+        <v>1624</v>
+      </c>
+      <c r="L308" t="s">
+        <v>19</v>
+      </c>
+      <c r="M308" t="s">
+        <v>22</v>
+      </c>
+      <c r="N308" t="s">
         <v>1625</v>
       </c>
-      <c r="L308" t="s">
-        <v>19</v>
-      </c>
-      <c r="M308" t="s">
-        <v>22</v>
-      </c>
-      <c r="N308" t="s">
+      <c r="O308" t="s">
         <v>1626</v>
       </c>
-      <c r="O308" t="s">
+      <c r="P308" t="s">
         <v>1627</v>
-      </c>
-      <c r="P308" t="s">
-        <v>1628</v>
       </c>
     </row>
     <row r="309" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
+        <v>1628</v>
+      </c>
+      <c r="B309" t="s">
         <v>1629</v>
-      </c>
-      <c r="B309" t="s">
-        <v>1630</v>
       </c>
       <c r="C309" t="s">
         <v>18</v>
@@ -21452,27 +21452,27 @@
         <v>20</v>
       </c>
       <c r="K309" t="s">
+        <v>1630</v>
+      </c>
+      <c r="L309" t="s">
+        <v>19</v>
+      </c>
+      <c r="M309" t="s">
+        <v>22</v>
+      </c>
+      <c r="N309" t="s">
         <v>1631</v>
       </c>
-      <c r="L309" t="s">
-        <v>19</v>
-      </c>
-      <c r="M309" t="s">
-        <v>22</v>
-      </c>
-      <c r="N309" t="s">
+      <c r="O309" t="s">
         <v>1632</v>
       </c>
-      <c r="O309" t="s">
+      <c r="P309" t="s">
         <v>1633</v>
-      </c>
-      <c r="P309" t="s">
-        <v>1634</v>
       </c>
     </row>
     <row r="310" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="B310" t="s">
         <v>1454</v>
@@ -21502,27 +21502,27 @@
         <v>20</v>
       </c>
       <c r="K310" t="s">
+        <v>1635</v>
+      </c>
+      <c r="L310" t="s">
+        <v>19</v>
+      </c>
+      <c r="M310" t="s">
+        <v>22</v>
+      </c>
+      <c r="N310" t="s">
         <v>1636</v>
       </c>
-      <c r="L310" t="s">
-        <v>19</v>
-      </c>
-      <c r="M310" t="s">
-        <v>22</v>
-      </c>
-      <c r="N310" t="s">
+      <c r="O310" t="s">
         <v>1637</v>
       </c>
-      <c r="O310" t="s">
+      <c r="P310" t="s">
         <v>1638</v>
-      </c>
-      <c r="P310" t="s">
-        <v>1639</v>
       </c>
     </row>
     <row r="311" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="B311" t="s">
         <v>1454</v>
@@ -21552,30 +21552,30 @@
         <v>20</v>
       </c>
       <c r="K311" t="s">
+        <v>1640</v>
+      </c>
+      <c r="L311" t="s">
+        <v>19</v>
+      </c>
+      <c r="M311" t="s">
+        <v>22</v>
+      </c>
+      <c r="N311" t="s">
         <v>1641</v>
       </c>
-      <c r="L311" t="s">
-        <v>19</v>
-      </c>
-      <c r="M311" t="s">
-        <v>22</v>
-      </c>
-      <c r="N311" t="s">
+      <c r="O311" t="s">
         <v>1642</v>
       </c>
-      <c r="O311" t="s">
+      <c r="P311" t="s">
         <v>1643</v>
-      </c>
-      <c r="P311" t="s">
-        <v>1644</v>
       </c>
     </row>
     <row r="312" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="B312" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="C312" t="s">
         <v>18</v>
@@ -21602,27 +21602,27 @@
         <v>20</v>
       </c>
       <c r="K312" t="s">
+        <v>1645</v>
+      </c>
+      <c r="L312" t="s">
+        <v>19</v>
+      </c>
+      <c r="M312" t="s">
+        <v>22</v>
+      </c>
+      <c r="N312" t="s">
         <v>1646</v>
       </c>
-      <c r="L312" t="s">
-        <v>19</v>
-      </c>
-      <c r="M312" t="s">
-        <v>22</v>
-      </c>
-      <c r="N312" t="s">
+      <c r="O312" t="s">
         <v>1647</v>
       </c>
-      <c r="O312" t="s">
+      <c r="P312" t="s">
         <v>1648</v>
-      </c>
-      <c r="P312" t="s">
-        <v>1649</v>
       </c>
     </row>
     <row r="313" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="B313" t="s">
         <v>1454</v>
@@ -21652,27 +21652,27 @@
         <v>20</v>
       </c>
       <c r="K313" t="s">
+        <v>1650</v>
+      </c>
+      <c r="L313" t="s">
+        <v>19</v>
+      </c>
+      <c r="M313" t="s">
+        <v>22</v>
+      </c>
+      <c r="N313" t="s">
         <v>1651</v>
       </c>
-      <c r="L313" t="s">
-        <v>19</v>
-      </c>
-      <c r="M313" t="s">
-        <v>22</v>
-      </c>
-      <c r="N313" t="s">
+      <c r="O313" t="s">
         <v>1652</v>
       </c>
-      <c r="O313" t="s">
+      <c r="P313" t="s">
         <v>1653</v>
-      </c>
-      <c r="P313" t="s">
-        <v>1654</v>
       </c>
     </row>
     <row r="314" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="B314" t="s">
         <v>1454</v>
@@ -21702,30 +21702,30 @@
         <v>20</v>
       </c>
       <c r="K314" t="s">
+        <v>1655</v>
+      </c>
+      <c r="L314" t="s">
+        <v>19</v>
+      </c>
+      <c r="M314" t="s">
+        <v>22</v>
+      </c>
+      <c r="N314" t="s">
         <v>1656</v>
       </c>
-      <c r="L314" t="s">
-        <v>19</v>
-      </c>
-      <c r="M314" t="s">
-        <v>22</v>
-      </c>
-      <c r="N314" t="s">
+      <c r="O314" t="s">
         <v>1657</v>
       </c>
-      <c r="O314" t="s">
+      <c r="P314" t="s">
         <v>1658</v>
-      </c>
-      <c r="P314" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="315" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="B315" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="C315" t="s">
         <v>18</v>
@@ -21752,30 +21752,30 @@
         <v>20</v>
       </c>
       <c r="K315" t="s">
+        <v>1660</v>
+      </c>
+      <c r="L315" t="s">
+        <v>19</v>
+      </c>
+      <c r="M315" t="s">
+        <v>22</v>
+      </c>
+      <c r="N315" t="s">
         <v>1661</v>
       </c>
-      <c r="L315" t="s">
-        <v>19</v>
-      </c>
-      <c r="M315" t="s">
-        <v>22</v>
-      </c>
-      <c r="N315" t="s">
+      <c r="O315" t="s">
         <v>1662</v>
       </c>
-      <c r="O315" t="s">
+      <c r="P315" t="s">
         <v>1663</v>
-      </c>
-      <c r="P315" t="s">
-        <v>1664</v>
       </c>
     </row>
     <row r="316" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="B316" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="C316" t="s">
         <v>18</v>
@@ -21802,30 +21802,30 @@
         <v>20</v>
       </c>
       <c r="K316" t="s">
+        <v>1665</v>
+      </c>
+      <c r="L316" t="s">
+        <v>19</v>
+      </c>
+      <c r="M316" t="s">
+        <v>22</v>
+      </c>
+      <c r="N316" t="s">
         <v>1666</v>
       </c>
-      <c r="L316" t="s">
-        <v>19</v>
-      </c>
-      <c r="M316" t="s">
-        <v>22</v>
-      </c>
-      <c r="N316" t="s">
+      <c r="O316" t="s">
         <v>1667</v>
       </c>
-      <c r="O316" t="s">
+      <c r="P316" t="s">
         <v>1668</v>
-      </c>
-      <c r="P316" t="s">
-        <v>1669</v>
       </c>
     </row>
     <row r="317" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="B317" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="C317" t="s">
         <v>18</v>
@@ -21852,30 +21852,30 @@
         <v>20</v>
       </c>
       <c r="K317" t="s">
+        <v>1670</v>
+      </c>
+      <c r="L317" t="s">
+        <v>19</v>
+      </c>
+      <c r="M317" t="s">
+        <v>22</v>
+      </c>
+      <c r="N317" t="s">
         <v>1671</v>
       </c>
-      <c r="L317" t="s">
-        <v>19</v>
-      </c>
-      <c r="M317" t="s">
-        <v>22</v>
-      </c>
-      <c r="N317" t="s">
+      <c r="O317" t="s">
         <v>1672</v>
       </c>
-      <c r="O317" t="s">
+      <c r="P317" t="s">
         <v>1673</v>
-      </c>
-      <c r="P317" t="s">
-        <v>1674</v>
       </c>
     </row>
     <row r="318" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="B318" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="C318" t="s">
         <v>18</v>
@@ -21902,30 +21902,30 @@
         <v>20</v>
       </c>
       <c r="K318" t="s">
+        <v>1675</v>
+      </c>
+      <c r="L318" t="s">
+        <v>19</v>
+      </c>
+      <c r="M318" t="s">
+        <v>22</v>
+      </c>
+      <c r="N318" t="s">
         <v>1676</v>
       </c>
-      <c r="L318" t="s">
-        <v>19</v>
-      </c>
-      <c r="M318" t="s">
-        <v>22</v>
-      </c>
-      <c r="N318" t="s">
+      <c r="O318" t="s">
         <v>1677</v>
       </c>
-      <c r="O318" t="s">
+      <c r="P318" t="s">
         <v>1678</v>
-      </c>
-      <c r="P318" t="s">
-        <v>1679</v>
       </c>
     </row>
     <row r="319" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
+        <v>1679</v>
+      </c>
+      <c r="B319" t="s">
         <v>1680</v>
-      </c>
-      <c r="B319" t="s">
-        <v>1681</v>
       </c>
       <c r="C319" t="s">
         <v>18</v>
@@ -21946,36 +21946,36 @@
         <v>0</v>
       </c>
       <c r="I319" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="J319" t="s">
         <v>20</v>
       </c>
       <c r="K319" t="s">
+        <v>1682</v>
+      </c>
+      <c r="L319" t="s">
+        <v>19</v>
+      </c>
+      <c r="M319" t="s">
+        <v>22</v>
+      </c>
+      <c r="N319" t="s">
         <v>1683</v>
       </c>
-      <c r="L319" t="s">
-        <v>19</v>
-      </c>
-      <c r="M319" t="s">
-        <v>22</v>
-      </c>
-      <c r="N319" t="s">
+      <c r="O319" t="s">
         <v>1684</v>
       </c>
-      <c r="O319" t="s">
+      <c r="P319" t="s">
         <v>1685</v>
-      </c>
-      <c r="P319" t="s">
-        <v>1686</v>
       </c>
     </row>
     <row r="320" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="B320" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="C320" t="s">
         <v>18</v>
@@ -21996,36 +21996,36 @@
         <v>0</v>
       </c>
       <c r="I320" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="J320" t="s">
         <v>20</v>
       </c>
       <c r="K320" t="s">
+        <v>1687</v>
+      </c>
+      <c r="L320" t="s">
+        <v>19</v>
+      </c>
+      <c r="M320" t="s">
+        <v>22</v>
+      </c>
+      <c r="N320" t="s">
         <v>1688</v>
       </c>
-      <c r="L320" t="s">
-        <v>19</v>
-      </c>
-      <c r="M320" t="s">
-        <v>22</v>
-      </c>
-      <c r="N320" t="s">
+      <c r="O320" t="s">
         <v>1689</v>
       </c>
-      <c r="O320" t="s">
+      <c r="P320" t="s">
         <v>1690</v>
-      </c>
-      <c r="P320" t="s">
-        <v>1691</v>
       </c>
     </row>
     <row r="321" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="B321" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="C321" t="s">
         <v>18</v>
@@ -22046,36 +22046,36 @@
         <v>0</v>
       </c>
       <c r="I321" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="J321" t="s">
         <v>20</v>
       </c>
       <c r="K321" t="s">
+        <v>1692</v>
+      </c>
+      <c r="L321" t="s">
+        <v>19</v>
+      </c>
+      <c r="M321" t="s">
+        <v>22</v>
+      </c>
+      <c r="N321" t="s">
         <v>1693</v>
       </c>
-      <c r="L321" t="s">
-        <v>19</v>
-      </c>
-      <c r="M321" t="s">
-        <v>22</v>
-      </c>
-      <c r="N321" t="s">
+      <c r="O321" t="s">
         <v>1694</v>
       </c>
-      <c r="O321" t="s">
+      <c r="P321" t="s">
         <v>1695</v>
-      </c>
-      <c r="P321" t="s">
-        <v>1696</v>
       </c>
     </row>
     <row r="322" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
+        <v>1696</v>
+      </c>
+      <c r="B322" t="s">
         <v>1697</v>
-      </c>
-      <c r="B322" t="s">
-        <v>1698</v>
       </c>
       <c r="C322" t="s">
         <v>18</v>
@@ -22102,30 +22102,30 @@
         <v>20</v>
       </c>
       <c r="K322" t="s">
+        <v>1698</v>
+      </c>
+      <c r="L322" t="s">
+        <v>19</v>
+      </c>
+      <c r="M322" t="s">
+        <v>22</v>
+      </c>
+      <c r="N322" t="s">
         <v>1699</v>
       </c>
-      <c r="L322" t="s">
-        <v>19</v>
-      </c>
-      <c r="M322" t="s">
-        <v>22</v>
-      </c>
-      <c r="N322" t="s">
+      <c r="O322" t="s">
         <v>1700</v>
       </c>
-      <c r="O322" t="s">
+      <c r="P322" t="s">
         <v>1701</v>
-      </c>
-      <c r="P322" t="s">
-        <v>1702</v>
       </c>
     </row>
     <row r="323" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
+        <v>1702</v>
+      </c>
+      <c r="B323" t="s">
         <v>1703</v>
-      </c>
-      <c r="B323" t="s">
-        <v>1466</v>
       </c>
       <c r="C323" t="s">
         <v>18</v>
@@ -22225,7 +22225,7 @@
         <v>1714</v>
       </c>
       <c r="B325" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C325" t="s">
         <v>18</v>
@@ -22275,7 +22275,7 @@
         <v>1719</v>
       </c>
       <c r="B326" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C326" t="s">
         <v>18</v>
@@ -22325,7 +22325,7 @@
         <v>1724</v>
       </c>
       <c r="B327" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C327" t="s">
         <v>18</v>
@@ -22375,7 +22375,7 @@
         <v>1729</v>
       </c>
       <c r="B328" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C328" t="s">
         <v>18</v>
@@ -22425,7 +22425,7 @@
         <v>1734</v>
       </c>
       <c r="B329" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C329" t="s">
         <v>18</v>
@@ -22475,7 +22475,7 @@
         <v>1739</v>
       </c>
       <c r="B330" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C330" t="s">
         <v>18</v>
@@ -22525,7 +22525,7 @@
         <v>1744</v>
       </c>
       <c r="B331" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C331" t="s">
         <v>18</v>
@@ -22575,7 +22575,7 @@
         <v>1749</v>
       </c>
       <c r="B332" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C332" t="s">
         <v>18</v>
@@ -22625,7 +22625,7 @@
         <v>1754</v>
       </c>
       <c r="B333" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C333" t="s">
         <v>18</v>
@@ -22675,7 +22675,7 @@
         <v>1759</v>
       </c>
       <c r="B334" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C334" t="s">
         <v>18</v>
@@ -22725,7 +22725,7 @@
         <v>1764</v>
       </c>
       <c r="B335" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C335" t="s">
         <v>18</v>
@@ -22775,7 +22775,7 @@
         <v>1769</v>
       </c>
       <c r="B336" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C336" t="s">
         <v>18</v>
@@ -22825,7 +22825,7 @@
         <v>1774</v>
       </c>
       <c r="B337" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C337" t="s">
         <v>18</v>
@@ -22846,7 +22846,7 @@
         <v>0</v>
       </c>
       <c r="I337" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="J337" t="s">
         <v>20</v>
@@ -22875,7 +22875,7 @@
         <v>1779</v>
       </c>
       <c r="B338" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C338" t="s">
         <v>18</v>
@@ -22896,7 +22896,7 @@
         <v>0</v>
       </c>
       <c r="I338" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="J338" t="s">
         <v>20</v>
@@ -22925,7 +22925,7 @@
         <v>1784</v>
       </c>
       <c r="B339" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C339" t="s">
         <v>18</v>
@@ -22946,7 +22946,7 @@
         <v>0</v>
       </c>
       <c r="I339" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="J339" t="s">
         <v>20</v>
@@ -22975,7 +22975,7 @@
         <v>1789</v>
       </c>
       <c r="B340" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C340" t="s">
         <v>18</v>
@@ -22996,7 +22996,7 @@
         <v>0</v>
       </c>
       <c r="I340" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="J340" t="s">
         <v>20</v>
@@ -23025,7 +23025,7 @@
         <v>1794</v>
       </c>
       <c r="B341" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C341" t="s">
         <v>18</v>
@@ -23046,7 +23046,7 @@
         <v>0</v>
       </c>
       <c r="I341" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="J341" t="s">
         <v>20</v>
@@ -23075,7 +23075,7 @@
         <v>1799</v>
       </c>
       <c r="B342" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C342" t="s">
         <v>18</v>
@@ -23175,7 +23175,7 @@
         <v>1808</v>
       </c>
       <c r="B344" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C344" t="s">
         <v>18</v>
@@ -23196,7 +23196,7 @@
         <v>0</v>
       </c>
       <c r="I344" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="J344" t="s">
         <v>20</v>
@@ -23225,7 +23225,7 @@
         <v>1812</v>
       </c>
       <c r="B345" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C345" t="s">
         <v>18</v>
@@ -23246,7 +23246,7 @@
         <v>0</v>
       </c>
       <c r="I345" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="J345" t="s">
         <v>20</v>
@@ -23275,7 +23275,7 @@
         <v>1817</v>
       </c>
       <c r="B346" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C346" t="s">
         <v>18</v>
@@ -23296,7 +23296,7 @@
         <v>0</v>
       </c>
       <c r="I346" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="J346" t="s">
         <v>20</v>
@@ -23325,7 +23325,7 @@
         <v>1822</v>
       </c>
       <c r="B347" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C347" t="s">
         <v>18</v>
@@ -23346,7 +23346,7 @@
         <v>0</v>
       </c>
       <c r="I347" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="J347" t="s">
         <v>20</v>
@@ -23375,7 +23375,7 @@
         <v>1827</v>
       </c>
       <c r="B348" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C348" t="s">
         <v>18</v>
@@ -23396,7 +23396,7 @@
         <v>0</v>
       </c>
       <c r="I348" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="J348" t="s">
         <v>20</v>
@@ -23425,7 +23425,7 @@
         <v>1832</v>
       </c>
       <c r="B349" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C349" t="s">
         <v>18</v>
@@ -23446,7 +23446,7 @@
         <v>0</v>
       </c>
       <c r="I349" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="J349" t="s">
         <v>20</v>
@@ -23525,7 +23525,7 @@
         <v>1842</v>
       </c>
       <c r="B351" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C351" t="s">
         <v>18</v>
@@ -23546,7 +23546,7 @@
         <v>0</v>
       </c>
       <c r="I351" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="J351" t="s">
         <v>20</v>

--- a/tools/importer/reports/import-grace-master.report.xlsx
+++ b/tools/importer/reports/import-grace-master.report.xlsx
@@ -3738,7 +3738,7 @@
     <t>industries/agriculture/agriculture-cdmo</t>
   </si>
   <si>
-    <t>2026-08-13T21:47:29.126Z</t>
+    <t>2026-08-15T18:34:58.050Z</t>
   </si>
   <si>
     <t>Agriculture CDMO</t>
@@ -3756,7 +3756,7 @@
     <t>industries/agriculture/animal-feed-agricultural-active-solutions</t>
   </si>
   <si>
-    <t>2026-08-13T21:48:22.397Z</t>
+    <t>2026-08-15T18:35:51.996Z</t>
   </si>
   <si>
     <t>Animal Feed and Agricultural Active Solutions</t>
@@ -3789,7 +3789,7 @@
     <t>industries/biofuels/bioethanol</t>
   </si>
   <si>
-    <t>2026-08-13T20:04:51.052Z</t>
+    <t>2026-08-15T18:36:46.144Z</t>
   </si>
   <si>
     <t>Bioethanol</t>
@@ -3819,7 +3819,7 @@
     <t>industries/chemical-processing/catalyst-supports</t>
   </si>
   <si>
-    <t>2026-08-13T19:41:35.387Z</t>
+    <t>2026-08-15T18:39:27.490Z</t>
   </si>
   <si>
     <t>Catalyst Supports</t>
@@ -3834,7 +3834,7 @@
     <t>industries/chemical-processing/custom-development</t>
   </si>
   <si>
-    <t>2026-08-13T19:42:30.244Z</t>
+    <t>2026-08-15T18:40:22.305Z</t>
   </si>
   <si>
     <t>Custom Development</t>
@@ -3849,7 +3849,7 @@
     <t>industries/chemical-processing/hydrogenation-catalysts</t>
   </si>
   <si>
-    <t>2026-08-13T20:02:32.750Z</t>
+    <t>2026-08-15T18:41:15.992Z</t>
   </si>
   <si>
     <t>Hydrogenation Catalysts</t>
@@ -3867,7 +3867,7 @@
     <t>industries/coatings/architectural</t>
   </si>
   <si>
-    <t>2026-08-13T19:45:15.395Z</t>
+    <t>2026-08-15T18:42:09.441Z</t>
   </si>
   <si>
     <t>Architectural</t>
@@ -3882,7 +3882,7 @@
     <t>industries/coatings/coil</t>
   </si>
   <si>
-    <t>2026-08-13T19:44:21.745Z</t>
+    <t>2026-08-15T18:43:03.926Z</t>
   </si>
   <si>
     <t>Coil</t>
@@ -3897,7 +3897,7 @@
     <t>industries/coatings/general-industrial-coatings</t>
   </si>
   <si>
-    <t>2026-08-13T19:47:04.958Z</t>
+    <t>2026-08-15T18:43:57.553Z</t>
   </si>
   <si>
     <t>General Industrial Coatings</t>
@@ -3912,7 +3912,7 @@
     <t>industries/coatings/inks-paper</t>
   </si>
   <si>
-    <t>2026-08-13T19:46:10.699Z</t>
+    <t>2026-08-15T18:45:27.129Z</t>
   </si>
   <si>
     <t>Inks and Paper</t>
@@ -3927,7 +3927,7 @@
     <t>industries/coatings/wood</t>
   </si>
   <si>
-    <t>2026-08-13T19:43:28.497Z</t>
+    <t>2026-08-15T18:46:21.164Z</t>
   </si>
   <si>
     <t>Wood</t>
@@ -3945,7 +3945,7 @@
     <t>industries/food-beverage/beer</t>
   </si>
   <si>
-    <t>2026-08-13T19:57:44.067Z</t>
+    <t>2026-08-15T18:47:13.785Z</t>
   </si>
   <si>
     <t>Beer</t>
@@ -3966,7 +3966,7 @@
     <t>industries/food-beverage/beverage</t>
   </si>
   <si>
-    <t>2026-08-13T20:00:25.398Z</t>
+    <t>2026-08-15T18:48:07.441Z</t>
   </si>
   <si>
     <t>Beverage</t>
@@ -3981,7 +3981,7 @@
     <t>industries/food-beverage/edible-oil-refining</t>
   </si>
   <si>
-    <t>2026-08-13T19:58:39.248Z</t>
+    <t>2026-08-15T18:51:26.359Z</t>
   </si>
   <si>
     <t>Edible Oil Refining</t>
@@ -3999,7 +3999,7 @@
     <t>industries/food-beverage/food-processing</t>
   </si>
   <si>
-    <t>2026-08-13T19:59:32.496Z</t>
+    <t>2026-08-15T18:52:20.946Z</t>
   </si>
   <si>
     <t>Food Processing</t>
@@ -4017,7 +4017,7 @@
     <t>industries/general-industrial/colloidal-silica-in-catalysts</t>
   </si>
   <si>
-    <t>2026-08-13T19:50:42.947Z</t>
+    <t>2026-08-15T18:53:13.584Z</t>
   </si>
   <si>
     <t>Colloidal Silica in Catalysts</t>
@@ -4035,7 +4035,7 @@
     <t>industries/general-industrial/construction</t>
   </si>
   <si>
-    <t>2026-08-13T19:53:29.000Z</t>
+    <t>2026-08-15T18:54:06.742Z</t>
   </si>
   <si>
     <t>Construction</t>
@@ -4050,7 +4050,7 @@
     <t>industries/general-industrial/investment-casting-binders</t>
   </si>
   <si>
-    <t>2026-08-13T19:51:38.395Z</t>
+    <t>2026-08-15T18:55:01.192Z</t>
   </si>
   <si>
     <t>Investment Casting Binders</t>
@@ -4065,7 +4065,7 @@
     <t>industries/general-industrial/process-adsorbents</t>
   </si>
   <si>
-    <t>2026-08-13T19:48:54.336Z</t>
+    <t>2026-08-15T18:55:53.545Z</t>
   </si>
   <si>
     <t>Process Adsorbents</t>
@@ -4080,7 +4080,7 @@
     <t>industries/general-industrial/refractory-additives</t>
   </si>
   <si>
-    <t>2026-08-13T19:52:34.615Z</t>
+    <t>2026-08-15T18:56:47.195Z</t>
   </si>
   <si>
     <t>Refractory Additives</t>
@@ -4095,7 +4095,7 @@
     <t>industries/general-industrial/static-adsorbents</t>
   </si>
   <si>
-    <t>2026-08-13T19:49:47.540Z</t>
+    <t>2026-08-15T18:57:41.078Z</t>
   </si>
   <si>
     <t>Static Adsorbents</t>
@@ -4110,7 +4110,7 @@
     <t>industries/nutraceutical-solutions/cbd-purification-formulation-delivery</t>
   </si>
   <si>
-    <t>2026-08-13T19:48:43.394Z</t>
+    <t>2026-08-15T18:58:34.235Z</t>
   </si>
   <si>
     <t>CBD Purfication, Formulation and Delivery</t>
@@ -4125,7 +4125,7 @@
     <t>industries/nutraceutical-solutions/lipid-purification-formulation-delivery</t>
   </si>
   <si>
-    <t>2026-08-13T19:47:49.988Z</t>
+    <t>2026-08-15T18:59:36.759Z</t>
   </si>
   <si>
     <t>Lipid Purfication, Formulation and Delivery</t>
@@ -4140,7 +4140,7 @@
     <t>industries/nutraceutical-solutions/nutraceutical-cdmo</t>
   </si>
   <si>
-    <t>2026-08-13T19:49:38.195Z</t>
+    <t>2026-08-15T19:00:30.960Z</t>
   </si>
   <si>
     <t>Nutraceutical CDMO</t>
@@ -4161,7 +4161,7 @@
     <t>industries/nutraceutical-solutions/traditional-herbal-medicine</t>
   </si>
   <si>
-    <t>2026-08-13T19:50:32.595Z</t>
+    <t>2026-08-15T19:01:25.597Z</t>
   </si>
   <si>
     <t>Traditional Herbal Medicine (THM) and Botanical Solutions</t>
@@ -4176,7 +4176,7 @@
     <t>industries/nutraceutical-solutions/vitamin-purification-formulation-delivery</t>
   </si>
   <si>
-    <t>2026-08-13T19:46:57.529Z</t>
+    <t>2026-08-15T19:02:20.283Z</t>
   </si>
   <si>
     <t>Vitamin Purification, Formulation and Delivery</t>
@@ -4194,7 +4194,7 @@
     <t>industries/personal-care/cosmetics</t>
   </si>
   <si>
-    <t>2026-08-13T19:55:55.928Z</t>
+    <t>2026-08-15T19:03:14.299Z</t>
   </si>
   <si>
     <t>Cosmetics</t>
@@ -4212,7 +4212,7 @@
     <t>industries/personal-care/toothpaste</t>
   </si>
   <si>
-    <t>2026-08-13T19:55:02.740Z</t>
+    <t>2026-08-15T19:04:08.161Z</t>
   </si>
   <si>
     <t>Toothpaste</t>
@@ -4227,7 +4227,7 @@
     <t>industries/pharmaceutical-solutions/fine-chemicals</t>
   </si>
   <si>
-    <t>2026-08-13T19:55:17.636Z</t>
+    <t>2026-08-15T19:05:35.948Z</t>
   </si>
   <si>
     <t>https://grace.com/industries/pharmaceutical-solutions/fine-chemicals/</t>
@@ -4239,7 +4239,7 @@
     <t>industries/pharmaceutical-solutions/packaging-adsorbents</t>
   </si>
   <si>
-    <t>2026-08-13T19:45:11.197Z</t>
+    <t>2026-08-15T19:15:47.865Z</t>
   </si>
   <si>
     <t>Packaging Adsorbents</t>
@@ -4254,7 +4254,7 @@
     <t>industries/pharmaceutical-solutions/purification-formulation-delivery</t>
   </si>
   <si>
-    <t>2026-08-13T19:41:36.288Z</t>
+    <t>2026-08-15T19:16:41.460Z</t>
   </si>
   <si>
     <t>Purification, Formulation and Delivery</t>
@@ -4269,7 +4269,7 @@
     <t>industries/plastics-and-polymers/custom-catalysts</t>
   </si>
   <si>
-    <t>2026-08-13T19:58:45.156Z</t>
+    <t>2026-08-15T19:20:48.168Z</t>
   </si>
   <si>
     <t>Custom Catalysts</t>
@@ -4416,7 +4416,7 @@
     <t>industries/refining-technologies/hydroprocessing</t>
   </si>
   <si>
-    <t>2026-08-14T08:58:02.910Z</t>
+    <t>2026-08-15T19:44:20.466Z</t>
   </si>
   <si>
     <t>Hydroprocessing</t>
@@ -4488,7 +4488,7 @@
     <t>industries/biofuels/biomass-based-diesel/first-generation-biodiesel</t>
   </si>
   <si>
-    <t>2026-08-13T20:03:05.293Z</t>
+    <t>2026-08-15T18:37:40.139Z</t>
   </si>
   <si>
     <t>First Generation Biodiesel</t>
@@ -4506,7 +4506,7 @@
     <t>industries/biofuels/biomass-based-diesel/renewable-diesel</t>
   </si>
   <si>
-    <t>2026-08-13T20:03:58.046Z</t>
+    <t>2026-08-15T18:38:34.036Z</t>
   </si>
   <si>
     <t>Renewable Diesel</t>
@@ -4521,7 +4521,7 @@
     <t>industries/pharmaceutical-solutions/fine-chemicals/consultative-services</t>
   </si>
   <si>
-    <t>2026-08-13T19:59:47.535Z</t>
+    <t>2026-08-15T19:06:28.737Z</t>
   </si>
   <si>
     <t>Consultative Services</t>
@@ -4536,7 +4536,7 @@
     <t>industries/pharmaceutical-solutions/fine-chemicals/custom-apis</t>
   </si>
   <si>
-    <t>2026-08-13T19:56:12.157Z</t>
+    <t>2026-08-15T19:09:11.700Z</t>
   </si>
   <si>
     <t>Custom APIs</t>
@@ -4551,7 +4551,7 @@
     <t>industries/pharmaceutical-solutions/fine-chemicals/facilities</t>
   </si>
   <si>
-    <t>2026-08-13T20:02:28.188Z</t>
+    <t>2026-08-15T19:10:04.813Z</t>
   </si>
   <si>
     <t>Facilities</t>
@@ -4584,7 +4584,7 @@
     <t>industries/pharmaceutical-solutions/fine-chemicals/generic-apis</t>
   </si>
   <si>
-    <t>2026-08-13T19:57:59.050Z</t>
+    <t>2026-08-15T19:13:05.962Z</t>
   </si>
   <si>
     <t>Generic APIs</t>
@@ -4599,7 +4599,7 @@
     <t>industries/pharmaceutical-solutions/fine-chemicals/integrated-scale-up</t>
   </si>
   <si>
-    <t>2026-08-13T19:58:53.146Z</t>
+    <t>2026-08-15T19:14:00.736Z</t>
   </si>
   <si>
     <t>Integrated Scale-Up</t>
@@ -4614,7 +4614,7 @@
     <t>industries/pharmaceutical-solutions/fine-chemicals/rsms-and-intermediates</t>
   </si>
   <si>
-    <t>2026-08-13T19:57:06.256Z</t>
+    <t>2026-08-15T19:14:54.364Z</t>
   </si>
   <si>
     <t>RSMs and Intermediates</t>
@@ -4629,7 +4629,7 @@
     <t>industries/pharmaceutical-solutions/purification-formulation-delivery/active-ingredient-delivery</t>
   </si>
   <si>
-    <t>2026-08-13T19:44:18.004Z</t>
+    <t>2026-08-15T19:17:35.574Z</t>
   </si>
   <si>
     <t>Active Ingredient Delivery</t>
@@ -4647,7 +4647,7 @@
     <t>industries/pharmaceutical-solutions/purification-formulation-delivery/chromatography</t>
   </si>
   <si>
-    <t>2026-08-13T19:42:31.146Z</t>
+    <t>2026-08-15T19:18:29.204Z</t>
   </si>
   <si>
     <t>Chromatography</t>
@@ -4665,7 +4665,7 @@
     <t>industries/pharmaceutical-solutions/purification-formulation-delivery/excipients</t>
   </si>
   <si>
-    <t>2026-08-13T19:43:24.551Z</t>
+    <t>2026-08-15T19:19:55.301Z</t>
   </si>
   <si>
     <t>Excipients</t>
@@ -4683,7 +4683,7 @@
     <t>industries/plastics-and-polymers/plastic-additives/silica-anti-blocking-agents</t>
   </si>
   <si>
-    <t>2026-08-13T20:00:31.750Z</t>
+    <t>2026-08-15T19:21:42.519Z</t>
   </si>
   <si>
     <t>Silica Anti-blocking Agents</t>
@@ -4701,7 +4701,7 @@
     <t>industries/plastics-and-polymers/plastic-additives/titanium-dioxide-extenders</t>
   </si>
   <si>
-    <t>2026-08-13T20:01:24.650Z</t>
+    <t>2026-08-15T19:22:37.156Z</t>
   </si>
   <si>
     <t>Titanium Dioxide Extenders</t>
@@ -4716,7 +4716,7 @@
     <t>industries/plastics-and-polymers/polyethylene-catalysts/pe-catalyst-components-and-supports</t>
   </si>
   <si>
-    <t>2026-08-13T19:45:11.697Z</t>
+    <t>2026-08-15T19:23:29.325Z</t>
   </si>
   <si>
     <t>PE Catalyst Components and Supports</t>
@@ -4731,7 +4731,7 @@
     <t>industries/plastics-and-polymers/polyethylene-catalysts/pe-gas-phase</t>
   </si>
   <si>
-    <t>2026-08-14T07:38:11.436Z</t>
+    <t>2026-08-15T19:24:22.526Z</t>
   </si>
   <si>
     <t>PE Gas Phase</t>
@@ -4746,7 +4746,7 @@
     <t>industries/plastics-and-polymers/polyethylene-catalysts/pe-hybrid</t>
   </si>
   <si>
-    <t>2026-08-13T19:48:48.943Z</t>
+    <t>2026-08-15T19:25:17.486Z</t>
   </si>
   <si>
     <t>PE Hybrid</t>
@@ -4761,7 +4761,7 @@
     <t>industries/plastics-and-polymers/polyethylene-catalysts/pe-slurry</t>
   </si>
   <si>
-    <t>2026-08-14T07:37:18.651Z</t>
+    <t>2026-08-15T19:26:12.058Z</t>
   </si>
   <si>
     <t>PE Slurry</t>
@@ -4776,7 +4776,7 @@
     <t>industries/plastics-and-polymers/polyethylene-catalysts/pe-solution</t>
   </si>
   <si>
-    <t>2026-08-13T19:47:55.263Z</t>
+    <t>2026-08-15T19:27:23.349Z</t>
   </si>
   <si>
     <t>PE Solution</t>
@@ -4791,7 +4791,7 @@
     <t>industries/plastics-and-polymers/polypropylene-catalysts/pp-bulk</t>
   </si>
   <si>
-    <t>2026-08-14T07:39:04.089Z</t>
+    <t>2026-08-15T19:28:16.889Z</t>
   </si>
   <si>
     <t>PP Bulk</t>
@@ -4806,7 +4806,7 @@
     <t>industries/plastics-and-polymers/polypropylene-catalysts/pp-gas-phase</t>
   </si>
   <si>
-    <t>2026-08-14T07:39:57.483Z</t>
+    <t>2026-08-15T19:29:09.946Z</t>
   </si>
   <si>
     <t>PP Gas Phase</t>
@@ -4821,7 +4821,7 @@
     <t>industries/plastics-and-polymers/polypropylene-catalysts/pp-slurry</t>
   </si>
   <si>
-    <t>2026-08-13T19:52:27.600Z</t>
+    <t>2026-08-15T19:30:03.638Z</t>
   </si>
   <si>
     <t>PP Slurry</t>
@@ -4848,7 +4848,7 @@
     <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-performance</t>
   </si>
   <si>
-    <t>2026-08-13T19:56:03.555Z</t>
+    <t>2026-08-15T19:30:57.100Z</t>
   </si>
   <si>
     <t>UNIPOL® PP Performance</t>
@@ -4863,7 +4863,7 @@
     <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-process</t>
   </si>
   <si>
-    <t>2026-08-13T19:54:14.694Z</t>
+    <t>2026-08-15T19:31:50.823Z</t>
   </si>
   <si>
     <t>UNIPOL® PP Process</t>
@@ -4875,7 +4875,7 @@
     <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-products</t>
   </si>
   <si>
-    <t>2026-08-13T19:55:09.606Z</t>
+    <t>2026-08-15T19:32:44.074Z</t>
   </si>
   <si>
     <t>UNIPOL® PP Products</t>
@@ -4890,7 +4890,7 @@
     <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-services</t>
   </si>
   <si>
-    <t>2026-08-13T19:56:57.071Z</t>
+    <t>2026-08-15T19:34:12.800Z</t>
   </si>
   <si>
     <t>UNIPOL® PP Services</t>
@@ -4908,7 +4908,7 @@
     <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-technology-ppartner-program</t>
   </si>
   <si>
-    <t>2026-08-13T19:57:50.862Z</t>
+    <t>2026-08-15T19:35:07.890Z</t>
   </si>
   <si>
     <t>PPartner Program™ Services</t>
@@ -4923,7 +4923,7 @@
     <t>industries/refining-technologies/fcc-additive-solutions/combustion-promoter</t>
   </si>
   <si>
-    <t>2026-08-14T08:57:10.011Z</t>
+    <t>2026-08-15T19:36:00.279Z</t>
   </si>
   <si>
     <t>Combustion Promoter</t>
@@ -4938,7 +4938,7 @@
     <t>industries/refining-technologies/fcc-additive-solutions/gasoline-sulphur-reduction</t>
   </si>
   <si>
-    <t>2026-08-14T08:55:23.031Z</t>
+    <t>2026-08-15T19:36:54.842Z</t>
   </si>
   <si>
     <t>Gasoline Sulphur Reduction</t>
@@ -4953,7 +4953,7 @@
     <t>industries/refining-technologies/fcc-additive-solutions/light-olefins</t>
   </si>
   <si>
-    <t>2026-08-14T08:54:28.613Z</t>
+    <t>2026-08-15T19:37:48.672Z</t>
   </si>
   <si>
     <t>Light Olefins</t>
@@ -4968,7 +4968,7 @@
     <t>industries/refining-technologies/fcc-additive-solutions/nox-reduction</t>
   </si>
   <si>
-    <t>2026-08-14T08:53:34.688Z</t>
+    <t>2026-08-15T19:38:41.792Z</t>
   </si>
   <si>
     <t>NOx Reduction</t>
@@ -4983,7 +4983,7 @@
     <t>industries/refining-technologies/fcc-additive-solutions/sox-reduction</t>
   </si>
   <si>
-    <t>2026-08-14T08:56:16.531Z</t>
+    <t>2026-08-15T19:39:35.148Z</t>
   </si>
   <si>
     <t>SOx Reduction</t>
@@ -4998,7 +4998,7 @@
     <t>industries/refining-technologies/fcc-catalyst-application/butylene-selectivity</t>
   </si>
   <si>
-    <t>2026-08-14T09:04:15.024Z</t>
+    <t>2026-08-15T19:40:29.640Z</t>
   </si>
   <si>
     <t>Butylene Selectivity</t>
@@ -5013,7 +5013,7 @@
     <t>industries/refining-technologies/fcc-catalyst-application/light-feed-performance</t>
   </si>
   <si>
-    <t>2026-08-14T09:02:28.927Z</t>
+    <t>2026-08-15T19:41:38.427Z</t>
   </si>
   <si>
     <t>Light Feed Performance</t>
@@ -5028,7 +5028,7 @@
     <t>industries/refining-technologies/fcc-catalyst-application/maximize-propylene</t>
   </si>
   <si>
-    <t>2026-08-14T09:01:36.416Z</t>
+    <t>2026-08-15T19:42:31.596Z</t>
   </si>
   <si>
     <t>Maximize Propylene</t>
@@ -5043,7 +5043,7 @@
     <t>industries/refining-technologies/fcc-catalyst-application/resid-conversion</t>
   </si>
   <si>
-    <t>2026-08-14T09:03:22.033Z</t>
+    <t>2026-08-15T19:43:26.257Z</t>
   </si>
   <si>
     <t>Resid Conversion</t>
@@ -5064,7 +5064,7 @@
     <t>industries/refining-technologies/hydroprocessing/distillate-hydrotreating-solutions</t>
   </si>
   <si>
-    <t>2026-08-13T21:46:36.990Z</t>
+    <t>2026-08-15T19:45:13.703Z</t>
   </si>
   <si>
     <t>Distillate Hydrotreating Solutions</t>
@@ -5079,7 +5079,7 @@
     <t>industries/refining-technologies/hydroprocessing/resid-hydrocracking-solutions</t>
   </si>
   <si>
-    <t>2026-08-13T21:45:43.655Z</t>
+    <t>2026-08-15T19:46:08.362Z</t>
   </si>
   <si>
     <t>Resid Hydrocracking Solutions</t>
@@ -5094,7 +5094,7 @@
     <t>industries/refining-technologies/hydroprocessing/resid-hydrotreating-solutions</t>
   </si>
   <si>
-    <t>2026-08-13T21:44:50.934Z</t>
+    <t>2026-08-15T19:47:01.059Z</t>
   </si>
   <si>
     <t>Resid Hydrotreating Solutions</t>
@@ -5112,7 +5112,7 @@
     <t>industries/refining-technologies/value-creation/specialized-evaluation-tools</t>
   </si>
   <si>
-    <t>2026-08-14T09:06:56.441Z</t>
+    <t>2026-08-15T19:48:27.241Z</t>
   </si>
   <si>
     <t>Specialized Evaluation Tools</t>
@@ -5130,7 +5130,7 @@
     <t>industries/refining-technologies/value-creation/sustainability</t>
   </si>
   <si>
-    <t>2026-08-14T09:06:02.821Z</t>
+    <t>2026-08-15T19:49:20.373Z</t>
   </si>
   <si>
     <t>Sustainable Solutions for FCC</t>
@@ -5148,7 +5148,7 @@
     <t>industries/refining-technologies/value-creation/technical-service-expertise</t>
   </si>
   <si>
-    <t>2026-08-14T09:05:08.778Z</t>
+    <t>2026-08-15T19:50:13.867Z</t>
   </si>
   <si>
     <t>Technical Service Expertise</t>
@@ -5562,7 +5562,7 @@
     <t>industries/pharmaceutical-solutions/fine-chemicals/consultative-services/quality-and-compliance</t>
   </si>
   <si>
-    <t>2026-08-13T20:01:35.443Z</t>
+    <t>2026-08-15T19:07:21.870Z</t>
   </si>
   <si>
     <t>Quality and Compliance</t>
@@ -5577,7 +5577,7 @@
     <t>industries/pharmaceutical-solutions/fine-chemicals/consultative-services/r-d</t>
   </si>
   <si>
-    <t>2026-08-13T20:00:41.014Z</t>
+    <t>2026-08-15T19:08:16.852Z</t>
   </si>
   <si>
     <t>R&amp;D</t>
@@ -5595,7 +5595,7 @@
     <t>industries/pharmaceutical-solutions/fine-chemicals/facilities/south-haven</t>
   </si>
   <si>
-    <t>2026-08-13T20:03:21.541Z</t>
+    <t>2026-08-15T19:10:59.200Z</t>
   </si>
   <si>
     <t>South Haven</t>
@@ -5610,7 +5610,7 @@
     <t>industries/pharmaceutical-solutions/fine-chemicals/facilities/tyrone</t>
   </si>
   <si>
-    <t>2026-08-13T20:04:15.119Z</t>
+    <t>2026-08-15T19:11:51.823Z</t>
   </si>
   <si>
     <t>Tyrone</t>

--- a/tools/importer/reports/import-grace-master.report.xlsx
+++ b/tools/importer/reports/import-grace-master.report.xlsx
@@ -3849,7 +3849,7 @@
     <t>industries/chemical-processing/hydrogenation-catalysts</t>
   </si>
   <si>
-    <t>2026-08-15T18:41:15.992Z</t>
+    <t>2026-08-15T22:45:16.514Z</t>
   </si>
   <si>
     <t>Hydrogenation Catalysts</t>
@@ -18125,7 +18125,7 @@
         <v>1276</v>
       </c>
       <c r="B243" t="s">
-        <v>1266</v>
+        <v>1044</v>
       </c>
       <c r="C243" t="s">
         <v>18</v>

--- a/tools/importer/reports/import-grace-master.report.xlsx
+++ b/tools/importer/reports/import-grace-master.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5102" uniqueCount="1865">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5102" uniqueCount="1866">
   <si>
     <t>_reportFile</t>
   </si>
@@ -451,13 +451,13 @@
     <t>industries/coatings.report.json</t>
   </si>
   <si>
-    <t>["hero-banner","video-overlay","table-two-column-content","columns-horizontal-teaser-featured","cards-category-grid","cards-featured-content"]</t>
+    <t>["hero-banner","video-overlay","table-two-column-content","columns-horizontal-teaser-featured","cards-category-grid","cards-featured-content","banner-cta"]</t>
   </si>
   <si>
     <t>industries/coatings</t>
   </si>
   <si>
-    <t>2026-08-16T09:49:35.990Z</t>
+    <t>2026-08-18T06:33:03.425Z</t>
   </si>
   <si>
     <t>Coatings</t>
@@ -490,7 +490,7 @@
     <t>industries/general-industrial</t>
   </si>
   <si>
-    <t>2026-08-13T19:47:59.907Z</t>
+    <t>2026-08-18T05:00:09.679Z</t>
   </si>
   <si>
     <t>General Industrial</t>
@@ -502,13 +502,13 @@
     <t>industries/nutraceutical-solutions.report.json</t>
   </si>
   <si>
-    <t>["hero-banner","columns-horizontal-teaser-featured","cards-category-grid","columns-horizontal-teaser-featured","cards-featured-content"]</t>
+    <t>["hero-banner","columns-horizontal-teaser-featured","cards-category-grid","featured-product-selector","cards-featured-content","banner-cta"]</t>
   </si>
   <si>
     <t>industries/nutraceutical-solutions</t>
   </si>
   <si>
-    <t>2026-08-13T19:46:04.850Z</t>
+    <t>2026-08-18T04:53:48.796Z</t>
   </si>
   <si>
     <t>Nutraceutical Solutions</t>
@@ -3435,13 +3435,13 @@
     <t>products/shieldex.report.json</t>
   </si>
   <si>
-    <t>["hero-banner","columns-brochure-promo","columns-horizontal-teaser-featured","cards-featured-content"]</t>
+    <t>["hero-banner","banner-cta","columns-brochure-promo","columns-horizontal-teaser-featured","cards-featured-content"]</t>
   </si>
   <si>
     <t>products/shieldex</t>
   </si>
   <si>
-    <t>2026-08-11T20:09:01.782Z</t>
+    <t>2026-08-17T22:11:16.136Z</t>
   </si>
   <si>
     <t>SHIELDEX® Anti-Corrosive Pigments</t>
@@ -3588,13 +3588,13 @@
     <t>products/trisyl-silica.report.json</t>
   </si>
   <si>
-    <t>["hero-banner","video-overlay","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq","columns-horizontal-teaser","cards-featured-content"]</t>
+    <t>["hero-banner","video-overlay","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq","custom-widget-news-archive","columns-horizontal-teaser","cards-featured-content"]</t>
   </si>
   <si>
     <t>products/trisyl-silica</t>
   </si>
   <si>
-    <t>2026-08-16T17:02:44.927Z</t>
+    <t>2026-08-17T22:12:10.070Z</t>
   </si>
   <si>
     <t>TRISYL® Silica</t>
@@ -3792,7 +3792,7 @@
     <t>industries/biofuels/biomass-based-diesel</t>
   </si>
   <si>
-    <t>2026-08-13T20:02:11.273Z</t>
+    <t>2026-08-18T06:40:07.688Z</t>
   </si>
   <si>
     <t>https://grace.com/industries/biofuels/biomass-based-diesel/</t>
@@ -3867,7 +3867,7 @@
     <t>industries/coatings/coil</t>
   </si>
   <si>
-    <t>2026-08-16T09:51:54.428Z</t>
+    <t>2026-08-18T04:57:27.725Z</t>
   </si>
   <si>
     <t>Coil</t>
@@ -3882,7 +3882,7 @@
     <t>industries/coatings/general-industrial-coatings</t>
   </si>
   <si>
-    <t>2026-08-16T09:54:34.336Z</t>
+    <t>2026-08-18T04:52:00.324Z</t>
   </si>
   <si>
     <t>General Industrial Coatings</t>
@@ -3909,10 +3909,13 @@
     <t>industries/coatings/wood.report.json</t>
   </si>
   <si>
+    <t>["hero-banner","featured-product-selector","cards-featured-content"]</t>
+  </si>
+  <si>
     <t>industries/coatings/wood</t>
   </si>
   <si>
-    <t>2026-08-16T09:50:29.678Z</t>
+    <t>2026-08-18T04:52:54.425Z</t>
   </si>
   <si>
     <t>Wood</t>
@@ -4056,10 +4059,13 @@
     <t>industries/general-industrial/refractory-additives.report.json</t>
   </si>
   <si>
+    <t>["hero-banner","columns-split-list","columns-horizontal-teaser-featured","cards-featured-content"]</t>
+  </si>
+  <si>
     <t>industries/general-industrial/refractory-additives</t>
   </si>
   <si>
-    <t>2026-08-15T18:56:47.195Z</t>
+    <t>2026-08-18T04:58:20.673Z</t>
   </si>
   <si>
     <t>Refractory Additives</t>
@@ -4173,7 +4179,7 @@
     <t>industries/personal-care/cosmetics</t>
   </si>
   <si>
-    <t>2026-08-15T19:03:14.299Z</t>
+    <t>2026-08-17T22:05:01.122Z</t>
   </si>
   <si>
     <t>Cosmetics</t>
@@ -4485,7 +4491,7 @@
     <t>industries/biofuels/biomass-based-diesel/renewable-diesel</t>
   </si>
   <si>
-    <t>2026-08-15T18:38:34.036Z</t>
+    <t>2026-08-18T07:00:16.926Z</t>
   </si>
   <si>
     <t>Renewable Diesel</t>
@@ -4840,9 +4846,6 @@
   </si>
   <si>
     <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-process.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","columns-split-list","columns-horizontal-teaser-featured","cards-featured-content"]</t>
   </si>
   <si>
     <t>industries/plastics-and-polymers/unipol-pp-process-technology/unipol-pp-process</t>
@@ -18366,7 +18369,7 @@
         <v>1297</v>
       </c>
       <c r="B248" t="s">
-        <v>1277</v>
+        <v>1298</v>
       </c>
       <c r="C248" t="s">
         <v>18</v>
@@ -18393,7 +18396,7 @@
         <v>20</v>
       </c>
       <c r="K248" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="L248" t="s">
         <v>19</v>
@@ -18402,21 +18405,21 @@
         <v>22</v>
       </c>
       <c r="N248" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="O248" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="P248" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="249" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="B249" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="C249" t="s">
         <v>18</v>
@@ -18443,7 +18446,7 @@
         <v>20</v>
       </c>
       <c r="K249" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="L249" t="s">
         <v>19</v>
@@ -18452,21 +18455,21 @@
         <v>22</v>
       </c>
       <c r="N249" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="O249" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="P249" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="250" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="B250" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="C250" t="s">
         <v>18</v>
@@ -18487,13 +18490,13 @@
         <v>1</v>
       </c>
       <c r="I250" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="J250" t="s">
         <v>20</v>
       </c>
       <c r="K250" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="L250" t="s">
         <v>19</v>
@@ -18502,21 +18505,21 @@
         <v>22</v>
       </c>
       <c r="N250" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="O250" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="P250" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="251" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B251" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="C251" t="s">
         <v>18</v>
@@ -18543,7 +18546,7 @@
         <v>20</v>
       </c>
       <c r="K251" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="L251" t="s">
         <v>19</v>
@@ -18552,21 +18555,21 @@
         <v>22</v>
       </c>
       <c r="N251" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="O251" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="P251" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="252" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B252" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="C252" t="s">
         <v>18</v>
@@ -18593,7 +18596,7 @@
         <v>20</v>
       </c>
       <c r="K252" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="L252" t="s">
         <v>19</v>
@@ -18602,21 +18605,21 @@
         <v>22</v>
       </c>
       <c r="N252" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="O252" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="P252" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="253" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="B253" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="C253" t="s">
         <v>18</v>
@@ -18643,7 +18646,7 @@
         <v>20</v>
       </c>
       <c r="K253" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="L253" t="s">
         <v>19</v>
@@ -18652,18 +18655,18 @@
         <v>22</v>
       </c>
       <c r="N253" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="O253" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="P253" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="254" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="B254" t="s">
         <v>1277</v>
@@ -18693,7 +18696,7 @@
         <v>20</v>
       </c>
       <c r="K254" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="L254" t="s">
         <v>19</v>
@@ -18702,18 +18705,18 @@
         <v>22</v>
       </c>
       <c r="N254" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="O254" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="P254" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="255" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="B255" t="s">
         <v>1277</v>
@@ -18743,7 +18746,7 @@
         <v>20</v>
       </c>
       <c r="K255" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="L255" t="s">
         <v>19</v>
@@ -18752,18 +18755,18 @@
         <v>22</v>
       </c>
       <c r="N255" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="O255" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="P255" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="256" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="B256" t="s">
         <v>1042</v>
@@ -18793,7 +18796,7 @@
         <v>20</v>
       </c>
       <c r="K256" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="L256" t="s">
         <v>19</v>
@@ -18802,21 +18805,21 @@
         <v>22</v>
       </c>
       <c r="N256" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="O256" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="P256" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="257" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B257" t="s">
-        <v>1277</v>
+        <v>1348</v>
       </c>
       <c r="C257" t="s">
         <v>18</v>
@@ -18843,7 +18846,7 @@
         <v>20</v>
       </c>
       <c r="K257" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="L257" t="s">
         <v>19</v>
@@ -18852,18 +18855,18 @@
         <v>22</v>
       </c>
       <c r="N257" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="O257" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="P257" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="258" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="B258" t="s">
         <v>1042</v>
@@ -18893,7 +18896,7 @@
         <v>20</v>
       </c>
       <c r="K258" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="L258" t="s">
         <v>19</v>
@@ -18902,18 +18905,18 @@
         <v>22</v>
       </c>
       <c r="N258" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="O258" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="P258" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="259" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="B259" t="s">
         <v>135</v>
@@ -18943,7 +18946,7 @@
         <v>20</v>
       </c>
       <c r="K259" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="L259" t="s">
         <v>19</v>
@@ -18952,18 +18955,18 @@
         <v>22</v>
       </c>
       <c r="N259" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="O259" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="P259" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="260" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="B260" t="s">
         <v>135</v>
@@ -18993,7 +18996,7 @@
         <v>20</v>
       </c>
       <c r="K260" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="L260" t="s">
         <v>19</v>
@@ -19002,18 +19005,18 @@
         <v>22</v>
       </c>
       <c r="N260" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="O260" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="P260" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="261" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="B261" t="s">
         <v>135</v>
@@ -19043,7 +19046,7 @@
         <v>20</v>
       </c>
       <c r="K261" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="L261" t="s">
         <v>19</v>
@@ -19052,21 +19055,21 @@
         <v>22</v>
       </c>
       <c r="N261" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="O261" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="P261" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="262" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="B262" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="C262" t="s">
         <v>18</v>
@@ -19087,13 +19090,13 @@
         <v>1</v>
       </c>
       <c r="I262" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="J262" t="s">
         <v>20</v>
       </c>
       <c r="K262" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="L262" t="s">
         <v>19</v>
@@ -19102,18 +19105,18 @@
         <v>22</v>
       </c>
       <c r="N262" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="O262" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="P262" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="263" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="B263" t="s">
         <v>54</v>
@@ -19143,7 +19146,7 @@
         <v>20</v>
       </c>
       <c r="K263" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="L263" t="s">
         <v>19</v>
@@ -19152,21 +19155,21 @@
         <v>22</v>
       </c>
       <c r="N263" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="O263" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="P263" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="264" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="B264" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="C264" t="s">
         <v>18</v>
@@ -19193,7 +19196,7 @@
         <v>20</v>
       </c>
       <c r="K264" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="L264" t="s">
         <v>19</v>
@@ -19202,21 +19205,21 @@
         <v>22</v>
       </c>
       <c r="N264" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="O264" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="P264" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="265" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="B265" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="C265" t="s">
         <v>18</v>
@@ -19243,7 +19246,7 @@
         <v>20</v>
       </c>
       <c r="K265" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="L265" t="s">
         <v>19</v>
@@ -19252,18 +19255,18 @@
         <v>22</v>
       </c>
       <c r="N265" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="O265" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="P265" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="266" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="B266" t="s">
         <v>54</v>
@@ -19293,7 +19296,7 @@
         <v>20</v>
       </c>
       <c r="K266" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="L266" t="s">
         <v>19</v>
@@ -19302,18 +19305,18 @@
         <v>22</v>
       </c>
       <c r="N266" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="O266" t="s">
         <v>1079</v>
       </c>
       <c r="P266" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="267" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="B267" t="s">
         <v>135</v>
@@ -19343,7 +19346,7 @@
         <v>20</v>
       </c>
       <c r="K267" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="L267" t="s">
         <v>19</v>
@@ -19352,18 +19355,18 @@
         <v>22</v>
       </c>
       <c r="N267" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="O267" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="P267" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="268" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="B268" t="s">
         <v>135</v>
@@ -19393,7 +19396,7 @@
         <v>20</v>
       </c>
       <c r="K268" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="L268" t="s">
         <v>19</v>
@@ -19402,18 +19405,18 @@
         <v>22</v>
       </c>
       <c r="N268" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="O268" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="P268" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="269" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="B269" t="s">
         <v>1042</v>
@@ -19443,7 +19446,7 @@
         <v>20</v>
       </c>
       <c r="K269" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="L269" t="s">
         <v>19</v>
@@ -19452,18 +19455,18 @@
         <v>22</v>
       </c>
       <c r="N269" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="O269" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="P269" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="270" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="B270" t="s">
         <v>54</v>
@@ -19493,7 +19496,7 @@
         <v>20</v>
       </c>
       <c r="K270" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="L270" t="s">
         <v>19</v>
@@ -19502,18 +19505,18 @@
         <v>22</v>
       </c>
       <c r="N270" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="O270" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="P270" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="271" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="B271" t="s">
         <v>135</v>
@@ -19543,7 +19546,7 @@
         <v>20</v>
       </c>
       <c r="K271" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="L271" t="s">
         <v>19</v>
@@ -19552,21 +19555,21 @@
         <v>22</v>
       </c>
       <c r="N271" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="O271" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="P271" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="272" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="B272" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="C272" t="s">
         <v>18</v>
@@ -19593,7 +19596,7 @@
         <v>20</v>
       </c>
       <c r="K272" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="L272" t="s">
         <v>19</v>
@@ -19602,18 +19605,18 @@
         <v>22</v>
       </c>
       <c r="N272" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="O272" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="P272" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="273" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="B273" t="s">
         <v>1042</v>
@@ -19643,7 +19646,7 @@
         <v>20</v>
       </c>
       <c r="K273" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="L273" t="s">
         <v>19</v>
@@ -19652,18 +19655,18 @@
         <v>22</v>
       </c>
       <c r="N273" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="O273" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="P273" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="274" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="B274" t="s">
         <v>157</v>
@@ -19693,7 +19696,7 @@
         <v>20</v>
       </c>
       <c r="K274" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="L274" t="s">
         <v>19</v>
@@ -19702,21 +19705,21 @@
         <v>22</v>
       </c>
       <c r="N274" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="O274" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="P274" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="275" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="B275" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="C275" t="s">
         <v>18</v>
@@ -19737,13 +19740,13 @@
         <v>1</v>
       </c>
       <c r="I275" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="J275" t="s">
         <v>20</v>
       </c>
       <c r="K275" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="L275" t="s">
         <v>19</v>
@@ -19752,21 +19755,21 @@
         <v>22</v>
       </c>
       <c r="N275" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="O275" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="P275" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="276" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="B276" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="C276" t="s">
         <v>18</v>
@@ -19793,7 +19796,7 @@
         <v>20</v>
       </c>
       <c r="K276" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="L276" t="s">
         <v>19</v>
@@ -19802,18 +19805,18 @@
         <v>22</v>
       </c>
       <c r="N276" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="O276" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="P276" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="277" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="B277" t="s">
         <v>186</v>
@@ -19843,7 +19846,7 @@
         <v>20</v>
       </c>
       <c r="K277" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="L277" t="s">
         <v>19</v>
@@ -19852,21 +19855,21 @@
         <v>22</v>
       </c>
       <c r="N277" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="O277" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="P277" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="278" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="B278" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="C278" t="s">
         <v>18</v>
@@ -19887,13 +19890,13 @@
         <v>1</v>
       </c>
       <c r="I278" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="J278" t="s">
         <v>20</v>
       </c>
       <c r="K278" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="L278" t="s">
         <v>19</v>
@@ -19902,18 +19905,18 @@
         <v>22</v>
       </c>
       <c r="N278" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="O278" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="P278" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="279" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="B279" t="s">
         <v>186</v>
@@ -19943,7 +19946,7 @@
         <v>20</v>
       </c>
       <c r="K279" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="L279" t="s">
         <v>19</v>
@@ -19952,21 +19955,21 @@
         <v>22</v>
       </c>
       <c r="N279" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="O279" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="P279" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="280" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="B280" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="C280" t="s">
         <v>40</v>
@@ -19993,7 +19996,7 @@
         <v>42</v>
       </c>
       <c r="K280" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="L280" t="b">
         <v>1</v>
@@ -20002,21 +20005,21 @@
         <v>22</v>
       </c>
       <c r="N280" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="O280" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="P280" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="281" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="B281" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="C281" t="s">
         <v>18</v>
@@ -20037,13 +20040,13 @@
         <v>0</v>
       </c>
       <c r="I281" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="J281" t="s">
         <v>20</v>
       </c>
       <c r="K281" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="L281" t="s">
         <v>19</v>
@@ -20052,18 +20055,18 @@
         <v>22</v>
       </c>
       <c r="N281" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="O281" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="P281" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="282" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="B282" t="s">
         <v>1277</v>
@@ -20093,7 +20096,7 @@
         <v>20</v>
       </c>
       <c r="K282" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="L282" t="s">
         <v>19</v>
@@ -20102,21 +20105,21 @@
         <v>22</v>
       </c>
       <c r="N282" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="O282" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="P282" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="283" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="B283" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="C283" t="s">
         <v>18</v>
@@ -20143,7 +20146,7 @@
         <v>20</v>
       </c>
       <c r="K283" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="L283" t="s">
         <v>19</v>
@@ -20152,18 +20155,18 @@
         <v>22</v>
       </c>
       <c r="N283" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="O283" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="P283" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="284" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="B284" t="s">
         <v>135</v>
@@ -20193,7 +20196,7 @@
         <v>20</v>
       </c>
       <c r="K284" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="L284" t="s">
         <v>19</v>
@@ -20202,18 +20205,18 @@
         <v>22</v>
       </c>
       <c r="N284" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="O284" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="P284" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="285" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="B285" t="s">
         <v>135</v>
@@ -20243,7 +20246,7 @@
         <v>20</v>
       </c>
       <c r="K285" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="L285" t="s">
         <v>19</v>
@@ -20252,18 +20255,18 @@
         <v>22</v>
       </c>
       <c r="N285" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="O285" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="P285" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="286" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="B286" t="s">
         <v>135</v>
@@ -20293,7 +20296,7 @@
         <v>20</v>
       </c>
       <c r="K286" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="L286" t="s">
         <v>19</v>
@@ -20302,21 +20305,21 @@
         <v>22</v>
       </c>
       <c r="N286" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="O286" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="P286" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="287" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="B287" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C287" t="s">
         <v>18</v>
@@ -20337,13 +20340,13 @@
         <v>1</v>
       </c>
       <c r="I287" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="J287" t="s">
         <v>20</v>
       </c>
       <c r="K287" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="L287" t="s">
         <v>19</v>
@@ -20352,18 +20355,18 @@
         <v>22</v>
       </c>
       <c r="N287" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="O287" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
       <c r="P287" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="288" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="B288" t="s">
         <v>135</v>
@@ -20393,7 +20396,7 @@
         <v>20</v>
       </c>
       <c r="K288" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="L288" t="s">
         <v>19</v>
@@ -20402,18 +20405,18 @@
         <v>22</v>
       </c>
       <c r="N288" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="O288" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="P288" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="289" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="B289" t="s">
         <v>135</v>
@@ -20443,7 +20446,7 @@
         <v>20</v>
       </c>
       <c r="K289" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="L289" t="s">
         <v>19</v>
@@ -20452,18 +20455,18 @@
         <v>22</v>
       </c>
       <c r="N289" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="O289" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="P289" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="290" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="B290" t="s">
         <v>135</v>
@@ -20493,7 +20496,7 @@
         <v>20</v>
       </c>
       <c r="K290" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="L290" t="s">
         <v>19</v>
@@ -20502,18 +20505,18 @@
         <v>22</v>
       </c>
       <c r="N290" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="O290" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="P290" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="291" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="B291" t="s">
         <v>135</v>
@@ -20543,7 +20546,7 @@
         <v>20</v>
       </c>
       <c r="K291" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="L291" t="s">
         <v>19</v>
@@ -20552,21 +20555,21 @@
         <v>22</v>
       </c>
       <c r="N291" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="O291" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="P291" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="292" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="B292" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
       <c r="C292" t="s">
         <v>18</v>
@@ -20593,7 +20596,7 @@
         <v>20</v>
       </c>
       <c r="K292" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="L292" t="s">
         <v>19</v>
@@ -20602,21 +20605,21 @@
         <v>22</v>
       </c>
       <c r="N292" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
       <c r="O292" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="P292" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="293" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="B293" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="C293" t="s">
         <v>18</v>
@@ -20643,7 +20646,7 @@
         <v>20</v>
       </c>
       <c r="K293" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="L293" t="s">
         <v>19</v>
@@ -20652,21 +20655,21 @@
         <v>22</v>
       </c>
       <c r="N293" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="O293" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="P293" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="294" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="B294" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="C294" t="s">
         <v>18</v>
@@ -20693,7 +20696,7 @@
         <v>20</v>
       </c>
       <c r="K294" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="L294" t="s">
         <v>19</v>
@@ -20702,21 +20705,21 @@
         <v>22</v>
       </c>
       <c r="N294" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="O294" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="P294" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="295" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="B295" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="C295" t="s">
         <v>18</v>
@@ -20743,7 +20746,7 @@
         <v>20</v>
       </c>
       <c r="K295" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="L295" t="s">
         <v>19</v>
@@ -20752,18 +20755,18 @@
         <v>22</v>
       </c>
       <c r="N295" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="O295" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="P295" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="296" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="B296" t="s">
         <v>1042</v>
@@ -20793,7 +20796,7 @@
         <v>20</v>
       </c>
       <c r="K296" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="L296" t="s">
         <v>19</v>
@@ -20802,18 +20805,18 @@
         <v>22</v>
       </c>
       <c r="N296" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="O296" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="P296" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="297" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="B297" t="s">
         <v>135</v>
@@ -20843,7 +20846,7 @@
         <v>20</v>
       </c>
       <c r="K297" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="L297" t="s">
         <v>19</v>
@@ -20852,18 +20855,18 @@
         <v>22</v>
       </c>
       <c r="N297" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="O297" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="P297" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="298" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="B298" t="s">
         <v>1042</v>
@@ -20893,7 +20896,7 @@
         <v>20</v>
       </c>
       <c r="K298" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="L298" t="s">
         <v>19</v>
@@ -20902,18 +20905,18 @@
         <v>22</v>
       </c>
       <c r="N298" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="O298" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="P298" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="299" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="B299" t="s">
         <v>135</v>
@@ -20943,7 +20946,7 @@
         <v>20</v>
       </c>
       <c r="K299" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="L299" t="s">
         <v>19</v>
@@ -20952,21 +20955,21 @@
         <v>22</v>
       </c>
       <c r="N299" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="O299" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="P299" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="300" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="B300" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="C300" t="s">
         <v>18</v>
@@ -20993,7 +20996,7 @@
         <v>20</v>
       </c>
       <c r="K300" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="L300" t="s">
         <v>19</v>
@@ -21002,18 +21005,18 @@
         <v>22</v>
       </c>
       <c r="N300" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="O300" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="P300" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="301" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="B301" t="s">
         <v>135</v>
@@ -21043,7 +21046,7 @@
         <v>20</v>
       </c>
       <c r="K301" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="L301" t="s">
         <v>19</v>
@@ -21052,18 +21055,18 @@
         <v>22</v>
       </c>
       <c r="N301" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="O301" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="P301" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="302" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="B302" t="s">
         <v>135</v>
@@ -21093,7 +21096,7 @@
         <v>20</v>
       </c>
       <c r="K302" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
       <c r="L302" t="s">
         <v>19</v>
@@ -21102,18 +21105,18 @@
         <v>22</v>
       </c>
       <c r="N302" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="O302" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="P302" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="303" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="B303" t="s">
         <v>1277</v>
@@ -21143,7 +21146,7 @@
         <v>20</v>
       </c>
       <c r="K303" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
       <c r="L303" t="s">
         <v>19</v>
@@ -21152,18 +21155,18 @@
         <v>22</v>
       </c>
       <c r="N303" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="O303" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="P303" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="304" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="B304" t="s">
         <v>19</v>
@@ -21193,7 +21196,7 @@
         <v>19</v>
       </c>
       <c r="K304" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="L304" t="s">
         <v>19</v>
@@ -21202,18 +21205,18 @@
         <v>389</v>
       </c>
       <c r="N304" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="O304" t="s">
         <v>19</v>
       </c>
       <c r="P304" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="305" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="B305" t="s">
         <v>1277</v>
@@ -21243,7 +21246,7 @@
         <v>20</v>
       </c>
       <c r="K305" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="L305" t="s">
         <v>19</v>
@@ -21252,21 +21255,21 @@
         <v>22</v>
       </c>
       <c r="N305" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="O305" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="P305" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="306" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="B306" t="s">
-        <v>1609</v>
+        <v>1348</v>
       </c>
       <c r="C306" t="s">
         <v>18</v>
@@ -21293,7 +21296,7 @@
         <v>20</v>
       </c>
       <c r="K306" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="L306" t="s">
         <v>19</v>
@@ -21302,18 +21305,18 @@
         <v>22</v>
       </c>
       <c r="N306" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="O306" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="P306" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="307" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="B307" t="s">
         <v>1277</v>
@@ -21343,7 +21346,7 @@
         <v>20</v>
       </c>
       <c r="K307" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="L307" t="s">
         <v>19</v>
@@ -21352,18 +21355,18 @@
         <v>22</v>
       </c>
       <c r="N307" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="O307" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="P307" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="308" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="B308" t="s">
         <v>1277</v>
@@ -21393,7 +21396,7 @@
         <v>20</v>
       </c>
       <c r="K308" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="L308" t="s">
         <v>19</v>
@@ -21402,21 +21405,21 @@
         <v>22</v>
       </c>
       <c r="N308" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="O308" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="P308" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="309" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="B309" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="C309" t="s">
         <v>18</v>
@@ -21443,7 +21446,7 @@
         <v>20</v>
       </c>
       <c r="K309" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="L309" t="s">
         <v>19</v>
@@ -21452,21 +21455,21 @@
         <v>22</v>
       </c>
       <c r="N309" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="O309" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="P309" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="310" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="B310" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="C310" t="s">
         <v>18</v>
@@ -21493,7 +21496,7 @@
         <v>20</v>
       </c>
       <c r="K310" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="L310" t="s">
         <v>19</v>
@@ -21502,21 +21505,21 @@
         <v>22</v>
       </c>
       <c r="N310" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="O310" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="P310" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="311" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="B311" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="C311" t="s">
         <v>18</v>
@@ -21543,7 +21546,7 @@
         <v>20</v>
       </c>
       <c r="K311" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="L311" t="s">
         <v>19</v>
@@ -21552,21 +21555,21 @@
         <v>22</v>
       </c>
       <c r="N311" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="O311" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="P311" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="312" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="B312" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="C312" t="s">
         <v>18</v>
@@ -21593,7 +21596,7 @@
         <v>20</v>
       </c>
       <c r="K312" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="L312" t="s">
         <v>19</v>
@@ -21602,21 +21605,21 @@
         <v>22</v>
       </c>
       <c r="N312" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="O312" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="P312" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="313" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="B313" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="C313" t="s">
         <v>18</v>
@@ -21643,7 +21646,7 @@
         <v>20</v>
       </c>
       <c r="K313" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="L313" t="s">
         <v>19</v>
@@ -21652,21 +21655,21 @@
         <v>22</v>
       </c>
       <c r="N313" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="O313" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="P313" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="314" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B314" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="C314" t="s">
         <v>18</v>
@@ -21693,7 +21696,7 @@
         <v>20</v>
       </c>
       <c r="K314" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="L314" t="s">
         <v>19</v>
@@ -21702,21 +21705,21 @@
         <v>22</v>
       </c>
       <c r="N314" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="O314" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="P314" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="315" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="B315" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="C315" t="s">
         <v>18</v>
@@ -21743,7 +21746,7 @@
         <v>20</v>
       </c>
       <c r="K315" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="L315" t="s">
         <v>19</v>
@@ -21752,21 +21755,21 @@
         <v>22</v>
       </c>
       <c r="N315" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="O315" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="P315" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="316" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="B316" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="C316" t="s">
         <v>18</v>
@@ -21793,7 +21796,7 @@
         <v>20</v>
       </c>
       <c r="K316" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="L316" t="s">
         <v>19</v>
@@ -21802,21 +21805,21 @@
         <v>22</v>
       </c>
       <c r="N316" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="O316" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="P316" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="317" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B317" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="C317" t="s">
         <v>18</v>
@@ -21843,7 +21846,7 @@
         <v>20</v>
       </c>
       <c r="K317" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="L317" t="s">
         <v>19</v>
@@ -21852,21 +21855,21 @@
         <v>22</v>
       </c>
       <c r="N317" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="O317" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="P317" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="318" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B318" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="C318" t="s">
         <v>18</v>
@@ -21893,7 +21896,7 @@
         <v>20</v>
       </c>
       <c r="K318" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="L318" t="s">
         <v>19</v>
@@ -21902,21 +21905,21 @@
         <v>22</v>
       </c>
       <c r="N318" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="O318" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="P318" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="319" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="B319" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="C319" t="s">
         <v>18</v>
@@ -21937,13 +21940,13 @@
         <v>0</v>
       </c>
       <c r="I319" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="J319" t="s">
         <v>20</v>
       </c>
       <c r="K319" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="L319" t="s">
         <v>19</v>
@@ -21952,21 +21955,21 @@
         <v>22</v>
       </c>
       <c r="N319" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="O319" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="P319" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="320" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="B320" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="C320" t="s">
         <v>18</v>
@@ -21987,13 +21990,13 @@
         <v>0</v>
       </c>
       <c r="I320" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="J320" t="s">
         <v>20</v>
       </c>
       <c r="K320" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="L320" t="s">
         <v>19</v>
@@ -22002,21 +22005,21 @@
         <v>22</v>
       </c>
       <c r="N320" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="O320" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="P320" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="321" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="B321" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="C321" t="s">
         <v>18</v>
@@ -22037,13 +22040,13 @@
         <v>0</v>
       </c>
       <c r="I321" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="J321" t="s">
         <v>20</v>
       </c>
       <c r="K321" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="L321" t="s">
         <v>19</v>
@@ -22052,21 +22055,21 @@
         <v>22</v>
       </c>
       <c r="N321" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="O321" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="P321" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="322" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="B322" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="C322" t="s">
         <v>18</v>
@@ -22087,13 +22090,13 @@
         <v>1</v>
       </c>
       <c r="I322" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="J322" t="s">
         <v>20</v>
       </c>
       <c r="K322" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="L322" t="s">
         <v>19</v>
@@ -22102,21 +22105,21 @@
         <v>22</v>
       </c>
       <c r="N322" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="O322" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="P322" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="323" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B323" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="C323" t="s">
         <v>18</v>
@@ -22143,7 +22146,7 @@
         <v>20</v>
       </c>
       <c r="K323" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="L323" t="s">
         <v>19</v>
@@ -22152,21 +22155,21 @@
         <v>22</v>
       </c>
       <c r="N323" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="O323" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="P323" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="324" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="B324" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="C324" t="s">
         <v>18</v>
@@ -22193,7 +22196,7 @@
         <v>20</v>
       </c>
       <c r="K324" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="L324" t="s">
         <v>19</v>
@@ -22202,21 +22205,21 @@
         <v>22</v>
       </c>
       <c r="N324" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="O324" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="P324" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="325" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="B325" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C325" t="s">
         <v>18</v>
@@ -22243,7 +22246,7 @@
         <v>20</v>
       </c>
       <c r="K325" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="L325" t="s">
         <v>19</v>
@@ -22252,21 +22255,21 @@
         <v>22</v>
       </c>
       <c r="N325" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="O325" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="P325" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="326" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="B326" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C326" t="s">
         <v>18</v>
@@ -22293,7 +22296,7 @@
         <v>20</v>
       </c>
       <c r="K326" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="L326" t="s">
         <v>19</v>
@@ -22302,21 +22305,21 @@
         <v>22</v>
       </c>
       <c r="N326" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="O326" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="P326" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="327" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="B327" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C327" t="s">
         <v>18</v>
@@ -22337,13 +22340,13 @@
         <v>0</v>
       </c>
       <c r="I327" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="J327" t="s">
         <v>20</v>
       </c>
       <c r="K327" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="L327" t="s">
         <v>19</v>
@@ -22352,21 +22355,21 @@
         <v>22</v>
       </c>
       <c r="N327" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="O327" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="P327" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="328" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="B328" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C328" t="s">
         <v>18</v>
@@ -22393,7 +22396,7 @@
         <v>20</v>
       </c>
       <c r="K328" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="L328" t="s">
         <v>19</v>
@@ -22402,21 +22405,21 @@
         <v>22</v>
       </c>
       <c r="N328" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="O328" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="P328" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="329" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="B329" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C329" t="s">
         <v>18</v>
@@ -22443,7 +22446,7 @@
         <v>20</v>
       </c>
       <c r="K329" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="L329" t="s">
         <v>19</v>
@@ -22452,21 +22455,21 @@
         <v>22</v>
       </c>
       <c r="N329" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="O329" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="P329" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="330" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="B330" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C330" t="s">
         <v>18</v>
@@ -22493,7 +22496,7 @@
         <v>20</v>
       </c>
       <c r="K330" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="L330" t="s">
         <v>19</v>
@@ -22502,21 +22505,21 @@
         <v>22</v>
       </c>
       <c r="N330" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="O330" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="P330" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="331" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="B331" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C331" t="s">
         <v>18</v>
@@ -22543,7 +22546,7 @@
         <v>20</v>
       </c>
       <c r="K331" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="L331" t="s">
         <v>19</v>
@@ -22552,21 +22555,21 @@
         <v>22</v>
       </c>
       <c r="N331" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="O331" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="P331" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="332" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="B332" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C332" t="s">
         <v>18</v>
@@ -22593,7 +22596,7 @@
         <v>20</v>
       </c>
       <c r="K332" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="L332" t="s">
         <v>19</v>
@@ -22602,21 +22605,21 @@
         <v>22</v>
       </c>
       <c r="N332" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="O332" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="P332" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="333" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="B333" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C333" t="s">
         <v>18</v>
@@ -22643,7 +22646,7 @@
         <v>20</v>
       </c>
       <c r="K333" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="L333" t="s">
         <v>19</v>
@@ -22652,21 +22655,21 @@
         <v>22</v>
       </c>
       <c r="N333" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="O333" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="P333" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="334" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="B334" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C334" t="s">
         <v>18</v>
@@ -22693,7 +22696,7 @@
         <v>20</v>
       </c>
       <c r="K334" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="L334" t="s">
         <v>19</v>
@@ -22702,21 +22705,21 @@
         <v>22</v>
       </c>
       <c r="N334" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="O334" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="P334" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="335" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="B335" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C335" t="s">
         <v>18</v>
@@ -22743,7 +22746,7 @@
         <v>20</v>
       </c>
       <c r="K335" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="L335" t="s">
         <v>19</v>
@@ -22752,21 +22755,21 @@
         <v>22</v>
       </c>
       <c r="N335" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="O335" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="P335" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="336" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="B336" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C336" t="s">
         <v>18</v>
@@ -22793,7 +22796,7 @@
         <v>20</v>
       </c>
       <c r="K336" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="L336" t="s">
         <v>19</v>
@@ -22802,21 +22805,21 @@
         <v>22</v>
       </c>
       <c r="N336" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="O336" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="P336" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="337" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="B337" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C337" t="s">
         <v>18</v>
@@ -22837,13 +22840,13 @@
         <v>0</v>
       </c>
       <c r="I337" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="J337" t="s">
         <v>20</v>
       </c>
       <c r="K337" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="L337" t="s">
         <v>19</v>
@@ -22852,21 +22855,21 @@
         <v>22</v>
       </c>
       <c r="N337" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="O337" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="P337" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="338" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="B338" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C338" t="s">
         <v>18</v>
@@ -22887,13 +22890,13 @@
         <v>0</v>
       </c>
       <c r="I338" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="J338" t="s">
         <v>20</v>
       </c>
       <c r="K338" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="L338" t="s">
         <v>19</v>
@@ -22902,21 +22905,21 @@
         <v>22</v>
       </c>
       <c r="N338" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="O338" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="P338" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="339" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="B339" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C339" t="s">
         <v>18</v>
@@ -22937,13 +22940,13 @@
         <v>0</v>
       </c>
       <c r="I339" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="J339" t="s">
         <v>20</v>
       </c>
       <c r="K339" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="L339" t="s">
         <v>19</v>
@@ -22952,21 +22955,21 @@
         <v>22</v>
       </c>
       <c r="N339" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="O339" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="P339" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="340" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="B340" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C340" t="s">
         <v>18</v>
@@ -22987,13 +22990,13 @@
         <v>0</v>
       </c>
       <c r="I340" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="J340" t="s">
         <v>20</v>
       </c>
       <c r="K340" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="L340" t="s">
         <v>19</v>
@@ -23002,21 +23005,21 @@
         <v>22</v>
       </c>
       <c r="N340" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="O340" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="P340" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="341" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="B341" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C341" t="s">
         <v>18</v>
@@ -23037,13 +23040,13 @@
         <v>0</v>
       </c>
       <c r="I341" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="J341" t="s">
         <v>20</v>
       </c>
       <c r="K341" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="L341" t="s">
         <v>19</v>
@@ -23052,21 +23055,21 @@
         <v>22</v>
       </c>
       <c r="N341" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="O341" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="P341" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="342" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="B342" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C342" t="s">
         <v>18</v>
@@ -23093,7 +23096,7 @@
         <v>20</v>
       </c>
       <c r="K342" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="L342" t="s">
         <v>19</v>
@@ -23102,18 +23105,18 @@
         <v>22</v>
       </c>
       <c r="N342" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="O342" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="P342" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="343" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="B343" t="s">
         <v>19</v>
@@ -23143,7 +23146,7 @@
         <v>19</v>
       </c>
       <c r="K343" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="L343" t="s">
         <v>19</v>
@@ -23152,21 +23155,21 @@
         <v>389</v>
       </c>
       <c r="N343" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="O343" t="s">
         <v>19</v>
       </c>
       <c r="P343" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="344" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="B344" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C344" t="s">
         <v>18</v>
@@ -23187,13 +23190,13 @@
         <v>0</v>
       </c>
       <c r="I344" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="J344" t="s">
         <v>20</v>
       </c>
       <c r="K344" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="L344" t="s">
         <v>19</v>
@@ -23202,21 +23205,21 @@
         <v>22</v>
       </c>
       <c r="N344" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="O344" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="P344" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="345" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="B345" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C345" t="s">
         <v>18</v>
@@ -23237,13 +23240,13 @@
         <v>0</v>
       </c>
       <c r="I345" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="J345" t="s">
         <v>20</v>
       </c>
       <c r="K345" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="L345" t="s">
         <v>19</v>
@@ -23252,21 +23255,21 @@
         <v>22</v>
       </c>
       <c r="N345" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="O345" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="P345" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="346" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="B346" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C346" t="s">
         <v>18</v>
@@ -23287,13 +23290,13 @@
         <v>0</v>
       </c>
       <c r="I346" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="J346" t="s">
         <v>20</v>
       </c>
       <c r="K346" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="L346" t="s">
         <v>19</v>
@@ -23302,21 +23305,21 @@
         <v>22</v>
       </c>
       <c r="N346" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="O346" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="P346" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="347" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="B347" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C347" t="s">
         <v>18</v>
@@ -23337,13 +23340,13 @@
         <v>0</v>
       </c>
       <c r="I347" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="J347" t="s">
         <v>20</v>
       </c>
       <c r="K347" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="L347" t="s">
         <v>19</v>
@@ -23352,21 +23355,21 @@
         <v>22</v>
       </c>
       <c r="N347" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="O347" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="P347" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="348" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B348" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C348" t="s">
         <v>18</v>
@@ -23387,13 +23390,13 @@
         <v>0</v>
       </c>
       <c r="I348" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="J348" t="s">
         <v>20</v>
       </c>
       <c r="K348" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="L348" t="s">
         <v>19</v>
@@ -23402,21 +23405,21 @@
         <v>22</v>
       </c>
       <c r="N348" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="O348" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="P348" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="349" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="B349" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C349" t="s">
         <v>18</v>
@@ -23437,13 +23440,13 @@
         <v>0</v>
       </c>
       <c r="I349" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="J349" t="s">
         <v>20</v>
       </c>
       <c r="K349" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="L349" t="s">
         <v>19</v>
@@ -23452,18 +23455,18 @@
         <v>22</v>
       </c>
       <c r="N349" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="O349" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="P349" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="350" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="B350" t="s">
         <v>18</v>
@@ -23493,7 +23496,7 @@
         <v>42</v>
       </c>
       <c r="K350" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="L350" t="b">
         <v>0</v>
@@ -23502,21 +23505,21 @@
         <v>22</v>
       </c>
       <c r="N350" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="O350" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="P350" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="351" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="B351" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C351" t="s">
         <v>18</v>
@@ -23537,13 +23540,13 @@
         <v>0</v>
       </c>
       <c r="I351" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="J351" t="s">
         <v>20</v>
       </c>
       <c r="K351" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="L351" t="s">
         <v>19</v>
@@ -23552,18 +23555,18 @@
         <v>22</v>
       </c>
       <c r="N351" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="O351" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="P351" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="352" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="B352" t="s">
         <v>135</v>
@@ -23593,7 +23596,7 @@
         <v>20</v>
       </c>
       <c r="K352" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="L352" t="s">
         <v>19</v>
@@ -23602,21 +23605,21 @@
         <v>22</v>
       </c>
       <c r="N352" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="O352" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="P352" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="353" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="B353" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="C353" t="s">
         <v>18</v>
@@ -23643,7 +23646,7 @@
         <v>20</v>
       </c>
       <c r="K353" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="L353" t="s">
         <v>19</v>
@@ -23652,21 +23655,21 @@
         <v>22</v>
       </c>
       <c r="N353" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="O353" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="P353" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="354" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="B354" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="C354" t="s">
         <v>18</v>
@@ -23693,7 +23696,7 @@
         <v>20</v>
       </c>
       <c r="K354" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="L354" t="s">
         <v>19</v>
@@ -23702,21 +23705,21 @@
         <v>22</v>
       </c>
       <c r="N354" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="O354" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="P354" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="355" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="B355" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="C355" t="s">
         <v>18</v>
@@ -23743,7 +23746,7 @@
         <v>20</v>
       </c>
       <c r="K355" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="L355" t="s">
         <v>19</v>
@@ -23752,13 +23755,13 @@
         <v>22</v>
       </c>
       <c r="N355" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="O355" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="P355" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-grace-master.report.xlsx
+++ b/tools/importer/reports/import-grace-master.report.xlsx
@@ -313,7 +313,7 @@
     <t>about-grace/leadership-team</t>
   </si>
   <si>
-    <t>2026-08-20T11:36:34.422Z</t>
+    <t>2026-08-20T13:22:02.526Z</t>
   </si>
   <si>
     <t>Leadership Team</t>
@@ -325,13 +325,13 @@
     <t>about-grace/locations.report.json</t>
   </si>
   <si>
-    <t>["cards-location-grid"]</t>
+    <t>["cards-location-grid","columns-location-detail"]</t>
   </si>
   <si>
     <t>about-grace/locations</t>
   </si>
   <si>
-    <t>2026-08-19T22:46:09.331Z</t>
+    <t>2026-08-20T15:14:06.443Z</t>
   </si>
   <si>
     <t>Locations</t>
